--- a/Excel/8_Fuel_WIP_v05.prename.bak.xlsx
+++ b/Excel/8_Fuel_WIP_v05.prename.bak.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36295E79-392F-443F-A16B-D983A0A20882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA8BF15-A958-40E9-9107-CD4FC3DA3151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" firstSheet="2" activeTab="6" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="28800" windowHeight="15345" firstSheet="4" activeTab="8" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -21,8 +21,11 @@
     <sheet name="8.1.1.1-2 Transport fuel" sheetId="69" r:id="rId6"/>
     <sheet name="8.2.1.1-2 Stationary fuel" sheetId="74" r:id="rId7"/>
     <sheet name="Constants - Fuel" sheetId="110" r:id="rId8"/>
-    <sheet name="Constants - Common" sheetId="123" r:id="rId9"/>
+    <sheet name="Constants - Common" sheetId="124" r:id="rId9"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId10"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -179,6 +182,7 @@
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData_DensityOfMethane_Data">'Constants - Common'!$D$175</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Fertiliser type f","FracGASFf","Basis";"Urea-based fertilisers",0.15,"Urea";"Ammonium-based fertilisers",0.08,"Ammonium";"Nitrate-based fertilisers",0.01,"Nitrate";"Ammonium-nitrate based fertilisers",0.05,"Ammonium-nitrate";"Other fertilisers",0.11,"Other"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_NIRReference">_xlfn.LAMBDA("IPCC 2019 Refinement Volume 4 Table 11.3 [1, p. 11]")</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Source">_xlfn.LAMBDA("VEERG 2026:Table 12.2.2.9")</definedName>
@@ -2981,176 +2985,6 @@
   <dxfs count="123">
     <dxf>
       <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -4010,6 +3844,176 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -8502,6 +8506,26 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -8598,12 +8622,12 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{051C654A-204B-46EF-884D-107B750FE1C8}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{40E387BC-857B-41BC-A1DD-6E7E6C21F092}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{18FCB515-E2BD-49D8-AB87-CF42BF6D3ECC}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{5C857A98-4878-4A91-9C3D-786E382AE81B}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8612,16 +8636,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5EE5A8BF-2469-430F-A289-FC17EEA0797E}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{2F15D483-5A68-454A-B15E-298C22B5067B}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{65AE068D-B090-4795-9000-82AFF06C29BA}" name="Gas">
+    <tableColumn id="1" xr3:uid="{AC3C6F3F-C61C-4ABD-937C-A6AA2EADE292}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{89B38382-646A-4BE2-B0ED-9CD3FA338D3E}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{E3B85ED3-A740-472D-846D-8B82112A7765}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8630,7 +8654,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{CC7F7206-F6DC-4977-8BA6-5B66E729F058}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{528C4C07-D520-4C08-AD75-09BFA5120E3D}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -8639,19 +8663,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{A59113C9-3F34-4871-974E-A6CA1AE1B53D}" name="Gas">
+    <tableColumn id="1" xr3:uid="{57482922-E239-44D1-AC97-F167F4071FF3}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{8A9A2E95-9422-4A2E-A829-CAB937EA66EA}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{0CCCB0E1-9F60-4997-8BFD-70F12449AB6F}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6925339E-FC73-4750-89B5-E376C2FF4EE2}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{13237EF5-D6C1-4E8F-9E28-888CF6BD50BF}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0C2C2843-AAD7-4110-9425-B9A58D67B736}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{4DC3AC58-CFD9-46A8-A678-66E543A3210D}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{ECA1F198-06FC-4A8C-A1C9-742052F2D9D4}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{CC2D1C3E-B353-4082-86FC-11E60E91D7F3}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8660,7 +8684,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{ED54C8D8-81BC-405E-A5EB-33320553524B}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{B51C754C-C547-4A49-B11B-57B6FEC9E811}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -8680,52 +8704,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{5323B435-CB20-421F-925A-5C9C0166AD48}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{C78F8194-D8E0-4358-AAAB-CFDE15DA2830}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3EA7F381-8B0C-4FE2-AEC8-30DBAB357FFE}" name="MAT" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{6540D119-9CF8-4773-A1D3-00A95BCEEFC6}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{D1DFDBA4-BF37-41DE-944A-29EAFC7C92FA}" name="MAP" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{035C56C1-0FF6-44D8-A550-5AF0FECECED4}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8BFB4055-A48F-4099-9DAD-2B89CFA85D17}" name="Frost days per year" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{2AF470BF-BA3F-40BA-A6DC-376287F94DCF}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{11B297D0-03A2-419E-94CC-954A849DF0A3}" name="Elevation" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{E99F3396-0330-4A28-B57F-DF312D0D0497}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{D2D67B8F-C337-4828-A293-DF4D210DA8E9}" name="MAP:PET" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{A1126D28-8E8B-4BB5-8C2E-7127098DC658}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{4F7D264F-6F68-4BE9-ABBF-BE097D0D650A}" name="Min temp" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{9C2AC696-E3EA-4A68-A018-B66AF6BCDA71}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BA331108-B37D-41FA-8849-AB10B05EDB97}" name="Max temp" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{F0FAC75B-E63F-4DAF-9638-A1D40557051A}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3A165571-B323-407F-8027-6CEB0101A9BA}" name="Min rainfall" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{4B31D27C-83B1-479E-8DB4-FA9967D168AC}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{53DD25D2-17AD-4F79-8A01-6F22E9818AA2}" name="Max rainfall" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{1E53C538-1298-4998-AC9F-CF29D2B879E4}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{D1DC7A68-991C-476A-9A7A-012CF00FBB12}" name="Min frost days" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{D9C5E60C-87C4-4C58-88FF-7F1D633F4FBF}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{8B2817D9-F13A-4EBF-87AA-C38A9412AF12}" name="Max frost days" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{E913C3BC-11C3-41BB-8A41-601D48A87967}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{13C2F614-A341-4EC9-9C71-3EFC05D1EDDB}" name="Min elevation" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{653ECD84-22B5-4903-827B-426ED610F7BC}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{40102B61-423D-42CC-B871-28E9C2F94887}" name="Max elevation" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{DB8939AF-4796-41B4-972A-57E9E15F2954}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{48651D3F-34AE-4FA6-8589-CAD0DF5C9CCC}" name="Min MAP:PET" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{C871C030-55AB-4FED-9ABC-809675D2BFA5}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{FF8F39A2-33DF-4331-96AE-5DC7BBA54DD0}" name="Max MAP:PET" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{68B0EA52-1CC8-4E54-B687-5EFC4BE5BEAC}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8734,16 +8758,16 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{8C3177F8-5CEE-4447-AB6A-52F19E3BC38D}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{1A340846-7852-4783-A896-CE0A67339173}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{80B116B5-85BD-4DEA-AC49-EAACB134EF60}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{4A88C6C5-17A7-4838-B5B0-EB1B3250A4F5}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CDC91B39-498A-4099-B2B2-0A2938BF01DE}" name="Wet or Dry Zone" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{A9A5DBDE-C3E0-473B-9FD2-4115217386E7}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8752,7 +8776,7 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{49E9786A-7B44-4964-805E-BC87E333ECF8}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{A992892C-076C-4C05-9B12-8760896F42D2}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -8760,16 +8784,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{3154A0A0-F5C0-4F29-8725-0167CC3E02F2}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{83260E2F-CD17-45E9-BCFC-119020794E01}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{349BD877-16FE-4478-A326-64617DF34C8D}" name="MAT">
+    <tableColumn id="2" xr3:uid="{EC05D0BD-28DC-4FC5-A5BA-915CDE5D5E6D}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F29B2C1E-3149-49A4-9147-00678EF218EE}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{733A50BE-7F26-43A0-9004-049CCEDD65DD}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{36B82F82-E3CE-448E-A4B0-A3A38D261D02}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{27AC5FE2-A983-4001-83D9-856CC41BFD18}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8778,7 +8802,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{D639789D-4975-49C1-9E23-6338AD8C1CC4}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{F66ACAB0-0A8B-45AB-BCD6-70113F6A11A1}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -8786,16 +8810,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D9D8DA76-97FE-4CEC-9819-D9409622EB0D}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{0D6EA4D7-3603-4F3A-904C-1FCD12CF3ACA}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3428040F-5055-46C1-8B55-2B36B5033E86}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{B3D26196-AB92-43E9-9BC2-65E5C274063B}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{FB0DCEE7-6054-45E7-89BE-354B397F6250}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{27C89F86-4D58-4ACD-BBD1-1F853215883E}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CDB75634-5F8A-4CD7-84D7-45D71CFA5933}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{367E0DF2-62DD-4201-B34D-48D537FCA47C}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8804,16 +8828,16 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{CFC0537B-4065-417C-BCFA-73F3A8D597A3}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{33681049-8FC9-4A6E-A16E-854B0D936131}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{9FAF9520-9889-4AE9-B6CC-FDE2E10EAD98}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{D518D73B-014F-4BBF-9662-94020E81A0DD}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6C96956C-286E-4803-93B5-8D7A561FBE4B}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{7B04E969-21C3-45AB-8878-4EC5F2DA7AA9}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8822,16 +8846,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{68FF86DD-0885-4976-BEEB-94AB1DD53149}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{688DD3BD-F5FB-42D9-B5C3-5DD51A4596F9}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{6B321226-8AD9-4746-AAFF-4041954CA60D}" name="Data source">
+    <tableColumn id="1" xr3:uid="{6F67AC24-1E5E-4399-AC5E-654FFFC017B3}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1CC291CD-853F-4B67-B09F-804F187D6F9B}" name="Data score">
+    <tableColumn id="2" xr3:uid="{AB216C63-C26D-47D9-A5D5-4EBAC4246810}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8840,16 +8864,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{C02C1423-B5DE-4FA6-A257-8CDE4D4D2BBB}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{6143E915-EC5F-4CD7-A9B9-AFB7BA5C0F62}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{CB763BC9-0431-4076-9924-BEA84AD15106}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{1988E8FD-007C-4BE8-804F-D03930E45B7A}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00CA7AD8-9B48-4522-8A26-31B6312F3F99}" name="FracWET" dataDxfId="36">
+    <tableColumn id="2" xr3:uid="{8A562D65-BBA8-4D78-A46A-5AC2978F0BD9}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8900,7 +8924,7 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{57AB5B1C-4113-45A9-B01E-845F3ABDF204}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{F87664D1-709A-48DA-99F3-0B1E638F468F}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -8909,19 +8933,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{A130E37A-5BE6-4352-8D8A-6A7D25A0FB7C}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{D55E48A2-37F1-41B1-823E-17D1E52CBE4F}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{195770B7-FB42-4A96-BE05-896F123743B8}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{7D57F18D-387D-43F8-A1E3-D82C1257BD25}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{59A910CC-53C7-4A58-BFD2-69858B6F92EA}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{84ADE3B4-886D-4B0C-B10F-7ADC1E372757}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5B5A42F2-1784-4DB3-BD73-6BB0D099DF09}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{AB438D6A-50F5-42C6-9398-B0D4A6C95DCE}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{18E56A98-FD2A-4EF9-9A00-D2E0006C6442}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{638725DE-CDD0-47BC-B33D-57F27BF46650}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8930,16 +8954,16 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{B128EAEF-C928-42FE-A611-01FE8E5BA562}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{2911F911-18AD-4C27-A454-434FA8D5F56C}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{17857C03-4A58-4397-80F2-B0BB055FF49E}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{9881D3F5-1850-44AD-8E5E-FCA2AC1D7F5A}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{FEAAE811-F1F7-4D6F-AA27-D390271B59DC}" name="FracWET" dataDxfId="35" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3BEAAAC6-15D8-4D5F-B8DB-D72567307C5E}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8948,16 +8972,16 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{7921A5F8-968C-4D9D-BDB3-7979D09CA4E0}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{CB356D66-590B-4376-9B92-B0E8E0C2D6A9}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{8656D55F-442D-402C-B490-2EB44EDBB425}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{DDBD77C6-F919-4BF7-9106-DA20B1D61C0B}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D1BC5256-FAEA-4E28-9E5B-1655327AD263}" name="EFPRP" dataDxfId="34" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{40E70A92-35B2-440E-9AC6-25E169CA44EE}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8966,16 +8990,16 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{3CE86F09-A7F7-4E4C-A84F-59B18397FB18}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{C9851DC7-83E7-4592-A1FD-97600FFE7A7A}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D3342927-0035-4306-A62A-19C77A5CD2DF}" name="Month">
+    <tableColumn id="1" xr3:uid="{0C35E1C0-7F9F-4F71-BC37-DC61EDF8F937}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3F5D2D37-7B1B-4CB5-BD4E-1C38384F3D09}" name="Season" dataDxfId="33" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{17DF294E-0CF9-438E-811D-D36199C9AE41}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8984,7 +9008,7 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{626B35D2-B93A-4EAC-BC99-CB91AB9C214C}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="41" xr:uid="{43A771C0-7E5D-422D-B637-8CB68DD672F8}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9004,52 +9028,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{AD0F3F82-0CD5-4AFA-A517-A0B150A11F03}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{7FC29B47-0963-44AE-B7E8-54A4D73A5BA5}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E4B8A111-9105-4D19-A179-50E19F585832}" name="MAT (ºC)" dataDxfId="32" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{C649891D-46B1-4E70-ADC4-05C47735D6DC}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{E8B0319C-9CD7-4BB4-B498-66F0701E8ADC}" name="Anaerobic lagoon" dataDxfId="31" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{3F48A9A1-50F5-4A4D-AABE-6BBB6F932D4C}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2A421C61-4FA8-4172-B1F4-AC66552F1813}" name="Digester / covered lagoons" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{7352FB9C-49F9-40DD-B3AA-E928E5AC76E5}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F49451B4-B1FF-44F4-99B7-13FC79B56A94}" name="Liquid systems" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{58017179-0F35-4111-A2DC-7D7982C315AC}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{825962E4-158F-4FB4-BBFC-FE1275CA56C5}" name="Daily spread" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{FEEE0F4A-9361-43F2-826D-475E9E176DFA}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{EC393134-A5CC-4085-842B-802B5081B2CC}" name="Composting (passive windrow)" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{3384DD87-D1BF-4A22-9844-2086E79A17DE}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{058A8699-29E9-46D3-8601-7CFAC2747B78}" name="Solid storage" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{72B5BD59-9406-47DC-9503-A507B020082A}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{93152892-1F11-4FA3-B66E-5153616432AC}" name="Pit storage" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{FE117AA4-33AF-48EF-AB0D-C3B4F72961C6}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{15F36153-D69E-4C94-B868-BB3EB0BF82B9}" name="Deep litter" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{FF6D7DE9-BFAA-4319-8BD4-E4A6E0A5354E}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{24A5CC0F-177F-4A5D-9140-031C83C88617}" name="Poultry manure with bedding" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{D174D439-910D-48E0-86AC-A6C85CEDCEF7}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{37658789-4A27-4160-9F7D-D89007434764}" name="Poultry manure without bedding" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{486C4209-6CE6-42FF-A27F-4F6BDB1A604F}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{4A74F03E-495F-470A-BA72-FD65D2C513E7}" name="Direct processing" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{B98FB885-1916-4941-8960-D2EDA80AD661}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{01A5436F-F31A-4FAF-AC6D-9167C126F2AA}" name="Direct application" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{CE9D2EF3-9068-4A77-958D-0A85412561DB}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{63D669E2-7FDF-4EC4-956A-3F47E391595C}" name="Pasture range and paddock" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{E7BC93A0-2828-4A16-AD56-D7204C45D58C}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{722C3877-73F4-460E-B3F4-3EFEB52CA427}" name="MAT raw" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{5149957B-287C-4AFA-A670-B58C52A93A50}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9058,16 +9082,16 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{B86AF18F-C170-4EB8-81EF-1F6E61AFC8AD}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="42" xr:uid="{CD928FDE-8EDA-4FBB-816E-7C4388E2E499}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{93603888-B9CA-4327-ADAA-1B89202E4FA3}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{E5BBE035-4502-4C10-9BD7-499199339B37}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A8E44BA1-BA32-4A72-938A-595C28A02C87}" name="EFNi &amp; EFN2Oi" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{6CA725B0-E06F-428E-9CA0-1BC6567FA0A8}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9258,20 +9282,20 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{636868FF-DEFE-4F2A-BBC2-8CFB583605B1}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{968D9E05-E3A1-47AC-99DE-37BD356ADBD8}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E888B033-D4C3-4F54-AD13-F79A64C033D8}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{C27A9FA7-B30A-41C8-9906-FEE8EA098981}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E18DD9BA-DB99-40DA-BCF4-0820EF8686E9}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{21A67BC8-05CF-409C-8065-34EB55DA88B2}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0974923D-DF7A-4763-86CF-35CCBEC9D948}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{9826AB49-A801-4947-AE2D-9F60206DE52A}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11820,87 +11844,87 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F32">
-    <cfRule type="cellIs" dxfId="16" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="52" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111:F112">
-    <cfRule type="cellIs" dxfId="15" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F123:F124">
-    <cfRule type="cellIs" dxfId="14" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F135:F136">
-    <cfRule type="cellIs" dxfId="13" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="49" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F147:F148">
-    <cfRule type="cellIs" dxfId="12" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="48" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F235:F236">
-    <cfRule type="cellIs" dxfId="11" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F240:F241">
-    <cfRule type="cellIs" dxfId="10" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F245:F246">
-    <cfRule type="cellIs" dxfId="9" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F269:F270">
-    <cfRule type="cellIs" dxfId="8" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F274:F275">
-    <cfRule type="cellIs" dxfId="7" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F279:F280">
-    <cfRule type="cellIs" dxfId="6" priority="83" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="83" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:J27 H28:H30 I31:J31 I33:J35 I37:J38 I189:J189 E195:G195 I195:J195">
-    <cfRule type="cellIs" dxfId="5" priority="79" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="79" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I42:J46">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I50:J50 I109:J109">
-    <cfRule type="cellIs" dxfId="3" priority="74" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="74" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I61:J63">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I67:J70">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I74:J78">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19958,7 +19982,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7BA7FC7-4EBC-403C-963C-03C31DE9D523}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{047E58F0-E671-4DDC-A57D-75F20EDAEC33}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -23950,17 +23974,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -24155,11 +24168,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADEAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwAgAGkAbgBjAGwAdQBkAGkAbgBnACAAbABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIAAgAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAANQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADkALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACAAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AYQBsACAAcwBlAGEAbQAgAG0AZQB0AGgAYQBuAGUAIAB0AGgAYQB0ACAAaQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAMAAuADAAMwA3ADcALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMgAsACAAMAAuADAAMwAsACAANQAxAC4ANgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAGEAbAAgAG0AaQBuAGUAIAB3AGEAcwB0AGUAIABnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADkALAAgADQALgA2ACwAIAAwAC4AMwAsACAANQA2AC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAKAByAGUAdgBlAHIAdABpAG4AZwAgAHQAbwAgAHMAdABhAG4AZABhAHIAZAAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAKQBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBwAHIAbwBjAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEUAdABoAGEAbgBlAFwAIgAsACAAMAAuADAANgAyADkALAAgAFwAIgBtADMAXAAiACwAIAA1ADYALgA1ACwAIAAwAC4AMAAzACwAIAAwAC4AMAAzACwAIAA1ADYALgA1ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AawBlACAAbwB2AGUAbgAgAGcAYQBzAFwAIgAsACAAMAAuADAAMQA4ADEALAAgAFwAIgBtADMAXAAiACwAIAAzADcALgAwACwAIAAwAC4AMAAzACwAIAAwAC4AMAA1ACwAIAAzADcALgAwADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGwAYQBzAHQAIABmAHUAcgBuAGEAYwBlACAAZwBhAHMAXAAiACwAIAAwAC4AMAAwADQAMAAsACAAXAAiAG0AMwBcACIALAAgADIAMwA0AC4AMAAsACAAMAAuADAAMwAsACAAMAAuADAAMgAsACAAMgAzADQALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAG8AdwBuACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMAAsACAAXAAiAG0AMwBcACIALAAgADYAMAAuADIALAAgADAALgAwADQALAAgADAALgAwADMALAAgADYAMAAuADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMgA1AC4AMwAsACAAXAAiAGsATABcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBlAG8AdQBzACAAZgBvAHMAcwBpAGwAIABmAHUAZQBsAHMAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAdABoAG8AcwBlACAAbQBlAG4AdABpAG8AbgBlAGQAIABpAG4AIAB0AGgAZQAgAGkAdABlAG0AcwAgAGEAYgBvAHYAZQBcACIALAAgADAALgAwADMAOQAwACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAYQBuAGQAZgBpAGwAbAAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQBlAHQAaABhAG4AZQAgAG8AbgBsAHkAKQBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADYALgA0ACwAIAAwAC4AMAAzACwAIAA2AC4ANAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBsAHUAZABnAGUAIABiAGkAbwBnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIAAoAG0AZQB0AGgAYQBuAGUAIABvAG4AbAB5ACkAXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAA2AC4ANAAsACAAMAAuADAAMwAsACAANgAuADQAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAIABiAGkAbwBnAGEAcwAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4ALAAgAG8AdABoAGUAcgAgAHQAaABhAG4AIAB0AGgAbwBzAGUAIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMAAuADAAMwA3ADAALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAANgAuADQALAAgADAALgAwADMALAAgADYALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBtAGUAdABoAGEAbgBlAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgAwADMALAAgADAALgAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAHkAZAByAG8AZwBlAG4AXAAiACwAIAAwAC4AMAAxADIAMgAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAAwAC4AMAAsACAAMAAuADUALAAgADAALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAMQAsACAAXAAiAEcASgBcACIALAAgADUAMQAuADQALAAgADAALgAxACwAIAAwAC4AMAAzACwAIAA1ADEALgA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAG8AdwBuACAAZwBhAHMAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcACIALAAgADEALAAgAFwAIgBHAEoAXAAiACwAIAA2ADAALgAyACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAzACwAIAA2ADAALgAyADcAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABcAHUAMAAwADIANwBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAdQAwADAAMgA3ACAAdwBlAHIAZQAgAGEAZABkAGUAZAAsACAAZQBhAGMAaAAgAHcAaQB0AGgAIABhAG4AIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAG8AZgAgADEAIABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAC4AIABUAGgAaQBzACAAaQBzACAAZgBvAHIAIAB1AHMAZQByAHMAIAB3AGgAbwAgAGgAYQB2AGUAIABmAHUAZQBsACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAZABhAHQAYQAgAGkAbgAgAEcASgAgAHIAYQB0AGgAZQByACAAdABoAGEAbgAgAG0AMwAuAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAZwBhAHMAZQBvAHUAcwAgAGYAdQBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIASQBuAGQAaQByAGUAYwB0ACAAKABTAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAuAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAANgBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAZgBvAHIAIABOAGEAdAB1AHIAYQBsACAARwBhAHMAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABNAGUAdAByAG8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAE4AYQB0AHUAcgBhAGwAIABHAGEAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AbwBuACAALQAgAE0AZQB0AHIAbwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgADEAMwAuADEALAAgADEANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgADEAMwAuADEALAAgADEANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIAA0AC4AMAAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAOAAuADgALAAgADcALgA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIAAxADAALgA3ACwAIAAxADAALgA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAANAAuADEALAAgADQALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAANAAuADAALAAgADQALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIAA0AC4AMQAsACAANAAuADAAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABOAFMAVwAgAGEAbgBkACAAQQBDAFQAIABzAHAAbABpAHQAIABpAG4AdABvACAAcwBlAHAAYQByAGEAdABlACAAcgBvAHcAcwAuACAAXAB1ADAAMAAyADcAQwBcAHUAMAAwADIANwAgAFYAYQBsAHUAZQBzACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIABhAG4AZAAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAcgBlAHAAbABhAGMAZQBkACAAdwBpAHQAaAAgAHQAaABvAHMAZQAgAGYAbwByACAAVgBpAGMAdABvAHIAaQBhACAAYQBuAGQAIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAByAGUAcwBwAGUAYwB0AGkAdgBlAGwAeQAuACAAKABTAGUAZQAgAGEAcABwAGUAbgBkAGkAYwBlAHMAKQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADIALAAgADIALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBBAHMAIABTAGMAbwBwAGUAIAAzACAAZgBhAGMAdABvAHIAcwAgAGEAcgBlACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGEAdAAgAHQAaABlACAAcABvAGkAbgB0ACAAdwBoAGUAcgBlACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzACAAaQBzACAAZABlAGwAaQB2AGUAcgBlAGQAIAB0AG8AIABlAG4AZAAgAHUAcwBlAHIAcwAsACAAaQB0ACAAaQBzACAAbgBlAGMAZQBzAHMAYQByAHkAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAGEAdAAgAGUAYQBjAGgAIABvAGYAIAB0AGgAZQAgAGwAbwBhAGQAIABjAGUAbgB0AHIAZQBzAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIARwBhAHMAIAByAGUAYQBjAGgAZQBzACAAZQBuAGQAIAB1AHMAZQByAHMAIABlAGkAdABoAGUAcgAgAGYAcgBvAG0AIAB0AGgAZQAgAG0AZQB0AHIAbwAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAbgBlAHQAdwBvAHIAawBzACAAbwByACAAZABpAHIAZQBjAHQAIABmAHIAbwBtACAAdABoAGUAIABoAGkAZwBoACAALQAgAHAAcgBlAHMAcwB1AHIAZQAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAcABpAHAAZQBsAGkAbgBlAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBIAG8AdQBzAGUAaABvAGwAZABzACAAYQBuAGQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdQBzAGUAcgBzACAAdABlAG4AZAAgAHQAbwAgAGIAZQAgAHMAZQByAHYAZQBkACAAYgB5ACAAdABoAGUAIABmAG8AcgBtAGUAcgAsACAAYQBuAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABnAGUAbgBlAHIAYQB0AG8AcgBzACAAYQBuAGQAIABsAGEAcgBnAGUAIABpAG4AZAB1AHMAdAByAGkAYQBsACAAcABsAGEAbgB0AHMAIABmAHIAbwBtACAAdABoAGUAIABsAGEAdAB0AGUAcgAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIABcACIATQBlAHQAcgBvACAAaQBzACAAZABlAGYAaQBuAGUAZAAgAGEAcwAgAGwAbwBjAGEAdABlAGQAIABvAG4AIABvAHIAIABlAGEAcwB0ACAAbwBmACAAdABoAGUAIABkAGkAdgBpAGQAaQBuAGcAIAByAGEAbgBnAGUAIABpAG4AIABOAFMAVwAsACAAaQBuAGMAbAB1AGQAaQBuAGcAIABDAGEAbgBiAGUAcgByAGEAIABhAG4AZAAgAFEAdQBlAGEAbgBiAGUAeQBhAG4ALAAgAE0AZQBsAGIAbwB1AHIAbgBlACwAIABCAHIAaQBzAGIAYQBuAGUALAAgAEEAZABlAGwAYQBpAGQAZQAgAG8AcgAgAFAAZQByAHQAaAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAE8AdABoAGUAcgB3AGkAcwBlACwAIAB0AGgAZQAgAG4AbwBuACAALQAgAG0AZQB0AHIAbwAgAGYAYQBjAHQAbwByACAAcwBoAG8AdQBsAGQAIABiAGUAIAB1AHMAZQBkAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBGAGEAYwB0AG8AcgBzACAAYQByAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgBvAHIAIABhAGwAbAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAB3AGgAaQBjAGgAIABtAGEAeQAgAGkAbgBjAGwAdQBkAGUAIABjAG8AYQBsACAAcwBlAGEAbQAgAG0AZQB0AGgAYQBuAGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAFQAYQBiAGwAZQAgADYAIABpAHMAIABuAG8AdAAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIAB0AG8AIABlAHQAaABhAG4AZQAuACAAUwBlAGUAIABUAGEAYgBsAGUAIAA3ACAASQBuAGQAaQByAGUAYwB0ACAAKABTAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAGUAdABoAGEAbgBlAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBDACAAPQAgAEMAbwBuAGYAaQBkAGUAbgB0AGkAYQBsAC4AIABTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAVABhAHMAbQBhAG4AaQBhACAAYQBuAGQAIAB0AGgAZQAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAYQByAGUAIABuAG8AdAAgAGEAdgBhAGkAbABhAGIAbABlACAAZAB1AGUAIAB0AG8AIABjAG8AbgBmAGkAZABlAG4AdABpAGEAbABpAHQAeQAgAGMAbwBuAHMAdAByAGEAaQBuAHQAcwAgAHQAaABhAHQAIABhAHIAaQBzAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABhACAAbABpAG0AaQB0AGUAZAAgAG4AdQBtAGIAZQByACAAbwBmACAATgBHAEUAUgAgAGQAYQB0AGEAIABpAG4AcAB1AHQAcwAuACAASQB0ACAAaQBzACAAcwB1AGcAZwBlAHMAdABlAGQAIAB0AGgAYQB0ACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAdABoAGUAIABWAGkAYwB0AG8AcgBpAGEAbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABpAHMAIABhAHAAcAByAG8AcAByAGkAYQB0AGUALABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgB3AGgAaQBsAGUAIABmAG8AcgAgAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHQAaABlACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAaQBzACAAYQBwAHAAcgBvAHAAcgBpAGEAdABlAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGQAbwAgAG4AbwB0ACAAaQBuAGMAbAB1AGQAZQAgAGYAdQBnAGkAdABpAHYAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGwAZQBhAGsAYQBnAGUAIABmAHIAbwBtACAAbABvAHcAIABwAHIAZQBzAHMAdQByAGUAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABpAG8AbgAgAHAAaQBwAGUAbABpAG4AZQAgAG4AZQB0AHcAbwByAGsAcwAgAHcAaABpAGwAZQAgAHQAaABvAHMAZQAgAGYAcgBvAG0AIABoAGkAZwBoACAAcAByAGUAcwBzAHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAGcAYQBzACAAbgBlAHQAdwBvAHIAawBzACAAYQByAGUAIABjAG8AbgBzAGkAZABlAHIAZQBkACAAbgBlAGcAbABpAGcAaQBiAGwAZQAuAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABsAGkAcQB1AGkAZAAgAGYAdQBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADEAKQAgAGEAbgBkACAAaQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAzACkAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAG8AZgAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAGMAZQByAHQAYQBpAG4AIABwAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAC4AXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAOABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgA1ACwAIAA4ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIABjAG8AbQBiAHUAcwB0AGUAZABcACIALAAgAFwAIgBFAG4AZQByAGcAeQAgAEMAbwBuAHQAZQBuAHQAIABGAGEAYwB0AG8AcgAgACgARwBKACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbAApAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB1AG4AaQB0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMATwAyAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMASAA0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AMgBPAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMAbwBtAGIAaQBuAGUAZAAgAGcAYQBzAGUAcwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABvAGkAbABzACAAKABvAHQAaABlAHIAIAB0AGgAYQBuACAAcABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABvAGkAbAAgAHUAcwBlAGQAIABhAHMAIABmAHUAZQBsACkALAAgAGUALgBnAC4AIABsAHUAYgByAGkAYwBhAG4AdABzAFwAIgAsACAAMwA4AC4AOAAsACAAXAAiAGsAbABcACIALAAgADEAMwAuADkALAAgADAALgAwACwAIAAwAC4AMAAsACAAMQAzAC4AOQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAZwByAGUAYQBzAGUAcwBcACIALAAgADMAOAAuADgALAAgAFwAIgBrAGwAXAAiACwAIAAzAC4ANQAsACAAMAAuADAALAAgADAALgAwACwAIAAzAC4ANQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAcgB1AGQAZQAgAG8AaQBsACAAaQBuAGMAbAB1AGQAaQBuAGcAIABjAHIAdQBkAGUAIABvAGkAbAAgAGMAbwBuAGQAZQBuAHMAYQB0AGUAcwBcACIALAAgADQANQAuADMALAAgAFwAIgB0AFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADYAOQAuADgAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABsAGkAcQB1AGkAZABzAFwAIgAsACAANAA2AC4ANQAsACAAXAAiAHQAXAAiACwAIAA2ADEALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAANgAxAC4AMgA4ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdQB0AG8AbQBvAHQAaQB2AGUAIABnAGEAcwBvAGwAaQBuAGUAIAAvACAAcABlAHQAcgBvAGwAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdAApAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAGsATABcACIALAAgADYANwAuADQALAAgADAALgAyACwAIAAwAC4AMgAsACAANgA3AC4AOAAwACwAIAAxADcALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuACAAZwBhAHMAbwBsAGkAbgBlAFwAIgAsACAAMwAzAC4AMQAsACAAXAAiAGsATABcACIALAAgADYANwAsACAAMAAuADIALAAgADAALgAyACwAIAA2ADcALgA0ADAALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBLAGUAcgBvAHMAZQBuAGUAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdAApAFwAIgAsACAAMwA3AC4ANQAsACAAXAAiAGsATABcACIALAAgADYAOAAuADkALAAgADAALgAwADEALAAgADAALgAyACwAIAA2ADkALgAxADEALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AIAB0AHUAcgBiAGkAbgBlACAAZgB1AGUAbAAgAC8AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADYAOQAuADgAMgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHQAaQBuAGcAIABvAGkAbABcACIALAAgADMANwAuADMALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA1ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4ANwAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADcAMAAuADIAMAAsACAAMQA3AC4AMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIABvAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMAA0ACwAIAAwAC4AMgAsACAANwAzAC4AOAA0ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABhAHIAbwBtAGEAdABpAGMAIABoAHkAZAByAG8AYwBhAHIAYgBvAG4AcwBcACIALAAgADMANAAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA3ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4AOQAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAGwAdgBlAG4AdABzADoAIABtAGkAbgBlAHIAYQBsACAAdAB1AHIAcABlAG4AdABpAG4AZQAgAG8AcgAgAHcAaABpAHQAZQAgAHMAcABpAHIAaQB0AHMAXAAiACwAIAAzADQALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4ANwAsACAAMAAuADAAMwAsACAAMAAuADIALAAgADYAOQAuADkAMwAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAcABlAHQAcgBvAGwAZQB1AG0AIABnAGEAcwAgACgATABQAEcAKQBcACIALAAgADIANQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA2ADAALgAyACwAIAAwAC4AMgAsACAAMAAuADIALAAgADYAMAAuADYAMAAsACAAMgAwAC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AYQBwAGgAdABoAGEAXAAiACwAIAAzADEALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAANgA5AC4AOAAyACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABjAG8AawBlAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAHQAXAAiACwAIAA5ADIALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAOQAyAC4AOAA4ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAaQBuAGUAcgB5ACAAZwBhAHMAIABhAG4AZAAgAGwAaQBxAHUAaQBkAHMAXAAiACwAIAA0ADIALgA5ACwAIABcACIAdABcACIALAAgADUANAAuADcALAAgADAALgAwADMALAAgADAALgAwADMALAAgADUANAAuADcANgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBmAGkAbgBlAHIAeQAgAGMAbwBrAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAdABcACIALAAgADkAMgAuADYALAAgADAALgAwADgALAAgADAALgAyACwAIAA5ADIALgA4ADgALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAHAAcgBvAGQAdQBjAHQAcwAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMwA0AC4ANAAsACAAXAAiAGsATABcACIALAAgADYAOQAuADgALAAgADAALgAwADIALAAgADAALgAxACwAIAA2ADkALgA5ADIALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBkAGkAZQBzAGUAbABcACIALAAgADMANAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQB0AGgAYQBuAG8AbAAgAGYAbwByACAAdQBzAGUAIABhAHMAIABhACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGkAbgB0AGUAcgBuAGEAbAAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABlAG4AZwBpAG4AZQBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBpAG8AZgB1AGUAbABzACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHQAaABvAHMAZQAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAIABhAG4AZAAgAGIAZQBsAG8AdwBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADAALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABhAHYAaQBhAHQAaQBvAG4AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBMAFwAIgAsACAAMAAuADAALAAgADAALgAwADIALAAgADAALgAyACwAIAAwAC4AMgAyACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBMAFwAIgAsACAAMAAuADAALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADMAMAAsACAAXAAiAE4ARQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4ARQBcAHUAMAAwADIANwAgAHYAYQBsAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABUAHIAYQBuAHMAcABvAHIAdABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsAHMAIABpAG4AIABkAGkAZgBmAGUAcgBlAG4AdAAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAFQAYQBiAGwAZQAgADkAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADYALAAgADEAMAAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHQAeQBwAGUAXAAiACwAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACgARwBKACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbAApAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB1AG4AaQB0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMATwAyAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMASAA0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AMgBPAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMAbwBtAGIAaQBuAGUAZAAgAGcAYQBzAGUAcwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAawBsAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADYANwAuADYAMgAsACAAMQA3AC4AMgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAANwAwAC4ANAAxACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAHAAZQB0AHIAbwBsAGUAdQBtACAAZwBhAHMAIAAoAEwAUABHACkAXAAiACwAIAAyADYALgAyACwAIABcACIAawBsAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADUALAAgADAALgAzACwAIAA2ADEALgAwADAALAAgADIAMAAuADIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEYAdQBlAGwAIABvAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAGwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4ANQAsACAANwA0AC4AMQA4ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBFAHQAaABhAG4AbwBsAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADIALAAgADAALgA0ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQgBpAG8AZABpAGUAcwBlAGwAXAAiACwAIAAzADQALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgA4ACwAIAAxAC4ANwAsACAAMgAuADUALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAAMAAuADUAMQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAE8AdABoAGUAcgAgAGIAaQBvAGYAdQBlAGwAcwBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADgALAAgADEALgA3ACwAIAAyAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAZwBoAHQAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADcALgAzACwAIAAwAC4AMwAsACAANQA5AC4AMAAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBsAFwAIgAsACAANQAxAC4ANAAsACAANwAuADMALAAgADAALgAzACwAIAA1ADkALgAwACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBDAG8AbQBwAHIAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAyAC4AOAAsACAAMAAuADMALAAgADUANAAuADUALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMgA1AC4AMwAsACAAXAAiAGsAbABcACIALAAgADUAMQAuADQALAAgADIALgA4ACwAIAAwAC4AMwAsACAANQA0AC4ANQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADAANwAsACAAMAAuADQALAAgADcAMAAuADMANwAsACAAMQA3AC4AMwAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADEALAAgADAALgA0ACwAIAA3ADAALgA0ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADkALAAgADAALgAyACwAIAAwAC4ANAAsACAANwAwAC4ANQAsACAAMQA3AC4AMwAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADcALAAgADAALgA0ACwAIAAwAC4ANAA3ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAxACwAIAAwAC4ANAAsACAAMAAuADUALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADQALAAgADAALgA2ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdABcACIALAAgADMAMwAuADEALAAgAFwAIgBrAGwAXAAiACwAIAA2ADcALgAwACwAIAAwAC4AMAA2ACwAIAAwAC4ANgAsACAANgA3AC4ANgA2ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0AFwAIgAsACAAMwA2AC4AOAAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADYALAAgADAALgAwADEALAAgADAALgA2ACwAIAA3ADAALgAyADEALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABhAHYAaQBhAHQAaQBvAG4AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADEALAAgADAALgA2ACwAIAAwAC4ANgAxACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARwBhAHMAbwBsAGkAbgBlAFwAIgAsACAAMwA0AC4AMgAsACAAXAAiAGsATABcACIALAAgADYANwAuADQALAAgADEAMAAuADEALAAgADAALgAzACwAIABcACIAXAAiACwAIAAxADcALgAyACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABzAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA1ACwAIABcACIAXAAiACwAIAAxADcALgAzACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABzAFwAIgAsACAAXAAiAEYAdQBlAGwAIABPAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAEwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMgAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEAOAAuADAALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AZgBmAC0AcgBvAGEAZAAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAgAGEAbgBkACAAZgBvAHIAZQBzAHQAcgB5ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMwAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEANwAuADMALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4ARQBcAHUAMAAwADIANwAgAHYAYQBsAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAE8AZgBmAC0AcgBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAATwBmAGYALQByAG8AYQBkACAAZQBxAHUAaQBwAG0AZQBuAHQAIABhAG4AZAAgAHYAZQBzAHMAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAaQBuACAAbwBmAGYALQByAG8AYQBkACAAZQBxAHUAaQBwAG0AZQBuAHQAIABhAG4AZAAgAHYAZQBzAHMAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIAB0AHkAcABlACAAdABcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQAgAHEAXAAiACwAIABcACIARQBDAFQAcgBhAG4AcwAsAHEAIAAoAEcASgAvAGsATAApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABDAE8AMgAgAEUARgBUAHIAYQBuACwAMQAsAHQAcQBnACAAKABrAGcAIABDAE8AMgAtAGUALwBHAEoAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAAQwBIADQAIABFAEYAVAByAGEAbgAsADEALAB0AGcAZwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAE4AMgBPACAARQBGAFQAcgBhAG4ALAAxACwAdABnAGcAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAEYAVAByAGEAbgBzACwAMwAsAHEAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAFAAZQB0AHIAbwBsAFwAIgAsACAAMwA0AC4AMgAsACAANgA3AC4ANAAsACAAMQAwAC4AMQAsACAAMAAuADMALAAgADEANwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcwBzAGUAbABcACIALAAgAFwAIgBEAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgADYAOQAuADkALAAgADAALgAyACwAIAAwAC4ANQAsACAAMQA3AC4AMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAEYAdQBlAGwAIABPAGkAbABcACIALAAgADMAOQAuADcALAAgADcAMwAuADYALAAgADAALgAyACwAIAAwAC4ANQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AZgBmAC0AcgBvAGEAZAAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAgAGEAbgBkACAAZgBvAHIAZQBzAHQAcgB5ACAAZQBxAHUAaQBwAG0AZQBuAHQAXAAiACwAIABcACIARABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIAA2ADkALgA5ACwAIAAwAC4AMwAsACAAMAAuADUALAAgADEANwAuADMAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIARgB1AGUAbABfAEcAZQB0AFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwAUwB0AHIAaQBuAGcAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAXABuACAAIAAgACAATABFAEYAVAAoAEMAZQBsAGwALAAgAEYASQBOAEQAKABcACIALAAgAFwAIgAsAEMAZQBsAGwAKQAgAC0AMQApAFwAbgApADsAXABuAFwAbgBGAHUAZQBsAF8ARwBlAHQAUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAFMAdAByAGkAbgBnAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFIASQBHAEgAVAAoAEMAZQBsAGwALABMAEUATgAoAEMAZQBsAGwAKQAtAEYASQBOAEQAKABcACIALAAgAFwAIgAsAEMAZQBsAGwAKQApAFwAbgApADsAXABuAFwAbgBGAHUAZQBsAF8AVABvAHQAYQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBcAG4APQAgAEwAQQBNAEIARABBACgAXABuACAAIAAgACAARgB1AGUAbABDAG8AbgBzAHUAbQBwAHQAaQBvAG4AQQByAHIAYQB5ACwAIABGAHUAZQBsAFUAcwBlAEEAcgByAGEAeQAsACAARgB1AGUAbABVAHMAZQAsACAARgB1AGUAbABUAHkAcABlAEEAcgByAGEAeQAsACAARgB1AGUAbABUAHkAcABlACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgAFMAVQBNACgAXABuACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAXABuACAAIAAgACAAIAAgACAAIABGAHUAZQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgACgARgB1AGUAbABUAHkAcABlAEEAcgByAGEAeQAgAD0AIABGAHUAZQBsAFQAeQBwAGUAKQAgACoAIABcAG4AIAAgACAAIAAgACAAIAAgACgARgB1AGUAbABVAHMAZQBBAHIAcgBhAHkAIAA9ACAARgB1AGUAbABVAHMAZQApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIAAwAFwAbgAgACAAKQBcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADgAOgAgAEYAdQBlAGwAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA4AC4AMQAgAEYAdQBlAGwAIABVAHMAZQAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQAsACAARQBDACwAIABFAEYALABcAG4AIAAgACAAIAAoAFEAIAAqACAARQBDACAAKgAgAEUARgApACAAKgAgADEAMAAgAF4AIAAtACAAMwBcAG4AIAAgACkAXABuADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcAG4AUQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIAB0AHkAcABlACAAcQAgAGMAbwBtAGIAdQBzAHQAZQBkACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAOgAgAGsATABcAG4ARQBDACAAOgAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAOgAgAEcASgAvAGsATABcAG4ARQBGACAAOgAgAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwAgADoAIABrAGcAIABDAE8AMgBlACAALwAgAEcASgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AVAByAGEAbgBzAHQAcQAsACAARQBDAF8AVAByAGEAbgBzAHEALAAgAEUARgBfAFQAcgBhAG4AcwAxAHQAcQBnACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEAXwBUAHIAYQBuAHMAdABxACwAIABFAEMAXwBUAHIAYQBuAHMAcQAsACAARQBGAF8AVAByAGEAbgBzADEAdABxAGcAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADgALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMgAuADMAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AdAAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcQBcAFwAbABlAGYAdAAoAFEAXwB7AFQAcgBhAG4AcwAsAHQAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEMAXwB7AFQAcgBhAG4AcwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBUAHIAYQBuAHMALAAxACwAdABxAGcAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBUAHIAYQBuAHMAdABxAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAFQAcgBhAG4AcwBxAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgAsACAAXAAiAEcASgAgAC8AIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFQAcgBhAG4AcwAxAHQAcQBnAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlACAALwAgAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHEAXAAiACwAIABcACIARgB1AGUAbAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAXAAiACwAIABcACIAVAByAGEAbgBzAHAAbwByAHQAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZwBcACIALAAgAFwAIgBHAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAXABuAFEAIAA6ACAAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAIAA6ACAAawBMAFwAbgBFAEMAIAA6ACAARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgADoAIABHAEoALwBrAEwAXABuAEUARgAgADoAIABTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAFMAQwBxACwAIABFAEMAXwBTAEMAcQAsACAARQBGAF8AUwBDADEAcQBnACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEAXwBTAEMAcQAsACAARQBDAF8AUwBDAHEALAAgAEUARgBfAFMAQwAxAHEAZwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAG8AcgAgAGUAYQBjAGgAIABHAEgARwAgAGYAcgBvAG0AIAB0AGgAZQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBnAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOAAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgADIALgAyACAARQBzAHQAaQBtAGEAdABpAG4AZwAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABlAG4AZQByAGcAeQAgAHMAbwB1AHIAYwBlAHMAIAAtACAAQwBhAGwAYwB1AGwAYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABsAGkAcQB1AGkAZAAgAGYAdQBlAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHQAIABcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHEAXABcAGwAZQBmAHQAKABRAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAUwBDACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFMAQwAsADEALABxAGcAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAFMAQwBxAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAdQBzAGUAZAAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAIgAsACAAXAAiAFYAYQByAGkAZQBzACAAYgBhAHMAZQBkACAAbwBuACAAZgB1AGUAbAAgAHQAeQBwAGUAOgAgAGsATAAsACAAbQAzACwAIABHAEoAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMAXwBTAEMAcQBcACIALAAgAFwAIgBFAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAIgAsACAAXAAiAEcASgAgAC8AIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFMAQwAxAHEAZwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQwBcACIALAAgAFwAIgBTAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGcAXAAiACwAIABcACIARwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAMQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQA1ADoAIABTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgBUAG8AdABhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGwAaQB2AGUAcwB0AG8AYwBrAFwAbgBFAFwAbgB0ACAAQwBPADIAZQBcAG4ARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AYwBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAG8AXABcAGwAZQBmAHQAKABOAF8AewBjAG8AfQBcAFwAdABpAG0AZQBzACAAVwBfAHsAYwBvAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAYwBvAH0AXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBOAF8AYwBvACAAPQAgAG4AdQBtAGIAZQByACAAbwBmACAAYQBuAGkAbQBhAGwAcwAgAHAAdQByAGMAaABhAHMAZQBkACAAaQBuACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAYwAgAGYAcgBvAG0AIABvAHIAaQBnAGkAbgAgAG8AXABuAFcAXwBjAG8AIAA9ACAAYQB2AGUAcgBhAGcAZQAgAGwAaQB2AGUAdwBlAGkAZwBoAHQAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAYQB0ACAAcABvAGkAbgB0ACAAbwBmACAAcAB1AHIAYwBoAGEAcwBlAFwAbgBFAEYAXwBjAG8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGEAbgBkACAAbwByAGkAZwBpAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABOAF8AYwBvACwAIABXAF8AYwBvACwAIABFAEYAXwBjAG8ALABcAG4AIAAgACAAIAAoAE4AXwBjAG8AIAAqACAAVwBfAGMAbwAgACoAIABFAEYAXwBjAG8AKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABsAGkAdgBlAHMAdABvAGMAawBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAHYAZQBzAHQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAHYAZQBzAHQAbwBjAGsAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AbwBcAFwAbABlAGYAdAAoAE4AXwB7AGMAbwB9AFwAXAB0AGkAbQBlAHMAIABXAF8AewBjAG8AfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBjAG8AfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAHYAZQBzAHQAbwBjAGsAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBfAGMAbwBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGEAbgBpAG0AYQBsAHMAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGkAbgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGMAIABmAHIAbwBtACAAbwByAGkAZwBpAG4AIABvAFwAIgAsACAAXAAiAGgAZQBhAGQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAF8AYwBvAFwAIgAsACAAXAAiAGEAdgBlAHIAYQBnAGUAIABsAGkAdgBlAHcAZQBpAGcAaAB0ACAAbwBmACAAcAB1AHIAYwBoAGEAcwBlAGQAIABsAGkAdgBlAHMAdABvAGMAawAgAGEAdAAgAHAAbwBpAG4AdAAgAG8AZgAgAHAAdQByAGMAaABhAHMAZQBcACIALAAgAFwAIgBrAGcALwBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AYwBvAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAcABlAHIAIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIABhAG4AZAAgAG8AcgBpAGcAaQBuAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAGcAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsACAAXAAiAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG8AXAAiACwAIABcACIAbwByAGkAZwBpAG4AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAGUAZQBkAFwAbgBFAFwAbgB0ACAAQwBPADIAZQBcAG4ARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagBcAFwAbABlAGYAdAAoAFEAXwBqAFwAXAB0AGkAbQBlAHMAIABFAEYAXwBqAFwAXAByAGkAZwBoAHQAKQBcAG4AUQBfAGoAIAA9ACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAZgBlAGUAZAAgAHQAeQBwAGUAIABqACAAcAB1AHIAYwBoAGEAcwBlAGQAXABuAEUARgBfAGoAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGYAZQBlAGQAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAZQBkAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBqACwAIABFAEYAXwBqACwAXABuACAAIAAgACAAUQBfAGoAIAAqACAARQBGAF8AagBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAGUAZQBkAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA1AC4AMgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAZQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBqAFwAXABsAGUAZgB0ACgAUQBfAGoAXABcAHQAaQBtAGUAcwAgAEUARgBfAGoAXABcAHIAaQBnAGgAdAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAGoAXAAiACwAIABcACIAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAZgBlAGUAZAAgAHQAeQBwAGUAIABqACAAcAB1AHIAYwBoAGEAcwBlAGQAXAAiACwAIABcACIAdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGoAXAAiACwAIABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGYAZQBlAGQAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAGsAZwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAIABcACIAZgBlAGUAZAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANQBfADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATQBpAG4AZQByAGEAbABTAHUAcABwAGwAZQBtAGUAbgB0AHMAXABuAFQAbwB0AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAbQBpAG4AZQByAGEAbAAgAHMAdQBwAHAAbABlAG0AZQBuAHQAcwBcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAG0AXABcAGwAZQBmAHQAKABRAF8AbQBcAFwAdABpAG0AZQBzACAARQBGAF8AbQBcAFwAcgBpAGcAaAB0ACkAXABuAFEAXwBtACAAPQAgAHQAbwB0AGEAbAAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AaQBuAGUAcgBhAGwAIABzAHUAcABwAGwAZQBtAGUAbgB0ACAAdAB5AHAAZQAgAG0AIAB1AHMAZQBkAFwAbgBFAEYAXwBtACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAcAB1AHIAYwBoAGEAcwBlAGQAIABtAGkAbgBlAHIAYQBsACAAcwB1AHAAcABsAGUAbQBlAG4AdABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBtACwAIABFAEYAXwBtACwAXABuACAAIAAgACAAUQBfAG0AIAAqACAARQBGAF8AbQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATQBpAG4AZQByAGEAbABTAHUAcABwAGwAZQBtAGUAbgB0AHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAbQBpAG4AZQByAGEAbAAgAHMAdQBwAHAAbABlAG0AZQBuAHQAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATQBpAG4AZQByAGEAbABTAHUAcABwAGwAZQBtAGUAbgB0AHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATQBpAG4AZQByAGEAbABTAHUAcABwAGwAZQBtAGUAbgB0AHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBtAFwAXABsAGUAZgB0ACgAUQBfAG0AXABcAHQAaQBtAGUAcwAgAEUARgBfAG0AXABcAHIAaQBnAGgAdAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBtAFwAIgAsACAAXAAiAHQAbwB0AGEAbAAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAG0AaQBuAGUAcgBhAGwAIABzAHUAcABwAGwAZQBtAGUAbgB0ACAAdAB5AHAAZQAgAG0AIAB1AHMAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBtAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAcAB1AHIAYwBoAGEAcwBlAGQAIABtAGkAbgBlAHIAYQBsACAAcwB1AHAAcABsAGUAbQBlAG4AdABcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8AawBnAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQBcACIALAAgAFwAIgBtAGkAbgBlAHIAYQBsACAAcwB1AHAAcABsAGUAbQBlAG4AdAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAbgBFAFwAbgB0ACAAQwBPADIAZQBcAG4ARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AZgBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGoAXABcAGwAZQBmAHQAKABUAE0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwBmAFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4AVABNAF8AagBmACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAcAB1AHIAYwBoAGEAcwBlAGQAIABhAG4AZAAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAbgBFAEYAXwBmACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAcAB1AHIAYwBoAGEAcwBlAGQAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQATQBfAGoAZgAsACAARQBGAF8AZgAsAFwAbgAgACAAIAAgACgAVABNAF8AagBmACAAKgAgAEUARgBfAGYAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgA0AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGYAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBqAFwAXABsAGUAZgB0ACgAVABNAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AZgBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAE0AXwBqAGYAXAAiACwAIABcACIAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGEAbgBkACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAIABcACIAawBnAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AZgBcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAG8AZgAgAHAAdQByAGMAaABhAHMAZQBkACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAGcAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsACAAXAAiAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAIABcACIAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGMAbwBtAHAAbwBuAGUAbgB0AHMAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBmAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AYwBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGoAXABcAGwAZQBmAHQAKAAoAEYAXwB7AGMAZgB9AFwAXAB0AGkAbQBlAHMAIABUAE0AXwB7AGoAZgB9ACkALwAxADAAMABcAFwAdABpAG0AZQBzACAARQBGAF8AYwBcAFwAcgBpAGcAaAB0ACkAXABuAEYAXwBjAGYAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwBvAG0AcABvAG4AZQBuAHQAIABjACAAYwBvAG4AdABhAGkAbgBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAZgBcAG4AVABNAF8AagBmACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAcAB1AHIAYwBoAGEAcwBlAGQAIABhAG4AZAAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAbgBFAEYAXwBjACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGgAZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABjAG8AbQBwAG8AbgBlAG4AdAAgAGMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARgBfAGMAZgAsACAAVABNAF8AagBmACwAIABFAEYAXwBjACwAXABuACAAIAAgACAAKAAoAEYAXwBjAGYAIAAqACAAVABNAF8AagBmACkAIAAvACAAMQAwADAAKQAgACoAIABFAEYAXwBjAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARgBfAGMAZgAsACAAVABNAF8AagBmACwAIABFAEYAXwBjACwAXABuACAAIAAgACAAKABGAF8AYwBmACAAKgAgAFQATQBfAGoAZgApACAAKgAgAEUARgBfAGMAIAAqACAAMQAwAF4ALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGMAbwBtAHAAbwBuAGUAbgB0AHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgA0AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBmAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AYwBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGoAXABcAGwAZQBmAHQAKABcAFwAZgByAGEAYwB7AEYAXwB7AGMAZgB9AFwAXAB0AGkAbQBlAHMAIABUAE0AXwB7AGoAZgB9AH0AewAxADAAMAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwBjAFwAXAByAGkAZwBoAHQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBmAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AYwBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGoAXABcAGwAZQBmAHQAKABGAF8AewBjAGYAfQBcAFwAdABpAG0AZQBzACAAVABNAF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AYwBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAXwBjAGYAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwBvAG0AcABvAG4AZQBuAHQAIABjACAAYwBvAG4AdABhAGkAbgBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAZgBcACIALAAgAFwAIgB3AHQAJQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQATQBfAGoAZgBcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAHAAdQByAGMAaABhAHMAZQBkACAAYQBuAGQAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBjAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGgAZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABjAG8AbQBwAG8AbgBlAG4AdAAgAGMAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAGsAZwAgAGMAbwBtAHAAbwBuAGUAbgB0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALAAgAFwAIgBmAGUAcgB0AGkAbABpAHMAZQByACAAYwBvAG0AcABvAG4AZQBuAHQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBmAFwAIgAsACAAXAAiAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsACAAXAAiAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIAByAGUAbQBvAHYAZQBzACAAZABpAHYAaQBzAGkAbwBuACAAYgB5ACAAMQAwADAAIABmAG8AcgAgAEYAXwBjAGYALAAgAHQAcgBlAGEAdABpAG4AZwAgAEYAXwBjAGYAIABhAHMAIABmAHIAYQBjAHQAaQBvAG4AIABpAG4AcwB0AGUAYQBkACAAbwBmACAAcABlAHIAYwBlAG4AdAAgAGIAZQBjAGEAdQBzAGUAIABpAHQAIABpAHMAIABhACAAZgByAGEAYwB0AGkAbwBuACAAaQBuACAAcwBjAG8AcABlACAAMQAgAGUAcQB1AGEAdABpAG8AbgBzAC4AIABDAG8AbgB2AGUAcgB0ACAAawBnACAAdABvACAAdABvAG4AbgBlAHMAIABiAHkAIABtAHUAdABpAHAAbAB5AGkAbgBnACAAYgB5ACAAMQAwAF4ALQAzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABmAGUAcgB0AGkAbABpAHMAZQByACAAcAByAG8AZAB1AGMAdAAgAGQAZQByAGkAdgBlAGQAIABmAHIAbwBtACAAYwBvAG0AcABvAG4AZQBuAHQAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARgBfAGMAZgAsACAARQBGAF8AYwAsAFwAbgAgACAAIAAgAEYAXwBjAGYAIAAqACAARQBGAF8AYwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABwAHIAbwBkAHUAYwB0ACAAZABlAHIAaQB2AGUAZAAgAGYAcgBvAG0AIABjAG8AbQBwAG8AbgBlAG4AdABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAGYAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMATwAyAGUALwBrAGcAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBBAEYAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwBYAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AZgA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AYwBcAFwAbABlAGYAdAAoAEYAXwB7AGMAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwBjAFwAXAByAGkAZwBoAHQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwBYAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAXwBjAGYAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwBvAG0AcABvAG4AZQBuAHQAIABjACAAYwBvAG4AdABhAGkAbgBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAZgBcACIALAAgAFwAIgB3AHQAJQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGMAXAAiACwAIABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAaABlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAbwBtAHAAbwBuAGUAbgB0ACAAYwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8AawBnACAAYwBvAG0AcABvAG4AZQBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsACAAXAAiAGYAZQByAHQAaQBsAGkAcwBlAHIAIABjAG8AbQBwAG8AbgBlAG4AdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAIABcACIAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAVABoAGkAcwAgAGUAcQB1AGEAdABpAG8AbgAgAGkAcwAgAGEAZABkAGUAZAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAYQBuACAARQBGACAAdgBhAGwAdQBlACAAZgByAG8AbQAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABjAG8AbQBwAG8AbgBlAG4AdABzACAAdABoAGEAdAAgAGMAYQBuACAAYgBlACAAdQBzAGUAZAAgAGkAbgAgADEANQAuADQALgAxAC4AMQAgACgAMQApAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAFwAbgBUAG8AdABhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBoAFwAXABsAGUAZgB0ACgAUQBfAGgAXABcAHQAaQBtAGUAcwAgAEUARgBfAGgAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRAF8AaAAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABhAGMAdABpAHYAZQAgAGkAbgBnAHIAZQBkAGkAZQBuAHQAcwAgAGkAbgAgAGEAZwByAGkAYwBoAGUAbQBpAGMAYQBsACAAdAB5AHAAZQAgAGgAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGEAbgBkACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwBcAG4ARQBGAF8AaAAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcAB1AHIAYwBoAGEAcwBlAGQAIABhAGcAcgBpAGMAaABlAG0AaQBjAGEAbAAgAGEAYwB0AGkAdgBlACAAaQBuAGcAcgBlAGQAaQBlAG4AdABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGgALAAgAEUARgBfAGgALABcAG4AIAAgACAAIAAoAFEAXwBoACAAKgAgAEUARgBfAGgAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADUAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAQQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADUAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAQQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADUAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAQQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGgAXABcAGwAZQBmAHQAKABRAF8AaABcAFwAdABpAG0AZQBzACAARQBGAF8AaABcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADUAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAQQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AaABcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABhAGMAdABpAHYAZQAgAGkAbgBnAHIAZQBkAGkAZQBuAHQAcwAgAGkAbgAgAGEAZwByAGkAYwBoAGUAbQBpAGMAYQBsACAAdAB5AHAAZQAgAGgAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGEAbgBkACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwBcACIALAAgAFwAIgBrAGcAIABhAGkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBoAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGEAZwByAGkAYwBoAGUAbQBpAGMAYQBsACAAYQBjAHQAaQB2AGUAIABpAG4AZwByAGUAZABpAGUAbgB0AFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAGcAIABhAGkAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBoAFwAIgAsACAAXAAiAGEAZwByAGkAYwBoAGUAbQBpAGMAYQBsACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAFwAbgBFAG0AYgBlAGQAZABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAcAB1AHIAYwBoAGEAcwBlAGQAIABsAGkAbQBlAFwAbgBFAFwAbgB0ACAAQwBPADIAZQBcAG4ARQA9AE0AXwBsAGkAbQBlAFwAXAB0AGkAbQBlAHMAIABFAEYAXwBsAFwAbgBNAF8AbABpAG0AZQAgAD0AIAB0AG8AdABhAGwAIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABsAGkAbQBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwBcAG4ARQBGAF8AbAAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcAB1AHIAYwBoAGEAcwBlAGQAIABsAGkAbQBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADYAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAG0AZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAF8AbABpAG0AZQAsACAARQBGAF8AbAAsAFwAbgAgACAAIAAgAE0AXwBsAGkAbQBlACAAKgAgAEUARgBfAGwAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA2AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQBtAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBiAGUAZABkAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGwAaQBtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADYAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAG0AZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADYAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAG0AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgA2AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA2AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQBtAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADYAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAG0AZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBNAF8AewBsAGkAbQBlAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAGwAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADYAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAG0AZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AbABpAG0AZQBcACIALAAgAFwAIgB0AG8AdABhAGwAIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABsAGkAbQBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwBcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AbABcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcAB1AHIAYwBoAGEAcwBlAGQAIABsAGkAbQBlAFwAIgAsACAAXAAiAHQAIABDAE8AMgBlAC8AdABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABTAGUAcgB2AGkAYwBlAHMAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAbwBmACAAcAB1AHIAYwBoAGEAcwBlAGQAIABzAGUAcgB2AGkAYwBlAHMAIABhAG4AZAAgAGMAbwBuAHQAcgBhAGMAdABvAHIAIABvAHAAZQByAGEAdABpAG8AbgBzAFwAbgBFAFwAbgB0ACAAQwBPADIAZQBcAG4ARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcABcAFwAbABlAGYAdAAoAEEAXwBwAFwAXAB0AGkAbQBlAHMAIABFAEYAXwBwAFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4AQQBfAHAAIAA9ACAAYQBjAHQAaQB2AGkAdAB5ACAAZABhAHQAYQAgAG8AZgAgAHQAaABlACAAcwBlAHIAdgBpAGMAZQAgAHQAaABhAHQAIAB3AGEAcwAgAHAAdQByAGMAaABhAHMAZQBkAFwAbgBFAEYAXwBwACAAPQAgAGwAaQBmAGUAIABjAHkAYwBsAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdABoAGUAIABwAHUAcgBjAGgAYQBzAGUAZAAgAHMAZQByAHYAaQBjAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABTAGUAcgB2AGkAYwBlAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBfAHAALAAgAEUARgBfAHAALABcAG4AIAAgACAAIAAoAEEAXwBwACAAKgAgAEUARgBfAHAAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABTAGUAcgB2AGkAYwBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAbwBmACAAcAB1AHIAYwBoAGEAcwBlAGQAIABzAGUAcgB2AGkAYwBlAHMAIABhAG4AZAAgAGMAbwBuAHQAcgBhAGMAdABvAHIAIABvAHAAZQByAGEAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABTAGUAcgB2AGkAYwBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABTAGUAcgB2AGkAYwBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA1AC4ANwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABTAGUAcgB2AGkAYwBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADcAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUwBlAHIAdgBpAGMAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcABcAFwAbABlAGYAdAAoAEEAXwBwAFwAXAB0AGkAbQBlAHMAIABFAEYAXwBwAFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABTAGUAcgB2AGkAYwBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBfAHAAXAAiACwAIABcACIAYQBjAHQAaQB2AGkAdAB5ACAAZABhAHQAYQAgAG8AZgAgAHQAaABlACAAcwBlAHIAdgBpAGMAZQAgAHQAaABhAHQAIAB3AGEAcwAgAHAAdQByAGMAaABhAHMAZQBkAFwAIgAsACAAXAAiAGgAYQAgAG8AcgAgAGgAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBwAFwAIgAsACAAXAAiAGwAaQBmAGUAIABjAHkAYwBsAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdABoAGUAIABwAHUAcgBjAGgAYQBzAGUAZAAgAHMAZQByAHYAaQBjAGUAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAGgAYQAgAG8AcgAgAGsAZwAgAEMATwAyAGUALwBoAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcABcACIALAAgAFwAIgBzAGUAcgB2AGkAYwBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBcAG4ARQBtAGIAZQBkAGQAZQBkACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdQBzAGUAIABvAGYAIABwAGEAYwBrAGEAZwBpAG4AZwAgAG0AYQB0AGUAcgBpAGEAbABzAFwAbgBFAFwAbgB0ACAAQwBPADIAZQBcAG4ARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcABcAFwAbABlAGYAdAAoAFEAXwBwAFwAXAB0AGkAbQBlAHMAIABFAEYAXwBwAFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4AUQBfAHAAIAA9ACAAdQBuAGkAdABzACAAbwBmACAAcABhAGMAawBhAGcAaQBuAGcAIAB0AHkAcABlACAAcABcAG4ARQBGAF8AcAAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcABhAGMAawBhAGcAaQBuAGcAIAB0AHkAcABlACAAcABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA4AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFAAYQBjAGsAYQBnAGkAbgBnAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBwACwAIABFAEYAXwBwACwAXABuACAAIAAgACAAKABRAF8AcAAgACoAIABFAEYAXwBwACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBiAGUAZABkAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHUAcwBlACAAbwBmACAAcABhAGMAawBhAGcAaQBuAGcAIABtAGEAdABlAHIAaQBhAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA4AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFAAYQBjAGsAYQBnAGkAbgBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADgALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBwAFwAXABsAGUAZgB0ACgAUQBfAHAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHAAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA4AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFAAYQBjAGsAYQBnAGkAbgBnAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBwAFwAIgAsACAAXAAiAHUAbgBpAHQAcwAgAG8AZgAgAHAAYQBjAGsAYQBnAGkAbgBnACAAdAB5AHAAZQAgAHAAXAAiACwAIABcACIAdQBuAGkAdABzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AcABcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcABhAGMAawBhAGcAaQBuAGcAIAB0AHkAcABlACAAcABcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8AdQBuAGkAdABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHAAXAAiACwAIABcACIAcABhAGMAawBhAGcAaQBuAGcAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAQwBoAGEAbgBnAGUAZAAgAHUAbgBpAHQAIABvAGYAIABRACAAZgByAG8AbQAgAFwAdQAwADAAMgA3AHUAbgBpAHQAcwBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AGsAZwBcAHUAMAAwADIANwAgAGEAcwAgAEUARgAgAGQAYQB0AGEAIABpAHMAIABpAG4AIABrAGcALgBcACIAKQA7AFwAbgAgACAAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABHAHIAbwB3AE0AZQBkAGkAYQBcAG4ARQBtAGIAZQBkAGQAZQBkACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdQBzAGUAIABvAGYAIABnAHIAbwB3ACAAbQBlAGQAaQBhACAAcAByAG8AZAB1AGMAdABzAFwAbgBFAFwAbgB0ACAAQwBPADIAZQBcAG4ARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AZwBcAFwAbABlAGYAdAAoAFEAXwBnAFwAXAB0AGkAbQBlAHMAIABFAEYAXwBnAFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4AUQBfAGcAIAA9ACAAdABvAHQAYQBsACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAZwByAG8AdwAgAG0AZQBkAGkAYQAgAHQAeQBwAGUAIABnAFwAbgBFAEYAXwBnACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABnAHIAbwB3ACAAbQBlAGQAaQBhACAAdAB5AHAAZQAgAGcAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABHAHIAbwB3AE0AZQBkAGkAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AZwAsACAARQBGAF8AZwAsAFwAbgAgACAAIAAgACgAUQBfAGcAIAAqACAARQBGAF8AZwApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AYgBlAGQAZABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHMAZQAgAG8AZgAgAGcAcgBvAHcAIABtAGUAZABpAGEAIABwAHIAbwBkAHUAYwB0AHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADkAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARwByAG8AdwBNAGUAZABpAGEAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADkAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARwByAG8AdwBNAGUAZABpAGEAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABHAHIAbwB3AE0AZQBkAGkAYQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgA5AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AZwBcAFwAbABlAGYAdAAoAFEAXwBnAFwAXAB0AGkAbQBlAHMAIABFAEYAXwBnAFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABHAHIAbwB3AE0AZQBkAGkAYQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZwBcACIALAAgAFwAIgB0AG8AdABhAGwAIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABnAHIAbwB3ACAAbQBlAGQAaQBhACAAdAB5AHAAZQAgAGcAXAAiACwAIABcACIAawBnACAAbwByACAAbQAzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AZwBcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZwByAG8AdwAgAG0AZQBkAGkAYQAgAHQAeQBwAGUAIABnAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAGcAIABvAHIAIABrAGcAIABDAE8AMgBlAC8AbQAzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZwBcACIALAAgAFwAIgBnAHIAbwB3ACAAbQBlAGQAaQBhACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAwAF8AMQBfADEAXwBfADEAXwBPAHQAaABlAHIAUAB1AHIAYwBoAGEAcwBlAGQARwBvAG8AZABzAEEAbgBkAFMAZQByAHYAaQBjAGUAcwBcAG4ATwB0AGgAZQByACAAcAB1AHIAYwBoAGEAcwBlAGQAIABnAG8AbwBkAHMAIABhAG4AZAAgAHMAZQByAHYAaQBjAGUAcwAgAGcAZQBuAGUAcgBpAGMAIABlAHMAdABpAG0AYQB0AGUAXABuAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgB0ACAAQwBPADIAZQBcAG4AZQBtAGkAcwBzAGkAbwBuAHMAPQBhAGMAdABpAHYAaQB0AHkAXwBkAGEAdABhAFwAXAB0AGkAbQBlAHMAIABlAG0AaQBzAHMAaQBvAG4AXwBmAGEAYwB0AG8AcgBcAG4AYQBjAHQAaQB2AGkAdAB5AF8AZABhAHQAYQAgAD0AIABtAGUAYQBzAHUAcgBlAGQAIABhAGMAdABpAHYAaQB0AHkAIABmAG8AcgAgAHQAaABlACAAcAB1AHIAYwBoAGEAcwBlAGQAIABnAG8AbwBkACAAbwByACAAcwBlAHIAdgBpAGMAZQBcAG4AZQBtAGkAcwBzAGkAbwBuAF8AZgBhAGMAdABvAHIAIAA9ACAAbABpAGYAZQBjAHkAYwBsAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGEAYwB0AGkAdgBpAHQAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAYwB0AGkAdgBpAHQAeQBfAGQAYQB0AGEALAAgAGUAbQBpAHMAcwBpAG8AbgBfAGYAYQBjAHQAbwByACwAXABuACAAIAAgACAAYQBjAHQAaQB2AGkAdAB5AF8AZABhAHQAYQAgACoAIABlAG0AaQBzAHMAaQBvAG4AXwBmAGEAYwB0AG8AcgBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AdABoAGUAcgAgAHAAdQByAGMAaABhAHMAZQBkACAAZwBvAG8AZABzACAAYQBuAGQAIABzAGUAcgB2AGkAYwBlAHMAIABnAGUAbgBlAHIAaQBjACAAZQBzAHQAaQBtAGEAdABlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAwAF8AMQBfADEAXwBfADEAXwBPAHQAaABlAHIAUAB1AHIAYwBoAGEAcwBlAGQARwBvAG8AZABzAEEAbgBkAFMAZQByAHYAaQBjAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADEAMAAsACAAZwBlAG4AZQByAGkAYwAgAHAAbABhAGMAZQBoAG8AbABkAGUAcgAgAGUAcQB1AGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAwAF8AMQBfADEAXwBfADEAXwBPAHQAaABlAHIAUAB1AHIAYwBoAGEAcwBlAGQARwBvAG8AZABzAEEAbgBkAFMAZQByAHYAaQBjAGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAwAF8AMQBfADEAXwBfADEAXwBPAHQAaABlAHIAUAB1AHIAYwBoAGEAcwBlAGQARwBvAG8AZABzAEEAbgBkAFMAZQByAHYAaQBjAGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGUAbQBpAHMAcwBpAG8AbgBzAD0AYQBjAHQAaQB2AGkAdAB5AFwAXABfAGQAYQB0AGEAXABcAHQAaQBtAGUAcwAgAGUAbQBpAHMAcwBpAG8AbgBcAFwAXwBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAwAF8AMQBfADEAXwBfADEAXwBPAHQAaABlAHIAUAB1AHIAYwBoAGEAcwBlAGQARwBvAG8AZABzAEEAbgBkAFMAZQByAHYAaQBjAGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBhAGMAdABpAHYAaQB0AHkAXwBkAGEAdABhAFwAIgAsACAAXAAiAG0AZQBhAHMAdQByAGUAZAAgAGEAYwB0AGkAdgBpAHQAeQAgAGYAbwByACAAdABoAGUAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGcAbwBvAGQAIABvAHIAIABzAGUAcgB2AGkAYwBlAFwAIgAsACAAXAAiAHYAYQByAGkAZQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZQBtAGkAcwBzAGkAbwBuAF8AZgBhAGMAdABvAHIAXAAiACwAIABcACIAbABpAGYAZQBjAHkAYwBsAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGEAYwB0AGkAdgBpAHQAeQBcACIALAAgAFwAIgB2AGEAcgBpAGUAcwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABcAG4AVABvAHQAYQBsACAAdQBwAHMAdAByAGUAYQBtACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwBjAG8AcABlACAAMQAgAGYAdQBlAGwAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBxAEUAXwB7AFcAVABUACwAdAByAGEAbgBzACwAcQB9ACsAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBxAEUAXwB7AFcAVABUACwAUwBDACwAcQB9AFwAbgBFAF8AVwBUAFQAdAByAGEAbgBzAHEAIAA9ACAAdQBwAHMAdAByAGUAYQBtACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwBjAG8AcABlACAAMQAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZgB1AGUAbAAgAHUAcwBlAFwAbgBFAF8AVwBUAFQAUwBDAHEAIAA9ACAAdQBwAHMAdAByAGUAYQBtACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwBjAG8AcABlACAAMQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgB1AGUAbAAgAHUAcwBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAFUAcABzAHQAcgBlAGEAbQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAdQBlAGwAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAFcAVABUAHQAcgBhAG4AcwBxACwAIABFAF8AVwBUAFQAUwBDAHEALABcAG4AIAAgACAAIABFAF8AVwBUAFQAdAByAGEAbgBzAHEAIAArACAARQBfAFcAVABUAFMAQwBxAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAdQBwAHMAdAByAGUAYQBtACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwBjAG8AcABlACAAMQAgAGYAdQBlAGwAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAFUAcABzAHQAcgBlAGEAbQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAdQBlAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAFUAcABzAHQAcgBlAGEAbQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAdQBlAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgAxADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAFUAcABzAHQAcgBlAGEAbQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAdQBlAGwAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAFUAcABzAHQAcgBlAGEAbQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAdQBlAGwAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBxAEUAXwB7AFcAVABUACwAdAByAGEAbgBzACwAcQB9ACsAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBxAEUAXwB7AFcAVABUACwAUwBDACwAcQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABVAHAAcwB0AHIAZQBhAG0ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAHUAZQBsAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAXwBXAFQAVAB0AHIAYQBuAHMAcQBcACIALAAgAFwAIgB1AHAAcwB0AHIAZQBhAG0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAGMAbwBwAGUAIAAxACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsACAAdQBzAGUAXAAiACwAIABcACIAdAAgAEMATwAyAGUAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGIAeQAgADEANQAuADEAMQAuADEALgAxACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAXwBXAFQAVABTAEMAcQBcACIALAAgAFwAIgB1AHAAcwB0AHIAZQBhAG0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAGMAbwBwAGUAIAAxACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAHUAZQBsACAAdQBzAGUAXAAiACwAIABcACIAdAAgAEMATwAyAGUAXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGIAeQAgADEANQAuADEAMQAuADEALgAxACAAKAAzACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADIAXwBVAHAAcwB0AHIAZQBhAG0AVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBcAG4AVQBwAHMAdAByAGUAYQBtACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwBjAG8AcABlACAAMQAgAGYAdQBlAGwAIAB1AHMAZQAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABwAHUAcgBwAG8AcwBlAHMAXABuAEUAXwBXAFQAVAB0AHIAYQBuAHMAcQBcAG4AdAAgAEMATwAyAGUAXABuAEUAXwB7AFcAVABUACwAdAByAGEAbgBzACwAcQB9AD0AUQBfAHsAVAByAGEAbgBzACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEMAXwB7AFQAcgBhAG4AcwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBUAHIAYQBuAHMALAAzACwAcQB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRAF8AVAByAGEAbgBzAHEAIAA9ACAAYQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAcQAgAGMAbwBtAGIAdQBzAHQAZQBkACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAbgBFAEMAXwBUAHIAYQBuAHMAcQAgAD0AIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcAG4ARQBGAF8AVAByAGEAbgBzADMAcQAgAD0AIABzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADIAXwBVAHAAcwB0AHIAZQBhAG0AVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AVAByAGEAbgBzAHEALAAgAEUAQwBfAFQAcgBhAG4AcwBxACwAIABFAEYAXwBUAHIAYQBuAHMAMwBxACwAXABuACAAIAAgACAAKABRAF8AVAByAGEAbgBzAHEAIAAqACAARQBDAF8AVAByAGEAbgBzAHEAIAAqACAARQBGAF8AVAByAGEAbgBzADMAcQApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBVAHAAcwB0AHIAZQBhAG0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAGMAbwBwAGUAIAAxACAAZgB1AGUAbAAgAHUAcwBlACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAHAAdQByAHAAbwBzAGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADIAXwBVAHAAcwB0AHIAZQBhAG0AVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAFcAVABUAHQAcgBhAG4AcwBxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAyAF8AVQBwAHMAdAByAGUAYQBtAFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA1AC4AMQAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAVwBUAFQALAB0AHIAYQBuAHMALABxAH0APQBRAF8AewBUAHIAYQBuAHMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAVAByAGEAbgBzACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFQAcgBhAG4AcwAsADMALABxAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAyAF8AVQBwAHMAdAByAGUAYQBtAFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAFQAcgBhAG4AcwBxAFwAIgAsACAAXAAiAGEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHEAIABjAG8AbQBiAHUAcwB0AGUAZAAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcACIALAAgAFwAIgBrAEwAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMAXwBUAHIAYQBuAHMAcQBcACIALAAgAFwAIgBlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcACIALAAgAFwAIgBHAEoALwBrAEwAIABvAHIAIABHAEoALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBUAHIAYQBuAHMAMwBxAFwAIgAsACAAXAAiAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8ARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMwBfAFUAcABzAHQAcgBlAGEAbQBTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXABuAFUAcABzAHQAcgBlAGEAbQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAYwBvAHAAZQAgADEAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAGYAdQBlAGwAIAB1AHMAZQBcAG4ARQBfAFcAVABUAFMAQwBxAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBfAHsAVwBUAFQALABTAEMALABxAH0APQBRAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAUwBDACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFMAQwAsADMALABxAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAFEAXwBTAEMAcQAgAD0AIABhAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIABxACAAdQBzAGUAZAAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAbgBFAEMAXwBTAEMAcQAgAD0AIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAbgBFAEYAXwBTAEMAMwBxACAAPQAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AUwBDAHEALAAgAEUAQwBfAFMAQwBxACwAIABFAEYAXwBTAEMAMwBxACwAXABuACAAIAAgACAAKABRAF8AUwBDAHEAIAAqACAARQBDAF8AUwBDAHEAIAAqACAARQBGAF8AUwBDADMAcQApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMwBfAFUAcABzAHQAcgBlAGEAbQBTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFUAcABzAHQAcgBlAGEAbQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAYwBvAHAAZQAgADEAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAGYAdQBlAGwAIAB1AHMAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AVwBUAFQAUwBDAHEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMwBfAFUAcABzAHQAcgBlAGEAbQBTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA1AC4AMQAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMwBfAFUAcABzAHQAcgBlAGEAbQBTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AFcAVABUACwAUwBDACwAcQB9AD0AUQBfAHsAUwBDACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEMAXwB7AFMAQwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBTAEMALAAzACwAcQB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMwBfAFUAcABzAHQAcgBlAGEAbQBTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAFMAQwBxAFwAIgAsACAAXAAiAGEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAawBMAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AUwBDAHEAXAAiACwAIABcACIAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwBcACIALAAgAFwAIgBHAEoALwBrAEwAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBTAEMAMwBxAFwAIgAsACAAXAAiAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBHAEoAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAHMAdABhAHQAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG0AXAAiACwAIABcACIAbQBlAHQAcgBvAHAAbwBsAGkAdABhAG4ALwBuAG8AbgAtAG0AZQB0AHIAbwBwAG8AbABpAHQAYQBuACAAbABvAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBzAHQAYQB0AGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AG0AZQB0AHIAbwAvAG4AbwBuAC0AbQBlAHQAcgBvAFwAdQAwADAAMgA3ACAAYQByAGcAdQBtAGUAbgB0AHMAIABhAHMAIABnAGEAcwBlAG8AdQBzACAAcwBjAG8AcABlACAAMwAgAEUARgBzACAAYQByAGUAIABzAHQAYQB0AGUAIABhAG4AZAAgAG0AZQB0AHIAbwAvAG4AbwBuAC0AbQBlAHQAcgBvACAAbABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkAC4AXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMQBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABcAG4AUwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAbABvAGMAYQB0AGkAbwBuACAAYgBhAHMAZQBkAFwAbgBFAF8AMwBlAGwAZQBjAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBfAHsAMwAsAGUAbABlAGMAfQA9AFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewAzACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRAF8AZQBsAGUAYwAgAD0AIABhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZABcAG4ARQBGAF8AMwBlAGwAZQBjACAAPQAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADEAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAEUARgBfADMAZQBsAGUAYwAsAFwAbgAgACAAIAAgACgAUQBfAGUAbABlAGMAIAAqACAARQBGAF8AMwBlAGwAZQBjACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABsAG8AYwBhAHQAaQBvAG4AIABiAGEAcwBlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AMwBlAGwAZQBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMQBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMQBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgAxADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMQBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7ADMALABlAGwAZQBjAH0APQBRAF8AewBlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAMwAsAGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADEAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAGUAbABlAGMAXAAiACwAIABcACIAYQBtAG8AdQBuAHQAIABvAGYAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAGcAcgBpAGQAXAAiACwAIABcACIAawBXAGgAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwAzAGUAbABlAGMAXAAiACwAIABcACIAcwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8AawBXAGgAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBnAFwAIgAsACAAXAAiAGcAcgBpAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAB3AGEAcwAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABcAG4AUwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAbQBhAHIAawBlAHQAIABiAGEAcwBlAGQAXABuAEUAXwAzAGUAbABlAGMAXABuAHQAIABDAE8AMgBlAFwAbgBFAF8AewAzACwAZQBsAGUAYwB9AD0AXABcAGwAZQBmAHQAWwBRAF8AewBlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAAoADEALQAoAFIAUABQACsASgBSAFAAUAApAFwAXAByAGkAZwBoAHQAKQAtAFwAXABsAGUAZgB0ACgAUgBFAEMAXwB7AHMAdQByAHIAZQBuAGQAZQByAGUAZAB9AC0AUgBFAEMAXwB7AG8AbgBzAGkAdABlAH0AXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAXAByAGkAZwBoAHQAXQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBSAE0ARgAzACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRAF8AZQBsAGUAYwAgAD0AIABhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZABcAG4AUgBQAFAAIAA9ACAAcgBlAG4AZQB3AGEAYgBsAGUAIABwAG8AdwBlAHIAIABwAGUAcgBjAGUAbgB0AGEAZwBlACAAdQBuAGQAZQByACAATABSAEUAVAAgAGYAbwByACAAdABoAGUAIABhAHAAcABsAGkAYwBhAGIAbABlACAAcABlAHIAaQBvAGQAXABuAEoAUgBQAFAAIAA9ACAAagB1AHIAaQBzAGQAaQBjAHQAaQBvAG4AYQBsACAAcgBlAG4AZQB3AGEAYgBsAGUAIABwAG8AdwBlAHIAIABwAGUAcgBjAGUAbgB0AGEAZwBlACAAZgBvAHIAIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIABwAGUAcgBpAG8AZABcAG4AUgBFAEMAXwBzAHUAcgByAGUAbgBkAGUAcgBlAGQAIAA9ACAAZQBsAGkAZwBpAGIAbABlACAAcgBlAG4AZQB3AGEAYgBsAGUAIABlAG4AZQByAGcAeQAgAGMAZQByAHQAaQBmAGkAYwBhAHQAZQBzACAAdgBvAGwAdQBuAHQAYQByAGkAbAB5ACAAcwB1AHIAcgBlAG4AZABlAHIAZQBkAFwAbgBSAEUAQwBfAG8AbgBzAGkAdABlACAAPQAgAGUAbABpAGcAaQBiAGwAZQAgAHIAZQBuAGUAdwBhAGIAbABlACAAZQBuAGUAcgBnAHkAIABjAGUAcgB0AGkAZgBpAGMAYQB0AGUAcwAgAGkAcwBzAHUAZQBkACAAZgBvAHIAIABvAG4AcwBpAHQAZQAgAGcAZQBuAGUAcgBhAHQAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAbgBFAEYAXwBSAE0ARgAzAGUAbABlAGMAIAA9ACAAcwBjAG8AcABlACAAMwAgAHIAZQBzAGkAZAB1AGEAbAAgAG0AaQB4ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBlAGwAZQBjACwAIABSAFAAUAAsACAASgBSAFAAUAAsACAAUgBFAEMAXwBzAHUAcgByAGUAbgBkAGUAcgBlAGQALAAgAFIARQBDAF8AbwBuAHMAaQB0AGUALAAgAEUARgBfAFIATQBGADMAZQBsAGUAYwAsAFwAbgAgACAAIAAgACgAKABRAF8AZQBsAGUAYwAgACoAIAAoADEAIAAtACAAKABSAFAAUAAgACsAIABKAFIAUABQACkAKQApACAALQAgACgAKABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAC0AIABSAEUAQwBfAG8AbgBzAGkAdABlACkAIAAqACAAMQAwACAAXgAgAC0AMwApACkAIAAqACAARQBGAF8AUgBNAEYAMwBlAGwAZQBjACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBlAGwAZQBjACwAIABSAFAAUAAsACAASgBSAFAAUAAsACAAUgBFAEMAXwBzAHUAcgByAGUAbgBkAGUAcgBlAGQALAAgAFIARQBDAF8AbwBuAHMAaQB0AGUALAAgAEUARgBfAFIATQBGADMAZQBsAGUAYwAsAFwAbgAgACAAIAAgACgAKABRAF8AZQBsAGUAYwAgACoAIAAoADEAIAAtACAAKABSAFAAUAAgACsAIABKAFIAUABQACkAKQApACAALQAgACgAKABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAC0AIABSAEUAQwBfAG8AbgBzAGkAdABlACkAIAAqACAAMQAwACAAXgAgADMAKQApACAAKgAgAEUARgBfAFIATQBGADMAZQBsAGUAYwAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAbQBhAHIAawBlAHQAIABiAGEAcwBlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAyAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwAzAGUAbABlAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAyAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgAxADIALgAxAC4AMgAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAyAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAyAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewAzACwAZQBsAGUAYwB9AD0AIABbACAAUQBfAHsAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAXABcAGwAZQBmAHQAKAAxAC0AKABSAFAAUAArAEoAUgBQAFAAKQBcAFwAcgBpAGcAaAB0ACkALQBcAFwAbABlAGYAdABcAFwAbABlAGYAdAAoACgAUgBFAEMAXwB7AHMAdQByAHIAZQBuAGQAZQByAGUAZAB9AC0AUgBFAEMAXwB7AG8AbgBzAGkAdABlAH0AXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAcgBpAGcAaAB0AF0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUgBNAEYAMwAsAGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7ADMALABlAGwAZQBjAH0APQAgAFsAIABRAF8AewBlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAAoADEALQAoAFIAUABQACsASgBSAFAAUAApAFwAXAByAGkAZwBoAHQAKQAtAFwAXABsAGUAZgB0AFwAXABsAGUAZgB0ACgAKABSAEUAQwBfAHsAcwB1AHIAcgBlAG4AZABlAHIAZQBkAH0ALQBSAEUAQwBfAHsAbwBuAHMAaQB0AGUAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsAMwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAcgBpAGcAaAB0AF0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUgBNAEYAMwAsAGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZQBsAGUAYwBcACIALAAgAFwAIgBhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZABcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAUABQAFwAIgAsACAAXAAiAHIAZQBuAGUAdwBhAGIAbABlACAAcABvAHcAZQByACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAHUAbgBkAGUAcgAgAEwAUgBFAFQAIABmAG8AcgAgAHQAaABlACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHAAZQByAGkAbwBkAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAUgBQAFAAXAAiACwAIABcACIAagB1AHIAaQBzAGQAaQBjAHQAaQBvAG4AYQBsACAAcgBlAG4AZQB3AGEAYgBsAGUAIABwAG8AdwBlAHIAIABwAGUAcgBjAGUAbgB0AGEAZwBlACAAZgBvAHIAIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIABwAGUAcgBpAG8AZABcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZABcACIALAAgAFwAIgBlAGwAaQBnAGkAYgBsAGUAIAByAGUAbgBlAHcAYQBiAGwAZQAgAGUAbgBlAHIAZwB5ACAAYwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIAB2AG8AbAB1AG4AdABhAHIAaQBsAHkAIABzAHUAcgByAGUAbgBkAGUAcgBlAGQAXAAiACwAIABcACIATQBXAGgAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAEUAQwBfAG8AbgBzAGkAdABlAFwAIgAsACAAXAAiAGUAbABpAGcAaQBiAGwAZQAgAHIAZQBuAGUAdwBhAGIAbABlACAAZQBuAGUAcgBnAHkAIABjAGUAcgB0AGkAZgBpAGMAYQB0AGUAcwAgAGkAcwBzAHUAZQBkACAAZgBvAHIAIABvAG4AcwBpAHQAZQAgAGcAZQBuAGUAcgBhAHQAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgAsACAAXAAiAE0AVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AUgBNAEYAMwBlAGwAZQBjAFwAIgAsACAAXAAiAHMAYwBvAHAAZQAgADMAIAByAGUAcwBpAGQAdQBhAGwAIABtAGkAeAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAGsAVwBoAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBzAHQAYQB0AGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABJAG4AIABvAHIAZABlAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAbQBlAGcAYQB3AGEAdAB0ACAAaABvAHUAcgBzACAAdABvACAAawBpAGwAbwB3AGEAdAB0ACAAaABvAHUAcgBzACwAIAB0AGgAZQAgAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAAYQBuAGQAIABSAEUAQwBfAG8AbgBzAGkAdABlACAAdgBhAHIAaQBhAGIAbABlAHMAIABhAHIAZQAgAG0AdQBsAHQAaQBwAGwAaQBlAGQAIABiAHkAIAAxADAAXgAzACAAaQBuAHMAdABlAGEAZAAgAG8AZgAgADEAMABeAC0AMwAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABzAGUAbgB0ACAAbwBmAGYAIABzAGkAdABlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGkAbgAgAGEAbgBvAHQAaABlAHIAIABmAGEAcgBtAGkAbgBnACAAcwB5AHMAdABlAG0AIABvAHIAIABlAG4AdABlAHIAcAByAGkAcwBlAFwAbgBFAFwAbgB0ACAATgAyAE8AXABuAEUAPQBFAF8AewBOADIATwB9ACsARQBfAHsAYQBkAH0AKwBFAF8AewBsAGUAYQBjAGgAfQBcAG4ARQBfAE4AMgBPACAAPQAgAGQAaQByAGUAYwB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAcwBvAGkAbABzACAAbwB1AHQAcwBpAGQAZQAgAG8AZgAgAHMAYwBvAHAAZQAgADEAIABiAG8AdQBuAGQAYQByAHkAXABuAEUAXwBhAGQAIAA9ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAHQAbwAgAHMAbwBpAGwAcwBcAG4ARQBfAGwAZQBhAGMAaAAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAcwBvAGkAbABzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAGEAbgB1AHIAZQBTAGUAbgB0AE8AZgBmAFMAaQB0AGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAE4AMgBPACwAIABFAF8AYQBkACwAIABFAF8AbABlAGEAYwBoACwAXABuACAAIAAgACAARQBfAE4AMgBPACAAKwAgAEUAXwBhAGQAIAArACAARQBfAGwAZQBhAGMAaABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAGEAbgB1AHIAZQBTAGUAbgB0AE8AZgBmAFMAaQB0AGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAcwBlAG4AdAAgAG8AZgBmACAAcwBpAHQAZQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABpAG4AIABhAG4AbwB0AGgAZQByACAAZgBhAHIAbQBpAG4AZwAgAHMAeQBzAHQAZQBtACAAbwByACAAZQBuAHQAZQByAHAAcgBpAHMAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgAxADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAGEAbgB1AHIAZQBTAGUAbgB0AE8AZgBmAFMAaQB0AGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAGEAbgB1AHIAZQBTAGUAbgB0AE8AZgBmAFMAaQB0AGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAD0ARQBfAHsATgAyAE8AfQArAEUAXwB7AGEAZAB9ACsARQBfAHsAbABlAGEAYwBoAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAGEAbgB1AHIAZQBTAGUAbgB0AE8AZgBmAFMAaQB0AGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBfAE4AMgBPAFwAIgAsACAAXAAiAGQAaQByAGUAYwB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAcwBvAGkAbABzACAAbwB1AHQAcwBpAGQAZQAgAG8AZgAgAHMAYwBvAHAAZQAgADEAIABiAG8AdQBuAGQAYQByAHkAXAAiACwAIABcACIAdAAgAE4AMgBPAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAXwBhAGQAXAAiACwAIABcACIAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAHQAbwAgAHMAbwBpAGwAcwBcACIALAAgAFwAIgB0ACAATgAyAE8AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBfAGwAZQBhAGMAaABcACIALAAgAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAcwBvAGkAbABzAFwAIgAsACAAXAAiAHQAIABOADIATwBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMwBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGwAaQBkAFcAYQBzAHQAZQBUAHIAZQBhAHQAbQBlAG4AdABGAGEAYwBpAGwAaQB0AHkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADMAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBsAGkAZABXAGEAcwB0AGUAVAByAGUAYQB0AG0AZQBuAHQARgBhAGMAaQBsAGkAdAB5AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARQBfAGEAZAAsACAARQBfAGwAZQBhAGMAaAAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACsAIABFAF8AYQBkACAAKwAgAEUAXwBsAGUAYQBjAGgAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMwBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGwAaQBkAFcAYQBzAHQAZQBUAHIAZQBhAHQAbQBlAG4AdABGAGEAYwBpAGwAaQB0AHkAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAbwBsAGkAZAAgAHcAYQBzAHQAZQAgAHMAZQBuAHQAIAB0AG8AIABhACAAdAByAGUAYQB0AG0AZQBuAHQAIABmAGEAYwBpAGwAaQB0AHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMwBfADEAXwAzAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AbABpAGQAVwBhAHMAdABlAFQAcgBlAGEAdABtAGUAbgB0AEYAYQBjAGkAbABpAHQAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADMAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBsAGkAZABXAGEAcwB0AGUAVAByAGUAYQB0AG0AZQBuAHQARgBhAGMAaQBsAGkAdAB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMwBfADEAXwAzAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AbABpAGQAVwBhAHMAdABlAFQAcgBlAGEAdABtAGUAbgB0AEYAYQBjAGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgAxADMALgAxAC4AMwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADMAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBsAGkAZABXAGEAcwB0AGUAVAByAGUAYQB0AG0AZQBuAHQARgBhAGMAaQBsAGkAdAB5AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMwBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGwAaQBkAFcAYQBzAHQAZQBUAHIAZQBhAHQAbQBlAG4AdABGAGEAYwBpAGwAaQB0AHkAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADMAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBsAGkAZABXAGEAcwB0AGUAVAByAGUAYQB0AG0AZQBuAHQARgBhAGMAaQBsAGkAdAB5AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXABuAEUAbQBiAGUAZABkAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHUAcABzAHQAcgBlAGEAbQAgAGYAcgBlAGkAZwBoAHQAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBmAFwAXABsAGUAZgB0ACgAKABXAF8AZgBcAFwAdABpAG0AZQBzACAARABfAGYAKQBcAFwAdABpAG0AZQBzACAARQBGAF8AZgBcAFwAcgBpAGcAaAB0ACkAXABuAFcAXwBmACAAPQAgAHQAbwB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAG8AbwBkAHMAIAB0AHIAYQBuAHMAcABvAHIAdABlAGQAIABwAGUAcgAgAGYAcgBlAGkAZwBoAHQAIAB0AHkAcABlACAAZgBcAG4ARABfAGYAIAA9ACAAdABvAHQAYQBsACAAZABpAHMAdABhAG4AYwBlACAAdAByAGEAbgBzAHAAbwByAHQAZQBkACAAcABlAHIAIABmAHIAZQBpAGcAaAB0ACAAdAB5AHAAZQAgAGYAXABuAEUARgBfAGYAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAcgBlAGkAZwBoAHQAIAB0AHkAcABlACAAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFcAXwBmACwAIABEAF8AZgAsACAARQBGAF8AZgAsAFwAbgAgACAAIAAgACgAVwBfAGYAIAAqACAARABfAGYAKQAgACoAIABFAEYAXwBmAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQA0AF8AMQBfADEAXwBfADEAXwBFAG0AYgBlAGQAZABlAGQARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBVAHAAcwB0AHIAZQBhAG0ARgByAGUAaQBnAGgAdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGIAZQBkAGQAZQBkACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdQBwAHMAdAByAGUAYQBtACAAZgByAGUAaQBnAGgAdABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQA0AF8AMQBfADEAXwBfADEAXwBFAG0AYgBlAGQAZABlAGQARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBVAHAAcwB0AHIAZQBhAG0ARgByAGUAaQBnAGgAdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQA0AF8AMQBfADEAXwBfADEAXwBFAG0AYgBlAGQAZABlAGQARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBVAHAAcwB0AHIAZQBhAG0ARgByAGUAaQBnAGgAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADEANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQA0AF8AMQBfADEAXwBfADEAXwBFAG0AYgBlAGQAZABlAGQARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBVAHAAcwB0AHIAZQBhAG0ARgByAGUAaQBnAGgAdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQA0AF8AMQBfADEAXwBfADEAXwBFAG0AYgBlAGQAZABlAGQARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBVAHAAcwB0AHIAZQBhAG0ARgByAGUAaQBnAGgAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGYAXABcAGwAZQBmAHQAKAAoAFcAXwBmAFwAXAB0AGkAbQBlAHMAIABEAF8AZgApAFwAXAB0AGkAbQBlAHMAIABFAEYAXwBmAFwAXAByAGkAZwBoAHQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQA0AF8AMQBfADEAXwBfADEAXwBFAG0AYgBlAGQAZABlAGQARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBVAHAAcwB0AHIAZQBhAG0ARgByAGUAaQBnAGgAdABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAF8AZgBcACIALAAgAFwAIgB0AG8AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBvAG8AZABzACAAdAByAGEAbgBzAHAAbwByAHQAZQBkACAAcABlAHIAIABmAHIAZQBpAGcAaAB0ACAAdAB5AHAAZQAgAGYAXAAiACwAIABcACIAdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAXwBmAFwAIgAsACAAXAAiAHQAbwB0AGEAbAAgAGQAaQBzAHQAYQBuAGMAZQAgAHQAcgBhAG4AcwBwAG8AcgB0AGUAZAAgAHAAZQByACAAZgByAGUAaQBnAGgAdAAgAHQAeQBwAGUAIABmAFwAIgAsACAAXAAiAGsAbQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGYAXAAiACwAIABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAcgBlAGkAZwBoAHQAIAB0AHkAcABlACAAZgBcACIALAAgAFwAIgB0ACAAQwBPADIAZQAvACgAdAAgAGsAbQApAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBcACIALAAgAFwAIgBmAHIAZQBpAGcAaAB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAHUAZQBsAF8ARwBlAHQAVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABTAHQAcgBpAG4AZwAiACwAIgBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgB1AGUAbABfAEcAZQB0AFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABTAHQAcgBpAG4AZwAiACwAIgBGAHUAZQBsAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgB1AGUAbABfAFQAbwB0AGEAbABDAG8AbgBzAHUAbQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVQBuAGkAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBVAG4AaQB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAHYAZQBzAHQAbwBjAGsAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAHYAZQBzAHQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAHYAZQBzAHQAbwBjAGsAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAHYAZQBzAHQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAHYAZQBzAHQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAHYAZQBzAHQAbwBjAGsAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAZQBkACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAZQBkAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATQBpAG4AZQByAGEAbABTAHUAcABwAGwAZQBtAGUAbgB0AHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwBYAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwBYAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwBYAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwBYAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADUAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAQQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADUAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAQQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADUAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAQQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADYAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAG0AZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA2AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQBtAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADYAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAG0AZQBfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADYAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAG0AZQBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA2AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQBtAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADcAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUwBlAHIAdgBpAGMAZQBzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABTAGUAcgB2AGkAYwBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADcAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUwBlAHIAdgBpAGMAZQBzAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABTAGUAcgB2AGkAYwBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABTAGUAcgB2AGkAYwBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABTAGUAcgB2AGkAYwBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA4AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFAAYQBjAGsAYQBnAGkAbgBnACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA4AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFAAYQBjAGsAYQBnAGkAbgBnAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA4AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFAAYQBjAGsAYQBnAGkAbgBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA4AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFAAYQBjAGsAYQBnAGkAbgBnAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA4AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFAAYQBjAGsAYQBnAGkAbgBnAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA4AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFAAYQBjAGsAYQBnAGkAbgBnAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AOQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABHAHIAbwB3AE0AZQBkAGkAYQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AOQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABHAHIAbwB3AE0AZQBkAGkAYQBfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AOQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABHAHIAbwB3AE0AZQBkAGkAYQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AOQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABHAHIAbwB3AE0AZQBkAGkAYQBfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADkAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARwByAG8AdwBNAGUAZABpAGEAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AOQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABHAHIAbwB3AE0AZQBkAGkAYQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AOQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABHAHIAbwB3AE0AZQBkAGkAYQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAwAF8AMQBfADEAXwBfADEAXwBPAHQAaABlAHIAUAB1AHIAYwBoAGEAcwBlAGQARwBvAG8AZABzAEEAbgBkAFMAZQByAHYAaQBjAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAFUAcABzAHQAcgBlAGEAbQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAdQBlAGwAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAFUAcABzAHQAcgBlAGEAbQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAdQBlAGwAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAFUAcABzAHQAcgBlAGEAbQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAdQBlAGwAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAFUAcABzAHQAcgBlAGEAbQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAdQBlAGwAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABVAHAAcwB0AHIAZQBhAG0ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAHUAZQBsAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAFUAcABzAHQAcgBlAGEAbQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAdQBlAGwAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAFUAcABzAHQAcgBlAGEAbQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAdQBlAGwAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADIAXwBVAHAAcwB0AHIAZQBhAG0AVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADIAXwBVAHAAcwB0AHIAZQBhAG0AVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADIAXwBVAHAAcwB0AHIAZQBhAG0AVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADIAXwBVAHAAcwB0AHIAZQBhAG0AVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAyAF8AVQBwAHMAdAByAGUAYQBtAFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADIAXwBVAHAAcwB0AHIAZQBhAG0AVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADIAXwBVAHAAcwB0AHIAZQBhAG0AVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMwBfAFUAcABzAHQAcgBlAGEAbQBTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMwBfAFUAcABzAHQAcgBlAGEAbQBTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMwBfAFUAcABzAHQAcgBlAGEAbQBTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMwBfAFUAcABzAHQAcgBlAGEAbQBTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADEAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMQBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADEAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMQBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMQBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMQBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAyAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBNAGEAcgBrAGUAdABCAGEAcwBlAGQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAyAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAyAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAyAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAyAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAyAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAGEAbgB1AHIAZQBTAGUAbgB0AE8AZgBmAFMAaQB0AGUAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQA0AF8AMQBfADEAXwBfADEAXwBFAG0AYgBlAGQAZABlAGQARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBVAHAAcwB0AHIAZQBhAG0ARgByAGUAaQBnAGgAdABfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -24168,18 +24188,11 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzACAAaQBuAGMAbAB1AGQAaQBuAGcAIABsAGkAcQB1AGUAZgBpAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgACAAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA1AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAAYwBvAG0AYgB1AHMAdABlAGQAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABDAG8AbgB0AGUAbgB0ACAARgBhAGMAdABvAHIAIAAoAEcASgAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwAKQBcACIALAAgAFwAIgBGAHUAZQBsACAAdQBuAGkAdABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAE8AMgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAEgANABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABOADIATwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAG8AbQBiAGkAbgBlAGQAIABnAGEAcwBlAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADAALgAyACwAIAAwAC4AMAAzACwAIAA1ADEALgA2ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AYQBsACAAbQBpAG4AZQAgAHcAYQBzAHQAZQAgAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4AOQAsACAANAAuADYALAAgADAALgAzACwAIAA1ADYALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAG0AcAByAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAoAHIAZQB2AGUAcgB0AGkAbgBnACAAdABvACAAcwB0AGEAbgBkAGEAcgBkACAAYwBvAG4AZABpAHQAaQBvAG4AcwApAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVQBuAHAAcgBvAGMAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAA2ADIAOQAsACAAXAAiAG0AMwBcACIALAAgADUANgAuADUALAAgADAALgAwADMALAAgADAALgAwADMALAAgADUANgAuADUANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBrAGUAIABvAHYAZQBuACAAZwBhAHMAXAAiACwAIAAwAC4AMAAxADgAMQAsACAAXAAiAG0AMwBcACIALAAgADMANwAuADAALAAgADAALgAwADMALAAgADAALgAwADUALAAgADMANwAuADAAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAbABhAHMAdAAgAGYAdQByAG4AYQBjAGUAIABnAGEAcwBcACIALAAgADAALgAwADAANAAwACwAIABcACIAbQAzAFwAIgAsACAAMgAzADQALgAwACwAIAAwAC4AMAAzACwAIAAwAC4AMAAyACwAIAAyADMANAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwBcACIALAAgADAALgAwADMAOQAwACwAIABcACIAbQAzAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADAANAAsACAAMAAuADAAMwAsACAANgAwAC4AMgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBMAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAGUAbwB1AHMAIABmAG8AcwBzAGkAbAAgAGYAdQBlAGwAcwAgAG8AdABoAGUAcgAgAHQAaABhAG4AIAB0AGgAbwBzAGUAIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMAAuADAAMwA5ADAALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABhAG4AZABmAGkAbABsACAAYgBpAG8AZwBhAHMAIAB0AGgAYQB0ACAAaQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAKABtAGUAdABoAGEAbgBlACAAbwBuAGwAeQApAFwAIgAsACAAMAAuADAAMwA3ADcALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAANgAuADQALAAgADAALgAwADMALAAgADYALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQBlAHQAaABhAG4AZQAgAG8AbgBsAHkAKQBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADYALgA0ACwAIAAwAC4AMAAzACwAIAA2AC4ANAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAsACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHQAaABvAHMAZQAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAwAC4AMAAzADcAMAAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAA2AC4ANAAsACAAMAAuADAAMwAsACAANgAuADQAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAG0AZQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAAMAAuADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAeQBkAHIAbwBnAGUAbgBcACIALAAgADAALgAwADEAMgAyACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADAALgAwACwAIAAwAC4ANQAsACAAMAAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAAiACwAIAAxACwAIABcACIARwBKAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAMQAsACAAXAAiAEcASgBcACIALAAgADYAMAAuADIALAAgADAALgAwADQALAAgADAALgAwADMALAAgADYAMAAuADIANwBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAVABvAHcAbgAgAGcAYQBzACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAB1ADAAMAAyADcAIAB3AGUAcgBlACAAYQBkAGQAZQBkACwAIABlAGEAYwBoACAAdwBpAHQAaAAgAGEAbgAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAMQAgAEcASgAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwALgAgAFQAaABpAHMAIABpAHMAIABmAG8AcgAgAHUAcwBlAHIAcwAgAHcAaABvACAAaABhAHYAZQAgAGYAdQBlAGwAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABkAGEAdABhACAAaQBuACAARwBKACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAbQAzAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBJAG4AZABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAC4AXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA2AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAdABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAE4AYQB0AHUAcgBhAGwAIABHAGEAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE0AZQB0AHIAbwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgAGYAbwByACAATgBhAHQAdQByAGEAbAAgAEcAYQBzACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgBvAG4AIAAtACAATQBlAHQAcgBvAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAMQAzAC4AMQAsACAAMQA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAMQAzAC4AMQAsACAAMQA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgADQALgAwACwAIAA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIAA4AC4AOAAsACAANwAuADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgADEAMAAuADcALAAgADEAMAAuADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIAA0AC4AMQAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIAA0AC4AMAAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgADQALgAxACwAIAA0AC4AMABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAE4AUwBXACAAYQBuAGQAIABBAEMAVAAgAHMAcABsAGkAdAAgAGkAbgB0AG8AIABzAGUAcABhAHIAYQB0AGUAIAByAG8AdwBzAC4AIABcAHUAMAAwADIANwBDAFwAdQAwADAAMgA3ACAAVgBhAGwAdQBlAHMAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAGEAbgBkACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAByAGUAcABsAGEAYwBlAGQAIAB3AGkAdABoACAAdABoAG8AcwBlACAAZgBvAHIAIABWAGkAYwB0AG8AcgBpAGEAIABhAG4AZAAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAHIAZQBzAHAAZQBjAHQAaQB2AGUAbAB5AC4AIAAoAFMAZQBlACAAYQBwAHAAZQBuAGQAaQBjAGUAcwApAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMgAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEEAcwAgAFMAYwBvAHAAZQAgADMAIABmAGEAYwB0AG8AcgBzACAAYQByAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAYQB0ACAAdABoAGUAIABwAG8AaQBuAHQAIAB3AGgAZQByAGUAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABpAHMAIABkAGUAbABpAHYAZQByAGUAZAAgAHQAbwAgAGUAbgBkACAAdQBzAGUAcgBzACwAIABpAHQAIABpAHMAIABuAGUAYwBlAHMAcwBhAHIAeQAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAYQB0ACAAZQBhAGMAaAAgAG8AZgAgAHQAaABlACAAbABvAGEAZAAgAGMAZQBuAHQAcgBlAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBHAGEAcwAgAHIAZQBhAGMAaABlAHMAIABlAG4AZAAgAHUAcwBlAHIAcwAgAGUAaQB0AGgAZQByACAAZgByAG8AbQAgAHQAaABlACAAbQBlAHQAcgBvACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABuAGUAdAB3AG8AcgBrAHMAIABvAHIAIABkAGkAcgBlAGMAdAAgAGYAcgBvAG0AIAB0AGgAZQAgAGgAaQBnAGgAIAAtACAAcAByAGUAcwBzAHUAcgBlACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABwAGkAcABlAGwAaQBuAGUAcwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAEgAbwB1AHMAZQBoAG8AbABkAHMAIABhAG4AZAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB1AHMAZQByAHMAIAB0AGUAbgBkACAAdABvACAAYgBlACAAcwBlAHIAdgBlAGQAIABiAHkAIAB0AGgAZQAgAGYAbwByAG0AZQByACwAIABhAG4AZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAGcAZQBuAGUAcgBhAHQAbwByAHMAIABhAG4AZAAgAGwAYQByAGcAZQAgAGkAbgBkAHUAcwB0AHIAaQBhAGwAIABwAGwAYQBuAHQAcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGwAYQB0AHQAZQByAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBNAGUAdAByAG8AIABpAHMAIABkAGUAZgBpAG4AZQBkACAAYQBzACAAbABvAGMAYQB0AGUAZAAgAG8AbgAgAG8AcgAgAGUAYQBzAHQAIABvAGYAIAB0AGgAZQAgAGQAaQB2AGkAZABpAG4AZwAgAHIAYQBuAGcAZQAgAGkAbgAgAE4AUwBXACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAEMAYQBuAGIAZQByAHIAYQAgAGEAbgBkACAAUQB1AGUAYQBuAGIAZQB5AGEAbgAsACAATQBlAGwAYgBvAHUAcgBuAGUALAAgAEIAcgBpAHMAYgBhAG4AZQAsACAAQQBkAGUAbABhAGkAZABlACAAbwByACAAUABlAHIAdABoAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIATwB0AGgAZQByAHcAaQBzAGUALAAgAHQAaABlACAAbgBvAG4AIAAtACAAbQBlAHQAcgBvACAAZgBhAGMAdABvAHIAIABzAGgAbwB1AGwAZAAgAGIAZQAgAHUAcwBlAGQALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEYAYQBjAHQAbwByAHMAIABhAHIAZQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAG8AcgAgAGEAbABsACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAHcAaABpAGMAaAAgAG0AYQB5ACAAaQBuAGMAbAB1AGQAZQAgAGMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIABcACIAVABhAGIAbABlACAANgAgAGkAcwAgAG4AbwB0ACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHQAbwAgAGUAdABoAGEAbgBlAC4AIABTAGUAZQAgAFQAYQBiAGwAZQAgADcAIABJAG4AZABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZQB0AGgAYQBuAGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEMAIAA9ACAAQwBvAG4AZgBpAGQAZQBuAHQAaQBhAGwALgAgAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIABhAG4AZAAgAHQAaABlACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIABhAHIAZQAgAG4AbwB0ACAAYQB2AGEAaQBsAGEAYgBsAGUAIABkAHUAZQAgAHQAbwAgAGMAbwBuAGYAaQBkAGUAbgB0AGkAYQBsAGkAdAB5ACAAYwBvAG4AcwB0AHIAYQBpAG4AdABzACAAdABoAGEAdAAgAGEAcgBpAHMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAGEAIABsAGkAbQBpAHQAZQBkACAAbgB1AG0AYgBlAHIAIABvAGYAIABOAEcARQBSACAAZABhAHQAYQAgAGkAbgBwAHUAdABzAC4AIABJAHQAIABpAHMAIABzAHUAZwBnAGUAcwB0AGUAZAAgAHQAaABhAHQAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAHQAaABlACAAdQBzAGUAIABvAGYAIAB0AGgAZQAgAFYAaQBjAHQAbwByAGkAYQBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGkAcwAgAGEAcABwAHIAbwBwAHIAaQBhAHQAZQAsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAHcAaABpAGwAZQAgAGYAbwByACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAdABoAGUAIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABpAHMAIABhAHAAcAByAG8AcAByAGkAYQB0AGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZABvACAAbgBvAHQAIABpAG4AYwBsAHUAZABlACAAZgB1AGcAaQB0AGkAdgBlACAAZQBtAGkAcwBzAGkAbwBuACAAbABlAGEAawBhAGcAZQAgAGYAcgBvAG0AIABsAG8AdwAgAHAAcgBlAHMAcwB1AHIAZQAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAcABpAHAAZQBsAGkAbgBlACAAbgBlAHQAdwBvAHIAawBzACAAdwBoAGkAbABlACAAdABoAG8AcwBlACAAZgByAG8AbQAgAGgAaQBnAGgAIABwAHIAZQBzAHMAdQByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAZwBhAHMAIABuAGUAdAB3AG8AcgBrAHMAIABhAHIAZQAgAGMAbwBuAHMAaQBkAGUAcgBlAGQAIABuAGUAZwBsAGkAZwBpAGIAbABlAC4AXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMALAAgAGkAbgBjAGwAdQBkAGkAbgBnACAAYwBlAHIAdABhAGkAbgAgAHAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMALgBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA4AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADUALAAgADgALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACAAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsAHMAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABwAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsACAAdQBzAGUAZAAgAGEAcwAgAGYAdQBlAGwAKQAsACAAZQAuAGcALgAgAGwAdQBiAHIAaQBjAGEAbgB0AHMAXAAiACwAIAAzADgALgA4ACwAIABcACIAawBsAFwAIgAsACAAMQAzAC4AOQAsACAAMAAuADAALAAgADAALgAwACwAIAAxADMALgA5ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABnAHIAZQBhAHMAZQBzAFwAIgAsACAAMwA4AC4AOAAsACAAXAAiAGsAbABcACIALAAgADMALgA1ACwAIAAwAC4AMAAsACAAMAAuADAALAAgADMALgA1ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAHUAZABlACAAbwBpAGwAIABpAG4AYwBsAHUAZABpAG4AZwAgAGMAcgB1AGQAZQAgAG8AaQBsACAAYwBvAG4AZABlAG4AcwBhAHQAZQBzAFwAIgAsACAANAA1AC4AMwAsACAAXAAiAHQAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAANgA5AC4AOAA4ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGwAaQBxAHUAaQBkAHMAXAAiACwAIAA0ADYALgA1ACwAIABcACIAdABcACIALAAgADYAMQAuADAALAAgADAALgAwADgALAAgADAALgAyACwAIAA2ADEALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB1AHQAbwBtAG8AdABpAHYAZQAgAGcAYQBzAG8AbABpAG4AZQAgAC8AIABwAGUAdAByAG8AbAAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADQALgAyACwAIABcACIAawBMAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADIALAAgADAALgAyACwAIAA2ADcALgA4ADAALAAgADEANwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AIABnAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADMALgAxACwAIABcACIAawBMAFwAIgAsACAANgA3ACwAIAAwAC4AMgAsACAAMAAuADIALAAgADYANwAuADQAMAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADcALgA1ACwAIABcACIAawBMAFwAIgAsACAANgA4AC4AOQAsACAAMAAuADAAMQAsACAAMAAuADIALAAgADYAOQAuADEAMQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgAgAHQAdQByAGIAaQBuAGUAIABmAHUAZQBsACAALwAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAAyACwAIAAwAC4AMgAsACAANgA5AC4AOAAyACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdABpAG4AZwAgAG8AaQBsAFwAIgAsACAAMwA3AC4AMwAsACAAXAAiAGsATABcACIALAAgADYAOQAuADUALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA3ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsATABcACIALAAgADYAOQAuADkALAAgADAALgAxACwAIAAwAC4AMgAsACAANwAwAC4AMgAwACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAG8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsATABcACIALAAgADcAMwAuADYALAAgADAALgAwADQALAAgADAALgAyACwAIAA3ADMALgA4ADQALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAGEAcgBvAG0AYQB0AGkAYwAgAGgAeQBkAHIAbwBjAGEAcgBiAG8AbgBzAFwAIgAsACAAMwA0AC4ANAAsACAAXAAiAGsATABcACIALAAgADYAOQAuADcALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA5ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AbAB2AGUAbgB0AHMAOgAgAG0AaQBuAGUAcgBhAGwAIAB0AHUAcgBwAGUAbgB0AGkAbgBlACAAbwByACAAdwBoAGkAdABlACAAcwBwAGkAcgBpAHQAcwBcACIALAAgADMANAAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA3ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4AOQAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABwAGUAdAByAG8AbABlAHUAbQAgAGcAYQBzACAAKABMAFAARwApAFwAIgAsACAAMgA1AC4ANwAsACAAXAAiAGsATABcACIALAAgADYAMAAuADIALAAgADAALgAyACwAIAAwAC4AMgAsACAANgAwAC4ANgAwACwAIAAyADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHAAaAB0AGgAYQBcACIALAAgADMAMQAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAA2ADkALgA4ADIALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGMAbwBrAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAdABcACIALAAgADkAMgAuADYALAAgADAALgAwADgALAAgADAALgAyACwAIAA5ADIALgA4ADgALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAZgBpAG4AZQByAHkAIABnAGEAcwAgAGEAbgBkACAAbABpAHEAdQBpAGQAcwBcACIALAAgADQAMgAuADkALAAgAFwAIgB0AFwAIgAsACAANQA0AC4ANwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAANQA0AC4ANwA2ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAaQBuAGUAcgB5ACAAYwBvAGsAZQBcACIALAAgADMANAAuADIALAAgAFwAIgB0AFwAIgAsACAAOQAyAC4ANgAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADkAMgAuADgAOAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAbwB0AGgAZQByACAAdABoAGEAbgAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAzADQALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOAAsACAAMAAuADAAMgAsACAAMAAuADEALAAgADYAOQAuADkAMgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA0AC4ANgAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBFAHQAaABhAG4AbwBsACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGEAIABmAHUAZQBsACAAaQBuACAAYQBuACAAaQBuAHQAZQByAG4AYQBsACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAGUAbgBnAGkAbgBlAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBmAHUAZQBsAHMAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAdABoAG8AcwBlACAAbQBlAG4AdABpAG8AbgBlAGQAIABpAG4AIAB0AGgAZQAgAGkAdABlAG0AcwAgAGEAYgBvAHYAZQAgAGEAbgBkACAAYgBlAGwAbwB3AFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGEAdgBpAGEAdABpAG8AbgAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADAALgAyADIALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMwAwACwAIABcACIATgBFAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAXAB1ADAAMAAyADcATgBFAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIABhAHMAIAB6AGUAcgBvACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AcwAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABUAHIAYQBuAHMAcABvAHIAdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAxACkAIABhAG4AZAAgAGkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAcwAgAGkAbgAgAGQAaQBmAGYAZQByAGUAbgB0ACAAdAByAGEAbgBzAHAAbwByAHQAIABlAHEAdQBpAHAAbQBlAG4AdABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAOQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIANgAsACAAMQAwACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBhAG4AcwBwAG8AcgB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBGAHUAZQBsACAAYwBvAG0AYgB1AHMAdABlAGQAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABDAG8AbgB0AGUAbgB0ACAARgBhAGMAdABvAHIAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIALAAgAFwAIgBTAG8AdQByAGMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEcAYQBzAG8AbABpAG4AZQBcACIALAAgADMANAAuADIALAAgAFwAIgBrAGwAXAAiACwAIAA2ADcALgA0ACwAIAAwAC4AMAAyACwAIAAwAC4AMgAsACAANgA3AC4ANgAyACwAIAAxADcALgAyACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADkALAAgADAALgAwADEALAAgADAALgA1ACwAIAA3ADAALgA0ADEALAAgADEANwAuADMALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAcABlAHQAcgBvAGwAZQB1AG0AIABnAGEAcwAgACgATABQAEcAKQBcACIALAAgADIANgAuADIALAAgAFwAIgBrAGwAXAAiACwAIAA2ADAALgAyACwAIAAwAC4ANQAsACAAMAAuADMALAAgADYAMQAuADAAMAAsACAAMgAwAC4AMgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARgB1AGUAbAAgAG8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsAbABcACIALAAgADcAMwAuADYALAAgADAALgAwADgALAAgADAALgA1ACwAIAA3ADQALgAxADgALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEUAdABoAGEAbgBvAGwAXAAiACwAIAAyADMALgA0ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAyACwAIAAwAC4AMgAsACAAMAAuADQALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBCAGkAbwBkAGkAZQBzAGUAbABcACIALAAgADMANAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADgALAAgADEALgA3ACwAIAAyAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADEALAAgADAALgA1ACwAIAAwAC4ANQAxACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATwB0AGgAZQByACAAYgBpAG8AZgB1AGUAbABzAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AOAAsACAAMQAuADcALAAgADIALgA1ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQwBvAG0AcAByAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAANwAuADMALAAgADAALgAzACwAIAA1ADkALgAwACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAGcAaAB0ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADIANQAuADMALAAgAFwAIgBrAGwAXAAiACwAIAA1ADEALgA0ACwAIAA3AC4AMwAsACAAMAAuADMALAAgADUAOQAuADAALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADIALgA4ACwAIAAwAC4AMwAsACAANQA0AC4ANQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBsAFwAIgAsACAANQAxAC4ANAAsACAAMgAuADgALAAgADAALgAzACwAIAA1ADQALgA1ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAHYAIABvAHIAIABoAGkAZwBoAGUAcgBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMAA3ACwAIAAwAC4ANAAsACAANwAwAC4AMwA3ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAGkAaQBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMQAsACAAMAAuADQALAAgADcAMAAuADQALAAgADEANwAuADMALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAIAAtACAARQB1AHIAbwAgAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA0ACwAIAA3ADAALgA1ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAHYAIABvAHIAIABoAGkAZwBoAGUAcgBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAANwAsACAAMAAuADQALAAgADAALgA0ADcALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAGkAaQBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgA0ACwAIAAwAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAIAATICAARQB1AHIAbwAgAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAyACwAIAAwAC4ANAAsACAAMAAuADYALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEcAYQBzAG8AbABpAG4AZQAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0AFwAIgAsACAAMwAzAC4AMQAsACAAXAAiAGsAbABcACIALAAgADYANwAuADAALAAgADAALgAwADYALAAgADAALgA2ACwAIAA2ADcALgA2ADYALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AXAAiACwAIABcACIASwBlAHIAbwBzAGUAbgBlACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGYAdQBlAGwAIABpAG4AIABhAG4AIABhAGkAcgBjAHIAYQBmAHQAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAMQAsACAAMAAuADYALAAgADcAMAAuADIAMQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGEAdgBpAGEAdABpAG8AbgAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAMQAsACAAMAAuADYALAAgADAALgA2ADEALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAcwBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAawBMAFwAIgAsACAANgA3AC4ANAAsACAAMQAwAC4AMQAsACAAMAAuADMALAAgAFwAIgBcACIALAAgADEANwAuADIALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMgAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEANwAuADMALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARgB1AGUAbAAgAE8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsATABcACIALAAgADcAMwAuADYALAAgADAALgAyACwAIAAwAC4ANQAsACAAXAAiAFwAIgAsACAAMQA4AC4AMAAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBmAGYALQByAG8AYQBkACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACAAYQBuAGQAIABmAG8AcgBlAHMAdAByAHkAIABlAHEAdQBpAHAAbQBlAG4AdABcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsATABcACIALAAgADYAOQAuADkALAAgADAALgAzACwAIAAwAC4ANQAsACAAXAAiAFwAIgAsACAAMQA3AC4AMwAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAXAB1ADAAMAAyADcATgBFAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIABhAHMAIAB6AGUAcgBvACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AcwAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAATwBmAGYALQByAGEAZAAgAGUAcQB1AGkAcABtAGUAbgB0ACAAYQBuAGQAIAB2AGUAcwBzAGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABPAGYAZgAtAHIAbwBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAxACkAIABhAG4AZAAgAGkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAIABpAG4AIABvAGYAZgAtAHIAbwBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlACAAcQBcACIALAAgAFwAIgBFAEMAVAByAGEAbgBzACwAcQAgACgARwBKAC8AawBMACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEMATwAyACAARQBGAFQAcgBhAG4ALAAxACwAdABxAGcAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABDAEgANAAgAEUARgBUAHIAYQBuACwAMQAsAHQAZwBnACAAKABrAGcAIABDAE8AMgAtAGUALwBHAEoAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAATgAyAE8AIABFAEYAVAByAGEAbgAsADEALAB0AGcAZwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUARgBUAHIAYQBuAHMALAAzACwAcQAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAXAAiACwAIABcACIAUABlAHQAcgBvAGwAXAAiACwAIAAzADQALgAyACwAIAA2ADcALgA0ACwAIAAxADAALgAxACwAIAAwAC4AMwAsACAAMQA3AC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsAFwAIgAsACAAMwA4AC4ANgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA1ACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAXAAiACwAIABcACIARgB1AGUAbAAgAE8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAANwAzAC4ANgAsACAAMAAuADIALAAgADAALgA1ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBmAGYALQByAG8AYQBkACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACAAYQBuAGQAIABmAG8AcgBlAHMAdAByAHkAIABlAHEAdQBpAHAAbQBlAG4AdABcACIALAAgAFwAIgBEAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgADYAOQAuADkALAAgADAALgAzACwAIAAwAC4ANQAsACAAMQA3AC4AMwBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBGAHUAZQBsAF8ARwBlAHQAVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABTAHQAcgBpAG4AZwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALABcAG4AIAAgACAAIABMAEUARgBUACgAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsACAAXAAiACwAQwBlAGwAbAApACAALQAxACkAXABuACkAOwBcAG4AXABuAEYAdQBlAGwAXwBHAGUAdABTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwAUwB0AHIAaQBuAGcAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAXABuACAAIAAgACAAUgBJAEcASABUACgAQwBlAGwAbAAsAEwARQBOACgAQwBlAGwAbAApAC0ARgBJAE4ARAAoAFwAIgAsACAAXAAiACwAQwBlAGwAbAApACkAXABuACkAOwBcAG4AXABuAEYAdQBlAGwAXwBUAG8AdABhAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuAFwAbgA9ACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAHUAZQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBBAHIAcgBhAHkALAAgAEYAdQBlAGwAVQBzAGUAQQByAHIAYQB5ACwAIABGAHUAZQBsAFUAcwBlACwAIABGAHUAZQBsAFQAeQBwAGUAQQByAHIAYQB5ACwAIABGAHUAZQBsAFQAeQBwAGUALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAUwBVAE0AKABcAG4AIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAEYAdQBlAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAKABGAHUAZQBsAFQAeQBwAGUAQQByAHIAYQB5ACAAPQAgAEYAdQBlAGwAVAB5AHAAZQApACAAKgAgAFwAbgAgACAAIAAgACAAIAAgACAAKABGAHUAZQBsAFUAcwBlAEEAcgByAGEAeQAgAD0AIABGAHUAZQBsAFUAcwBlACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgADAAXABuACAAIAApAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AOAA6ACAARgB1AGUAbAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADgALgAxACAARgB1AGUAbAAgAFUAcwBlACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAAZgB1AGUAbABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRACwAIABFAEMALAAgAEUARgAsAFwAbgAgACAAIAAgACgAUQAgACoAIABFAEMAIAAqACAARQBGACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAbgBRACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAAawBMAFwAbgBFAEMAIAA6ACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAARwBKAC8AawBMAFwAbgBFAEYAIAA6ACAAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBUAHIAYQBuAHMAdABxACwAIABFAEMAXwBUAHIAYQBuAHMAcQAsACAARQBGAF8AVAByAGEAbgBzADEAdABxAGcALABcAG4AIAAgACAAIABWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACgAUQBfAFQAcgBhAG4AcwB0AHEALAAgAEUAQwBfAFQAcgBhAG4AcwBxACwAIABFAEYAXwBUAHIAYQBuAHMAMQB0AHEAZwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIAAyAC4AMwAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBnAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB0ACAAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBxAFwAXABsAGUAZgB0ACgAUQBfAHsAVAByAGEAbgBzACwAdABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAVAByAGEAbgBzACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFQAcgBhAG4AcwAsADEALAB0AHEAZwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAFQAcgBhAG4AcwB0AHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIABjAG8AbQBiAHUAcwB0AGUAZAAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcACIALAAgAFwAIgBWAGEAcgBpAGUAcwAgAGIAYQBzAGUAZAAgAG8AbgAgAGYAdQBlAGwAIAB0AHkAcABlADoAIABrAEwALAAgAG0AMwAsACAARwBKAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AVAByAGEAbgBzAHEAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXAAiACwAIABcACIARwBKACAALwAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AVAByAGEAbgBzADEAdABxAGcAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBhAG4AcwBcACIALAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBnAFwAIgAsACAAXAAiAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwBcAG4AUQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIAB0AHkAcABlACAAcQAgAHUAcwBlAGQAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgADoAIABrAEwAXABuAEUAQwAgADoAIABFAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzACAAOgAgAEcASgAvAGsATABcAG4ARQBGACAAOgAgAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAIAA6ACAAawBnACAAQwBPADIAZQAgAC8AIABHAEoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AUwBDAHEALAAgAEUAQwBfAFMAQwBxACwAIABFAEYAXwBTAEMAMQBxAGcALABcAG4AIAAgACAAIABWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACgAUQBfAFMAQwBxACwAIABFAEMAXwBTAEMAcQAsACAARQBGAF8AUwBDADEAcQBnACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA4AC4AMgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMgAuADIAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGUAbgBlAHIAZwB5ACAAcwBvAHUAcgBjAGUAcwAgAC0AIABDAGEAbABjAHUAbABhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AdAAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcQBcAFwAbABlAGYAdAAoAFEAXwB7AFMAQwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUwBDACwAMQAsAHEAZwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AUwBDAHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAFMAQwBxAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIARwBKACAALwAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AUwBDADEAcQBnAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAgAC8AIABHAEoAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBxAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBDAFwAIgAsACAAXAAiAFMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZwBcACIALAAgAFwAIgBHAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADUAOgAgAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANQBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAHYAZQBzAHQAbwBjAGsAXABuAFQAbwB0AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAbABpAHYAZQBzAHQAbwBjAGsAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AbwBcAFwAbABlAGYAdAAoAE4AXwB7AGMAbwB9AFwAXAB0AGkAbQBlAHMAIABXAF8AewBjAG8AfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBjAG8AfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAE4AXwBjAG8AIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABhAG4AaQBtAGEAbABzACAAcAB1AHIAYwBoAGEAcwBlAGQAIABpAG4AIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIABjACAAZgByAG8AbQAgAG8AcgBpAGcAaQBuACAAbwBcAG4AVwBfAGMAbwAgAD0AIABhAHYAZQByAGEAZwBlACAAbABpAHYAZQB3AGUAaQBnAGgAdAAgAG8AZgAgAHAAdQByAGMAaABhAHMAZQBkACAAbABpAHYAZQBzAHQAbwBjAGsAIABhAHQAIABwAG8AaQBuAHQAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAXABuAEUARgBfAGMAbwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAYQBuAGQAIABvAHIAaQBnAGkAbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBjAG8ALAAgAFcAXwBjAG8ALAAgAEUARgBfAGMAbwAsAFwAbgAgACAAIAAgACgATgBfAGMAbwAgACoAIABXAF8AYwBvACAAKgAgAEUARgBfAGMAbwApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQB2AGUAcwB0AG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGwAaQB2AGUAcwB0AG8AYwBrAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQB2AGUAcwB0AG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA1AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGMAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBvAFwAXABsAGUAZgB0ACgATgBfAHsAYwBvAH0AXABcAHQAaQBtAGUAcwAgAFcAXwB7AGMAbwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGMAbwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AYwBvAFwAIgAsACAAXAAiAG4AdQBtAGIAZQByACAAbwBmACAAYQBuAGkAbQBhAGwAcwAgAHAAdQByAGMAaABhAHMAZQBkACAAaQBuACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAYwAgAGYAcgBvAG0AIABvAHIAaQBnAGkAbgAgAG8AXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAXwBjAG8AXAAiACwAIABcACIAYQB2AGUAcgBhAGcAZQAgAGwAaQB2AGUAdwBlAGkAZwBoAHQAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAYQB0ACAAcABvAGkAbgB0ACAAbwBmACAAcAB1AHIAYwBoAGEAcwBlAFwAIgAsACAAXAAiAGsAZwAvAGgAZQBhAGQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBjAG8AXAAiACwAIABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGEAbgBkACAAbwByAGkAZwBpAG4AXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAGsAZwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAIABcACIAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbwBcACIALAAgAFwAIgBvAHIAaQBnAGkAbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAZQBkAFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGYAZQBlAGQAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBqAFwAXABsAGUAZgB0ACgAUQBfAGoAXABcAHQAaQBtAGUAcwAgAEUARgBfAGoAXABcAHIAaQBnAGgAdAApAFwAbgBRAF8AagAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABmAGUAZQBkACAAdAB5AHAAZQAgAGoAIABwAHUAcgBjAGgAYQBzAGUAZABcAG4ARQBGAF8AagAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAG8AZgAgAHAAdQByAGMAaABhAHMAZQBkACAAZgBlAGUAZABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGoALAAgAEUARgBfAGoALABcAG4AIAAgACAAIABRAF8AagAgACoAIABFAEYAXwBqAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGYAZQBlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgAyAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGoAXABcAGwAZQBmAHQAKABRAF8AagBcAFwAdABpAG0AZQBzACAARQBGAF8AagBcAFwAcgBpAGcAaAB0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AagBcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABmAGUAZQBkACAAdAB5AHAAZQAgAGoAIABwAHUAcgBjAGgAYQBzAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AagBcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAG8AZgAgAHAAdQByAGMAaABhAHMAZQBkACAAZgBlAGUAZABcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8AawBnAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALAAgAFwAIgBmAGUAZQBkACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBcAG4AVABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABtAGkAbgBlAHIAYQBsACAAcwB1AHAAcABsAGUAbQBlAG4AdABzAFwAbgBFAFwAbgB0ACAAQwBPADIAZQBcAG4ARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AbQBcAFwAbABlAGYAdAAoAFEAXwBtAFwAXAB0AGkAbQBlAHMAIABFAEYAXwBtAFwAXAByAGkAZwBoAHQAKQBcAG4AUQBfAG0AIAA9ACAAdABvAHQAYQBsACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAbQBpAG4AZQByAGEAbAAgAHMAdQBwAHAAbABlAG0AZQBuAHQAIAB0AHkAcABlACAAbQAgAHUAcwBlAGQAXABuAEUARgBfAG0AIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG0AaQBuAGUAcgBhAGwAIABzAHUAcABwAGwAZQBtAGUAbgB0AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATQBpAG4AZQByAGEAbABTAHUAcABwAGwAZQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAG0ALAAgAEUARgBfAG0ALABcAG4AIAAgACAAIABRAF8AbQAgACoAIABFAEYAXwBtAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABtAGkAbgBlAHIAYQBsACAAcwB1AHAAcABsAGUAbQBlAG4AdABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATQBpAG4AZQByAGEAbABTAHUAcABwAGwAZQBtAGUAbgB0AHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA1AC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAG0AXABcAGwAZQBmAHQAKABRAF8AbQBcAFwAdABpAG0AZQBzACAARQBGAF8AbQBcAFwAcgBpAGcAaAB0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATQBpAG4AZQByAGEAbABTAHUAcABwAGwAZQBtAGUAbgB0AHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAG0AXAAiACwAIABcACIAdABvAHQAYQBsACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAbQBpAG4AZQByAGEAbAAgAHMAdQBwAHAAbABlAG0AZQBuAHQAIAB0AHkAcABlACAAbQAgAHUAcwBlAGQAXAAiACwAIABcACIAdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAG0AXAAiACwAIABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG0AaQBuAGUAcgBhAGwAIABzAHUAcABwAGwAZQBtAGUAbgB0AFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAGcAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBtAFwAIgAsACAAXAAiAG0AaQBuAGUAcgBhAGwAIABzAHUAcABwAGwAZQBtAGUAbgB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBmAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagBcAFwAbABlAGYAdAAoAFQATQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAGYAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBUAE0AXwBqAGYAIAA9ACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGEAbgBkACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXABuAEUARgBfAGYAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABNAF8AagBmACwAIABFAEYAXwBmACwAXABuACAAIAAgACAAKABUAE0AXwBqAGYAIAAqACAARQBGAF8AZgApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADQALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AZgBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGoAXABcAGwAZQBmAHQAKABUAE0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwBmAFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQATQBfAGoAZgBcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAHAAdQByAGMAaABhAHMAZQBkACAAYQBuAGQAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBmAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAcAB1AHIAYwBoAGEAcwBlAGQAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAGsAZwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAIABcACIAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBcACIALAAgAFwAIgBpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYwBvAG0AcABvAG4AZQBuAHQAcwBcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGYAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagBcAFwAbABlAGYAdAAoACgARgBfAHsAYwBmAH0AXABcAHQAaQBtAGUAcwAgAFQATQBfAHsAagBmAH0AKQAvADEAMAAwAFwAXAB0AGkAbQBlAHMAIABFAEYAXwBjAFwAXAByAGkAZwBoAHQAKQBcAG4ARgBfAGMAZgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAG8AbQBwAG8AbgBlAG4AdAAgAGMAIABjAG8AbgB0AGEAaQBuAGUAZAAgAHcAaQB0AGgAaQBuACAAdABoAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABmAFwAbgBUAE0AXwBqAGYAIAA9ACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGEAbgBkACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXABuAEUARgBfAGMAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAaABlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAbwBtAHAAbwBuAGUAbgB0ACAAYwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAF8AYwBmACwAIABUAE0AXwBqAGYALAAgAEUARgBfAGMALABcAG4AIAAgACAAIAAoACgARgBfAGMAZgAgACoAIABUAE0AXwBqAGYAKQAgAC8AIAAxADAAMAApACAAKgAgAEUARgBfAGMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAF8AYwBmACwAIABUAE0AXwBqAGYALAAgAEUARgBfAGMALABcAG4AIAAgACAAIAAoAEYAXwBjAGYAIAAqACAAVABNAF8AagBmACkAIAAqACAARQBGAF8AYwAgACoAIAAxADAAXgAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYwBvAG0AcABvAG4AZQBuAHQAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADQALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGYAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagBcAFwAbABlAGYAdAAoAFwAXABmAHIAYQBjAHsARgBfAHsAYwBmAH0AXABcAHQAaQBtAGUAcwAgAFQATQBfAHsAagBmAH0AfQB7ADEAMAAwAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAGMAXABcAHIAaQBnAGgAdAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGYAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagBcAFwAbABlAGYAdAAoAEYAXwB7AGMAZgB9AFwAXAB0AGkAbQBlAHMAIABUAE0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwBjAFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAGMAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAG8AbQBwAG8AbgBlAG4AdAAgAGMAIABjAG8AbgB0AGEAaQBuAGUAZAAgAHcAaQB0AGgAaQBuACAAdABoAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABmAFwAIgAsACAAXAAiAHcAdAAlAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABNAF8AagBmAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAcAB1AHIAYwBoAGEAcwBlAGQAIABhAG4AZAAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGMAXAAiACwAIABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAaABlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAbwBtAHAAbwBuAGUAbgB0ACAAYwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8AawBnACAAYwBvAG0AcABvAG4AZQBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsACAAXAAiAGYAZQByAHQAaQBsAGkAcwBlAHIAIABjAG8AbQBwAG8AbgBlAG4AdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAIABcACIAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAIABcACIAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAHIAZQBtAG8AdgBlAHMAIABkAGkAdgBpAHMAaQBvAG4AIABiAHkAIAAxADAAMAAgAGYAbwByACAARgBfAGMAZgAsACAAdAByAGUAYQB0AGkAbgBnACAARgBfAGMAZgAgAGEAcwAgAGYAcgBhAGMAdABpAG8AbgAgAGkAbgBzAHQAZQBhAGQAIABvAGYAIABwAGUAcgBjAGUAbgB0ACAAYgBlAGMAYQB1AHMAZQAgAGkAdAAgAGkAcwAgAGEAIABmAHIAYQBjAHQAaQBvAG4AIABpAG4AIABzAGMAbwBwAGUAIAAxACAAZQBxAHUAYQB0AGkAbwBuAHMALgAgAEMAbwBuAHYAZQByAHQAIABrAGcAIAB0AG8AIAB0AG8AbgBuAGUAcwAgAGIAeQAgAG0AdQB0AGkAcABsAHkAaQBuAGcAIABiAHkAIAAxADAAXgAtADMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABwAHIAbwBkAHUAYwB0ACAAZABlAHIAaQB2AGUAZAAgAGYAcgBvAG0AIABjAG8AbQBwAG8AbgBlAG4AdABzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAF8AYwBmACwAIABFAEYAXwBjACwAXABuACAAIAAgACAARgBfAGMAZgAgACoAIABFAEYAXwBjAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwBYAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHAAcgBvAGQAdQBjAHQAIABkAGUAcgBpAHYAZQBkACAAZgByAG8AbQAgAGMAbwBtAHAAbwBuAGUAbgB0AHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwBYAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBPADIAZQAvAGsAZwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAEEARgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwBYAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwBmAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjAFwAXABsAGUAZgB0ACgARgBfAHsAYwBmAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAGMAXABcAHIAaQBnAGgAdAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAGMAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAG8AbQBwAG8AbgBlAG4AdAAgAGMAIABjAG8AbgB0AGEAaQBuAGUAZAAgAHcAaQB0AGgAaQBuACAAdABoAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABmAFwAIgAsACAAXAAiAHcAdAAlAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AYwBcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdABoAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwBvAG0AcABvAG4AZQBuAHQAIABjAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAGcAIABjAG8AbQBwAG8AbgBlAG4AdABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAIABcACIAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGMAbwBtAHAAbwBuAGUAbgB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBcACIALAAgAFwAIgBpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABUAGgAaQBzACAAZQBxAHUAYQB0AGkAbwBuACAAaQBzACAAYQBkAGQAZQBkACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIABhAG4AIABFAEYAIAB2AGEAbAB1AGUAIABmAHIAbwBtACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGMAbwBtAHAAbwBuAGUAbgB0AHMAIAB0AGgAYQB0ACAAYwBhAG4AIABiAGUAIAB1AHMAZQBkACAAaQBuACAAMQA1AC4ANAAuADEALgAxACAAKAAxACkAXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXABuAFQAbwB0AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAYQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGgAXABcAGwAZQBmAHQAKABRAF8AaABcAFwAdABpAG0AZQBzACAARQBGAF8AaABcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAFEAXwBoACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAGEAYwB0AGkAdgBlACAAaQBuAGcAcgBlAGQAaQBlAG4AdABzACAAaQBuACAAYQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAIAB0AHkAcABlACAAaAAgAHAAdQByAGMAaABhAHMAZQBkACAAYQBuAGQAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAbgBFAEYAXwBoACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGEAZwByAGkAYwBoAGUAbQBpAGMAYQBsACAAYQBjAHQAaQB2AGUAIABpAG4AZwByAGUAZABpAGUAbgB0AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADUAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAQQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AaAAsACAARQBGAF8AaAAsAFwAbgAgACAAIAAgACgAUQBfAGgAIAAqACAARQBGAF8AaAApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAYQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADUAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAQQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AaABcAFwAbABlAGYAdAAoAFEAXwBoAFwAXAB0AGkAbQBlAHMAIABFAEYAXwBoAFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBoAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAGEAYwB0AGkAdgBlACAAaQBuAGcAcgBlAGQAaQBlAG4AdABzACAAaQBuACAAYQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAIAB0AHkAcABlACAAaAAgAHAAdQByAGMAaABhAHMAZQBkACAAYQBuAGQAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAIgAsACAAXAAiAGsAZwAgAGEAaQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGgAXAAiACwAIABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHAAdQByAGMAaABhAHMAZQBkACAAYQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAIABhAGMAdABpAHYAZQAgAGkAbgBnAHIAZQBkAGkAZQBuAHQAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAGsAZwAgAGEAaQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGgAXAAiACwAIABcACIAYQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwA2AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQBtAGUAXABuAEUAbQBiAGUAZABkAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGwAaQBtAGUAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0ATQBfAGwAaQBtAGUAXABcAHQAaQBtAGUAcwAgAEUARgBfAGwAXABuAE0AXwBsAGkAbQBlACAAPQAgAHQAbwB0AGEAbAAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAGwAaQBtAGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAbgBFAEYAXwBsACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGwAaQBtAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBsAGkAbQBlACwAIABFAEYAXwBsACwAXABuACAAIAAgACAATQBfAGwAaQBtAGUAIAAqACAARQBGAF8AbABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADYAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAG0AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGIAZQBkAGQAZQBkACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAG8AcgAgAHAAdQByAGMAaABhAHMAZQBkACAAbABpAG0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA2AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQBtAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADYALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADYAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAG0AZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AE0AXwB7AGwAaQBtAGUAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBsAGkAbQBlAFwAIgAsACAAXAAiAHQAbwB0AGEAbAAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAGwAaQBtAGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBsAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGwAaQBtAGUAXAAiACwAIABcACIAdAAgAEMATwAyAGUALwB0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAHMAZQByAHYAaQBjAGUAcwAgAGEAbgBkACAAYwBvAG4AdAByAGEAYwB0AG8AcgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBwAFwAXABsAGUAZgB0ACgAQQBfAHAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHAAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBBAF8AcAAgAD0AIABhAGMAdABpAHYAaQB0AHkAIABkAGEAdABhACAAbwBmACAAdABoAGUAIABzAGUAcgB2AGkAYwBlACAAdABoAGEAdAAgAHcAYQBzACAAcAB1AHIAYwBoAGEAcwBlAGQAXABuAEUARgBfAHAAIAA9ACAAbABpAGYAZQAgAGMAeQBjAGwAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGgAZQAgAHAAdQByAGMAaABhAHMAZQBkACAAcwBlAHIAdgBpAGMAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAF8AcAAsACAARQBGAF8AcAAsAFwAbgAgACAAIAAgACgAQQBfAHAAIAAqACAARQBGAF8AcAApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAHMAZQByAHYAaQBjAGUAcwAgAGEAbgBkACAAYwBvAG4AdAByAGEAYwB0AG8AcgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADcAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUwBlAHIAdgBpAGMAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgA3AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABTAGUAcgB2AGkAYwBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBwAFwAXABsAGUAZgB0ACgAQQBfAHAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHAAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAF8AcABcACIALAAgAFwAIgBhAGMAdABpAHYAaQB0AHkAIABkAGEAdABhACAAbwBmACAAdABoAGUAIABzAGUAcgB2AGkAYwBlACAAdABoAGEAdAAgAHcAYQBzACAAcAB1AHIAYwBoAGEAcwBlAGQAXAAiACwAIABcACIAaABhACAAbwByACAAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAHAAXAAiACwAIABcACIAbABpAGYAZQAgAGMAeQBjAGwAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGgAZQAgAHAAdQByAGMAaABhAHMAZQBkACAAcwBlAHIAdgBpAGMAZQBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8AaABhACAAbwByACAAawBnACAAQwBPADIAZQAvAGgAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsACAAXAAiAHMAZQByAHYAaQBjAGUAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwA4AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFAAYQBjAGsAYQBnAGkAbgBnAFwAbgBFAG0AYgBlAGQAZABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHMAZQAgAG8AZgAgAHAAYQBjAGsAYQBnAGkAbgBnACAAbQBhAHQAZQByAGkAYQBsAHMAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBwAFwAXABsAGUAZgB0ACgAUQBfAHAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHAAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRAF8AcAAgAD0AIAB1AG4AaQB0AHMAIABvAGYAIABwAGEAYwBrAGEAZwBpAG4AZwAgAHQAeQBwAGUAIABwAFwAbgBFAEYAXwBwACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABwAGEAYwBrAGEAZwBpAG4AZwAgAHQAeQBwAGUAIABwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAHAALAAgAEUARgBfAHAALABcAG4AIAAgACAAIAAoAFEAXwBwACAAKgAgAEUARgBfAHAAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGIAZQBkAGQAZQBkACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdQBzAGUAIABvAGYAIABwAGEAYwBrAGEAZwBpAG4AZwAgAG0AYQB0AGUAcgBpAGEAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA4AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFAAYQBjAGsAYQBnAGkAbgBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA4AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFAAYQBjAGsAYQBnAGkAbgBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA1AC4AOAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHAAXABcAGwAZQBmAHQAKABRAF8AcABcAFwAdABpAG0AZQBzACAARQBGAF8AcABcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAHAAXAAiACwAIABcACIAdQBuAGkAdABzACAAbwBmACAAcABhAGMAawBhAGcAaQBuAGcAIAB0AHkAcABlACAAcABcACIALAAgAFwAIgB1AG4AaQB0AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBwAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABwAGEAYwBrAGEAZwBpAG4AZwAgAHQAeQBwAGUAIABwAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwB1AG4AaQB0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcABcACIALAAgAFwAIgBwAGEAYwBrAGEAZwBpAG4AZwAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABDAGgAYQBuAGcAZQBkACAAdQBuAGkAdAAgAG8AZgAgAFEAIABmAHIAbwBtACAAXAB1ADAAMAAyADcAdQBuAGkAdABzAFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcAawBnAFwAdQAwADAAMgA3ACAAYQBzACAARQBGACAAZABhAHQAYQAgAGkAcwAgAGkAbgAgAGsAZwAuAFwAIgApADsAXABuACAAIABcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAFwAbgBFAG0AYgBlAGQAZABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHMAZQAgAG8AZgAgAGcAcgBvAHcAIABtAGUAZABpAGEAIABwAHIAbwBkAHUAYwB0AHMAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBnAFwAXABsAGUAZgB0ACgAUQBfAGcAXABcAHQAaQBtAGUAcwAgAEUARgBfAGcAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRAF8AZwAgAD0AIAB0AG8AdABhAGwAIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABnAHIAbwB3ACAAbQBlAGQAaQBhACAAdAB5AHAAZQAgAGcAXABuAEUARgBfAGcAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGcAcgBvAHcAIABtAGUAZABpAGEAIAB0AHkAcABlACAAZwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBnACwAIABFAEYAXwBnACwAXABuACAAIAAgACAAKABRAF8AZwAgACoAIABFAEYAXwBnACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADkAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARwByAG8AdwBNAGUAZABpAGEAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBiAGUAZABkAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHUAcwBlACAAbwBmACAAZwByAG8AdwAgAG0AZQBkAGkAYQAgAHAAcgBvAGQAdQBjAHQAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABHAHIAbwB3AE0AZQBkAGkAYQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABHAHIAbwB3AE0AZQBkAGkAYQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADkALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADkAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARwByAG8AdwBNAGUAZABpAGEAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADkAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARwByAG8AdwBNAGUAZABpAGEAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBnAFwAXABsAGUAZgB0ACgAUQBfAGcAXABcAHQAaQBtAGUAcwAgAEUARgBfAGcAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBnAFwAIgAsACAAXAAiAHQAbwB0AGEAbAAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAGcAcgBvAHcAIABtAGUAZABpAGEAIAB0AHkAcABlACAAZwBcACIALAAgAFwAIgBrAGcAIABvAHIAIABtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBnAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABnAHIAbwB3ACAAbQBlAGQAaQBhACAAdAB5AHAAZQAgAGcAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAGsAZwAgAG8AcgAgAGsAZwAgAEMATwAyAGUALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBnAFwAIgAsACAAXAAiAGcAcgBvAHcAIABtAGUAZABpAGEAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAFwAbgBPAHQAaABlAHIAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGcAbwBvAGQAcwAgAGEAbgBkACAAcwBlAHIAdgBpAGMAZQBzACAAZwBlAG4AZQByAGkAYwAgAGUAcwB0AGkAbQBhAHQAZQBcAG4AZQBtAGkAcwBzAGkAbwBuAHMAXABuAHQAIABDAE8AMgBlAFwAbgBlAG0AaQBzAHMAaQBvAG4AcwA9AGEAYwB0AGkAdgBpAHQAeQBfAGQAYQB0AGEAXABcAHQAaQBtAGUAcwAgAGUAbQBpAHMAcwBpAG8AbgBfAGYAYQBjAHQAbwByAFwAbgBhAGMAdABpAHYAaQB0AHkAXwBkAGEAdABhACAAPQAgAG0AZQBhAHMAdQByAGUAZAAgAGEAYwB0AGkAdgBpAHQAeQAgAGYAbwByACAAdABoAGUAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGcAbwBvAGQAIABvAHIAIABzAGUAcgB2AGkAYwBlAFwAbgBlAG0AaQBzAHMAaQBvAG4AXwBmAGEAYwB0AG8AcgAgAD0AIABsAGkAZgBlAGMAeQBjAGwAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAYQBjAHQAaQB2AGkAdAB5AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQBjAHQAaQB2AGkAdAB5AF8AZABhAHQAYQAsACAAZQBtAGkAcwBzAGkAbwBuAF8AZgBhAGMAdABvAHIALABcAG4AIAAgACAAIABhAGMAdABpAHYAaQB0AHkAXwBkAGEAdABhACAAKgAgAGUAbQBpAHMAcwBpAG8AbgBfAGYAYQBjAHQAbwByAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAwAF8AMQBfADEAXwBfADEAXwBPAHQAaABlAHIAUAB1AHIAYwBoAGEAcwBlAGQARwBvAG8AZABzAEEAbgBkAFMAZQByAHYAaQBjAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAAcAB1AHIAYwBoAGEAcwBlAGQAIABnAG8AbwBkAHMAIABhAG4AZAAgAHMAZQByAHYAaQBjAGUAcwAgAGcAZQBuAGUAcgBpAGMAIABlAHMAdABpAG0AYQB0AGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA1AC4AMQAwACwAIABnAGUAbgBlAHIAaQBjACAAcABsAGEAYwBlAGgAbwBsAGQAZQByACAAZQBxAHUAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZQBtAGkAcwBzAGkAbwBuAHMAPQBhAGMAdABpAHYAaQB0AHkAXABcAF8AZABhAHQAYQBcAFwAdABpAG0AZQBzACAAZQBtAGkAcwBzAGkAbwBuAFwAXABfAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGEAYwB0AGkAdgBpAHQAeQBfAGQAYQB0AGEAXAAiACwAIABcACIAbQBlAGEAcwB1AHIAZQBkACAAYQBjAHQAaQB2AGkAdAB5ACAAZgBvAHIAIAB0AGgAZQAgAHAAdQByAGMAaABhAHMAZQBkACAAZwBvAG8AZAAgAG8AcgAgAHMAZQByAHYAaQBjAGUAXAAiACwAIABcACIAdgBhAHIAaQBlAHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AXwBmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBsAGkAZgBlAGMAeQBjAGwAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAYQBjAHQAaQB2AGkAdAB5AFwAIgAsACAAXAAiAHYAYQByAGkAZQBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABVAHAAcwB0AHIAZQBhAG0ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAHUAZQBsAFwAbgBUAG8AdABhAGwAIAB1AHAAcwB0AHIAZQBhAG0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAGMAbwBwAGUAIAAxACAAZgB1AGUAbAAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgBcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHEARQBfAHsAVwBUAFQALAB0AHIAYQBuAHMALABxAH0AKwBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHEARQBfAHsAVwBUAFQALABTAEMALABxAH0AXABuAEUAXwBXAFQAVAB0AHIAYQBuAHMAcQAgAD0AIAB1AHAAcwB0AHIAZQBhAG0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAGMAbwBwAGUAIAAxACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsACAAdQBzAGUAXABuAEUAXwBXAFQAVABTAEMAcQAgAD0AIAB1AHAAcwB0AHIAZQBhAG0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAGMAbwBwAGUAIAAxACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAHUAZQBsACAAdQBzAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AVwBUAFQAdAByAGEAbgBzAHEALAAgAEUAXwBXAFQAVABTAEMAcQAsAFwAbgAgACAAIAAgAEUAXwBXAFQAVAB0AHIAYQBuAHMAcQAgACsAIABFAF8AVwBUAFQAUwBDAHEAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABVAHAAcwB0AHIAZQBhAG0ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAHUAZQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIAB1AHAAcwB0AHIAZQBhAG0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAGMAbwBwAGUAIAAxACAAZgB1AGUAbAAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABVAHAAcwB0AHIAZQBhAG0ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAHUAZQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADEAMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHEARQBfAHsAVwBUAFQALAB0AHIAYQBuAHMALABxAH0AKwBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHEARQBfAHsAVwBUAFQALABTAEMALABxAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAFUAcABzAHQAcgBlAGEAbQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAdQBlAGwAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBfAFcAVABUAHQAcgBhAG4AcwBxAFwAIgAsACAAXAAiAHUAcABzAHQAcgBlAGEAbQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAYwBvAHAAZQAgADEAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAIAB1AHMAZQBcACIALAAgAFwAIgB0ACAAQwBPADIAZQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAYgB5ACAAMQA1AC4AMQAxAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBfAFcAVABUAFMAQwBxAFwAIgAsACAAXAAiAHUAcABzAHQAcgBlAGEAbQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAYwBvAHAAZQAgADEAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAGYAdQBlAGwAIAB1AHMAZQBcACIALAAgAFwAIgB0ACAAQwBPADIAZQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAYgB5ACAAMQA1AC4AMQAxAC4AMQAuADEAIAAoADMAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBVAHAAcwB0AHIAZQBhAG0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAGMAbwBwAGUAIAAxACAAZgB1AGUAbAAgAHUAcwBlACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAHAAdQByAHAAbwBzAGUAcwBcAG4ARQBfAFcAVABUAHQAcgBhAG4AcwBxAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBfAHsAVwBUAFQALAB0AHIAYQBuAHMALABxAH0APQBRAF8AewBUAHIAYQBuAHMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAVAByAGEAbgBzACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFQAcgBhAG4AcwAsADMALABxAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAFEAXwBUAHIAYQBuAHMAcQAgAD0AIABhAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXABuAEUAQwBfAFQAcgBhAG4AcwBxACAAPQAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAbgBFAEYAXwBUAHIAYQBuAHMAMwBxACAAPQAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBUAHIAYQBuAHMAcQAsACAARQBDAF8AVAByAGEAbgBzAHEALAAgAEUARgBfAFQAcgBhAG4AcwAzAHEALABcAG4AIAAgACAAIAAoAFEAXwBUAHIAYQBuAHMAcQAgACoAIABFAEMAXwBUAHIAYQBuAHMAcQAgACoAIABFAEYAXwBUAHIAYQBuAHMAMwBxACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAyAF8AVQBwAHMAdAByAGUAYQBtAFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFUAcABzAHQAcgBlAGEAbQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAYwBvAHAAZQAgADEAIABmAHUAZQBsACAAdQBzAGUAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAcAB1AHIAcABvAHMAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AVwBUAFQAdAByAGEAbgBzAHEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAyAF8AVQBwAHMAdAByAGUAYQBtAFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADIAXwBVAHAAcwB0AHIAZQBhAG0AVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgAxADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAyAF8AVQBwAHMAdAByAGUAYQBtAFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAyAF8AVQBwAHMAdAByAGUAYQBtAFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBXAFQAVAAsAHQAcgBhAG4AcwAsAHEAfQA9AFEAXwB7AFQAcgBhAG4AcwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBUAHIAYQBuAHMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAVAByAGEAbgBzACwAMwAsAHEAfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADIAXwBVAHAAcwB0AHIAZQBhAG0AVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AVAByAGEAbgBzAHEAXAAiACwAIABcACIAYQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAcQAgAGMAbwBtAGIAdQBzAHQAZQBkACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgAsACAAXAAiAGsATABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAFQAcgBhAG4AcwBxAFwAIgAsACAAXAAiAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgAsACAAXAAiAEcASgAvAGsATAAgAG8AcgAgAEcASgAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFQAcgBhAG4AcwAzAHEAXAAiACwAIABcACIAcwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBHAEoAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBcAG4AVQBwAHMAdAByAGUAYQBtACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwBjAG8AcABlACAAMQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgB1AGUAbAAgAHUAcwBlAFwAbgBFAF8AVwBUAFQAUwBDAHEAXABuAHQAIABDAE8AMgBlAFwAbgBFAF8AewBXAFQAVAAsAFMAQwAsAHEAfQA9AFEAXwB7AFMAQwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUwBDACwAMwAsAHEAfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4AUQBfAFMAQwBxACAAPQAgAGEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXABuAEUAQwBfAFMAQwBxACAAPQAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXABuAEUARgBfAFMAQwAzAHEAIAA9ACAAcwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBTAEMAcQAsACAARQBDAF8AUwBDAHEALAAgAEUARgBfAFMAQwAzAHEALABcAG4AIAAgACAAIAAoAFEAXwBTAEMAcQAgACoAIABFAEMAXwBTAEMAcQAgACoAIABFAEYAXwBTAEMAMwBxACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVQBwAHMAdAByAGUAYQBtACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwBjAG8AcABlACAAMQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgB1AGUAbAAgAHUAcwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMwBfAFUAcABzAHQAcgBlAGEAbQBTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBXAFQAVABTAEMAcQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgAxADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAVwBUAFQALABTAEMALABxAH0APQBRAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAUwBDACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFMAQwAsADMALABxAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AUwBDAHEAXAAiACwAIABcACIAYQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAcQAgAHUAcwBlAGQAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwBcACIALAAgAFwAIgBrAEwAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMAXwBTAEMAcQBcACIALAAgAFwAIgBlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAIgAsACAAXAAiAEcASgAvAGsATABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFMAQwAzAHEAXAAiACwAIABcACIAcwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAcwB0AGEAdABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQBcACIALAAgAFwAIgBtAGUAdAByAG8AcABvAGwAaQB0AGEAbgAvAG4AbwBuAC0AbQBlAHQAcgBvAHAAbwBsAGkAdABhAG4AIABsAG8AYwBhAHQAaQBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHMAdABhAHQAZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAbQBlAHQAcgBvAC8AbgBvAG4ALQBtAGUAdAByAG8AXAB1ADAAMAAyADcAIABhAHIAZwB1AG0AZQBuAHQAcwAgAGEAcwAgAGcAYQBzAGUAbwB1AHMAIABzAGMAbwBwAGUAIAAzACAARQBGAHMAIABhAHIAZQAgAHMAdABhAHQAZQAgAGEAbgBkACAAbQBlAHQAcgBvAC8AbgBvAG4ALQBtAGUAdAByAG8AIABsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQALgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFwAbgBTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABsAG8AYwBhAHQAaQBvAG4AIABiAGEAcwBlAGQAXABuAEUAXwAzAGUAbABlAGMAXABuAHQAIABDAE8AMgBlAFwAbgBFAF8AewAzACwAZQBsAGUAYwB9AD0AUQBfAHsAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7ADMALABlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAFEAXwBlAGwAZQBjACAAPQAgAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAbgBFAEYAXwAzAGUAbABlAGMAIAA9ACAAcwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMQBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AZQBsAGUAYwAsACAARQBGAF8AMwBlAGwAZQBjACwAXABuACAAIAAgACAAKABRAF8AZQBsAGUAYwAgACoAIABFAEYAXwAzAGUAbABlAGMAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADEAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAGwAbwBjAGEAdABpAG8AbgAgAGIAYQBzAGUAZABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADEAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwAzAGUAbABlAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADEAMgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADEAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAMwAsAGUAbABlAGMAfQA9AFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewAzACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMQBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZQBsAGUAYwBcACIALAAgAFwAIgBhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZABcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfADMAZQBsAGUAYwBcACIALAAgAFwAIgBzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHAAdQByAGMAaABhAHMAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAFcAaABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGcAXAAiACwAIABcACIAZwByAGkAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHcAYQBzACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAFwAbgBTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABtAGEAcgBrAGUAdAAgAGIAYQBzAGUAZABcAG4ARQBfADMAZQBsAGUAYwBcAG4AdAAgAEMATwAyAGUAXABuAEUAXwB7ADMALABlAGwAZQBjAH0APQBcAFwAbABlAGYAdABbAFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0ACgAMQAtACgAUgBQAFAAKwBKAFIAUABQACkAXABcAHIAaQBnAGgAdAApAC0AXABcAGwAZQBmAHQAKABSAEUAQwBfAHsAcwB1AHIAcgBlAG4AZABlAHIAZQBkAH0ALQBSAEUAQwBfAHsAbwBuAHMAaQB0AGUAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABcAHIAaQBnAGgAdABdAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFIATQBGADMALABlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAFEAXwBlAGwAZQBjACAAPQAgAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAbgBSAFAAUAAgAD0AIAByAGUAbgBlAHcAYQBiAGwAZQAgAHAAbwB3AGUAcgAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIAB1AG4AZABlAHIAIABMAFIARQBUACAAZgBvAHIAIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIABwAGUAcgBpAG8AZABcAG4ASgBSAFAAUAAgAD0AIABqAHUAcgBpAHMAZABpAGMAdABpAG8AbgBhAGwAIAByAGUAbgBlAHcAYQBiAGwAZQAgAHAAbwB3AGUAcgAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABmAG8AcgAgAHQAaABlACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHAAZQByAGkAbwBkAFwAbgBSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAD0AIABlAGwAaQBnAGkAYgBsAGUAIAByAGUAbgBlAHcAYQBiAGwAZQAgAGUAbgBlAHIAZwB5ACAAYwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIAB2AG8AbAB1AG4AdABhAHIAaQBsAHkAIABzAHUAcgByAGUAbgBkAGUAcgBlAGQAXABuAFIARQBDAF8AbwBuAHMAaQB0AGUAIAA9ACAAZQBsAGkAZwBpAGIAbABlACAAcgBlAG4AZQB3AGEAYgBsAGUAIABlAG4AZQByAGcAeQAgAGMAZQByAHQAaQBmAGkAYwBhAHQAZQBzACAAaQBzAHMAdQBlAGQAIABmAG8AcgAgAG8AbgBzAGkAdABlACAAZwBlAG4AZQByAGEAdABlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXABuAEUARgBfAFIATQBGADMAZQBsAGUAYwAgAD0AIABzAGMAbwBwAGUAIAAzACAAcgBlAHMAaQBkAHUAYQBsACAAbQBpAHgAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAyAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAFIAUABQACwAIABKAFIAUABQACwAIABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAsACAAUgBFAEMAXwBvAG4AcwBpAHQAZQAsACAARQBGAF8AUgBNAEYAMwBlAGwAZQBjACwAXABuACAAIAAgACAAKAAoAFEAXwBlAGwAZQBjACAAKgAgACgAMQAgAC0AIAAoAFIAUABQACAAKwAgAEoAUgBQAFAAKQApACkAIAAtACAAKAAoAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAALQAgAFIARQBDAF8AbwBuAHMAaQB0AGUAKQAgACoAIAAxADAAIABeACAALQAzACkAKQAgACoAIABFAEYAXwBSAE0ARgAzAGUAbABlAGMAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAyAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBNAGEAcgBrAGUAdABCAGEAcwBlAGQAVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAFIAUABQACwAIABKAFIAUABQACwAIABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAsACAAUgBFAEMAXwBvAG4AcwBpAHQAZQAsACAARQBGAF8AUgBNAEYAMwBlAGwAZQBjACwAXABuACAAIAAgACAAKAAoAFEAXwBlAGwAZQBjACAAKgAgACgAMQAgAC0AIAAoAFIAUABQACAAKwAgAEoAUgBQAFAAKQApACkAIAAtACAAKAAoAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAALQAgAFIARQBDAF8AbwBuAHMAaQB0AGUAKQAgACoAIAAxADAAIABeACAAMwApACkAIAAqACAARQBGAF8AUgBNAEYAMwBlAGwAZQBjACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABtAGEAcgBrAGUAdAAgAGIAYQBzAGUAZABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfADMAZQBsAGUAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADEAMgAuADEALgAyACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7ADMALABlAGwAZQBjAH0APQAgAFsAIABRAF8AewBlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAAoADEALQAoAFIAUABQACsASgBSAFAAUAApAFwAXAByAGkAZwBoAHQAKQAtAFwAXABsAGUAZgB0AFwAXABsAGUAZgB0ACgAKABSAEUAQwBfAHsAcwB1AHIAcgBlAG4AZABlAHIAZQBkAH0ALQBSAEUAQwBfAHsAbwBuAHMAaQB0AGUAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABcAHIAaQBnAGgAdAApAFwAXAByAGkAZwBoAHQAXQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBSAE0ARgAzACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAMwAsAGUAbABlAGMAfQA9ACAAWwAgAFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0ACgAMQAtACgAUgBQAFAAKwBKAFIAUABQACkAXABcAHIAaQBnAGgAdAApAC0AXABcAGwAZQBmAHQAXABcAGwAZQBmAHQAKAAoAFIARQBDAF8AewBzAHUAcgByAGUAbgBkAGUAcgBlAGQAfQAtAFIARQBDAF8AewBvAG4AcwBpAHQAZQB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAzAH0AXABcAHIAaQBnAGgAdAApAFwAXAByAGkAZwBoAHQAXQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBSAE0ARgAzACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBlAGwAZQBjAFwAIgAsACAAXAAiAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAIgAsACAAXAAiAGsAVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBQAFAAXAAiACwAIABcACIAcgBlAG4AZQB3AGEAYgBsAGUAIABwAG8AdwBlAHIAIABwAGUAcgBjAGUAbgB0AGEAZwBlACAAdQBuAGQAZQByACAATABSAEUAVAAgAGYAbwByACAAdABoAGUAIABhAHAAcABsAGkAYwBhAGIAbABlACAAcABlAHIAaQBvAGQAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgBSAFAAUABcACIALAAgAFwAIgBqAHUAcgBpAHMAZABpAGMAdABpAG8AbgBhAGwAIAByAGUAbgBlAHcAYQBiAGwAZQAgAHAAbwB3AGUAcgAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABmAG8AcgAgAHQAaABlACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHAAZQByAGkAbwBkAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkAFwAIgAsACAAXAAiAGUAbABpAGcAaQBiAGwAZQAgAHIAZQBuAGUAdwBhAGIAbABlACAAZQBuAGUAcgBnAHkAIABjAGUAcgB0AGkAZgBpAGMAYQB0AGUAcwAgAHYAbwBsAHUAbgB0AGEAcgBpAGwAeQAgAHMAdQByAHIAZQBuAGQAZQByAGUAZABcACIALAAgAFwAIgBNAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIARQBDAF8AbwBuAHMAaQB0AGUAXAAiACwAIABcACIAZQBsAGkAZwBpAGIAbABlACAAcgBlAG4AZQB3AGEAYgBsAGUAIABlAG4AZQByAGcAeQAgAGMAZQByAHQAaQBmAGkAYwBhAHQAZQBzACAAaQBzAHMAdQBlAGQAIABmAG8AcgAgAG8AbgBzAGkAdABlACAAZwBlAG4AZQByAGEAdABlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACwAIABcACIATQBXAGgAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBSAE0ARgAzAGUAbABlAGMAXAAiACwAIABcACIAcwBjAG8AcABlACAAMwAgAHIAZQBzAGkAZAB1AGEAbAAgAG0AaQB4ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8AawBXAGgAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAHMAdABhAHQAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAEkAbgAgAG8AcgBkAGUAcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABtAGUAZwBhAHcAYQB0AHQAIABoAG8AdQByAHMAIAB0AG8AIABrAGkAbABvAHcAYQB0AHQAIABoAG8AdQByAHMALAAgAHQAaABlACAAUgBFAEMAXwBzAHUAcgByAGUAbgBkAGUAcgBlAGQAIABhAG4AZAAgAFIARQBDAF8AbwBuAHMAaQB0AGUAIAB2AGEAcgBpAGEAYgBsAGUAcwAgAGEAcgBlACAAbQB1AGwAdABpAHAAbABpAGUAZAAgAGIAeQAgADEAMABeADMAIABpAG4AcwB0AGUAYQBkACAAbwBmACAAMQAwAF4ALQAzAC4AXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAHMAZQBuAHQAIABvAGYAZgAgAHMAaQB0AGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAaQBuACAAYQBuAG8AdABoAGUAcgAgAGYAYQByAG0AaQBuAGcAIABzAHkAcwB0AGUAbQAgAG8AcgAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAXABuAEUAXABuAHQAIABOADIATwBcAG4ARQA9AEUAXwB7AE4AMgBPAH0AKwBFAF8AewBhAGQAfQArAEUAXwB7AGwAZQBhAGMAaAB9AFwAbgBFAF8ATgAyAE8AIAA9ACAAZABpAHIAZQBjAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIABzAG8AaQBsAHMAIABvAHUAdABzAGkAZABlACAAbwBmACAAcwBjAG8AcABlACAAMQAgAGIAbwB1AG4AZABhAHIAeQBcAG4ARQBfAGEAZAAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAcwBvAGkAbABzAFwAbgBFAF8AbABlAGEAYwBoACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIABzAG8AaQBsAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEUAXwBhAGQALAAgAEUAXwBsAGUAYQBjAGgALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAArACAARQBfAGEAZAAgACsAIABFAF8AbABlAGEAYwBoAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABzAGUAbgB0ACAAbwBmAGYAIABzAGkAdABlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGkAbgAgAGEAbgBvAHQAaABlAHIAIABmAGEAcgBtAGkAbgBnACAAcwB5AHMAdABlAG0AIABvAHIAIABlAG4AdABlAHIAcAByAGkAcwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADEAMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBFAF8AewBOADIATwB9ACsARQBfAHsAYQBkAH0AKwBFAF8AewBsAGUAYQBjAGgAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAF8ATgAyAE8AXAAiACwAIABcACIAZABpAHIAZQBjAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIABzAG8AaQBsAHMAIABvAHUAdABzAGkAZABlACAAbwBmACAAcwBjAG8AcABlACAAMQAgAGIAbwB1AG4AZABhAHIAeQBcACIALAAgAFwAIgB0ACAATgAyAE8AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBfAGEAZABcACIALAAgAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAcwBvAGkAbABzAFwAIgAsACAAXAAiAHQAIABOADIATwBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAF8AbABlAGEAYwBoAFwAIgAsACAAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIABzAG8AaQBsAHMAXAAiACwAIABcACIAdAAgAE4AMgBPAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANQBfADEAMwBfADEAXwAzAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AbABpAGQAVwBhAHMAdABlAFQAcgBlAGEAdABtAGUAbgB0AEYAYQBjAGkAbABpAHQAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMwBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGwAaQBkAFcAYQBzAHQAZQBUAHIAZQBhAHQAbQBlAG4AdABGAGEAYwBpAGwAaQB0AHkAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAE4AMgBPACwAIABFAF8AYQBkACwAIABFAF8AbABlAGEAYwBoACwAXABuACAAIAAgACAARQBfAE4AMgBPACAAKwAgAEUAXwBhAGQAIAArACAARQBfAGwAZQBhAGMAaABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMwBfADEAXwAzAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AbABpAGQAVwBhAHMAdABlAFQAcgBlAGEAdABtAGUAbgB0AEYAYQBjAGkAbABpAHQAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwBvAGwAaQBkACAAdwBhAHMAdABlACAAcwBlAG4AdAAgAHQAbwAgAGEAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADMAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBsAGkAZABXAGEAcwB0AGUAVAByAGUAYQB0AG0AZQBuAHQARgBhAGMAaQBsAGkAdAB5AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMwBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGwAaQBkAFcAYQBzAHQAZQBUAHIAZQBhAHQAbQBlAG4AdABGAGEAYwBpAGwAaQB0AHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADMAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBsAGkAZABXAGEAcwB0AGUAVAByAGUAYQB0AG0AZQBuAHQARgBhAGMAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADEAMwAuADEALgAzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMwBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGwAaQBkAFcAYQBzAHQAZQBUAHIAZQBhAHQAbQBlAG4AdABGAGEAYwBpAGwAaQB0AHkAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMwBfADEAXwAzAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AbABpAGQAVwBhAHMAdABlAFQAcgBlAGEAdABtAGUAbgB0AEYAYQBjAGkAbABpAHQAeQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMwBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGwAaQBkAFcAYQBzAHQAZQBUAHIAZQBhAHQAbQBlAG4AdABGAGEAYwBpAGwAaQB0AHkAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQA0AF8AMQBfADEAXwBfADEAXwBFAG0AYgBlAGQAZABlAGQARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBVAHAAcwB0AHIAZQBhAG0ARgByAGUAaQBnAGgAdABcAG4ARQBtAGIAZQBkAGQAZQBkACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdQBwAHMAdAByAGUAYQBtACAAZgByAGUAaQBnAGgAdABcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGYAXABcAGwAZQBmAHQAKAAoAFcAXwBmAFwAXAB0AGkAbQBlAHMAIABEAF8AZgApAFwAXAB0AGkAbQBlAHMAIABFAEYAXwBmAFwAXAByAGkAZwBoAHQAKQBcAG4AVwBfAGYAIAA9ACAAdABvAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAbwBvAGQAcwAgAHQAcgBhAG4AcwBwAG8AcgB0AGUAZAAgAHAAZQByACAAZgByAGUAaQBnAGgAdAAgAHQAeQBwAGUAIABmAFwAbgBEAF8AZgAgAD0AIAB0AG8AdABhAGwAIABkAGkAcwB0AGEAbgBjAGUAIAB0AHIAYQBuAHMAcABvAHIAdABlAGQAIABwAGUAcgAgAGYAcgBlAGkAZwBoAHQAIAB0AHkAcABlACAAZgBcAG4ARQBGAF8AZgAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgByAGUAaQBnAGgAdAAgAHQAeQBwAGUAIABmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVwBfAGYALAAgAEQAXwBmACwAIABFAEYAXwBmACwAXABuACAAIAAgACAAKABXAF8AZgAgACoAIABEAF8AZgApACAAKgAgAEUARgBfAGYAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AYgBlAGQAZABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHAAcwB0AHIAZQBhAG0AIABmAHIAZQBpAGcAaAB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA1AC4AMQA0AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AZgBcAFwAbABlAGYAdAAoACgAVwBfAGYAXABcAHQAaQBtAGUAcwAgAEQAXwBmACkAXABcAHQAaQBtAGUAcwAgAEUARgBfAGYAXABcAHIAaQBnAGgAdAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAXwBmAFwAIgAsACAAXAAiAHQAbwB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAG8AbwBkAHMAIAB0AHIAYQBuAHMAcABvAHIAdABlAGQAIABwAGUAcgAgAGYAcgBlAGkAZwBoAHQAIAB0AHkAcABlACAAZgBcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGYAXAAiACwAIABcACIAdABvAHQAYQBsACAAZABpAHMAdABhAG4AYwBlACAAdAByAGEAbgBzAHAAbwByAHQAZQBkACAAcABlAHIAIABmAHIAZQBpAGcAaAB0ACAAdAB5AHAAZQAgAGYAXAAiACwAIABcACIAawBtAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AZgBcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgByAGUAaQBnAGgAdAAgAHQAeQBwAGUAIABmAFwAIgAsACAAXAAiAHQAIABDAE8AMgBlAC8AKAB0ACAAawBtACkAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBmAFwAIgAsACAAXAAiAGYAcgBlAGkAZwBoAHQAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBHAGUAdABUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAFMAdAByAGkAbgBnACIALAAiAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAHUAZQBsAF8ARwBlAHQAUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAFMAdAByAGkAbgBnACIALAAiAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAHUAZQBsAF8AVABvAHQAYQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBVAG4AaQB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFUAbgBpAHQAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQB2AGUAcwB0AG8AYwBrAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAZQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATQBpAG4AZQByAGEAbABTAHUAcABwAGwAZQBtAGUAbgB0AHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwBYAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwBYAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADUAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAQQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADUAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAQQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA2AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQBtAGUAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADYAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAG0AZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADYAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAG0AZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA2AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQBtAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA2AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQBtAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABTAGUAcgB2AGkAYwBlAHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADcAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUwBlAHIAdgBpAGMAZQBzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABTAGUAcgB2AGkAYwBlAHMAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADcAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUwBlAHIAdgBpAGMAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA4AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFAAYQBjAGsAYQBnAGkAbgBnAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AOQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABHAHIAbwB3AE0AZQBkAGkAYQBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADkAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARwByAG8AdwBNAGUAZABpAGEAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAwAF8AMQBfADEAXwBfADEAXwBPAHQAaABlAHIAUAB1AHIAYwBoAGEAcwBlAGQARwBvAG8AZABzAEEAbgBkAFMAZQByAHYAaQBjAGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAFUAcABzAHQAcgBlAGEAbQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAdQBlAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABVAHAAcwB0AHIAZQBhAG0ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAHUAZQBsAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADIAXwBVAHAAcwB0AHIAZQBhAG0AVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAyAF8AVQBwAHMAdAByAGUAYQBtAFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMwBfAFUAcABzAHQAcgBlAGEAbQBTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMwBfAFUAcABzAHQAcgBlAGEAbQBTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMQBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADEAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMQBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADEAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAyAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAGEAbgB1AHIAZQBTAGUAbgB0AE8AZgBmAFMAaQB0AGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQA0AF8AMQBfADEAXwBfADEAXwBFAG0AYgBlAGQAZABlAGQARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBVAHAAcwB0AHIAZQBhAG0ARgByAGUAaQBnAGgAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24198,18 +24211,29 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Excel/8_Fuel_WIP_v05.prename.bak.xlsx
+++ b/Excel/8_Fuel_WIP_v05.prename.bak.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA8BF15-A958-40E9-9107-CD4FC3DA3151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B767B83B-7ACC-4E56-B7B1-96E6D84BDA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="28800" windowHeight="15345" firstSheet="4" activeTab="8" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1350" yWindow="360" windowWidth="36255" windowHeight="19140" firstSheet="4" activeTab="8" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -23,9 +23,6 @@
     <sheet name="Constants - Fuel" sheetId="110" r:id="rId8"/>
     <sheet name="Constants - Common" sheetId="124" r:id="rId9"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId10"/>
-  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -41,7 +38,17 @@
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Title">_xlfn.LAMBDA("Convert nitrous oxide emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Variable">_xlfn.LAMBDA("EN2O CO2e")</definedName>
-    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
+    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray,
+    _xlfn.XLOOKUP(
+        MEDIAN(
+            ROUND(_xlpm.Temperature, 0),
+            MIN(_xlpm.TemperatureArray),
+            MAX(_xlpm.TemperatureArray)
+        ),
+        _xlpm.TemperatureArray,
+        _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)
+    )
+)</definedName>
     <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag))))</definedName>
@@ -57,9 +64,28 @@
     <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTable">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse,
+    IFERROR(
+        _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1,
+            _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)
+        ),
+        IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)
+    )
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse,
+    _xlfn.XLOOKUP(1, (_xlpm.LookupArray1=_xlpm.LookupValue1)*(_xlpm.LookupArray2=_xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse))
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell,
+    SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) -1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlink">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet">_xlfn.LAMBDA(_xlpm.TargetCell,
+  _xlfn.LET(
+    _xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"),
+    _xlpm.addr, CELL("address", _xlpm.TargetCell),
+    "#" &amp; _xlpm.addr
+  )
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -264,30 +290,52 @@
     <definedName name="Fuel_Equations.VEERG_8_2_1_1__1_FuelCombustionStationary_Unit">_xlfn.LAMBDA("t CO2-e")</definedName>
     <definedName name="Fuel_Equations.VEERG_8_2_1_1__1_FuelCombustionStationary_Variable">_xlfn.LAMBDA("E_g")</definedName>
     <definedName name="Fuel_Equations.VEERG_8_FuelCombustion">_xlfn.LAMBDA(_xlpm.Q,_xlpm.EC,_xlpm.EF, (_xlpm.Q * _xlpm.EC * _xlpm.EF) * 10 ^ -3)</definedName>
-    <definedName name="Fuel_InputFunctions.Fuel_GetStationaryFuelString">_xlfn.LAMBDA(_xlpm.Cell, RIGHT(_xlpm.Cell, LEN(_xlpm.Cell) - FIND(", ", _xlpm.Cell) - 1))</definedName>
+    <definedName name="Fuel_InputFunctions.Fuel_GetStationaryFuelString">_xlfn.LAMBDA(_xlpm.Cell,
+    RIGHT(_xlpm.Cell,LEN(_xlpm.Cell)-FIND(", ",_xlpm.Cell))
+)</definedName>
     <definedName name="Fuel_InputFunctions.Fuel_GetTransportFuelString">_xlfn.LAMBDA(_xlpm.Cell, LEFT(_xlpm.Cell, FIND(", ", _xlpm.Cell) - 1))</definedName>
     <definedName name="Fuel_InputFunctions.Fuel_TotalConsumption">_xlfn.LAMBDA(_xlpm.FuelConsumptionArray,_xlpm.FuelUseArray,_xlpm.FuelUse,_xlpm.FuelTypeArray,_xlpm.FuelType, IFERROR(SUM(_xlfn._xlws.FILTER(_xlpm.FuelConsumptionArray, (_xlpm.FuelTypeArray = _xlpm.FuelType) * (_xlpm.FuelUseArray = _xlpm.FuelUse))), 0))</definedName>
-    <definedName name="Fuel_SourceData.Fuel_Scope1EmissionFactorsStationaryGaseous_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(19, 7, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Fuel combusted","Energy Content Factor (GJ per unit of fuel)","Fuel unit","Scope 1 Emission Factor (kg CO2 - e / GJ) CO2","Scope 1 Emission Factor (kg CO2 - e / GJ) CH4","Scope 1 Emission Factor (kg CO2 - e / GJ) N2O","Scope 1 Emission Factor (kg CO2 - e / GJ) Combined gases";"Natural gas distributed in a pipeline",0.0393,"m3",51.4,0.1,0.03,51.53;"Coal seam methane that is captured for combustion",0.0377,"m3",51.4,0.2,0.03,51.63;"Coal mine waste gas that is captured for combustion",0.0377,"m3",51.9,4.6,0.3,56.8;"Compressed natural gas(reverting to standard conditions)",0.0393,"m3",51.4,0.1,0.03,51.53;"Unprocessed natural gas",0.0393,"m3",51.4,0.1,0.03,51.53;"Ethane",0.0629,"m3",56.5,0.03,0.03,56.56;"Coke oven gas",0.0181,"m3",37,0.03,0.05,37.08;"Blast furnace gas",0.004,"m3",234,0.03,0.02,234.05;"Town gas",0.039,"m3",60.2,0.04,0.03,60.27;"Liquefied natural gas",25.3,"kL",51.4,0.1,0.03,51.53;"Gaseous fossil fuels other than those mentioned in the items above",0.039,"m3",51.4,0.1,0.03,51.53;"Landfill biogas that is captured for combustion (methane only)",0.0377,"m3",0,6.4,0.03,6.43;"Sludge biogas that is captured for combustion (methane only)",0.0377,"m3",0,6.4,0.03,6.43;"A biogas that is captured for combustion, other than those mentioned in the items above",0.037,"m3",0,6.4,0.03,6.43;"Biomethane",0.0393,"m3",0,0.1,0.03,0.13;"Hydrogen",0.0122,"m3",0,0,0.5,0.5;"Natural gas distributed in a pipeline - Gigajoules",1,"GJ",51.4,0.1,0.03,51.53;"Town gas - Gigajoules",1,"GJ",60.2,0.04,0.03,60.27}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Fuel_SourceData.Fuel_Scope1EmissionFactorsStationaryGaseous_Data">_xlfn.LAMBDA(
+  _xlfn.MAKEARRAY(19, 7,
+    _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+      INDEX({"Fuel combusted","Energy Content Factor (GJ per unit of fuel)","Fuel unit","Scope 1 Emission Factor (kg CO2 - e / GJ) CO2","Scope 1 Emission Factor (kg CO2 - e / GJ) CH4","Scope 1 Emission Factor (kg CO2 - e / GJ) N2O","Scope 1 Emission Factor (kg CO2 - e / GJ) Combined gases";"Natural gas distributed in a pipeline",0.0393,"m3",51.4,0.1,0.03,51.53;"Coal seam methane that is captured for combustion",0.0377,"m3",51.4,0.2,0.03,51.63;"Coal mine waste gas that is captured for combustion",0.0377,"m3",51.9,4.6,0.3,56.8;"Compressed natural gas(reverting to standard conditions)",0.0393,"m3",51.4,0.1,0.03,51.53;"Unprocessed natural gas",0.0393,"m3",51.4,0.1,0.03,51.53;"Ethane",0.0629,"m3",56.5,0.03,0.03,56.56;"Coke oven gas",0.0181,"m3",37,0.03,0.05,37.08;"Blast furnace gas",0.004,"m3",234,0.03,0.02,234.05;"Town gas",0.039,"m3",60.2,0.04,0.03,60.27;"Liquefied natural gas",25.3,"kL",51.4,0.1,0.03,51.53;"Gaseous fossil fuels other than those mentioned in the items above",0.039,"m3",51.4,0.1,0.03,51.53;"Landfill biogas that is captured for combustion (methane only)",0.0377,"m3",0,6.4,0.03,6.43;"Sludge biogas that is captured for combustion (methane only)",0.0377,"m3",0,6.4,0.03,6.43;"A biogas that is captured for combustion, other than those mentioned in the items above",0.037,"m3",0,6.4,0.03,6.43;"Biomethane",0.0393,"m3",0,0.1,0.03,0.13;"Hydrogen",0.0122,"m3",0,0,0.5,0.5;"Natural gas distributed in a pipeline - Gigajoules",1,"GJ",51.4,0.1,0.03,51.53;"Town gas - Gigajoules",1,"GJ",60.2,0.04,0.03,60.27}, _xlpm.r, _xlpm.c)
+)))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1EmissionFactorsStationaryGaseous_Description">_xlfn.LAMBDA(("Direct (Scope 1) emission factors for the consumption of gaseous fuels including liquefied natural gas  "))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1EmissionFactorsStationaryGaseous_Source">_xlfn.LAMBDA(("Australian National Greenhouse Accounts Factors 2025 - Table 5"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1EmissionFactorsStationaryGaseous_Title">_xlfn.LAMBDA(("Fuel scope 1 emission factors - Stationary gaseous fuels"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1EmissionFactorsStationaryGaseous_Variation">_xlfn.LAMBDA(("VARIATION OF SOURCE DATA: 'Natural gas distributed in a pipeline - Gigajoules' and 'Town gas - Gigajoules' were added, each with an energy content factor of 1 GJ per unit of fuel. This is for users who have fuel consumption data in GJ rather than m3."))</definedName>
-    <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsStationaryLiquid_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(25, 8, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Fuel combusted","Energy Content Factor (GJ per unit of fuel)","Fuel unit","Scope 1 Emission Factor (kg CO2 - e / GJ) CO2","Scope 1 Emission Factor (kg CO2 - e / GJ) CH4","Scope 1 Emission Factor (kg CO2 - e / GJ) N2O","Scope 1 Emission Factor (kg CO2 - e / GJ) Combined gases","Scope 3 Emission Factor (kg CO2 - e / GJ)";"Petroleum based oils (other than petroleum based oil used as fuel), e.g. lubricants",38.8,"kl",13.9,0,0,13.9,18;"Petroleum based greases",38.8,"kl",3.5,0,0,3.5,18;"Crude oil including crude oil condensates",45.3,"t",69.6,0.08,0.2,69.88,"NE";"Other natural gas liquids",46.5,"t",61,0.08,0.2,61.28,"NE";"Automotive gasoline / petrol (other than for use as fuel in an aircraft)",34.2,"kL",67.4,0.2,0.2,67.8,17.2;"Aviation gasoline",33.1,"kL",67,0.2,0.2,67.4,18;"Kerosene (other than for use as fuel in an aircraft)",37.5,"kL",68.9,0.01,0.2,69.11,18;"Aviation turbine fuel / kerosene",36.8,"kL",69.6,0.02,0.2,69.82,18;"Heating oil",37.3,"kL",69.5,0.03,0.2,69.73,18;"Diesel oil",38.6,"kL",69.9,0.1,0.2,70.2,17.3;"Fuel oil",39.7,"kL",73.6,0.04,0.2,73.84,18;"Liquefied aromatic hydrocarbons",34.4,"kL",69.7,0.03,0.2,69.93,18;"Solvents: mineral turpentine or white spirits",34.4,"kL",69.7,0.03,0.2,69.93,18;"Liquefied petroleum gas (LPG)",25.7,"kL",60.2,0.2,0.2,60.6,20.2;"Naphtha",31.4,"kL",69.8,0.01,0.01,69.82,18;"Petroleum coke",34.2,"t",92.6,0.08,0.2,92.88,18;"Refinery gas and liquids",42.9,"t",54.7,0.03,0.03,54.76,18;"Refinery coke",34.2,"t",92.6,0.08,0.2,92.88,18;"Petroleum based products other than mentioned in the items above",34.4,"kL",69.8,0.02,0.1,69.92,18;"Biodiesel",34.6,"kL",0,0.08,0.2,0.28,"NE";"Ethanol for use as a fuel in an internal combustion engine",23.4,"kL",0,0.08,0.2,0.28,"NE";"Biofuels other than those mentioned in the items above and below",23.4,"kL",0,0.08,0.2,0.28,"NE";"Renewable aviation kerosene",36.8,"kL",0,0.02,0.2,0.22,"NE";"Renewable diesel",38.6,"kL",0,0.1,0.2,0.3,"NE"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsStationaryLiquid_Data">_xlfn.LAMBDA(
+  _xlfn.MAKEARRAY(25, 8,
+    _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+      INDEX({"Fuel combusted","Energy Content Factor (GJ per unit of fuel)","Fuel unit","Scope 1 Emission Factor (kg CO2 - e / GJ) CO2","Scope 1 Emission Factor (kg CO2 - e / GJ) CH4","Scope 1 Emission Factor (kg CO2 - e / GJ) N2O","Scope 1 Emission Factor (kg CO2 - e / GJ) Combined gases","Scope 3 Emission Factor (kg CO2 - e / GJ)";"Petroleum based oils (other than petroleum based oil used as fuel), e.g. lubricants",38.8,"kl",13.9,0,0,13.9,18;"Petroleum based greases",38.8,"kl",3.5,0,0,3.5,18;"Crude oil including crude oil condensates",45.3,"t",69.6,0.08,0.2,69.88,"NE";"Other natural gas liquids",46.5,"t",61,0.08,0.2,61.28,"NE";"Automotive gasoline / petrol (other than for use as fuel in an aircraft)",34.2,"kL",67.4,0.2,0.2,67.8,17.2;"Aviation gasoline",33.1,"kL",67,0.2,0.2,67.4,18;"Kerosene (other than for use as fuel in an aircraft)",37.5,"kL",68.9,0.01,0.2,69.11,18;"Aviation turbine fuel / kerosene",36.8,"kL",69.6,0.02,0.2,69.82,18;"Heating oil",37.3,"kL",69.5,0.03,0.2,69.73,18;"Diesel oil",38.6,"kL",69.9,0.1,0.2,70.2,17.3;"Fuel oil",39.7,"kL",73.6,0.04,0.2,73.84,18;"Liquefied aromatic hydrocarbons",34.4,"kL",69.7,0.03,0.2,69.93,18;"Solvents: mineral turpentine or white spirits",34.4,"kL",69.7,0.03,0.2,69.93,18;"Liquefied petroleum gas (LPG)",25.7,"kL",60.2,0.2,0.2,60.6,20.2;"Naphtha",31.4,"kL",69.8,0.01,0.01,69.82,18;"Petroleum coke",34.2,"t",92.6,0.08,0.2,92.88,18;"Refinery gas and liquids",42.9,"t",54.7,0.03,0.03,54.76,18;"Refinery coke",34.2,"t",92.6,0.08,0.2,92.88,18;"Petroleum based products other than mentioned in the items above",34.4,"kL",69.8,0.02,0.1,69.92,18;"Biodiesel",34.6,"kL",0,0.08,0.2,0.28,"NE";"Ethanol for use as a fuel in an internal combustion engine",23.4,"kL",0,0.08,0.2,0.28,"NE";"Biofuels other than those mentioned in the items above and below",23.4,"kL",0,0.08,0.2,0.28,"NE";"Renewable aviation kerosene",36.8,"kL",0,0.02,0.2,0.22,"NE";"Renewable diesel",38.6,"kL",0,0.1,0.2,0.3,"NE"}, _xlpm.r, _xlpm.c)
+)))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsStationaryLiquid_Description">_xlfn.LAMBDA(("Direct (Scope 1) and indirect (scope 3) emission factors for the consumption of liquid fuels, including certain petroleum based products for stationary energy purposes."))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsStationaryLiquid_Source">_xlfn.LAMBDA(("Australian National Greenhouse Accounts Factors 2025 - Table 8"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsStationaryLiquid_Title">_xlfn.LAMBDA(("Fuel scope 1 and 3 emission factors - Stationary liquid fuels"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsStationaryLiquid_Variation">_xlfn.LAMBDA("VARIATION OF SOURCE DATA: 'NE' values returned as zero for calculations.")</definedName>
-    <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransport_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(26, 10, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Transport type","Fuel combusted","Energy Content Factor(GJ per unit of fuel)","Fuel unit","Scope 1 Emission Factor (kg CO2 - e / GJ) CO2","Scope 1 Emission Factor (kg CO2 - e / GJ) CH4","Scope 1 Emission Factor (kg CO2 - e / GJ) N2O","Scope 1 Emission Factor (kg CO2 - e / GJ) Combined gases","Scope 3 Emission Factor (kg CO2 - e / GJ)","Source";"Cars and light commercial vehicles","Gasoline",34.2,"kl",67.4,0.02,0.2,67.62,17.2,"NGAF 2025: Table 9";"Cars and light commercial vehicles","Diesel oil",38.6,"kl",69.9,0.01,0.5,70.41,17.3,"NGAF 2025: Table 9";"Cars and light commercial vehicles","Liquefied petroleum gas (LPG)",26.2,"kl",60.2,0.5,0.3,61,20.2,"NGAF 2025: Table 9";"Cars and light commercial vehicles","Fuel oil",39.7,"kl",73.6,0.08,0.5,74.18,18,"NGAF 2025: Table 9";"Cars and light commercial vehicles","Ethanol",23.4,"kl",0,0.2,0.2,0.4,"NE","NGAF 2025: Table 9";"Cars and light commercial vehicles","Biodiesel",34.6,"kl",0,0.8,1.7,2.5,"NE","NGAF 2025: Table 9";"Cars and light commercial vehicles","Renewable diesel",38.6,"kl",0,0.01,0.5,0.51,"NE","NGAF 2025: Table 9";"Cars and light commercial vehicles","Other biofuels",23.4,"kl",0,0.8,1.7,2.5,"NE","NGAF 2025: Table 9";"Light duty vehicles","Compressed natural gas",0.0393,"m3",51.4,7.3,0.3,59,18,"NGAF 2025: Table 9";"Light duty vehicles","Liquefied natural gas",25.3,"kl",51.4,7.3,0.3,59,18,"NGAF 2025: Table 9";"Heavy duty vehicles","Compressed natural gas",0.0393,"m3",51.4,2.8,0.3,54.5,18,"NGAF 2025: Table 9";"Heavy duty vehicles","Liquefied natural gas",25.3,"kl",51.4,2.8,0.3,54.5,18,"NGAF 2025: Table 9";"Heavy duty vehicles","Diesel oil - Euro iv or higher",38.6,"kl",69.9,0.07,0.4,70.37,17.3,"NGAF 2025: Table 9";"Heavy duty vehicles","Diesel oil - Euro iii",38.6,"kl",69.9,0.1,0.4,70.4,17.3,"NGAF 2025: Table 9";"Heavy duty vehicles","Diesel oil - Euro i",38.6,"kl",69.9,0.2,0.4,70.5,17.3,"NGAF 2025: Table 9";"Heavy duty vehicles","Renewable diesel – Euro iv or higher",38.6,"kl",0,0.07,0.4,0.47,"NE","NGAF 2025: Table 9";"Heavy duty vehicles","Renewable diesel – Euro iii",38.6,"kl",0,0.1,0.4,0.5,"NE","NGAF 2025: Table 9";"Heavy duty vehicles","Renewable diesel – Euro i",38.6,"kl",0,0.2,0.4,0.6,"NE","NGAF 2025: Table 9";"Aviation","Gasoline for use as fuel in an aircraft",33.1,"kl",67,0.06,0.6,67.66,18,"NGAF 2025: Table 9";"Aviation","Kerosene for use as fuel in an aircraft",36.8,"kl",69.6,0.01,0.6,70.21,18,"NGAF 2025: Table 9";"Aviation","Renewable aviation kerosene",36.8,"kl",0,0.01,0.6,0.61,"NE","NGAF 2025: Table 9";"Vessels","Gasoline",34.2,"kL",67.4,10.1,0.3,"",17.2,"VEERG 2026: Table A.4.2.1";"Vessels","Diesel oil",38.6,"kL",69.9,0.2,0.5,"",17.3,"VEERG 2026: Table A.4.2.1";"Vessels","Fuel Oil",39.7,"kL",73.6,0.2,0.5,"",18,"VEERG 2026: Table A.4.2.1";"Off-road Agriculture and forestry equipment","Diesel oil",38.6,"kL",69.9,0.3,0.5,"",17.3,"VEERG 2026: Table A.4.2.1"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransport_Data">_xlfn.LAMBDA(
+  _xlfn.MAKEARRAY(26, 10,
+    _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+      INDEX({"Transport type","Fuel combusted","Energy Content Factor(GJ per unit of fuel)","Fuel unit","Scope 1 Emission Factor (kg CO2 - e / GJ) CO2","Scope 1 Emission Factor (kg CO2 - e / GJ) CH4","Scope 1 Emission Factor (kg CO2 - e / GJ) N2O","Scope 1 Emission Factor (kg CO2 - e / GJ) Combined gases","Scope 3 Emission Factor (kg CO2 - e / GJ)","Source";"Cars and light commercial vehicles","Gasoline",34.2,"kl",67.4,0.02,0.2,67.62,17.2,"NGAF 2025: Table 9";"Cars and light commercial vehicles","Diesel oil",38.6,"kl",69.9,0.01,0.5,70.41,17.3,"NGAF 2025: Table 9";"Cars and light commercial vehicles","Liquefied petroleum gas (LPG)",26.2,"kl",60.2,0.5,0.3,61,20.2,"NGAF 2025: Table 9";"Cars and light commercial vehicles","Fuel oil",39.7,"kl",73.6,0.08,0.5,74.18,18,"NGAF 2025: Table 9";"Cars and light commercial vehicles","Ethanol",23.4,"kl",0,0.2,0.2,0.4,"NE","NGAF 2025: Table 9";"Cars and light commercial vehicles","Biodiesel",34.6,"kl",0,0.8,1.7,2.5,"NE","NGAF 2025: Table 9";"Cars and light commercial vehicles","Renewable diesel",38.6,"kl",0,0.01,0.5,0.51,"NE","NGAF 2025: Table 9";"Cars and light commercial vehicles","Other biofuels",23.4,"kl",0,0.8,1.7,2.5,"NE","NGAF 2025: Table 9";"Light duty vehicles","Compressed natural gas",0.0393,"m3",51.4,7.3,0.3,59,18,"NGAF 2025: Table 9";"Light duty vehicles","Liquefied natural gas",25.3,"kl",51.4,7.3,0.3,59,18,"NGAF 2025: Table 9";"Heavy duty vehicles","Compressed natural gas",0.0393,"m3",51.4,2.8,0.3,54.5,18,"NGAF 2025: Table 9";"Heavy duty vehicles","Liquefied natural gas",25.3,"kl",51.4,2.8,0.3,54.5,18,"NGAF 2025: Table 9";"Heavy duty vehicles","Diesel oil - Euro iv or higher",38.6,"kl",69.9,0.07,0.4,70.37,17.3,"NGAF 2025: Table 9";"Heavy duty vehicles","Diesel oil - Euro iii",38.6,"kl",69.9,0.1,0.4,70.4,17.3,"NGAF 2025: Table 9";"Heavy duty vehicles","Diesel oil - Euro i",38.6,"kl",69.9,0.2,0.4,70.5,17.3,"NGAF 2025: Table 9";"Heavy duty vehicles","Renewable diesel – Euro iv or higher",38.6,"kl",0,0.07,0.4,0.47,"NE","NGAF 2025: Table 9";"Heavy duty vehicles","Renewable diesel – Euro iii",38.6,"kl",0,0.1,0.4,0.5,"NE","NGAF 2025: Table 9";"Heavy duty vehicles","Renewable diesel – Euro i",38.6,"kl",0,0.2,0.4,0.6,"NE","NGAF 2025: Table 9";"Aviation","Gasoline for use as fuel in an aircraft",33.1,"kl",67,0.06,0.6,67.66,18,"NGAF 2025: Table 9";"Aviation","Kerosene for use as fuel in an aircraft",36.8,"kl",69.6,0.01,0.6,70.21,18,"NGAF 2025: Table 9";"Aviation","Renewable aviation kerosene",36.8,"kl",0,0.01,0.6,0.61,"NE","NGAF 2025: Table 9";"Vessels","Gasoline",34.2,"kL",67.4,10.1,0.3,"",17.2,"VEERG 2026: Table A.4.2.1";"Vessels","Diesel oil",38.6,"kL",69.9,0.2,0.5,"",17.3,"VEERG 2026: Table A.4.2.1";"Vessels","Fuel Oil",39.7,"kL",73.6,0.2,0.5,"",18,"VEERG 2026: Table A.4.2.1";"Off-road Agriculture and forestry equipment","Diesel oil",38.6,"kL",69.9,0.3,0.5,"",17.3,"VEERG 2026: Table A.4.2.1"}, _xlpm.r, _xlpm.c)
+)))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransport_Description">_xlfn.LAMBDA(("Direct (scope 1) and indirect (scope 3) emission factors for the consumption of transport fuels in different transport equipment"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransport_Source">_xlfn.LAMBDA(("Australian National Greenhouse Accounts Factors 2025 - Table 9"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransport_Title">_xlfn.LAMBDA(("Fuel scope 1 and 3 emission factors - Transport"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransport_Variation">_xlfn.LAMBDA("VARIATION OF SOURCE DATA: 'NE' values returned as zero for calculations.")</definedName>
-    <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransportOffRoad_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 7, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Transport type t","Fuel type q","ECTrans,q (GJ/kL)","Scope 1 CO2 EFTran,1,tqg (kg CO2-e/GJ)","Scope 1 CH4 EFTran,1,tgg (kg CO2-e/GJ)","Scope 1 N2O EFTran,1,tgg (kg CO2-e/GJ)","Scope 3 EFTrans,3,q (kg CO2-e/GJ)";"Vessel","Petrol",34.2,67.4,10.1,0.3,17.2;"Vessel","Diesel",38.6,69.9,0.2,0.5,17.3;"Vessel","Fuel Oil",39.7,73.6,0.2,0.5,18;"Off-road Agriculture and forestry equipment","Diesel",38.6,69.9,0.3,0.5,17.3}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransportOffRoad_Data">_xlfn.LAMBDA(
+  _xlfn.MAKEARRAY(5, 7,
+    _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+      INDEX({"Transport type t","Fuel type q","ECTrans,q (GJ/kL)","Scope 1 CO2 EFTran,1,tqg (kg CO2-e/GJ)","Scope 1 CH4 EFTran,1,tgg (kg CO2-e/GJ)","Scope 1 N2O EFTran,1,tgg (kg CO2-e/GJ)","Scope 3 EFTrans,3,q (kg CO2-e/GJ)";"Vessel","Petrol",34.2,67.4,10.1,0.3,17.2;"Vessel","Diesel",38.6,69.9,0.2,0.5,17.3;"Vessel","Fuel Oil",39.7,73.6,0.2,0.5,18;"Off-road Agriculture and forestry equipment","Diesel",38.6,69.9,0.3,0.5,17.3}, _xlpm.r, _xlpm.c)
+)))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransportOffRoad_Description">_xlfn.LAMBDA(("Direct (scope 1) and indirect (scope 3) emission factors for the consumption of fuels in off-road equipment and vessels"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransportOffRoad_Source">_xlfn.LAMBDA(("VEERG 2026: Table A.4.2.1"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransportOffRoad_Title">_xlfn.LAMBDA(("Fuel scope 1 and 3 emission factors - Off-road equipment and vessels"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope3EmissionFactorsStationaryGaseous_Appendices">_xlfn.LAMBDA(_xlfn.MAKEARRAY(12, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"-","As Scope 3 factors are calculated at the point where natural gas is delivered to end users, it is necessary to calculate consumption at each of the load centres.";"","Gas reaches end users either from the metro distribution networks or direct from the high - pressure distribution pipelines.";"","Households and commercial users tend to be served by the former, and electricity generators and large industrial plants from the latter.";"-","Metro is defined as located on or east of the dividing range in NSW, including Canberra and Queanbeyan, Melbourne, Brisbane, Adelaide or Perth.";"","Otherwise, the non - metro factor should be used.";"-","Factors are calculated for all natural gas distributed in a pipeline which may include coal seam methane.";"-","Table 6 is not applicable to ethane. See Table 7 Indirect (Scope 3) emissions from the consumption of ethane.";"-","C = Confidential. Scope 3 emission factors for Tasmania and the Northern Territory are not available due to confidentiality constraints that arise";"","from the use of a limited number of NGER data inputs. It is suggested that for Tasmania the use of the Victorian emission factors is appropriate,";"","while for Northern Territory the use of the Western Australian emission factors is appropriate.";"-","Scope 3 emission factors do not include fugitive emission leakage from low pressure natural gas distribution pipeline networks while those from high pressure";"","gas networks are considered negligible."}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Fuel_SourceData.Fuel_Scope3EmissionFactorsStationaryGaseous_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State or territory","Scope 3 Emission Factors for Natural Gas (kg CO2 - e / GJ) Metro","Scope 3 Emission Factors for Natural Gas (kg CO2 - e / GJ) Non - Metro";"New South Wales",13.1,14;"ACT",13.1,14;"Victoria",4,4;"Queensland",8.8,7.9;"South Australia",10.7,10.6;"Western Australia",4.1,4;"Tasmania",4,4;"Northern Territory",4.1,4}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Fuel_SourceData.Fuel_Scope3EmissionFactorsStationaryGaseous_Data">_xlfn.LAMBDA(
+  _xlfn.MAKEARRAY(9, 3,
+    _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+      INDEX({"State or territory","Scope 3 Emission Factors for Natural Gas (kg CO2 - e / GJ) Metro","Scope 3 Emission Factors for Natural Gas (kg CO2 - e / GJ) Non - Metro";"New South Wales",13.1,14;"ACT",13.1,14;"Victoria",4,4;"Queensland",8.8,7.9;"South Australia",10.7,10.6;"Western Australia",4.1,4;"Tasmania",4,4;"Northern Territory",4.1,4}, _xlpm.r, _xlpm.c)
+)))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope3EmissionFactorsStationaryGaseous_Description">_xlfn.LAMBDA(("Indirect (Scope 3) emission factors for the consumption of natural gas."))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope3EmissionFactorsStationaryGaseous_Source">_xlfn.LAMBDA(("Australian National Greenhouse Accounts Factors 2025 - Table 6"))</definedName>
     <definedName name="Fuel_SourceData.Fuel_Scope3EmissionFactorsStationaryGaseous_Title">_xlfn.LAMBDA(("Fuel scope 3 emission factors - Stationary gaseous fuels"))</definedName>
@@ -349,7 +397,13 @@
     <definedName name="Scope3_Equations.VEERG_15_11_1_1__3_UpstreamStationaryFuelEmissions_Variable">_xlfn.LAMBDA("E_WTTSCq")</definedName>
     <definedName name="Scope3_Equations.VEERG_15_11_1_1__3_UpstreamStationaryFuelEmissions_Variation">_xlfn.LAMBDA("VARIATION ON SOURCE: Added 'state' and 'metro/non-metro' arguments as gaseous scope 3 EFs are state and metro/non-metro location-based.")</definedName>
     <definedName name="Scope3_Equations.VEERG_15_12_1_1__1_UpstreamPurchasedElectricityLocationBased">_xlfn.LAMBDA(_xlpm.Q_elec,_xlpm.EF_3elec, (_xlpm.Q_elec * _xlpm.EF_3elec) * 10 ^ -3)</definedName>
-    <definedName name="Scope3_Equations.VEERG_15_12_1_1__1_UpstreamPurchasedElectricityLocationBased_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Q_elec","amount of electricity purchased from the grid","kWh","Input";"EF_3elec","scope 3 emission factor for purchased electricity","kg CO2e/kWh","Constant"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Scope3_Equations.VEERG_15_12_1_1__1_UpstreamPurchasedElectricityLocationBased_Arguments">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(3, 4,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Q_elec","amount of electricity purchased from the grid","kWh","Input";"EF_3elec","scope 3 emission factor for purchased electricity","kg CO2e/kWh","Constant";"g","grid electricity was purchased from","","Input"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
     <definedName name="Scope3_Equations.VEERG_15_12_1_1__1_UpstreamPurchasedElectricityLocationBased_LatexEquation">_xlfn.LAMBDA("E_{3,elec}=Q_{elec}\times EF_{3,elec}\times 10^{-3}")</definedName>
     <definedName name="Scope3_Equations.VEERG_15_12_1_1__1_UpstreamPurchasedElectricityLocationBased_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Scope3_Equations.VEERG_15_12_1_1__1_UpstreamPurchasedElectricityLocationBased_Source">_xlfn.LAMBDA("VEERG 2026: 15.12.1.1, Equation (1)")</definedName>
@@ -357,13 +411,24 @@
     <definedName name="Scope3_Equations.VEERG_15_12_1_1__1_UpstreamPurchasedElectricityLocationBased_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Scope3_Equations.VEERG_15_12_1_1__1_UpstreamPurchasedElectricityLocationBased_Variable">_xlfn.LAMBDA("E_3elec")</definedName>
     <definedName name="Scope3_Equations.VEERG_15_12_1_2__1_UpstreamPurchasedElectricityMarketBased">_xlfn.LAMBDA(_xlpm.Q_elec,_xlpm.RPP,_xlpm.JRPP,_xlpm.REC_surrendered,_xlpm.REC_onsite,_xlpm.EF_RMF3elec, ((_xlpm.Q_elec * (1 - (_xlpm.RPP + _xlpm.JRPP))) - ((_xlpm.REC_surrendered - _xlpm.REC_onsite) * 10 ^ -3)) * _xlpm.EF_RMF3elec * 10 ^ -3)</definedName>
-    <definedName name="Scope3_Equations.VEERG_15_12_1_2__1_UpstreamPurchasedElectricityMarketBased_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Q_elec","amount of electricity purchased from the grid","kWh","Input";"RPP","renewable power percentage under LRET for the applicable period","fraction","Input";"JRPP","jurisdictional renewable power percentage for the applicable period","fraction","Input";"REC_surrendered","eligible renewable energy certificates voluntarily surrendered","MWh","Input";"REC_onsite","eligible renewable energy certificates issued for onsite generated electricity","MWh","Input";"EF_RMF3elec","scope 3 residual mix emission factor for electricity","kg CO2e/kWh","Constant"}, _xlpm.r, _xlpm.c))))</definedName>
-    <definedName name="Scope3_Equations.VEERG_15_12_1_2__1_UpstreamPurchasedElectricityMarketBased_LatexEquation">_xlfn.LAMBDA("E_{3,elec}=\left[Q_{elec}\times\left(1-(RPP+JRPP)\right)-\left(REC_{surrendered}-REC_{onsite}\right)\times 10^{-3}\right]\times EF_{RMF3,elec}\times 10^{-3}")</definedName>
+    <definedName name="Scope3_Equations.VEERG_15_12_1_2__1_UpstreamPurchasedElectricityMarketBased_Arguments">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(7, 4,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Q_elec","amount of electricity purchased from the grid","kWh","Input";"RPP","renewable power percentage under LRET for the applicable period","fraction","Input";"JRPP","jurisdictional renewable power percentage for the applicable period","fraction","Input";"REC_surrendered","eligible renewable energy certificates voluntarily surrendered","MWh","Input";"REC_onsite","eligible renewable energy certificates issued for onsite generated electricity","MWh","Input";"EF_RMF3elec","scope 3 residual mix emission factor for electricity","kg CO2e/kWh","Constant";"i","state","","Input"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
+    <definedName name="Scope3_Equations.VEERG_15_12_1_2__1_UpstreamPurchasedElectricityMarketBased_LatexEquation">_xlfn.LAMBDA("E_{3,elec}= [ Q_{elec}\times\left(1-(RPP+JRPP)\right)-\left\left((REC_{surrendered}-REC_{onsite}\right)\times 10^{-3}\right)\right]\times EF_{RMF3,elec}\times 10^{-3}")</definedName>
+    <definedName name="Scope3_Equations.VEERG_15_12_1_2__1_UpstreamPurchasedElectricityMarketBased_LatexEquationVariation">_xlfn.LAMBDA("E_{3,elec}= [ Q_{elec}\times\left(1-(RPP+JRPP)\right)-\left\left((REC_{surrendered}-REC_{onsite}\right)\times 10^{3}\right)\right]\times EF_{RMF3,elec}\times 10^{-3}")</definedName>
     <definedName name="Scope3_Equations.VEERG_15_12_1_2__1_UpstreamPurchasedElectricityMarketBased_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Scope3_Equations.VEERG_15_12_1_2__1_UpstreamPurchasedElectricityMarketBased_Source">_xlfn.LAMBDA("VEERG 2026: 15.12.1.2, Equation (1)")</definedName>
     <definedName name="Scope3_Equations.VEERG_15_12_1_2__1_UpstreamPurchasedElectricityMarketBased_Title">_xlfn.LAMBDA("Scope 3 emissions from purchased electricity market based")</definedName>
     <definedName name="Scope3_Equations.VEERG_15_12_1_2__1_UpstreamPurchasedElectricityMarketBased_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Scope3_Equations.VEERG_15_12_1_2__1_UpstreamPurchasedElectricityMarketBased_Variable">_xlfn.LAMBDA("E_3elec")</definedName>
+    <definedName name="Scope3_Equations.VEERG_15_12_1_2__1_UpstreamPurchasedElectricityMarketBased_Variation">_xlfn.LAMBDA("VARIATION ON SOURCE: In order to convert megawatt hours to kilowatt hours, the REC_surrendered and REC_onsite variables are multiplied by 10^3 instead of 10^-3.")</definedName>
+    <definedName name="Scope3_Equations.VEERG_15_12_1_2__1_UpstreamPurchasedElectricityMarketBasedVariation">_xlfn.LAMBDA(_xlpm.Q_elec,_xlpm.RPP,_xlpm.JRPP,_xlpm.REC_surrendered,_xlpm.REC_onsite,_xlpm.EF_RMF3elec,
+    ((_xlpm.Q_elec * (1 - (_xlpm.RPP + _xlpm.JRPP))) - ((_xlpm.REC_surrendered - _xlpm.REC_onsite) * 10 ^ 3)) * _xlpm.EF_RMF3elec * 10 ^ -3
+  )</definedName>
     <definedName name="Scope3_Equations.VEERG_15_13_1_1__1_EmissionsFromManureSentOffSite">_xlfn.LAMBDA(_xlpm.E_N2O,_xlpm.E_ad,_xlpm.E_leach, _xlpm.E_N2O + _xlpm.E_ad + _xlpm.E_leach)</definedName>
     <definedName name="Scope3_Equations.VEERG_15_13_1_1__1_EmissionsFromManureSentOffSite_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"E_N2O","direct nitrous oxide emissions from application of manure to soils outside of scope 1 boundary","t N2O","Calculated";"E_ad","nitrous oxide emissions from atmospheric deposition of manure to soils","t N2O","Calculated";"E_leach","nitrous oxide emissions from nitrogen leaching and runoff of manure to soils","t N2O","Calculated"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Scope3_Equations.VEERG_15_13_1_1__1_EmissionsFromManureSentOffSite_LatexEquation">_xlfn.LAMBDA("E=E_{N2O}+E_{ad}+E_{leach}")</definedName>
@@ -372,6 +437,16 @@
     <definedName name="Scope3_Equations.VEERG_15_13_1_1__1_EmissionsFromManureSentOffSite_Title">_xlfn.LAMBDA("Emissions from manure sent off site applied to soils in another farming system or enterprise")</definedName>
     <definedName name="Scope3_Equations.VEERG_15_13_1_1__1_EmissionsFromManureSentOffSite_Unit">_xlfn.LAMBDA("t N2O")</definedName>
     <definedName name="Scope3_Equations.VEERG_15_13_1_1__1_EmissionsFromManureSentOffSite_Variable">_xlfn.LAMBDA("E")</definedName>
+    <definedName name="Scope3_Equations.VEERG_15_13_1_3__1_EmissionsFromSolidWasteTreatmentFacility">_xlfn.LAMBDA(_xlpm.E_N2O,_xlpm.E_ad,_xlpm.E_leach,
+    _xlpm.E_N2O + _xlpm.E_ad + _xlpm.E_leach
+  )</definedName>
+    <definedName name="Scope3_Equations.VEERG_15_13_1_3__1_EmissionsFromSolidWasteTreatmentFacility_Arguments">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Scope3_Equations.VEERG_15_13_1_3__1_EmissionsFromSolidWasteTreatmentFacility_LatexEquation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Scope3_Equations.VEERG_15_13_1_3__1_EmissionsFromSolidWasteTreatmentFacility_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Scope3_Equations.VEERG_15_13_1_3__1_EmissionsFromSolidWasteTreatmentFacility_Source">_xlfn.LAMBDA("VEERG 2026: 15.13.1.3")</definedName>
+    <definedName name="Scope3_Equations.VEERG_15_13_1_3__1_EmissionsFromSolidWasteTreatmentFacility_Title">_xlfn.LAMBDA("Emissions from solid waste sent to a treatment facility")</definedName>
+    <definedName name="Scope3_Equations.VEERG_15_13_1_3__1_EmissionsFromSolidWasteTreatmentFacility_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
+    <definedName name="Scope3_Equations.VEERG_15_13_1_3__1_EmissionsFromSolidWasteTreatmentFacility_Variable">_xlfn.LAMBDA("E")</definedName>
     <definedName name="Scope3_Equations.VEERG_15_14_1_1__1_EmbeddedEmissionsFromUpstreamFreight">_xlfn.LAMBDA(_xlpm.W_f,_xlpm.D_f,_xlpm.EF_f, (_xlpm.W_f * _xlpm.D_f) * _xlpm.EF_f)</definedName>
     <definedName name="Scope3_Equations.VEERG_15_14_1_1__1_EmbeddedEmissionsFromUpstreamFreight_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"W_f","total mass of goods transported per freight type f","t","Input";"D_f","total distance transported per freight type f","km","Input";"EF_f","emission factor for freight type f","t CO2e/(t km)","Constant";"f","freight type","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Scope3_Equations.VEERG_15_14_1_1__1_EmbeddedEmissionsFromUpstreamFreight_LatexEquation">_xlfn.LAMBDA("E=\sum\nolimits_f\left((W_f\times D_f)\times EF_f\right)")</definedName>
@@ -2985,870 +3060,6 @@
   <dxfs count="123">
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FFC44340"/>
       </font>
       <fill>
@@ -5153,6 +4364,870 @@
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -8506,26 +8581,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Home"/>
-      <sheetName val="Constants - Common"/>
-      <sheetName val="Acknowledgements"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -8591,7 +8646,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6E44059A-C219-4316-A7A0-AD77B0121F06}" name="Table_Input_Fuel" displayName="Table_Input_Fuel" ref="D16:J21" totalsRowDxfId="110" headerRowCellStyle="Input table column header">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6E44059A-C219-4316-A7A0-AD77B0121F06}" name="Table_Input_Fuel" displayName="Table_Input_Fuel" ref="D16:J21" totalsRowDxfId="74" headerRowCellStyle="Input table column header">
   <autoFilter ref="D16:J21" xr:uid="{6E44059A-C219-4316-A7A0-AD77B0121F06}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -8602,20 +8657,20 @@
     <filterColumn colId="6" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="7">
-    <tableColumn id="2" xr3:uid="{9540E705-999C-466B-A6B4-24C60E9153AE}" name="Fuel use (select)" totalsRowFunction="average" totalsRowDxfId="109" dataCellStyle="Input select" totalsRowCellStyle="Input select"/>
-    <tableColumn id="3" xr3:uid="{30909C53-73F3-46FE-93B7-F60E126CD84F}" name="Fuel type (select)" totalsRowDxfId="108" dataCellStyle="Input select" totalsRowCellStyle="Input select"/>
-    <tableColumn id="4" xr3:uid="{9DFFE0DC-C289-47FB-8F0C-2D2F480EEE4C}" name="Amount purchased" totalsRowDxfId="107" totalsRowCellStyle="Content bold"/>
-    <tableColumn id="6" xr3:uid="{29AE264C-132E-48F6-8BA3-262EAF9E4687}" name="Amount unit" totalsRowDxfId="106" dataCellStyle="Input number general calculated" totalsRowCellStyle="Input text calculated">
+    <tableColumn id="2" xr3:uid="{9540E705-999C-466B-A6B4-24C60E9153AE}" name="Fuel use (select)" totalsRowFunction="average" totalsRowDxfId="73" dataCellStyle="Input select" totalsRowCellStyle="Input select"/>
+    <tableColumn id="3" xr3:uid="{30909C53-73F3-46FE-93B7-F60E126CD84F}" name="Fuel type (select)" totalsRowDxfId="72" dataCellStyle="Input select" totalsRowCellStyle="Input select"/>
+    <tableColumn id="4" xr3:uid="{9DFFE0DC-C289-47FB-8F0C-2D2F480EEE4C}" name="Amount purchased" totalsRowDxfId="71" totalsRowCellStyle="Content bold"/>
+    <tableColumn id="6" xr3:uid="{29AE264C-132E-48F6-8BA3-262EAF9E4687}" name="Amount unit" totalsRowDxfId="70" dataCellStyle="Input number general calculated" totalsRowCellStyle="Input text calculated">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_LookupValueInTable(Table_Input_Fuel[[#This Row],[Fuel type (select)]],Table_FuelTypes_Units[Fuel type], Table_FuelTypes_Units[Input Unit])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B9F0EEB0-BF4E-4AB9-8B4B-25BBC232DE33}" name="Percent consumed" totalsRowDxfId="105" totalsRowCellStyle="Input percent">
+    <tableColumn id="5" xr3:uid="{B9F0EEB0-BF4E-4AB9-8B4B-25BBC232DE33}" name="Percent consumed" totalsRowDxfId="69" totalsRowCellStyle="Input percent">
       <calculatedColumnFormula>1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{AE1D2D8C-400E-46F5-850E-2BBEDF1657F8}" name="Amount consumed" totalsRowFunction="custom" totalsRowDxfId="104" dataCellStyle="Input number general calculated" totalsRowCellStyle="Input number 3 decimal places calculated">
+    <tableColumn id="1" xr3:uid="{AE1D2D8C-400E-46F5-850E-2BBEDF1657F8}" name="Amount consumed" totalsRowFunction="custom" totalsRowDxfId="68" dataCellStyle="Input number general calculated" totalsRowCellStyle="Input number 3 decimal places calculated">
       <calculatedColumnFormula>Table_Input_Fuel[[#This Row],[Amount purchased]]*Table_Input_Fuel[[#This Row],[Percent consumed]]*IF(Table_Input_Fuel[[#This Row],[Amount unit]]="L", 10^-3, 1)</calculatedColumnFormula>
       <totalsRowFormula>SUM(Table_Input_Fuel[Amount consumed])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{8CCEBD2E-3C11-4ACD-ABE1-916844C8F176}" name="Amount consumed unit" totalsRowDxfId="103" dataCellStyle="Input number general calculated"/>
+    <tableColumn id="7" xr3:uid="{8CCEBD2E-3C11-4ACD-ABE1-916844C8F176}" name="Amount consumed unit" totalsRowDxfId="67" dataCellStyle="Input number general calculated"/>
   </tableColumns>
   <tableStyleInfo name="Editable table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8707,49 +8762,49 @@
     <tableColumn id="1" xr3:uid="{C78F8194-D8E0-4358-AAAB-CFDE15DA2830}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6540D119-9CF8-4773-A1D3-00A95BCEEFC6}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{6540D119-9CF8-4773-A1D3-00A95BCEEFC6}" name="MAT" totalsRowDxfId="110" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{035C56C1-0FF6-44D8-A550-5AF0FECECED4}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{035C56C1-0FF6-44D8-A550-5AF0FECECED4}" name="MAP" totalsRowDxfId="109" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2AF470BF-BA3F-40BA-A6DC-376287F94DCF}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{2AF470BF-BA3F-40BA-A6DC-376287F94DCF}" name="Frost days per year" totalsRowDxfId="108" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{E99F3396-0330-4A28-B57F-DF312D0D0497}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{E99F3396-0330-4A28-B57F-DF312D0D0497}" name="Elevation" totalsRowDxfId="107" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A1126D28-8E8B-4BB5-8C2E-7127098DC658}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{A1126D28-8E8B-4BB5-8C2E-7127098DC658}" name="MAP:PET" totalsRowDxfId="106" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{9C2AC696-E3EA-4A68-A018-B66AF6BCDA71}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{9C2AC696-E3EA-4A68-A018-B66AF6BCDA71}" name="Min temp" totalsRowDxfId="105" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{F0FAC75B-E63F-4DAF-9638-A1D40557051A}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{F0FAC75B-E63F-4DAF-9638-A1D40557051A}" name="Max temp" totalsRowDxfId="104" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{4B31D27C-83B1-479E-8DB4-FA9967D168AC}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{4B31D27C-83B1-479E-8DB4-FA9967D168AC}" name="Min rainfall" totalsRowDxfId="103" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1E53C538-1298-4998-AC9F-CF29D2B879E4}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{1E53C538-1298-4998-AC9F-CF29D2B879E4}" name="Max rainfall" totalsRowDxfId="102" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{D9C5E60C-87C4-4C58-88FF-7F1D633F4FBF}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{D9C5E60C-87C4-4C58-88FF-7F1D633F4FBF}" name="Min frost days" totalsRowDxfId="101" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{E913C3BC-11C3-41BB-8A41-601D48A87967}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{E913C3BC-11C3-41BB-8A41-601D48A87967}" name="Max frost days" totalsRowDxfId="100" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{653ECD84-22B5-4903-827B-426ED610F7BC}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{653ECD84-22B5-4903-827B-426ED610F7BC}" name="Min elevation" totalsRowDxfId="99" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{DB8939AF-4796-41B4-972A-57E9E15F2954}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{DB8939AF-4796-41B4-972A-57E9E15F2954}" name="Max elevation" totalsRowDxfId="98" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{C871C030-55AB-4FED-9ABC-809675D2BFA5}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{C871C030-55AB-4FED-9ABC-809675D2BFA5}" name="Min MAP:PET" totalsRowDxfId="97" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{68B0EA52-1CC8-4E54-B687-5EFC4BE5BEAC}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{68B0EA52-1CC8-4E54-B687-5EFC4BE5BEAC}" name="Max MAP:PET" totalsRowDxfId="96" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8767,7 +8822,7 @@
     <tableColumn id="1" xr3:uid="{4A88C6C5-17A7-4838-B5B0-EB1B3250A4F5}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A9A5DBDE-C3E0-473B-9FD2-4115217386E7}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{A9A5DBDE-C3E0-473B-9FD2-4115217386E7}" name="Wet or Dry Zone" totalsRowDxfId="95" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8873,7 +8928,7 @@
     <tableColumn id="1" xr3:uid="{1988E8FD-007C-4BE8-804F-D03930E45B7A}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8A562D65-BBA8-4D78-A46A-5AC2978F0BD9}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{8A562D65-BBA8-4D78-A46A-5AC2978F0BD9}" name="FracWET" dataDxfId="94">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8882,7 +8937,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{2781308E-D97C-445B-A805-DE74F822CC4F}" name="Table_Fuel_EFs_StationaryLiquid" displayName="Table_Fuel_EFs_StationaryLiquid" ref="D53:K77" totalsRowShown="0" headerRowDxfId="102" dataDxfId="101">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{2781308E-D97C-445B-A805-DE74F822CC4F}" name="Table_Fuel_EFs_StationaryLiquid" displayName="Table_Fuel_EFs_StationaryLiquid" ref="D53:K77" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
   <autoFilter ref="D53:K77" xr:uid="{2781308E-D97C-445B-A805-DE74F822CC4F}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -8894,28 +8949,28 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{116B9F07-FAFA-45B6-8BAF-D037C420E4F7}" name="Fuel combusted" dataDxfId="100">
+    <tableColumn id="1" xr3:uid="{116B9F07-FAFA-45B6-8BAF-D037C420E4F7}" name="Fuel combusted" dataDxfId="64">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsStationaryLiquid_Data(), Table_Fuel_EFs_StationaryLiquid[[#Headers],[Fuel combusted]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A9A16324-59CF-4AFF-A845-5DBEFF96AF36}" name="Energy Content Factor (GJ per unit of fuel)" dataDxfId="99">
+    <tableColumn id="2" xr3:uid="{A9A16324-59CF-4AFF-A845-5DBEFF96AF36}" name="Energy Content Factor (GJ per unit of fuel)" dataDxfId="63">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsStationaryLiquid_Data(), Table_Fuel_EFs_StationaryLiquid[[#Headers],[Fuel combusted]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{D90C1066-FE05-40B0-93E8-B444B2515AC4}" name="Fuel unit" dataDxfId="98">
+    <tableColumn id="3" xr3:uid="{D90C1066-FE05-40B0-93E8-B444B2515AC4}" name="Fuel unit" dataDxfId="62">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsStationaryLiquid_Data(), Table_Fuel_EFs_StationaryLiquid[[#Headers],[Fuel combusted]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{6C9BACBD-72E6-4C6C-8E91-9FC2EE427A52}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) CO2" dataDxfId="97">
+    <tableColumn id="4" xr3:uid="{6C9BACBD-72E6-4C6C-8E91-9FC2EE427A52}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) CO2" dataDxfId="61">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsStationaryLiquid_Data(), Table_Fuel_EFs_StationaryLiquid[[#Headers],[Fuel combusted]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9C1D1D67-0EE2-4865-BD1D-E11FDD50B838}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) CH4" dataDxfId="96">
+    <tableColumn id="5" xr3:uid="{9C1D1D67-0EE2-4865-BD1D-E11FDD50B838}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) CH4" dataDxfId="60">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsStationaryLiquid_Data(), Table_Fuel_EFs_StationaryLiquid[[#Headers],[Fuel combusted]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{422B50D3-73D6-4895-B780-E80D65DEA437}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) N2O" dataDxfId="95">
+    <tableColumn id="6" xr3:uid="{422B50D3-73D6-4895-B780-E80D65DEA437}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) N2O" dataDxfId="59">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsStationaryLiquid_Data(), Table_Fuel_EFs_StationaryLiquid[[#Headers],[Fuel combusted]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3D29A47C-AFAA-45B9-B05D-9137798FA43D}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) Combined gases" dataDxfId="94">
+    <tableColumn id="7" xr3:uid="{3D29A47C-AFAA-45B9-B05D-9137798FA43D}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) Combined gases" dataDxfId="58">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsStationaryLiquid_Data(), Table_Fuel_EFs_StationaryLiquid[[#Headers],[Fuel combusted]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BA6033AB-70D7-4E8F-B8F8-2A659A19966B}" name="Scope 3 Emission Factor (kg CO2 - e / GJ)" dataDxfId="93">
+    <tableColumn id="8" xr3:uid="{BA6033AB-70D7-4E8F-B8F8-2A659A19966B}" name="Scope 3 Emission Factor (kg CO2 - e / GJ)" dataDxfId="57">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsStationaryLiquid_Data(), Table_Fuel_EFs_StationaryLiquid[[#Headers],[Fuel combusted]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8963,7 +9018,7 @@
     <tableColumn id="1" xr3:uid="{9881D3F5-1850-44AD-8E5E-FCA2AC1D7F5A}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3BEAAAC6-15D8-4D5F-B8DB-D72567307C5E}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3BEAAAC6-15D8-4D5F-B8DB-D72567307C5E}" name="FracWET" dataDxfId="93" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8981,7 +9036,7 @@
     <tableColumn id="1" xr3:uid="{DDBD77C6-F919-4BF7-9106-DA20B1D61C0B}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{40E70A92-35B2-440E-9AC6-25E169CA44EE}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{40E70A92-35B2-440E-9AC6-25E169CA44EE}" name="EFPRP" dataDxfId="92" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8999,7 +9054,7 @@
     <tableColumn id="1" xr3:uid="{0C35E1C0-7F9F-4F71-BC37-DC61EDF8F937}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{17DF294E-0CF9-438E-811D-D36199C9AE41}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{17DF294E-0CF9-438E-811D-D36199C9AE41}" name="Season" dataDxfId="91" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9031,49 +9086,49 @@
     <tableColumn id="1" xr3:uid="{7FC29B47-0963-44AE-B7E8-54A4D73A5BA5}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C649891D-46B1-4E70-ADC4-05C47735D6DC}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{C649891D-46B1-4E70-ADC4-05C47735D6DC}" name="MAT (ºC)" dataDxfId="90" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{3F48A9A1-50F5-4A4D-AABE-6BBB6F932D4C}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{3F48A9A1-50F5-4A4D-AABE-6BBB6F932D4C}" name="Anaerobic lagoon" dataDxfId="89" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{7352FB9C-49F9-40DD-B3AA-E928E5AC76E5}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{7352FB9C-49F9-40DD-B3AA-E928E5AC76E5}" name="Digester / covered lagoons" dataDxfId="88" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{58017179-0F35-4111-A2DC-7D7982C315AC}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{58017179-0F35-4111-A2DC-7D7982C315AC}" name="Liquid systems" dataDxfId="87" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{FEEE0F4A-9361-43F2-826D-475E9E176DFA}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{FEEE0F4A-9361-43F2-826D-475E9E176DFA}" name="Daily spread" dataDxfId="86" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3384DD87-D1BF-4A22-9844-2086E79A17DE}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{3384DD87-D1BF-4A22-9844-2086E79A17DE}" name="Composting (passive windrow)" dataDxfId="85" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{72B5BD59-9406-47DC-9503-A507B020082A}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{72B5BD59-9406-47DC-9503-A507B020082A}" name="Solid storage" dataDxfId="84" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{FE117AA4-33AF-48EF-AB0D-C3B4F72961C6}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{FE117AA4-33AF-48EF-AB0D-C3B4F72961C6}" name="Pit storage" dataDxfId="83" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FF6D7DE9-BFAA-4319-8BD4-E4A6E0A5354E}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{FF6D7DE9-BFAA-4319-8BD4-E4A6E0A5354E}" name="Deep litter" dataDxfId="82" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{D174D439-910D-48E0-86AC-A6C85CEDCEF7}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{D174D439-910D-48E0-86AC-A6C85CEDCEF7}" name="Poultry manure with bedding" dataDxfId="81" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{486C4209-6CE6-42FF-A27F-4F6BDB1A604F}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{486C4209-6CE6-42FF-A27F-4F6BDB1A604F}" name="Poultry manure without bedding" dataDxfId="80" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{B98FB885-1916-4941-8960-D2EDA80AD661}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{B98FB885-1916-4941-8960-D2EDA80AD661}" name="Direct processing" dataDxfId="79" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{CE9D2EF3-9068-4A77-958D-0A85412561DB}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{CE9D2EF3-9068-4A77-958D-0A85412561DB}" name="Direct application" dataDxfId="78" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{E7BC93A0-2828-4A16-AD56-D7204C45D58C}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{E7BC93A0-2828-4A16-AD56-D7204C45D58C}" name="Pasture range and paddock" dataDxfId="77" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{5149957B-287C-4AFA-A670-B58C52A93A50}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{5149957B-287C-4AFA-A670-B58C52A93A50}" name="MAT raw" dataDxfId="76" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9091,7 +9146,7 @@
     <tableColumn id="1" xr3:uid="{E5BBE035-4502-4C10-9BD7-499199339B37}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6CA725B0-E06F-428E-9CA0-1BC6567FA0A8}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{6CA725B0-E06F-428E-9CA0-1BC6567FA0A8}" name="EFNi &amp; EFN2Oi" dataDxfId="75" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9100,7 +9155,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{52589EE1-5F69-4B49-BF30-7629445C4436}" name="Table_Fuel_EFs_Transport" displayName="Table_Fuel_EFs_Transport" ref="D9:L34" totalsRowShown="0" headerRowDxfId="92" dataDxfId="91">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{52589EE1-5F69-4B49-BF30-7629445C4436}" name="Table_Fuel_EFs_Transport" displayName="Table_Fuel_EFs_Transport" ref="D9:L34" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
   <autoFilter ref="D9:L34" xr:uid="{52589EE1-5F69-4B49-BF30-7629445C4436}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9113,31 +9168,31 @@
     <filterColumn colId="8" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{8D6C44B0-0762-4110-AC2D-7FEE6A4ACB70}" name="Transport type" dataDxfId="90">
+    <tableColumn id="1" xr3:uid="{8D6C44B0-0762-4110-AC2D-7FEE6A4ACB70}" name="Transport type" dataDxfId="54">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransport_Data(), Table_Fuel_EFs_Transport[[#Headers],[Transport type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3A6969F6-FF37-4AA5-AE1C-FE6AA1A0B2B2}" name="Fuel combusted" dataDxfId="89">
+    <tableColumn id="2" xr3:uid="{3A6969F6-FF37-4AA5-AE1C-FE6AA1A0B2B2}" name="Fuel combusted" dataDxfId="53">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransport_Data(), Table_Fuel_EFs_Transport[[#Headers],[Transport type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{432B61FE-9A6D-43B7-8616-F6CFE6FB153A}" name="Energy Content Factor (GJ per unit of fuel)" dataDxfId="88">
+    <tableColumn id="3" xr3:uid="{432B61FE-9A6D-43B7-8616-F6CFE6FB153A}" name="Energy Content Factor (GJ per unit of fuel)" dataDxfId="52">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransport_Data(), Table_Fuel_EFs_Transport[[#Headers],[Transport type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{71D7F858-6D97-44C6-8413-957075191C0B}" name="Fuel unit" dataDxfId="87">
+    <tableColumn id="4" xr3:uid="{71D7F858-6D97-44C6-8413-957075191C0B}" name="Fuel unit" dataDxfId="51">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransport_Data(), Table_Fuel_EFs_Transport[[#Headers],[Transport type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{C388B4A9-A36E-4EC9-B5CE-2EA624A56083}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) CO2" dataDxfId="86">
+    <tableColumn id="8" xr3:uid="{C388B4A9-A36E-4EC9-B5CE-2EA624A56083}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) CO2" dataDxfId="50">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransport_Data(), Table_Fuel_EFs_Transport[[#Headers],[Transport type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{4E84DFC1-37C7-4930-B71E-DB7CDCBDD458}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) CH4" dataDxfId="85">
+    <tableColumn id="9" xr3:uid="{4E84DFC1-37C7-4930-B71E-DB7CDCBDD458}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) CH4" dataDxfId="49">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransport_Data(), Table_Fuel_EFs_Transport[[#Headers],[Transport type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{BA43FF41-AF40-4D8F-8B75-A6223466550A}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) N2O" dataDxfId="84">
+    <tableColumn id="10" xr3:uid="{BA43FF41-AF40-4D8F-8B75-A6223466550A}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) N2O" dataDxfId="48">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransport_Data(), Table_Fuel_EFs_Transport[[#Headers],[Transport type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{FBCCF4E4-B3CA-463F-B53D-380ECF4BF688}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) Combined gases" dataDxfId="83">
+    <tableColumn id="11" xr3:uid="{FBCCF4E4-B3CA-463F-B53D-380ECF4BF688}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) Combined gases" dataDxfId="47">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransport_Data(), Table_Fuel_EFs_Transport[[#Headers],[Transport type]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{E2A89F98-94A5-4737-A469-DEAA99554138}" name="Scope 3 Emission Factor (kg CO2 - e / GJ)" dataDxfId="82">
+    <tableColumn id="12" xr3:uid="{E2A89F98-94A5-4737-A469-DEAA99554138}" name="Scope 3 Emission Factor (kg CO2 - e / GJ)" dataDxfId="46">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransport_Data(), Table_Fuel_EFs_Transport[[#Headers],[Transport type]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9146,7 +9201,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{5CE27F6B-DBAC-48D7-85B3-77E92E77D6C0}" name="Table_FuelTypesPerUse" displayName="Table_FuelTypesPerUse" ref="D130:I139" totalsRowShown="0" headerRowDxfId="81" dataDxfId="80">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{5CE27F6B-DBAC-48D7-85B3-77E92E77D6C0}" name="Table_FuelTypesPerUse" displayName="Table_FuelTypesPerUse" ref="D130:I139" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44">
   <autoFilter ref="D130:I139" xr:uid="{5CE27F6B-DBAC-48D7-85B3-77E92E77D6C0}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9156,19 +9211,19 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{532D4BA3-A3CE-460F-A250-E2A6690A9C59}" name="Generators" dataDxfId="79"/>
-    <tableColumn id="2" xr3:uid="{6E069153-6950-4C63-9ADE-F4A2F0DF67AF}" name="Power standalone machinery or heating" dataDxfId="78"/>
-    <tableColumn id="3" xr3:uid="{3917BF44-833D-42F1-B3B3-C62FEF76A321}" name="Aviation" dataDxfId="77"/>
-    <tableColumn id="5" xr3:uid="{4F35E2A0-90CD-4AC1-B52F-870485779A73}" name="Cars and light commercial vehicles" dataDxfId="76"/>
-    <tableColumn id="7" xr3:uid="{1651A844-7E2B-435C-A7B4-4B0FFD5577CE}" name="Off-road Agriculture and forestry equipment" dataDxfId="75" dataCellStyle="Content bold"/>
-    <tableColumn id="8" xr3:uid="{FCED622E-3FDD-4E8D-B2D1-E4C99EF7323A}" name="Vessels" dataDxfId="74" dataCellStyle="Content bold"/>
+    <tableColumn id="1" xr3:uid="{532D4BA3-A3CE-460F-A250-E2A6690A9C59}" name="Generators" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{6E069153-6950-4C63-9ADE-F4A2F0DF67AF}" name="Power standalone machinery or heating" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{3917BF44-833D-42F1-B3B3-C62FEF76A321}" name="Aviation" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{4F35E2A0-90CD-4AC1-B52F-870485779A73}" name="Cars and light commercial vehicles" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{1651A844-7E2B-435C-A7B4-4B0FFD5577CE}" name="Off-road Agriculture and forestry equipment" dataDxfId="39" dataCellStyle="Content bold"/>
+    <tableColumn id="8" xr3:uid="{FCED622E-3FDD-4E8D-B2D1-E4C99EF7323A}" name="Vessels" dataDxfId="38" dataCellStyle="Content bold"/>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{2DFA7F9E-607A-4EC9-89A5-ADF4BF63C858}" name="Table_Fuel_EFs_StationaryGaseous" displayName="Table_Fuel_EFs_StationaryGaseous" ref="D86:J104" totalsRowShown="0" headerRowDxfId="73" dataDxfId="72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{2DFA7F9E-607A-4EC9-89A5-ADF4BF63C858}" name="Table_Fuel_EFs_StationaryGaseous" displayName="Table_Fuel_EFs_StationaryGaseous" ref="D86:J104" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36">
   <autoFilter ref="D86:J104" xr:uid="{2DFA7F9E-607A-4EC9-89A5-ADF4BF63C858}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -9179,25 +9234,25 @@
     <filterColumn colId="6" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{576104C6-5F3C-42C2-96A5-3F8A6D95B719}" name="Fuel combusted" dataDxfId="71">
+    <tableColumn id="1" xr3:uid="{576104C6-5F3C-42C2-96A5-3F8A6D95B719}" name="Fuel combusted" dataDxfId="35">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1EmissionFactorsStationaryGaseous_Data(), Table_Fuel_EFs_StationaryGaseous[[#Headers],[Fuel combusted]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{249B0D76-8ABD-4FA7-AE7E-9500D03E43DD}" name="Energy Content Factor (GJ per unit of fuel)" dataDxfId="70">
+    <tableColumn id="2" xr3:uid="{249B0D76-8ABD-4FA7-AE7E-9500D03E43DD}" name="Energy Content Factor (GJ per unit of fuel)" dataDxfId="34">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1EmissionFactorsStationaryGaseous_Data(), Table_Fuel_EFs_StationaryGaseous[[#Headers],[Fuel combusted]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{C67F3A46-C70C-439C-A78F-80B7E5662B6A}" name="Fuel unit" dataDxfId="69">
+    <tableColumn id="3" xr3:uid="{C67F3A46-C70C-439C-A78F-80B7E5662B6A}" name="Fuel unit" dataDxfId="33">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1EmissionFactorsStationaryGaseous_Data(), Table_Fuel_EFs_StationaryGaseous[[#Headers],[Fuel combusted]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B9C45459-33F6-4505-BE9E-03D5C5B7CF41}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) CO2" dataDxfId="68">
+    <tableColumn id="4" xr3:uid="{B9C45459-33F6-4505-BE9E-03D5C5B7CF41}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) CO2" dataDxfId="32">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1EmissionFactorsStationaryGaseous_Data(), Table_Fuel_EFs_StationaryGaseous[[#Headers],[Fuel combusted]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{484A6982-10DC-4FC8-9C4C-E978774599C6}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) CH4" dataDxfId="67">
+    <tableColumn id="5" xr3:uid="{484A6982-10DC-4FC8-9C4C-E978774599C6}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) CH4" dataDxfId="31">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1EmissionFactorsStationaryGaseous_Data(), Table_Fuel_EFs_StationaryGaseous[[#Headers],[Fuel combusted]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{AEE83219-7CD0-494F-84B0-A8CB1BD0A5FA}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) N2O" dataDxfId="66">
+    <tableColumn id="6" xr3:uid="{AEE83219-7CD0-494F-84B0-A8CB1BD0A5FA}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) N2O" dataDxfId="30">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1EmissionFactorsStationaryGaseous_Data(), Table_Fuel_EFs_StationaryGaseous[[#Headers],[Fuel combusted]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3B70B10C-4767-4B84-90B0-F26D20C968BC}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) Combined gases" dataDxfId="65">
+    <tableColumn id="7" xr3:uid="{3B70B10C-4767-4B84-90B0-F26D20C968BC}" name="Scope 1 Emission Factor (kg CO2 - e / GJ) Combined gases" dataDxfId="29">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1EmissionFactorsStationaryGaseous_Data(), Table_Fuel_EFs_StationaryGaseous[[#Headers],[Fuel combusted]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9206,20 +9261,20 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{7D6CE29D-2354-4FAC-9965-9A66FFA42416}" name="Table_Fuel_EFs_StationaryGaseous34" displayName="Table_Fuel_EFs_StationaryGaseous34" ref="D112:F120" headerRowDxfId="64" totalsRowDxfId="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{7D6CE29D-2354-4FAC-9965-9A66FFA42416}" name="Table_Fuel_EFs_StationaryGaseous34" displayName="Table_Fuel_EFs_StationaryGaseous34" ref="D112:F120" headerRowDxfId="28" totalsRowDxfId="27">
   <autoFilter ref="D112:F120" xr:uid="{7D6CE29D-2354-4FAC-9965-9A66FFA42416}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{ECC6D32E-EE87-4C56-B924-DE2296D3A17A}" name="State or territory" totalsRowDxfId="62">
+    <tableColumn id="1" xr3:uid="{ECC6D32E-EE87-4C56-B924-DE2296D3A17A}" name="State or territory" totalsRowDxfId="26">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope3EmissionFactorsStationaryGaseous_Data(), Table_Fuel_EFs_StationaryGaseous34[[#Headers],[State or territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0BD20FE8-E5F8-4C9A-BA5E-E08126295979}" name="Metro" totalsRowDxfId="61">
+    <tableColumn id="2" xr3:uid="{0BD20FE8-E5F8-4C9A-BA5E-E08126295979}" name="Metro" totalsRowDxfId="25">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope3EmissionFactorsStationaryGaseous_Data(), Table_Fuel_EFs_StationaryGaseous34[[#Headers],[State or territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{25FB53B2-D2E0-4CEA-8D3F-87F6DBB9EB6B}" name="Non-metro" totalsRowDxfId="60">
+    <tableColumn id="3" xr3:uid="{25FB53B2-D2E0-4CEA-8D3F-87F6DBB9EB6B}" name="Non-metro" totalsRowDxfId="24">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope3EmissionFactorsStationaryGaseous_Data(), Table_Fuel_EFs_StationaryGaseous34[[#Headers],[State or territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9237,7 +9292,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{792636F9-F5FE-469C-B560-C7E663FA77BA}" name="Fuel type"/>
     <tableColumn id="2" xr3:uid="{529B0AD7-20FC-4E42-A872-AF12092332B1}" name="Unit"/>
-    <tableColumn id="3" xr3:uid="{B7CB8D6E-D4CE-4D2D-960F-4D58A56628AE}" name="Input Unit" dataDxfId="59"/>
+    <tableColumn id="3" xr3:uid="{B7CB8D6E-D4CE-4D2D-960F-4D58A56628AE}" name="Input Unit" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9258,22 +9313,22 @@
     <tableColumn id="1" xr3:uid="{4C846971-D1AE-40B6-93C3-4B2219305A91}" name="Transport type t">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransportOffRoad_Data(), Table_SourceData_Fuel_TransportOffroad[[#Headers],[Transport type t]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{82F6DC4A-0F92-4452-8487-4E43D14ADFD1}" name="Fuel type q" dataDxfId="58" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{82F6DC4A-0F92-4452-8487-4E43D14ADFD1}" name="Fuel type q" dataDxfId="22" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransportOffRoad_Data(), Table_SourceData_Fuel_TransportOffroad[[#Headers],[Transport type t]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{3C4A929E-9ED1-4901-B86F-83D8164C35AA}" name="ECTrans,q (GJ/kL)" dataDxfId="57" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{3C4A929E-9ED1-4901-B86F-83D8164C35AA}" name="ECTrans,q (GJ/kL)" dataDxfId="21" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransportOffRoad_Data(), Table_SourceData_Fuel_TransportOffroad[[#Headers],[Transport type t]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CC9C9248-897D-415C-976A-2C740F057EB1}" name="Scope 1 CO2 EFTran,1,tqg (kg CO2-e/GJ)" dataDxfId="56" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{CC9C9248-897D-415C-976A-2C740F057EB1}" name="Scope 1 CO2 EFTran,1,tqg (kg CO2-e/GJ)" dataDxfId="20" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransportOffRoad_Data(), Table_SourceData_Fuel_TransportOffroad[[#Headers],[Transport type t]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{786BC3D5-A6A8-43D0-B256-FFFC5437A688}" name="Scope 1 CH4 EFTran,1,tgg (kg CO2-e/GJ)" dataDxfId="55" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{786BC3D5-A6A8-43D0-B256-FFFC5437A688}" name="Scope 1 CH4 EFTran,1,tgg (kg CO2-e/GJ)" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransportOffRoad_Data(), Table_SourceData_Fuel_TransportOffroad[[#Headers],[Transport type t]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{6D5BCB7A-89DA-40E3-B7CA-1C29764B596B}" name="Scope 1 N2O EFTran,1,tgg (kg CO2-e/GJ)" dataDxfId="54" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{6D5BCB7A-89DA-40E3-B7CA-1C29764B596B}" name="Scope 1 N2O EFTran,1,tgg (kg CO2-e/GJ)" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransportOffRoad_Data(), Table_SourceData_Fuel_TransportOffroad[[#Headers],[Transport type t]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{7E1DA076-D5F8-4B6F-B281-1DB030412A87}" name="Scope 3 EFTrans,3,q (kg CO2-e/GJ)" dataDxfId="53" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{7E1DA076-D5F8-4B6F-B281-1DB030412A87}" name="Scope 3 EFTrans,3,q (kg CO2-e/GJ)" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Fuel_SourceData.Fuel_Scope1Scope3EmissionFactorsTransportOffRoad_Data(), Table_SourceData_Fuel_TransportOffroad[[#Headers],[Transport type t]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11844,87 +11899,87 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F32">
-    <cfRule type="cellIs" dxfId="52" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111:F112">
-    <cfRule type="cellIs" dxfId="51" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F123:F124">
-    <cfRule type="cellIs" dxfId="50" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F135:F136">
-    <cfRule type="cellIs" dxfId="49" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="13" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F147:F148">
-    <cfRule type="cellIs" dxfId="48" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F235:F236">
-    <cfRule type="cellIs" dxfId="47" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F240:F241">
-    <cfRule type="cellIs" dxfId="46" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F245:F246">
-    <cfRule type="cellIs" dxfId="45" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F269:F270">
-    <cfRule type="cellIs" dxfId="44" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F274:F275">
-    <cfRule type="cellIs" dxfId="43" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F279:F280">
-    <cfRule type="cellIs" dxfId="42" priority="83" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="83" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:J27 H28:H30 I31:J31 I33:J35 I37:J38 I189:J189 E195:G195 I195:J195">
-    <cfRule type="cellIs" dxfId="41" priority="79" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="79" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I42:J46">
-    <cfRule type="cellIs" dxfId="40" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I50:J50 I109:J109">
-    <cfRule type="cellIs" dxfId="39" priority="74" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="74" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I61:J63">
-    <cfRule type="cellIs" dxfId="38" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I67:J70">
-    <cfRule type="cellIs" dxfId="37" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I74:J78">
-    <cfRule type="cellIs" dxfId="36" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23974,6 +24029,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -24168,18 +24234,11 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzACAAaQBuAGMAbAB1AGQAaQBuAGcAIABsAGkAcQB1AGUAZgBpAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgACAAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA1AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAAYwBvAG0AYgB1AHMAdABlAGQAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABDAG8AbgB0AGUAbgB0ACAARgBhAGMAdABvAHIAIAAoAEcASgAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwAKQBcACIALAAgAFwAIgBGAHUAZQBsACAAdQBuAGkAdABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAE8AMgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAEgANABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABOADIATwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAG8AbQBiAGkAbgBlAGQAIABnAGEAcwBlAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADAALgAyACwAIAAwAC4AMAAzACwAIAA1ADEALgA2ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AYQBsACAAbQBpAG4AZQAgAHcAYQBzAHQAZQAgAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4AOQAsACAANAAuADYALAAgADAALgAzACwAIAA1ADYALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAG0AcAByAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAoAHIAZQB2AGUAcgB0AGkAbgBnACAAdABvACAAcwB0AGEAbgBkAGEAcgBkACAAYwBvAG4AZABpAHQAaQBvAG4AcwApAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVQBuAHAAcgBvAGMAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAA2ADIAOQAsACAAXAAiAG0AMwBcACIALAAgADUANgAuADUALAAgADAALgAwADMALAAgADAALgAwADMALAAgADUANgAuADUANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBrAGUAIABvAHYAZQBuACAAZwBhAHMAXAAiACwAIAAwAC4AMAAxADgAMQAsACAAXAAiAG0AMwBcACIALAAgADMANwAuADAALAAgADAALgAwADMALAAgADAALgAwADUALAAgADMANwAuADAAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAbABhAHMAdAAgAGYAdQByAG4AYQBjAGUAIABnAGEAcwBcACIALAAgADAALgAwADAANAAwACwAIABcACIAbQAzAFwAIgAsACAAMgAzADQALgAwACwAIAAwAC4AMAAzACwAIAAwAC4AMAAyACwAIAAyADMANAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwBcACIALAAgADAALgAwADMAOQAwACwAIABcACIAbQAzAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADAANAAsACAAMAAuADAAMwAsACAANgAwAC4AMgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBMAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAGUAbwB1AHMAIABmAG8AcwBzAGkAbAAgAGYAdQBlAGwAcwAgAG8AdABoAGUAcgAgAHQAaABhAG4AIAB0AGgAbwBzAGUAIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMAAuADAAMwA5ADAALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABhAG4AZABmAGkAbABsACAAYgBpAG8AZwBhAHMAIAB0AGgAYQB0ACAAaQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAKABtAGUAdABoAGEAbgBlACAAbwBuAGwAeQApAFwAIgAsACAAMAAuADAAMwA3ADcALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAANgAuADQALAAgADAALgAwADMALAAgADYALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQBlAHQAaABhAG4AZQAgAG8AbgBsAHkAKQBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADYALgA0ACwAIAAwAC4AMAAzACwAIAA2AC4ANAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAsACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHQAaABvAHMAZQAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAwAC4AMAAzADcAMAAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAA2AC4ANAAsACAAMAAuADAAMwAsACAANgAuADQAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAG0AZQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAAMAAuADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAeQBkAHIAbwBnAGUAbgBcACIALAAgADAALgAwADEAMgAyACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADAALgAwACwAIAAwAC4ANQAsACAAMAAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAAiACwAIAAxACwAIABcACIARwBKAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAMQAsACAAXAAiAEcASgBcACIALAAgADYAMAAuADIALAAgADAALgAwADQALAAgADAALgAwADMALAAgADYAMAAuADIANwBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAVABvAHcAbgAgAGcAYQBzACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAB1ADAAMAAyADcAIAB3AGUAcgBlACAAYQBkAGQAZQBkACwAIABlAGEAYwBoACAAdwBpAHQAaAAgAGEAbgAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAMQAgAEcASgAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwALgAgAFQAaABpAHMAIABpAHMAIABmAG8AcgAgAHUAcwBlAHIAcwAgAHcAaABvACAAaABhAHYAZQAgAGYAdQBlAGwAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABkAGEAdABhACAAaQBuACAARwBKACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAbQAzAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBJAG4AZABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAC4AXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA2AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAdABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAE4AYQB0AHUAcgBhAGwAIABHAGEAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE0AZQB0AHIAbwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgAGYAbwByACAATgBhAHQAdQByAGEAbAAgAEcAYQBzACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgBvAG4AIAAtACAATQBlAHQAcgBvAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAMQAzAC4AMQAsACAAMQA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAMQAzAC4AMQAsACAAMQA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgADQALgAwACwAIAA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIAA4AC4AOAAsACAANwAuADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgADEAMAAuADcALAAgADEAMAAuADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIAA0AC4AMQAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIAA0AC4AMAAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgADQALgAxACwAIAA0AC4AMABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAE4AUwBXACAAYQBuAGQAIABBAEMAVAAgAHMAcABsAGkAdAAgAGkAbgB0AG8AIABzAGUAcABhAHIAYQB0AGUAIAByAG8AdwBzAC4AIABcAHUAMAAwADIANwBDAFwAdQAwADAAMgA3ACAAVgBhAGwAdQBlAHMAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAGEAbgBkACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAByAGUAcABsAGEAYwBlAGQAIAB3AGkAdABoACAAdABoAG8AcwBlACAAZgBvAHIAIABWAGkAYwB0AG8AcgBpAGEAIABhAG4AZAAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAHIAZQBzAHAAZQBjAHQAaQB2AGUAbAB5AC4AIAAoAFMAZQBlACAAYQBwAHAAZQBuAGQAaQBjAGUAcwApAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMgAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEEAcwAgAFMAYwBvAHAAZQAgADMAIABmAGEAYwB0AG8AcgBzACAAYQByAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAYQB0ACAAdABoAGUAIABwAG8AaQBuAHQAIAB3AGgAZQByAGUAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABpAHMAIABkAGUAbABpAHYAZQByAGUAZAAgAHQAbwAgAGUAbgBkACAAdQBzAGUAcgBzACwAIABpAHQAIABpAHMAIABuAGUAYwBlAHMAcwBhAHIAeQAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAYQB0ACAAZQBhAGMAaAAgAG8AZgAgAHQAaABlACAAbABvAGEAZAAgAGMAZQBuAHQAcgBlAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBHAGEAcwAgAHIAZQBhAGMAaABlAHMAIABlAG4AZAAgAHUAcwBlAHIAcwAgAGUAaQB0AGgAZQByACAAZgByAG8AbQAgAHQAaABlACAAbQBlAHQAcgBvACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABuAGUAdAB3AG8AcgBrAHMAIABvAHIAIABkAGkAcgBlAGMAdAAgAGYAcgBvAG0AIAB0AGgAZQAgAGgAaQBnAGgAIAAtACAAcAByAGUAcwBzAHUAcgBlACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABwAGkAcABlAGwAaQBuAGUAcwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAEgAbwB1AHMAZQBoAG8AbABkAHMAIABhAG4AZAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB1AHMAZQByAHMAIAB0AGUAbgBkACAAdABvACAAYgBlACAAcwBlAHIAdgBlAGQAIABiAHkAIAB0AGgAZQAgAGYAbwByAG0AZQByACwAIABhAG4AZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAGcAZQBuAGUAcgBhAHQAbwByAHMAIABhAG4AZAAgAGwAYQByAGcAZQAgAGkAbgBkAHUAcwB0AHIAaQBhAGwAIABwAGwAYQBuAHQAcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGwAYQB0AHQAZQByAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBNAGUAdAByAG8AIABpAHMAIABkAGUAZgBpAG4AZQBkACAAYQBzACAAbABvAGMAYQB0AGUAZAAgAG8AbgAgAG8AcgAgAGUAYQBzAHQAIABvAGYAIAB0AGgAZQAgAGQAaQB2AGkAZABpAG4AZwAgAHIAYQBuAGcAZQAgAGkAbgAgAE4AUwBXACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAEMAYQBuAGIAZQByAHIAYQAgAGEAbgBkACAAUQB1AGUAYQBuAGIAZQB5AGEAbgAsACAATQBlAGwAYgBvAHUAcgBuAGUALAAgAEIAcgBpAHMAYgBhAG4AZQAsACAAQQBkAGUAbABhAGkAZABlACAAbwByACAAUABlAHIAdABoAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIATwB0AGgAZQByAHcAaQBzAGUALAAgAHQAaABlACAAbgBvAG4AIAAtACAAbQBlAHQAcgBvACAAZgBhAGMAdABvAHIAIABzAGgAbwB1AGwAZAAgAGIAZQAgAHUAcwBlAGQALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEYAYQBjAHQAbwByAHMAIABhAHIAZQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAG8AcgAgAGEAbABsACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAHcAaABpAGMAaAAgAG0AYQB5ACAAaQBuAGMAbAB1AGQAZQAgAGMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIABcACIAVABhAGIAbABlACAANgAgAGkAcwAgAG4AbwB0ACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHQAbwAgAGUAdABoAGEAbgBlAC4AIABTAGUAZQAgAFQAYQBiAGwAZQAgADcAIABJAG4AZABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZQB0AGgAYQBuAGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEMAIAA9ACAAQwBvAG4AZgBpAGQAZQBuAHQAaQBhAGwALgAgAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIABhAG4AZAAgAHQAaABlACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIABhAHIAZQAgAG4AbwB0ACAAYQB2AGEAaQBsAGEAYgBsAGUAIABkAHUAZQAgAHQAbwAgAGMAbwBuAGYAaQBkAGUAbgB0AGkAYQBsAGkAdAB5ACAAYwBvAG4AcwB0AHIAYQBpAG4AdABzACAAdABoAGEAdAAgAGEAcgBpAHMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAGEAIABsAGkAbQBpAHQAZQBkACAAbgB1AG0AYgBlAHIAIABvAGYAIABOAEcARQBSACAAZABhAHQAYQAgAGkAbgBwAHUAdABzAC4AIABJAHQAIABpAHMAIABzAHUAZwBnAGUAcwB0AGUAZAAgAHQAaABhAHQAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAHQAaABlACAAdQBzAGUAIABvAGYAIAB0AGgAZQAgAFYAaQBjAHQAbwByAGkAYQBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGkAcwAgAGEAcABwAHIAbwBwAHIAaQBhAHQAZQAsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAHcAaABpAGwAZQAgAGYAbwByACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAdABoAGUAIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABpAHMAIABhAHAAcAByAG8AcAByAGkAYQB0AGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZABvACAAbgBvAHQAIABpAG4AYwBsAHUAZABlACAAZgB1AGcAaQB0AGkAdgBlACAAZQBtAGkAcwBzAGkAbwBuACAAbABlAGEAawBhAGcAZQAgAGYAcgBvAG0AIABsAG8AdwAgAHAAcgBlAHMAcwB1AHIAZQAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAcABpAHAAZQBsAGkAbgBlACAAbgBlAHQAdwBvAHIAawBzACAAdwBoAGkAbABlACAAdABoAG8AcwBlACAAZgByAG8AbQAgAGgAaQBnAGgAIABwAHIAZQBzAHMAdQByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAZwBhAHMAIABuAGUAdAB3AG8AcgBrAHMAIABhAHIAZQAgAGMAbwBuAHMAaQBkAGUAcgBlAGQAIABuAGUAZwBsAGkAZwBpAGIAbABlAC4AXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMALAAgAGkAbgBjAGwAdQBkAGkAbgBnACAAYwBlAHIAdABhAGkAbgAgAHAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMALgBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA4AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADUALAAgADgALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACAAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsAHMAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABwAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsACAAdQBzAGUAZAAgAGEAcwAgAGYAdQBlAGwAKQAsACAAZQAuAGcALgAgAGwAdQBiAHIAaQBjAGEAbgB0AHMAXAAiACwAIAAzADgALgA4ACwAIABcACIAawBsAFwAIgAsACAAMQAzAC4AOQAsACAAMAAuADAALAAgADAALgAwACwAIAAxADMALgA5ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABnAHIAZQBhAHMAZQBzAFwAIgAsACAAMwA4AC4AOAAsACAAXAAiAGsAbABcACIALAAgADMALgA1ACwAIAAwAC4AMAAsACAAMAAuADAALAAgADMALgA1ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAHUAZABlACAAbwBpAGwAIABpAG4AYwBsAHUAZABpAG4AZwAgAGMAcgB1AGQAZQAgAG8AaQBsACAAYwBvAG4AZABlAG4AcwBhAHQAZQBzAFwAIgAsACAANAA1AC4AMwAsACAAXAAiAHQAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAANgA5AC4AOAA4ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGwAaQBxAHUAaQBkAHMAXAAiACwAIAA0ADYALgA1ACwAIABcACIAdABcACIALAAgADYAMQAuADAALAAgADAALgAwADgALAAgADAALgAyACwAIAA2ADEALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB1AHQAbwBtAG8AdABpAHYAZQAgAGcAYQBzAG8AbABpAG4AZQAgAC8AIABwAGUAdAByAG8AbAAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADQALgAyACwAIABcACIAawBMAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADIALAAgADAALgAyACwAIAA2ADcALgA4ADAALAAgADEANwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AIABnAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADMALgAxACwAIABcACIAawBMAFwAIgAsACAANgA3ACwAIAAwAC4AMgAsACAAMAAuADIALAAgADYANwAuADQAMAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADcALgA1ACwAIABcACIAawBMAFwAIgAsACAANgA4AC4AOQAsACAAMAAuADAAMQAsACAAMAAuADIALAAgADYAOQAuADEAMQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgAgAHQAdQByAGIAaQBuAGUAIABmAHUAZQBsACAALwAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAAyACwAIAAwAC4AMgAsACAANgA5AC4AOAAyACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdABpAG4AZwAgAG8AaQBsAFwAIgAsACAAMwA3AC4AMwAsACAAXAAiAGsATABcACIALAAgADYAOQAuADUALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA3ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsATABcACIALAAgADYAOQAuADkALAAgADAALgAxACwAIAAwAC4AMgAsACAANwAwAC4AMgAwACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAG8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsATABcACIALAAgADcAMwAuADYALAAgADAALgAwADQALAAgADAALgAyACwAIAA3ADMALgA4ADQALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAGEAcgBvAG0AYQB0AGkAYwAgAGgAeQBkAHIAbwBjAGEAcgBiAG8AbgBzAFwAIgAsACAAMwA0AC4ANAAsACAAXAAiAGsATABcACIALAAgADYAOQAuADcALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA5ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AbAB2AGUAbgB0AHMAOgAgAG0AaQBuAGUAcgBhAGwAIAB0AHUAcgBwAGUAbgB0AGkAbgBlACAAbwByACAAdwBoAGkAdABlACAAcwBwAGkAcgBpAHQAcwBcACIALAAgADMANAAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA3ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4AOQAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABwAGUAdAByAG8AbABlAHUAbQAgAGcAYQBzACAAKABMAFAARwApAFwAIgAsACAAMgA1AC4ANwAsACAAXAAiAGsATABcACIALAAgADYAMAAuADIALAAgADAALgAyACwAIAAwAC4AMgAsACAANgAwAC4ANgAwACwAIAAyADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHAAaAB0AGgAYQBcACIALAAgADMAMQAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAA2ADkALgA4ADIALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGMAbwBrAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAdABcACIALAAgADkAMgAuADYALAAgADAALgAwADgALAAgADAALgAyACwAIAA5ADIALgA4ADgALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAZgBpAG4AZQByAHkAIABnAGEAcwAgAGEAbgBkACAAbABpAHEAdQBpAGQAcwBcACIALAAgADQAMgAuADkALAAgAFwAIgB0AFwAIgAsACAANQA0AC4ANwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAANQA0AC4ANwA2ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAaQBuAGUAcgB5ACAAYwBvAGsAZQBcACIALAAgADMANAAuADIALAAgAFwAIgB0AFwAIgAsACAAOQAyAC4ANgAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADkAMgAuADgAOAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAbwB0AGgAZQByACAAdABoAGEAbgAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAzADQALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOAAsACAAMAAuADAAMgAsACAAMAAuADEALAAgADYAOQAuADkAMgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA0AC4ANgAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBFAHQAaABhAG4AbwBsACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGEAIABmAHUAZQBsACAAaQBuACAAYQBuACAAaQBuAHQAZQByAG4AYQBsACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAGUAbgBnAGkAbgBlAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBmAHUAZQBsAHMAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAdABoAG8AcwBlACAAbQBlAG4AdABpAG8AbgBlAGQAIABpAG4AIAB0AGgAZQAgAGkAdABlAG0AcwAgAGEAYgBvAHYAZQAgAGEAbgBkACAAYgBlAGwAbwB3AFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGEAdgBpAGEAdABpAG8AbgAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADAALgAyADIALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMwAwACwAIABcACIATgBFAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAXAB1ADAAMAAyADcATgBFAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIABhAHMAIAB6AGUAcgBvACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AcwAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABUAHIAYQBuAHMAcABvAHIAdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAxACkAIABhAG4AZAAgAGkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAcwAgAGkAbgAgAGQAaQBmAGYAZQByAGUAbgB0ACAAdAByAGEAbgBzAHAAbwByAHQAIABlAHEAdQBpAHAAbQBlAG4AdABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAOQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIANgAsACAAMQAwACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBhAG4AcwBwAG8AcgB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBGAHUAZQBsACAAYwBvAG0AYgB1AHMAdABlAGQAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABDAG8AbgB0AGUAbgB0ACAARgBhAGMAdABvAHIAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIALAAgAFwAIgBTAG8AdQByAGMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEcAYQBzAG8AbABpAG4AZQBcACIALAAgADMANAAuADIALAAgAFwAIgBrAGwAXAAiACwAIAA2ADcALgA0ACwAIAAwAC4AMAAyACwAIAAwAC4AMgAsACAANgA3AC4ANgAyACwAIAAxADcALgAyACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADkALAAgADAALgAwADEALAAgADAALgA1ACwAIAA3ADAALgA0ADEALAAgADEANwAuADMALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAcABlAHQAcgBvAGwAZQB1AG0AIABnAGEAcwAgACgATABQAEcAKQBcACIALAAgADIANgAuADIALAAgAFwAIgBrAGwAXAAiACwAIAA2ADAALgAyACwAIAAwAC4ANQAsACAAMAAuADMALAAgADYAMQAuADAAMAAsACAAMgAwAC4AMgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARgB1AGUAbAAgAG8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsAbABcACIALAAgADcAMwAuADYALAAgADAALgAwADgALAAgADAALgA1ACwAIAA3ADQALgAxADgALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEUAdABoAGEAbgBvAGwAXAAiACwAIAAyADMALgA0ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAyACwAIAAwAC4AMgAsACAAMAAuADQALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBCAGkAbwBkAGkAZQBzAGUAbABcACIALAAgADMANAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADgALAAgADEALgA3ACwAIAAyAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADEALAAgADAALgA1ACwAIAAwAC4ANQAxACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATwB0AGgAZQByACAAYgBpAG8AZgB1AGUAbABzAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AOAAsACAAMQAuADcALAAgADIALgA1ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQwBvAG0AcAByAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAANwAuADMALAAgADAALgAzACwAIAA1ADkALgAwACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAGcAaAB0ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADIANQAuADMALAAgAFwAIgBrAGwAXAAiACwAIAA1ADEALgA0ACwAIAA3AC4AMwAsACAAMAAuADMALAAgADUAOQAuADAALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADIALgA4ACwAIAAwAC4AMwAsACAANQA0AC4ANQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBsAFwAIgAsACAANQAxAC4ANAAsACAAMgAuADgALAAgADAALgAzACwAIAA1ADQALgA1ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAHYAIABvAHIAIABoAGkAZwBoAGUAcgBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMAA3ACwAIAAwAC4ANAAsACAANwAwAC4AMwA3ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAGkAaQBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMQAsACAAMAAuADQALAAgADcAMAAuADQALAAgADEANwAuADMALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAIAAtACAARQB1AHIAbwAgAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA0ACwAIAA3ADAALgA1ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAHYAIABvAHIAIABoAGkAZwBoAGUAcgBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAANwAsACAAMAAuADQALAAgADAALgA0ADcALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAGkAaQBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgA0ACwAIAAwAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAIAATICAARQB1AHIAbwAgAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAyACwAIAAwAC4ANAAsACAAMAAuADYALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEcAYQBzAG8AbABpAG4AZQAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0AFwAIgAsACAAMwAzAC4AMQAsACAAXAAiAGsAbABcACIALAAgADYANwAuADAALAAgADAALgAwADYALAAgADAALgA2ACwAIAA2ADcALgA2ADYALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AXAAiACwAIABcACIASwBlAHIAbwBzAGUAbgBlACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGYAdQBlAGwAIABpAG4AIABhAG4AIABhAGkAcgBjAHIAYQBmAHQAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAMQAsACAAMAAuADYALAAgADcAMAAuADIAMQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGEAdgBpAGEAdABpAG8AbgAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAMQAsACAAMAAuADYALAAgADAALgA2ADEALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAcwBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAawBMAFwAIgAsACAANgA3AC4ANAAsACAAMQAwAC4AMQAsACAAMAAuADMALAAgAFwAIgBcACIALAAgADEANwAuADIALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMgAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEANwAuADMALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARgB1AGUAbAAgAE8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsATABcACIALAAgADcAMwAuADYALAAgADAALgAyACwAIAAwAC4ANQAsACAAXAAiAFwAIgAsACAAMQA4AC4AMAAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBmAGYALQByAG8AYQBkACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACAAYQBuAGQAIABmAG8AcgBlAHMAdAByAHkAIABlAHEAdQBpAHAAbQBlAG4AdABcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsATABcACIALAAgADYAOQAuADkALAAgADAALgAzACwAIAAwAC4ANQAsACAAXAAiAFwAIgAsACAAMQA3AC4AMwAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAXAB1ADAAMAAyADcATgBFAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIABhAHMAIAB6AGUAcgBvACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AcwAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAATwBmAGYALQByAGEAZAAgAGUAcQB1AGkAcABtAGUAbgB0ACAAYQBuAGQAIAB2AGUAcwBzAGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABPAGYAZgAtAHIAbwBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAxACkAIABhAG4AZAAgAGkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAIABpAG4AIABvAGYAZgAtAHIAbwBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlACAAcQBcACIALAAgAFwAIgBFAEMAVAByAGEAbgBzACwAcQAgACgARwBKAC8AawBMACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEMATwAyACAARQBGAFQAcgBhAG4ALAAxACwAdABxAGcAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABDAEgANAAgAEUARgBUAHIAYQBuACwAMQAsAHQAZwBnACAAKABrAGcAIABDAE8AMgAtAGUALwBHAEoAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAATgAyAE8AIABFAEYAVAByAGEAbgAsADEALAB0AGcAZwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUARgBUAHIAYQBuAHMALAAzACwAcQAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAXAAiACwAIABcACIAUABlAHQAcgBvAGwAXAAiACwAIAAzADQALgAyACwAIAA2ADcALgA0ACwAIAAxADAALgAxACwAIAAwAC4AMwAsACAAMQA3AC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsAFwAIgAsACAAMwA4AC4ANgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA1ACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAXAAiACwAIABcACIARgB1AGUAbAAgAE8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAANwAzAC4ANgAsACAAMAAuADIALAAgADAALgA1ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBmAGYALQByAG8AYQBkACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACAAYQBuAGQAIABmAG8AcgBlAHMAdAByAHkAIABlAHEAdQBpAHAAbQBlAG4AdABcACIALAAgAFwAIgBEAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgADYAOQAuADkALAAgADAALgAzACwAIAAwAC4ANQAsACAAMQA3AC4AMwBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBGAHUAZQBsAF8ARwBlAHQAVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABTAHQAcgBpAG4AZwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALABcAG4AIAAgACAAIABMAEUARgBUACgAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsACAAXAAiACwAQwBlAGwAbAApACAALQAxACkAXABuACkAOwBcAG4AXABuAEYAdQBlAGwAXwBHAGUAdABTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwAUwB0AHIAaQBuAGcAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAXABuACAAIAAgACAAUgBJAEcASABUACgAQwBlAGwAbAAsAEwARQBOACgAQwBlAGwAbAApAC0ARgBJAE4ARAAoAFwAIgAsACAAXAAiACwAQwBlAGwAbAApACkAXABuACkAOwBcAG4AXABuAEYAdQBlAGwAXwBUAG8AdABhAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuAFwAbgA9ACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAHUAZQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBBAHIAcgBhAHkALAAgAEYAdQBlAGwAVQBzAGUAQQByAHIAYQB5ACwAIABGAHUAZQBsAFUAcwBlACwAIABGAHUAZQBsAFQAeQBwAGUAQQByAHIAYQB5ACwAIABGAHUAZQBsAFQAeQBwAGUALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAUwBVAE0AKABcAG4AIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAEYAdQBlAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAKABGAHUAZQBsAFQAeQBwAGUAQQByAHIAYQB5ACAAPQAgAEYAdQBlAGwAVAB5AHAAZQApACAAKgAgAFwAbgAgACAAIAAgACAAIAAgACAAKABGAHUAZQBsAFUAcwBlAEEAcgByAGEAeQAgAD0AIABGAHUAZQBsAFUAcwBlACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgADAAXABuACAAIAApAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AOAA6ACAARgB1AGUAbAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADgALgAxACAARgB1AGUAbAAgAFUAcwBlACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAAZgB1AGUAbABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRACwAIABFAEMALAAgAEUARgAsAFwAbgAgACAAIAAgACgAUQAgACoAIABFAEMAIAAqACAARQBGACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAbgBRACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAAawBMAFwAbgBFAEMAIAA6ACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAARwBKAC8AawBMAFwAbgBFAEYAIAA6ACAAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBUAHIAYQBuAHMAdABxACwAIABFAEMAXwBUAHIAYQBuAHMAcQAsACAARQBGAF8AVAByAGEAbgBzADEAdABxAGcALABcAG4AIAAgACAAIABWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACgAUQBfAFQAcgBhAG4AcwB0AHEALAAgAEUAQwBfAFQAcgBhAG4AcwBxACwAIABFAEYAXwBUAHIAYQBuAHMAMQB0AHEAZwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIAAyAC4AMwAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBnAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB0ACAAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBxAFwAXABsAGUAZgB0ACgAUQBfAHsAVAByAGEAbgBzACwAdABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAVAByAGEAbgBzACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFQAcgBhAG4AcwAsADEALAB0AHEAZwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAFQAcgBhAG4AcwB0AHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIABjAG8AbQBiAHUAcwB0AGUAZAAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcACIALAAgAFwAIgBWAGEAcgBpAGUAcwAgAGIAYQBzAGUAZAAgAG8AbgAgAGYAdQBlAGwAIAB0AHkAcABlADoAIABrAEwALAAgAG0AMwAsACAARwBKAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AVAByAGEAbgBzAHEAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXAAiACwAIABcACIARwBKACAALwAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AVAByAGEAbgBzADEAdABxAGcAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBhAG4AcwBcACIALAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBnAFwAIgAsACAAXAAiAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwBcAG4AUQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIAB0AHkAcABlACAAcQAgAHUAcwBlAGQAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgADoAIABrAEwAXABuAEUAQwAgADoAIABFAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzACAAOgAgAEcASgAvAGsATABcAG4ARQBGACAAOgAgAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAIAA6ACAAawBnACAAQwBPADIAZQAgAC8AIABHAEoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AUwBDAHEALAAgAEUAQwBfAFMAQwBxACwAIABFAEYAXwBTAEMAMQBxAGcALABcAG4AIAAgACAAIABWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACgAUQBfAFMAQwBxACwAIABFAEMAXwBTAEMAcQAsACAARQBGAF8AUwBDADEAcQBnACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA4AC4AMgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMgAuADIAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGUAbgBlAHIAZwB5ACAAcwBvAHUAcgBjAGUAcwAgAC0AIABDAGEAbABjAHUAbABhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AdAAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcQBcAFwAbABlAGYAdAAoAFEAXwB7AFMAQwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUwBDACwAMQAsAHEAZwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AUwBDAHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAFMAQwBxAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIARwBKACAALwAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AUwBDADEAcQBnAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAgAC8AIABHAEoAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBxAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBDAFwAIgAsACAAXAAiAFMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZwBcACIALAAgAFwAIgBHAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADUAOgAgAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANQBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAHYAZQBzAHQAbwBjAGsAXABuAFQAbwB0AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAbABpAHYAZQBzAHQAbwBjAGsAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AbwBcAFwAbABlAGYAdAAoAE4AXwB7AGMAbwB9AFwAXAB0AGkAbQBlAHMAIABXAF8AewBjAG8AfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBjAG8AfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAE4AXwBjAG8AIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABhAG4AaQBtAGEAbABzACAAcAB1AHIAYwBoAGEAcwBlAGQAIABpAG4AIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIABjACAAZgByAG8AbQAgAG8AcgBpAGcAaQBuACAAbwBcAG4AVwBfAGMAbwAgAD0AIABhAHYAZQByAGEAZwBlACAAbABpAHYAZQB3AGUAaQBnAGgAdAAgAG8AZgAgAHAAdQByAGMAaABhAHMAZQBkACAAbABpAHYAZQBzAHQAbwBjAGsAIABhAHQAIABwAG8AaQBuAHQAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAXABuAEUARgBfAGMAbwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAYQBuAGQAIABvAHIAaQBnAGkAbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBjAG8ALAAgAFcAXwBjAG8ALAAgAEUARgBfAGMAbwAsAFwAbgAgACAAIAAgACgATgBfAGMAbwAgACoAIABXAF8AYwBvACAAKgAgAEUARgBfAGMAbwApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQB2AGUAcwB0AG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGwAaQB2AGUAcwB0AG8AYwBrAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQB2AGUAcwB0AG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA1AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGMAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBvAFwAXABsAGUAZgB0ACgATgBfAHsAYwBvAH0AXABcAHQAaQBtAGUAcwAgAFcAXwB7AGMAbwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGMAbwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AYwBvAFwAIgAsACAAXAAiAG4AdQBtAGIAZQByACAAbwBmACAAYQBuAGkAbQBhAGwAcwAgAHAAdQByAGMAaABhAHMAZQBkACAAaQBuACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAYwAgAGYAcgBvAG0AIABvAHIAaQBnAGkAbgAgAG8AXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAXwBjAG8AXAAiACwAIABcACIAYQB2AGUAcgBhAGcAZQAgAGwAaQB2AGUAdwBlAGkAZwBoAHQAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAYQB0ACAAcABvAGkAbgB0ACAAbwBmACAAcAB1AHIAYwBoAGEAcwBlAFwAIgAsACAAXAAiAGsAZwAvAGgAZQBhAGQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBjAG8AXAAiACwAIABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGEAbgBkACAAbwByAGkAZwBpAG4AXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAGsAZwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAIABcACIAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbwBcACIALAAgAFwAIgBvAHIAaQBnAGkAbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAZQBkAFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGYAZQBlAGQAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBqAFwAXABsAGUAZgB0ACgAUQBfAGoAXABcAHQAaQBtAGUAcwAgAEUARgBfAGoAXABcAHIAaQBnAGgAdAApAFwAbgBRAF8AagAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABmAGUAZQBkACAAdAB5AHAAZQAgAGoAIABwAHUAcgBjAGgAYQBzAGUAZABcAG4ARQBGAF8AagAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAG8AZgAgAHAAdQByAGMAaABhAHMAZQBkACAAZgBlAGUAZABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGoALAAgAEUARgBfAGoALABcAG4AIAAgACAAIABRAF8AagAgACoAIABFAEYAXwBqAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGYAZQBlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgAyAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGoAXABcAGwAZQBmAHQAKABRAF8AagBcAFwAdABpAG0AZQBzACAARQBGAF8AagBcAFwAcgBpAGcAaAB0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AagBcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABmAGUAZQBkACAAdAB5AHAAZQAgAGoAIABwAHUAcgBjAGgAYQBzAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AagBcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAG8AZgAgAHAAdQByAGMAaABhAHMAZQBkACAAZgBlAGUAZABcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8AawBnAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALAAgAFwAIgBmAGUAZQBkACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBcAG4AVABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABtAGkAbgBlAHIAYQBsACAAcwB1AHAAcABsAGUAbQBlAG4AdABzAFwAbgBFAFwAbgB0ACAAQwBPADIAZQBcAG4ARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AbQBcAFwAbABlAGYAdAAoAFEAXwBtAFwAXAB0AGkAbQBlAHMAIABFAEYAXwBtAFwAXAByAGkAZwBoAHQAKQBcAG4AUQBfAG0AIAA9ACAAdABvAHQAYQBsACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAbQBpAG4AZQByAGEAbAAgAHMAdQBwAHAAbABlAG0AZQBuAHQAIAB0AHkAcABlACAAbQAgAHUAcwBlAGQAXABuAEUARgBfAG0AIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG0AaQBuAGUAcgBhAGwAIABzAHUAcABwAGwAZQBtAGUAbgB0AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATQBpAG4AZQByAGEAbABTAHUAcABwAGwAZQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAG0ALAAgAEUARgBfAG0ALABcAG4AIAAgACAAIABRAF8AbQAgACoAIABFAEYAXwBtAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABtAGkAbgBlAHIAYQBsACAAcwB1AHAAcABsAGUAbQBlAG4AdABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATQBpAG4AZQByAGEAbABTAHUAcABwAGwAZQBtAGUAbgB0AHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA1AC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAG0AXABcAGwAZQBmAHQAKABRAF8AbQBcAFwAdABpAG0AZQBzACAARQBGAF8AbQBcAFwAcgBpAGcAaAB0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATQBpAG4AZQByAGEAbABTAHUAcABwAGwAZQBtAGUAbgB0AHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAG0AXAAiACwAIABcACIAdABvAHQAYQBsACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAbQBpAG4AZQByAGEAbAAgAHMAdQBwAHAAbABlAG0AZQBuAHQAIAB0AHkAcABlACAAbQAgAHUAcwBlAGQAXAAiACwAIABcACIAdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAG0AXAAiACwAIABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG0AaQBuAGUAcgBhAGwAIABzAHUAcABwAGwAZQBtAGUAbgB0AFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAGcAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBtAFwAIgAsACAAXAAiAG0AaQBuAGUAcgBhAGwAIABzAHUAcABwAGwAZQBtAGUAbgB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBmAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagBcAFwAbABlAGYAdAAoAFQATQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAGYAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBUAE0AXwBqAGYAIAA9ACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGEAbgBkACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXABuAEUARgBfAGYAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABNAF8AagBmACwAIABFAEYAXwBmACwAXABuACAAIAAgACAAKABUAE0AXwBqAGYAIAAqACAARQBGAF8AZgApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADQALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AZgBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGoAXABcAGwAZQBmAHQAKABUAE0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwBmAFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQATQBfAGoAZgBcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAHAAdQByAGMAaABhAHMAZQBkACAAYQBuAGQAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBmAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAcAB1AHIAYwBoAGEAcwBlAGQAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAGsAZwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAIABcACIAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBcACIALAAgAFwAIgBpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYwBvAG0AcABvAG4AZQBuAHQAcwBcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGYAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagBcAFwAbABlAGYAdAAoACgARgBfAHsAYwBmAH0AXABcAHQAaQBtAGUAcwAgAFQATQBfAHsAagBmAH0AKQAvADEAMAAwAFwAXAB0AGkAbQBlAHMAIABFAEYAXwBjAFwAXAByAGkAZwBoAHQAKQBcAG4ARgBfAGMAZgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAG8AbQBwAG8AbgBlAG4AdAAgAGMAIABjAG8AbgB0AGEAaQBuAGUAZAAgAHcAaQB0AGgAaQBuACAAdABoAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABmAFwAbgBUAE0AXwBqAGYAIAA9ACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGEAbgBkACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXABuAEUARgBfAGMAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAaABlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAbwBtAHAAbwBuAGUAbgB0ACAAYwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAF8AYwBmACwAIABUAE0AXwBqAGYALAAgAEUARgBfAGMALABcAG4AIAAgACAAIAAoACgARgBfAGMAZgAgACoAIABUAE0AXwBqAGYAKQAgAC8AIAAxADAAMAApACAAKgAgAEUARgBfAGMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAF8AYwBmACwAIABUAE0AXwBqAGYALAAgAEUARgBfAGMALABcAG4AIAAgACAAIAAoAEYAXwBjAGYAIAAqACAAVABNAF8AagBmACkAIAAqACAARQBGAF8AYwAgACoAIAAxADAAXgAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYwBvAG0AcABvAG4AZQBuAHQAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADQALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGYAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagBcAFwAbABlAGYAdAAoAFwAXABmAHIAYQBjAHsARgBfAHsAYwBmAH0AXABcAHQAaQBtAGUAcwAgAFQATQBfAHsAagBmAH0AfQB7ADEAMAAwAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAGMAXABcAHIAaQBnAGgAdAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGYAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagBcAFwAbABlAGYAdAAoAEYAXwB7AGMAZgB9AFwAXAB0AGkAbQBlAHMAIABUAE0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwBjAFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAGMAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAG8AbQBwAG8AbgBlAG4AdAAgAGMAIABjAG8AbgB0AGEAaQBuAGUAZAAgAHcAaQB0AGgAaQBuACAAdABoAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABmAFwAIgAsACAAXAAiAHcAdAAlAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABNAF8AagBmAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAcAB1AHIAYwBoAGEAcwBlAGQAIABhAG4AZAAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGMAXAAiACwAIABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAaABlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAbwBtAHAAbwBuAGUAbgB0ACAAYwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8AawBnACAAYwBvAG0AcABvAG4AZQBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsACAAXAAiAGYAZQByAHQAaQBsAGkAcwBlAHIAIABjAG8AbQBwAG8AbgBlAG4AdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAIABcACIAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAIABcACIAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAHIAZQBtAG8AdgBlAHMAIABkAGkAdgBpAHMAaQBvAG4AIABiAHkAIAAxADAAMAAgAGYAbwByACAARgBfAGMAZgAsACAAdAByAGUAYQB0AGkAbgBnACAARgBfAGMAZgAgAGEAcwAgAGYAcgBhAGMAdABpAG8AbgAgAGkAbgBzAHQAZQBhAGQAIABvAGYAIABwAGUAcgBjAGUAbgB0ACAAYgBlAGMAYQB1AHMAZQAgAGkAdAAgAGkAcwAgAGEAIABmAHIAYQBjAHQAaQBvAG4AIABpAG4AIABzAGMAbwBwAGUAIAAxACAAZQBxAHUAYQB0AGkAbwBuAHMALgAgAEMAbwBuAHYAZQByAHQAIABrAGcAIAB0AG8AIAB0AG8AbgBuAGUAcwAgAGIAeQAgAG0AdQB0AGkAcABsAHkAaQBuAGcAIABiAHkAIAAxADAAXgAtADMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABwAHIAbwBkAHUAYwB0ACAAZABlAHIAaQB2AGUAZAAgAGYAcgBvAG0AIABjAG8AbQBwAG8AbgBlAG4AdABzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAF8AYwBmACwAIABFAEYAXwBjACwAXABuACAAIAAgACAARgBfAGMAZgAgACoAIABFAEYAXwBjAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwBYAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHAAcgBvAGQAdQBjAHQAIABkAGUAcgBpAHYAZQBkACAAZgByAG8AbQAgAGMAbwBtAHAAbwBuAGUAbgB0AHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwBYAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBPADIAZQAvAGsAZwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAEEARgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwBYAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwBmAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjAFwAXABsAGUAZgB0ACgARgBfAHsAYwBmAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAGMAXABcAHIAaQBnAGgAdAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAGMAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAG8AbQBwAG8AbgBlAG4AdAAgAGMAIABjAG8AbgB0AGEAaQBuAGUAZAAgAHcAaQB0AGgAaQBuACAAdABoAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABmAFwAIgAsACAAXAAiAHcAdAAlAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AYwBcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdABoAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwBvAG0AcABvAG4AZQBuAHQAIABjAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAGcAIABjAG8AbQBwAG8AbgBlAG4AdABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAIABcACIAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGMAbwBtAHAAbwBuAGUAbgB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBcACIALAAgAFwAIgBpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABUAGgAaQBzACAAZQBxAHUAYQB0AGkAbwBuACAAaQBzACAAYQBkAGQAZQBkACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIABhAG4AIABFAEYAIAB2AGEAbAB1AGUAIABmAHIAbwBtACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGMAbwBtAHAAbwBuAGUAbgB0AHMAIAB0AGgAYQB0ACAAYwBhAG4AIABiAGUAIAB1AHMAZQBkACAAaQBuACAAMQA1AC4ANAAuADEALgAxACAAKAAxACkAXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXABuAFQAbwB0AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAYQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGgAXABcAGwAZQBmAHQAKABRAF8AaABcAFwAdABpAG0AZQBzACAARQBGAF8AaABcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAFEAXwBoACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAGEAYwB0AGkAdgBlACAAaQBuAGcAcgBlAGQAaQBlAG4AdABzACAAaQBuACAAYQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAIAB0AHkAcABlACAAaAAgAHAAdQByAGMAaABhAHMAZQBkACAAYQBuAGQAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAbgBFAEYAXwBoACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGEAZwByAGkAYwBoAGUAbQBpAGMAYQBsACAAYQBjAHQAaQB2AGUAIABpAG4AZwByAGUAZABpAGUAbgB0AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADUAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAQQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AaAAsACAARQBGAF8AaAAsAFwAbgAgACAAIAAgACgAUQBfAGgAIAAqACAARQBGAF8AaAApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAYQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADUAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAQQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AaABcAFwAbABlAGYAdAAoAFEAXwBoAFwAXAB0AGkAbQBlAHMAIABFAEYAXwBoAFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBoAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAGEAYwB0AGkAdgBlACAAaQBuAGcAcgBlAGQAaQBlAG4AdABzACAAaQBuACAAYQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAIAB0AHkAcABlACAAaAAgAHAAdQByAGMAaABhAHMAZQBkACAAYQBuAGQAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAIgAsACAAXAAiAGsAZwAgAGEAaQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGgAXAAiACwAIABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHAAdQByAGMAaABhAHMAZQBkACAAYQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAIABhAGMAdABpAHYAZQAgAGkAbgBnAHIAZQBkAGkAZQBuAHQAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAGsAZwAgAGEAaQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGgAXAAiACwAIABcACIAYQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwA2AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQBtAGUAXABuAEUAbQBiAGUAZABkAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGwAaQBtAGUAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0ATQBfAGwAaQBtAGUAXABcAHQAaQBtAGUAcwAgAEUARgBfAGwAXABuAE0AXwBsAGkAbQBlACAAPQAgAHQAbwB0AGEAbAAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAGwAaQBtAGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAbgBFAEYAXwBsACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGwAaQBtAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBsAGkAbQBlACwAIABFAEYAXwBsACwAXABuACAAIAAgACAATQBfAGwAaQBtAGUAIAAqACAARQBGAF8AbABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADYAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAG0AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGIAZQBkAGQAZQBkACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAG8AcgAgAHAAdQByAGMAaABhAHMAZQBkACAAbABpAG0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA2AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQBtAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADYALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADYAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAG0AZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AE0AXwB7AGwAaQBtAGUAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBsAGkAbQBlAFwAIgAsACAAXAAiAHQAbwB0AGEAbAAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAGwAaQBtAGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBsAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGwAaQBtAGUAXAAiACwAIABcACIAdAAgAEMATwAyAGUALwB0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAHMAZQByAHYAaQBjAGUAcwAgAGEAbgBkACAAYwBvAG4AdAByAGEAYwB0AG8AcgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBwAFwAXABsAGUAZgB0ACgAQQBfAHAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHAAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBBAF8AcAAgAD0AIABhAGMAdABpAHYAaQB0AHkAIABkAGEAdABhACAAbwBmACAAdABoAGUAIABzAGUAcgB2AGkAYwBlACAAdABoAGEAdAAgAHcAYQBzACAAcAB1AHIAYwBoAGEAcwBlAGQAXABuAEUARgBfAHAAIAA9ACAAbABpAGYAZQAgAGMAeQBjAGwAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGgAZQAgAHAAdQByAGMAaABhAHMAZQBkACAAcwBlAHIAdgBpAGMAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAF8AcAAsACAARQBGAF8AcAAsAFwAbgAgACAAIAAgACgAQQBfAHAAIAAqACAARQBGAF8AcAApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAHMAZQByAHYAaQBjAGUAcwAgAGEAbgBkACAAYwBvAG4AdAByAGEAYwB0AG8AcgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADcAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUwBlAHIAdgBpAGMAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgA3AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABTAGUAcgB2AGkAYwBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBwAFwAXABsAGUAZgB0ACgAQQBfAHAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHAAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAF8AcABcACIALAAgAFwAIgBhAGMAdABpAHYAaQB0AHkAIABkAGEAdABhACAAbwBmACAAdABoAGUAIABzAGUAcgB2AGkAYwBlACAAdABoAGEAdAAgAHcAYQBzACAAcAB1AHIAYwBoAGEAcwBlAGQAXAAiACwAIABcACIAaABhACAAbwByACAAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAHAAXAAiACwAIABcACIAbABpAGYAZQAgAGMAeQBjAGwAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGgAZQAgAHAAdQByAGMAaABhAHMAZQBkACAAcwBlAHIAdgBpAGMAZQBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8AaABhACAAbwByACAAawBnACAAQwBPADIAZQAvAGgAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsACAAXAAiAHMAZQByAHYAaQBjAGUAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwA4AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFAAYQBjAGsAYQBnAGkAbgBnAFwAbgBFAG0AYgBlAGQAZABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHMAZQAgAG8AZgAgAHAAYQBjAGsAYQBnAGkAbgBnACAAbQBhAHQAZQByAGkAYQBsAHMAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBwAFwAXABsAGUAZgB0ACgAUQBfAHAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHAAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRAF8AcAAgAD0AIAB1AG4AaQB0AHMAIABvAGYAIABwAGEAYwBrAGEAZwBpAG4AZwAgAHQAeQBwAGUAIABwAFwAbgBFAEYAXwBwACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABwAGEAYwBrAGEAZwBpAG4AZwAgAHQAeQBwAGUAIABwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAHAALAAgAEUARgBfAHAALABcAG4AIAAgACAAIAAoAFEAXwBwACAAKgAgAEUARgBfAHAAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGIAZQBkAGQAZQBkACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdQBzAGUAIABvAGYAIABwAGEAYwBrAGEAZwBpAG4AZwAgAG0AYQB0AGUAcgBpAGEAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA4AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFAAYQBjAGsAYQBnAGkAbgBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA4AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFAAYQBjAGsAYQBnAGkAbgBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA1AC4AOAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHAAXABcAGwAZQBmAHQAKABRAF8AcABcAFwAdABpAG0AZQBzACAARQBGAF8AcABcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAHAAXAAiACwAIABcACIAdQBuAGkAdABzACAAbwBmACAAcABhAGMAawBhAGcAaQBuAGcAIAB0AHkAcABlACAAcABcACIALAAgAFwAIgB1AG4AaQB0AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBwAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABwAGEAYwBrAGEAZwBpAG4AZwAgAHQAeQBwAGUAIABwAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwB1AG4AaQB0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcABcACIALAAgAFwAIgBwAGEAYwBrAGEAZwBpAG4AZwAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABDAGgAYQBuAGcAZQBkACAAdQBuAGkAdAAgAG8AZgAgAFEAIABmAHIAbwBtACAAXAB1ADAAMAAyADcAdQBuAGkAdABzAFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcAawBnAFwAdQAwADAAMgA3ACAAYQBzACAARQBGACAAZABhAHQAYQAgAGkAcwAgAGkAbgAgAGsAZwAuAFwAIgApADsAXABuACAAIABcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAFwAbgBFAG0AYgBlAGQAZABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHMAZQAgAG8AZgAgAGcAcgBvAHcAIABtAGUAZABpAGEAIABwAHIAbwBkAHUAYwB0AHMAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBnAFwAXABsAGUAZgB0ACgAUQBfAGcAXABcAHQAaQBtAGUAcwAgAEUARgBfAGcAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRAF8AZwAgAD0AIAB0AG8AdABhAGwAIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABnAHIAbwB3ACAAbQBlAGQAaQBhACAAdAB5AHAAZQAgAGcAXABuAEUARgBfAGcAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGcAcgBvAHcAIABtAGUAZABpAGEAIAB0AHkAcABlACAAZwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBnACwAIABFAEYAXwBnACwAXABuACAAIAAgACAAKABRAF8AZwAgACoAIABFAEYAXwBnACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADkAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARwByAG8AdwBNAGUAZABpAGEAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBiAGUAZABkAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHUAcwBlACAAbwBmACAAZwByAG8AdwAgAG0AZQBkAGkAYQAgAHAAcgBvAGQAdQBjAHQAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABHAHIAbwB3AE0AZQBkAGkAYQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABHAHIAbwB3AE0AZQBkAGkAYQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADkALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADkAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARwByAG8AdwBNAGUAZABpAGEAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADkAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARwByAG8AdwBNAGUAZABpAGEAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBnAFwAXABsAGUAZgB0ACgAUQBfAGcAXABcAHQAaQBtAGUAcwAgAEUARgBfAGcAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBnAFwAIgAsACAAXAAiAHQAbwB0AGEAbAAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAGcAcgBvAHcAIABtAGUAZABpAGEAIAB0AHkAcABlACAAZwBcACIALAAgAFwAIgBrAGcAIABvAHIAIABtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBnAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABnAHIAbwB3ACAAbQBlAGQAaQBhACAAdAB5AHAAZQAgAGcAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAGsAZwAgAG8AcgAgAGsAZwAgAEMATwAyAGUALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBnAFwAIgAsACAAXAAiAGcAcgBvAHcAIABtAGUAZABpAGEAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAFwAbgBPAHQAaABlAHIAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGcAbwBvAGQAcwAgAGEAbgBkACAAcwBlAHIAdgBpAGMAZQBzACAAZwBlAG4AZQByAGkAYwAgAGUAcwB0AGkAbQBhAHQAZQBcAG4AZQBtAGkAcwBzAGkAbwBuAHMAXABuAHQAIABDAE8AMgBlAFwAbgBlAG0AaQBzAHMAaQBvAG4AcwA9AGEAYwB0AGkAdgBpAHQAeQBfAGQAYQB0AGEAXABcAHQAaQBtAGUAcwAgAGUAbQBpAHMAcwBpAG8AbgBfAGYAYQBjAHQAbwByAFwAbgBhAGMAdABpAHYAaQB0AHkAXwBkAGEAdABhACAAPQAgAG0AZQBhAHMAdQByAGUAZAAgAGEAYwB0AGkAdgBpAHQAeQAgAGYAbwByACAAdABoAGUAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGcAbwBvAGQAIABvAHIAIABzAGUAcgB2AGkAYwBlAFwAbgBlAG0AaQBzAHMAaQBvAG4AXwBmAGEAYwB0AG8AcgAgAD0AIABsAGkAZgBlAGMAeQBjAGwAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAYQBjAHQAaQB2AGkAdAB5AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQBjAHQAaQB2AGkAdAB5AF8AZABhAHQAYQAsACAAZQBtAGkAcwBzAGkAbwBuAF8AZgBhAGMAdABvAHIALABcAG4AIAAgACAAIABhAGMAdABpAHYAaQB0AHkAXwBkAGEAdABhACAAKgAgAGUAbQBpAHMAcwBpAG8AbgBfAGYAYQBjAHQAbwByAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAwAF8AMQBfADEAXwBfADEAXwBPAHQAaABlAHIAUAB1AHIAYwBoAGEAcwBlAGQARwBvAG8AZABzAEEAbgBkAFMAZQByAHYAaQBjAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAAcAB1AHIAYwBoAGEAcwBlAGQAIABnAG8AbwBkAHMAIABhAG4AZAAgAHMAZQByAHYAaQBjAGUAcwAgAGcAZQBuAGUAcgBpAGMAIABlAHMAdABpAG0AYQB0AGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA1AC4AMQAwACwAIABnAGUAbgBlAHIAaQBjACAAcABsAGEAYwBlAGgAbwBsAGQAZQByACAAZQBxAHUAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZQBtAGkAcwBzAGkAbwBuAHMAPQBhAGMAdABpAHYAaQB0AHkAXABcAF8AZABhAHQAYQBcAFwAdABpAG0AZQBzACAAZQBtAGkAcwBzAGkAbwBuAFwAXABfAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGEAYwB0AGkAdgBpAHQAeQBfAGQAYQB0AGEAXAAiACwAIABcACIAbQBlAGEAcwB1AHIAZQBkACAAYQBjAHQAaQB2AGkAdAB5ACAAZgBvAHIAIAB0AGgAZQAgAHAAdQByAGMAaABhAHMAZQBkACAAZwBvAG8AZAAgAG8AcgAgAHMAZQByAHYAaQBjAGUAXAAiACwAIABcACIAdgBhAHIAaQBlAHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AXwBmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBsAGkAZgBlAGMAeQBjAGwAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAYQBjAHQAaQB2AGkAdAB5AFwAIgAsACAAXAAiAHYAYQByAGkAZQBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABVAHAAcwB0AHIAZQBhAG0ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAHUAZQBsAFwAbgBUAG8AdABhAGwAIAB1AHAAcwB0AHIAZQBhAG0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAGMAbwBwAGUAIAAxACAAZgB1AGUAbAAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgBcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHEARQBfAHsAVwBUAFQALAB0AHIAYQBuAHMALABxAH0AKwBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHEARQBfAHsAVwBUAFQALABTAEMALABxAH0AXABuAEUAXwBXAFQAVAB0AHIAYQBuAHMAcQAgAD0AIAB1AHAAcwB0AHIAZQBhAG0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAGMAbwBwAGUAIAAxACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsACAAdQBzAGUAXABuAEUAXwBXAFQAVABTAEMAcQAgAD0AIAB1AHAAcwB0AHIAZQBhAG0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAGMAbwBwAGUAIAAxACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAHUAZQBsACAAdQBzAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AVwBUAFQAdAByAGEAbgBzAHEALAAgAEUAXwBXAFQAVABTAEMAcQAsAFwAbgAgACAAIAAgAEUAXwBXAFQAVAB0AHIAYQBuAHMAcQAgACsAIABFAF8AVwBUAFQAUwBDAHEAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABVAHAAcwB0AHIAZQBhAG0ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAHUAZQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIAB1AHAAcwB0AHIAZQBhAG0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAGMAbwBwAGUAIAAxACAAZgB1AGUAbAAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABVAHAAcwB0AHIAZQBhAG0ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAHUAZQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADEAMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHEARQBfAHsAVwBUAFQALAB0AHIAYQBuAHMALABxAH0AKwBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHEARQBfAHsAVwBUAFQALABTAEMALABxAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAFUAcABzAHQAcgBlAGEAbQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAdQBlAGwAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBfAFcAVABUAHQAcgBhAG4AcwBxAFwAIgAsACAAXAAiAHUAcABzAHQAcgBlAGEAbQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAYwBvAHAAZQAgADEAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAIAB1AHMAZQBcACIALAAgAFwAIgB0ACAAQwBPADIAZQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAYgB5ACAAMQA1AC4AMQAxAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBfAFcAVABUAFMAQwBxAFwAIgAsACAAXAAiAHUAcABzAHQAcgBlAGEAbQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAYwBvAHAAZQAgADEAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAGYAdQBlAGwAIAB1AHMAZQBcACIALAAgAFwAIgB0ACAAQwBPADIAZQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAYgB5ACAAMQA1AC4AMQAxAC4AMQAuADEAIAAoADMAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBVAHAAcwB0AHIAZQBhAG0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAGMAbwBwAGUAIAAxACAAZgB1AGUAbAAgAHUAcwBlACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAHAAdQByAHAAbwBzAGUAcwBcAG4ARQBfAFcAVABUAHQAcgBhAG4AcwBxAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBfAHsAVwBUAFQALAB0AHIAYQBuAHMALABxAH0APQBRAF8AewBUAHIAYQBuAHMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAVAByAGEAbgBzACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFQAcgBhAG4AcwAsADMALABxAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAFEAXwBUAHIAYQBuAHMAcQAgAD0AIABhAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXABuAEUAQwBfAFQAcgBhAG4AcwBxACAAPQAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAbgBFAEYAXwBUAHIAYQBuAHMAMwBxACAAPQAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBUAHIAYQBuAHMAcQAsACAARQBDAF8AVAByAGEAbgBzAHEALAAgAEUARgBfAFQAcgBhAG4AcwAzAHEALABcAG4AIAAgACAAIAAoAFEAXwBUAHIAYQBuAHMAcQAgACoAIABFAEMAXwBUAHIAYQBuAHMAcQAgACoAIABFAEYAXwBUAHIAYQBuAHMAMwBxACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAyAF8AVQBwAHMAdAByAGUAYQBtAFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFUAcABzAHQAcgBlAGEAbQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAYwBvAHAAZQAgADEAIABmAHUAZQBsACAAdQBzAGUAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAcAB1AHIAcABvAHMAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AVwBUAFQAdAByAGEAbgBzAHEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAyAF8AVQBwAHMAdAByAGUAYQBtAFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADIAXwBVAHAAcwB0AHIAZQBhAG0AVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgAxADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAyAF8AVQBwAHMAdAByAGUAYQBtAFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAyAF8AVQBwAHMAdAByAGUAYQBtAFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBXAFQAVAAsAHQAcgBhAG4AcwAsAHEAfQA9AFEAXwB7AFQAcgBhAG4AcwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBUAHIAYQBuAHMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAVAByAGEAbgBzACwAMwAsAHEAfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADIAXwBVAHAAcwB0AHIAZQBhAG0AVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AVAByAGEAbgBzAHEAXAAiACwAIABcACIAYQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAcQAgAGMAbwBtAGIAdQBzAHQAZQBkACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgAsACAAXAAiAGsATABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAFQAcgBhAG4AcwBxAFwAIgAsACAAXAAiAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgAsACAAXAAiAEcASgAvAGsATAAgAG8AcgAgAEcASgAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFQAcgBhAG4AcwAzAHEAXAAiACwAIABcACIAcwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBHAEoAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBcAG4AVQBwAHMAdAByAGUAYQBtACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwBjAG8AcABlACAAMQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgB1AGUAbAAgAHUAcwBlAFwAbgBFAF8AVwBUAFQAUwBDAHEAXABuAHQAIABDAE8AMgBlAFwAbgBFAF8AewBXAFQAVAAsAFMAQwAsAHEAfQA9AFEAXwB7AFMAQwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUwBDACwAMwAsAHEAfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4AUQBfAFMAQwBxACAAPQAgAGEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXABuAEUAQwBfAFMAQwBxACAAPQAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXABuAEUARgBfAFMAQwAzAHEAIAA9ACAAcwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBTAEMAcQAsACAARQBDAF8AUwBDAHEALAAgAEUARgBfAFMAQwAzAHEALABcAG4AIAAgACAAIAAoAFEAXwBTAEMAcQAgACoAIABFAEMAXwBTAEMAcQAgACoAIABFAEYAXwBTAEMAMwBxACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVQBwAHMAdAByAGUAYQBtACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwBjAG8AcABlACAAMQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgB1AGUAbAAgAHUAcwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMwBfAFUAcABzAHQAcgBlAGEAbQBTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBXAFQAVABTAEMAcQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgAxADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAVwBUAFQALABTAEMALABxAH0APQBRAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAUwBDACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFMAQwAsADMALABxAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AUwBDAHEAXAAiACwAIABcACIAYQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAcQAgAHUAcwBlAGQAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwBcACIALAAgAFwAIgBrAEwAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMAXwBTAEMAcQBcACIALAAgAFwAIgBlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAIgAsACAAXAAiAEcASgAvAGsATABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFMAQwAzAHEAXAAiACwAIABcACIAcwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAcwB0AGEAdABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQBcACIALAAgAFwAIgBtAGUAdAByAG8AcABvAGwAaQB0AGEAbgAvAG4AbwBuAC0AbQBlAHQAcgBvAHAAbwBsAGkAdABhAG4AIABsAG8AYwBhAHQAaQBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHMAdABhAHQAZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAbQBlAHQAcgBvAC8AbgBvAG4ALQBtAGUAdAByAG8AXAB1ADAAMAAyADcAIABhAHIAZwB1AG0AZQBuAHQAcwAgAGEAcwAgAGcAYQBzAGUAbwB1AHMAIABzAGMAbwBwAGUAIAAzACAARQBGAHMAIABhAHIAZQAgAHMAdABhAHQAZQAgAGEAbgBkACAAbQBlAHQAcgBvAC8AbgBvAG4ALQBtAGUAdAByAG8AIABsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQALgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFwAbgBTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABsAG8AYwBhAHQAaQBvAG4AIABiAGEAcwBlAGQAXABuAEUAXwAzAGUAbABlAGMAXABuAHQAIABDAE8AMgBlAFwAbgBFAF8AewAzACwAZQBsAGUAYwB9AD0AUQBfAHsAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7ADMALABlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAFEAXwBlAGwAZQBjACAAPQAgAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAbgBFAEYAXwAzAGUAbABlAGMAIAA9ACAAcwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMQBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AZQBsAGUAYwAsACAARQBGAF8AMwBlAGwAZQBjACwAXABuACAAIAAgACAAKABRAF8AZQBsAGUAYwAgACoAIABFAEYAXwAzAGUAbABlAGMAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADEAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAGwAbwBjAGEAdABpAG8AbgAgAGIAYQBzAGUAZABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADEAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwAzAGUAbABlAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADEAMgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADEAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAMwAsAGUAbABlAGMAfQA9AFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewAzACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMQBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZQBsAGUAYwBcACIALAAgAFwAIgBhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZABcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfADMAZQBsAGUAYwBcACIALAAgAFwAIgBzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHAAdQByAGMAaABhAHMAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAFcAaABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGcAXAAiACwAIABcACIAZwByAGkAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHcAYQBzACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAFwAbgBTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABtAGEAcgBrAGUAdAAgAGIAYQBzAGUAZABcAG4ARQBfADMAZQBsAGUAYwBcAG4AdAAgAEMATwAyAGUAXABuAEUAXwB7ADMALABlAGwAZQBjAH0APQBcAFwAbABlAGYAdABbAFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0ACgAMQAtACgAUgBQAFAAKwBKAFIAUABQACkAXABcAHIAaQBnAGgAdAApAC0AXABcAGwAZQBmAHQAKABSAEUAQwBfAHsAcwB1AHIAcgBlAG4AZABlAHIAZQBkAH0ALQBSAEUAQwBfAHsAbwBuAHMAaQB0AGUAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABcAHIAaQBnAGgAdABdAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFIATQBGADMALABlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAFEAXwBlAGwAZQBjACAAPQAgAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAbgBSAFAAUAAgAD0AIAByAGUAbgBlAHcAYQBiAGwAZQAgAHAAbwB3AGUAcgAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIAB1AG4AZABlAHIAIABMAFIARQBUACAAZgBvAHIAIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIABwAGUAcgBpAG8AZABcAG4ASgBSAFAAUAAgAD0AIABqAHUAcgBpAHMAZABpAGMAdABpAG8AbgBhAGwAIAByAGUAbgBlAHcAYQBiAGwAZQAgAHAAbwB3AGUAcgAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABmAG8AcgAgAHQAaABlACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHAAZQByAGkAbwBkAFwAbgBSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAD0AIABlAGwAaQBnAGkAYgBsAGUAIAByAGUAbgBlAHcAYQBiAGwAZQAgAGUAbgBlAHIAZwB5ACAAYwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIAB2AG8AbAB1AG4AdABhAHIAaQBsAHkAIABzAHUAcgByAGUAbgBkAGUAcgBlAGQAXABuAFIARQBDAF8AbwBuAHMAaQB0AGUAIAA9ACAAZQBsAGkAZwBpAGIAbABlACAAcgBlAG4AZQB3AGEAYgBsAGUAIABlAG4AZQByAGcAeQAgAGMAZQByAHQAaQBmAGkAYwBhAHQAZQBzACAAaQBzAHMAdQBlAGQAIABmAG8AcgAgAG8AbgBzAGkAdABlACAAZwBlAG4AZQByAGEAdABlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXABuAEUARgBfAFIATQBGADMAZQBsAGUAYwAgAD0AIABzAGMAbwBwAGUAIAAzACAAcgBlAHMAaQBkAHUAYQBsACAAbQBpAHgAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAyAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAFIAUABQACwAIABKAFIAUABQACwAIABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAsACAAUgBFAEMAXwBvAG4AcwBpAHQAZQAsACAARQBGAF8AUgBNAEYAMwBlAGwAZQBjACwAXABuACAAIAAgACAAKAAoAFEAXwBlAGwAZQBjACAAKgAgACgAMQAgAC0AIAAoAFIAUABQACAAKwAgAEoAUgBQAFAAKQApACkAIAAtACAAKAAoAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAALQAgAFIARQBDAF8AbwBuAHMAaQB0AGUAKQAgACoAIAAxADAAIABeACAALQAzACkAKQAgACoAIABFAEYAXwBSAE0ARgAzAGUAbABlAGMAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAyAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBNAGEAcgBrAGUAdABCAGEAcwBlAGQAVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAFIAUABQACwAIABKAFIAUABQACwAIABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAsACAAUgBFAEMAXwBvAG4AcwBpAHQAZQAsACAARQBGAF8AUgBNAEYAMwBlAGwAZQBjACwAXABuACAAIAAgACAAKAAoAFEAXwBlAGwAZQBjACAAKgAgACgAMQAgAC0AIAAoAFIAUABQACAAKwAgAEoAUgBQAFAAKQApACkAIAAtACAAKAAoAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAALQAgAFIARQBDAF8AbwBuAHMAaQB0AGUAKQAgACoAIAAxADAAIABeACAAMwApACkAIAAqACAARQBGAF8AUgBNAEYAMwBlAGwAZQBjACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABtAGEAcgBrAGUAdAAgAGIAYQBzAGUAZABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfADMAZQBsAGUAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADEAMgAuADEALgAyACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7ADMALABlAGwAZQBjAH0APQAgAFsAIABRAF8AewBlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAAoADEALQAoAFIAUABQACsASgBSAFAAUAApAFwAXAByAGkAZwBoAHQAKQAtAFwAXABsAGUAZgB0AFwAXABsAGUAZgB0ACgAKABSAEUAQwBfAHsAcwB1AHIAcgBlAG4AZABlAHIAZQBkAH0ALQBSAEUAQwBfAHsAbwBuAHMAaQB0AGUAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABcAHIAaQBnAGgAdAApAFwAXAByAGkAZwBoAHQAXQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBSAE0ARgAzACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAMwAsAGUAbABlAGMAfQA9ACAAWwAgAFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0ACgAMQAtACgAUgBQAFAAKwBKAFIAUABQACkAXABcAHIAaQBnAGgAdAApAC0AXABcAGwAZQBmAHQAXABcAGwAZQBmAHQAKAAoAFIARQBDAF8AewBzAHUAcgByAGUAbgBkAGUAcgBlAGQAfQAtAFIARQBDAF8AewBvAG4AcwBpAHQAZQB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAzAH0AXABcAHIAaQBnAGgAdAApAFwAXAByAGkAZwBoAHQAXQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBSAE0ARgAzACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBlAGwAZQBjAFwAIgAsACAAXAAiAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAIgAsACAAXAAiAGsAVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBQAFAAXAAiACwAIABcACIAcgBlAG4AZQB3AGEAYgBsAGUAIABwAG8AdwBlAHIAIABwAGUAcgBjAGUAbgB0AGEAZwBlACAAdQBuAGQAZQByACAATABSAEUAVAAgAGYAbwByACAAdABoAGUAIABhAHAAcABsAGkAYwBhAGIAbABlACAAcABlAHIAaQBvAGQAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgBSAFAAUABcACIALAAgAFwAIgBqAHUAcgBpAHMAZABpAGMAdABpAG8AbgBhAGwAIAByAGUAbgBlAHcAYQBiAGwAZQAgAHAAbwB3AGUAcgAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABmAG8AcgAgAHQAaABlACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHAAZQByAGkAbwBkAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkAFwAIgAsACAAXAAiAGUAbABpAGcAaQBiAGwAZQAgAHIAZQBuAGUAdwBhAGIAbABlACAAZQBuAGUAcgBnAHkAIABjAGUAcgB0AGkAZgBpAGMAYQB0AGUAcwAgAHYAbwBsAHUAbgB0AGEAcgBpAGwAeQAgAHMAdQByAHIAZQBuAGQAZQByAGUAZABcACIALAAgAFwAIgBNAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIARQBDAF8AbwBuAHMAaQB0AGUAXAAiACwAIABcACIAZQBsAGkAZwBpAGIAbABlACAAcgBlAG4AZQB3AGEAYgBsAGUAIABlAG4AZQByAGcAeQAgAGMAZQByAHQAaQBmAGkAYwBhAHQAZQBzACAAaQBzAHMAdQBlAGQAIABmAG8AcgAgAG8AbgBzAGkAdABlACAAZwBlAG4AZQByAGEAdABlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACwAIABcACIATQBXAGgAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBSAE0ARgAzAGUAbABlAGMAXAAiACwAIABcACIAcwBjAG8AcABlACAAMwAgAHIAZQBzAGkAZAB1AGEAbAAgAG0AaQB4ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8AawBXAGgAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAHMAdABhAHQAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAEkAbgAgAG8AcgBkAGUAcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABtAGUAZwBhAHcAYQB0AHQAIABoAG8AdQByAHMAIAB0AG8AIABrAGkAbABvAHcAYQB0AHQAIABoAG8AdQByAHMALAAgAHQAaABlACAAUgBFAEMAXwBzAHUAcgByAGUAbgBkAGUAcgBlAGQAIABhAG4AZAAgAFIARQBDAF8AbwBuAHMAaQB0AGUAIAB2AGEAcgBpAGEAYgBsAGUAcwAgAGEAcgBlACAAbQB1AGwAdABpAHAAbABpAGUAZAAgAGIAeQAgADEAMABeADMAIABpAG4AcwB0AGUAYQBkACAAbwBmACAAMQAwAF4ALQAzAC4AXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAHMAZQBuAHQAIABvAGYAZgAgAHMAaQB0AGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAaQBuACAAYQBuAG8AdABoAGUAcgAgAGYAYQByAG0AaQBuAGcAIABzAHkAcwB0AGUAbQAgAG8AcgAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAXABuAEUAXABuAHQAIABOADIATwBcAG4ARQA9AEUAXwB7AE4AMgBPAH0AKwBFAF8AewBhAGQAfQArAEUAXwB7AGwAZQBhAGMAaAB9AFwAbgBFAF8ATgAyAE8AIAA9ACAAZABpAHIAZQBjAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIABzAG8AaQBsAHMAIABvAHUAdABzAGkAZABlACAAbwBmACAAcwBjAG8AcABlACAAMQAgAGIAbwB1AG4AZABhAHIAeQBcAG4ARQBfAGEAZAAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAcwBvAGkAbABzAFwAbgBFAF8AbABlAGEAYwBoACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIABzAG8AaQBsAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEUAXwBhAGQALAAgAEUAXwBsAGUAYQBjAGgALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAArACAARQBfAGEAZAAgACsAIABFAF8AbABlAGEAYwBoAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABzAGUAbgB0ACAAbwBmAGYAIABzAGkAdABlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGkAbgAgAGEAbgBvAHQAaABlAHIAIABmAGEAcgBtAGkAbgBnACAAcwB5AHMAdABlAG0AIABvAHIAIABlAG4AdABlAHIAcAByAGkAcwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADEAMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBFAF8AewBOADIATwB9ACsARQBfAHsAYQBkAH0AKwBFAF8AewBsAGUAYQBjAGgAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAF8ATgAyAE8AXAAiACwAIABcACIAZABpAHIAZQBjAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIABzAG8AaQBsAHMAIABvAHUAdABzAGkAZABlACAAbwBmACAAcwBjAG8AcABlACAAMQAgAGIAbwB1AG4AZABhAHIAeQBcACIALAAgAFwAIgB0ACAATgAyAE8AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBfAGEAZABcACIALAAgAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAcwBvAGkAbABzAFwAIgAsACAAXAAiAHQAIABOADIATwBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAF8AbABlAGEAYwBoAFwAIgAsACAAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIABzAG8AaQBsAHMAXAAiACwAIABcACIAdAAgAE4AMgBPAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANQBfADEAMwBfADEAXwAzAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AbABpAGQAVwBhAHMAdABlAFQAcgBlAGEAdABtAGUAbgB0AEYAYQBjAGkAbABpAHQAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMwBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGwAaQBkAFcAYQBzAHQAZQBUAHIAZQBhAHQAbQBlAG4AdABGAGEAYwBpAGwAaQB0AHkAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAE4AMgBPACwAIABFAF8AYQBkACwAIABFAF8AbABlAGEAYwBoACwAXABuACAAIAAgACAARQBfAE4AMgBPACAAKwAgAEUAXwBhAGQAIAArACAARQBfAGwAZQBhAGMAaABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMwBfADEAXwAzAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AbABpAGQAVwBhAHMAdABlAFQAcgBlAGEAdABtAGUAbgB0AEYAYQBjAGkAbABpAHQAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwBvAGwAaQBkACAAdwBhAHMAdABlACAAcwBlAG4AdAAgAHQAbwAgAGEAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADMAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBsAGkAZABXAGEAcwB0AGUAVAByAGUAYQB0AG0AZQBuAHQARgBhAGMAaQBsAGkAdAB5AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMwBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGwAaQBkAFcAYQBzAHQAZQBUAHIAZQBhAHQAbQBlAG4AdABGAGEAYwBpAGwAaQB0AHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADMAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBsAGkAZABXAGEAcwB0AGUAVAByAGUAYQB0AG0AZQBuAHQARgBhAGMAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADEAMwAuADEALgAzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMwBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGwAaQBkAFcAYQBzAHQAZQBUAHIAZQBhAHQAbQBlAG4AdABGAGEAYwBpAGwAaQB0AHkAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMwBfADEAXwAzAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AbABpAGQAVwBhAHMAdABlAFQAcgBlAGEAdABtAGUAbgB0AEYAYQBjAGkAbABpAHQAeQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMwBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGwAaQBkAFcAYQBzAHQAZQBUAHIAZQBhAHQAbQBlAG4AdABGAGEAYwBpAGwAaQB0AHkAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQA0AF8AMQBfADEAXwBfADEAXwBFAG0AYgBlAGQAZABlAGQARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBVAHAAcwB0AHIAZQBhAG0ARgByAGUAaQBnAGgAdABcAG4ARQBtAGIAZQBkAGQAZQBkACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdQBwAHMAdAByAGUAYQBtACAAZgByAGUAaQBnAGgAdABcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGYAXABcAGwAZQBmAHQAKAAoAFcAXwBmAFwAXAB0AGkAbQBlAHMAIABEAF8AZgApAFwAXAB0AGkAbQBlAHMAIABFAEYAXwBmAFwAXAByAGkAZwBoAHQAKQBcAG4AVwBfAGYAIAA9ACAAdABvAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAbwBvAGQAcwAgAHQAcgBhAG4AcwBwAG8AcgB0AGUAZAAgAHAAZQByACAAZgByAGUAaQBnAGgAdAAgAHQAeQBwAGUAIABmAFwAbgBEAF8AZgAgAD0AIAB0AG8AdABhAGwAIABkAGkAcwB0AGEAbgBjAGUAIAB0AHIAYQBuAHMAcABvAHIAdABlAGQAIABwAGUAcgAgAGYAcgBlAGkAZwBoAHQAIAB0AHkAcABlACAAZgBcAG4ARQBGAF8AZgAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgByAGUAaQBnAGgAdAAgAHQAeQBwAGUAIABmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVwBfAGYALAAgAEQAXwBmACwAIABFAEYAXwBmACwAXABuACAAIAAgACAAKABXAF8AZgAgACoAIABEAF8AZgApACAAKgAgAEUARgBfAGYAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AYgBlAGQAZABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHAAcwB0AHIAZQBhAG0AIABmAHIAZQBpAGcAaAB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA1AC4AMQA0AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AZgBcAFwAbABlAGYAdAAoACgAVwBfAGYAXABcAHQAaQBtAGUAcwAgAEQAXwBmACkAXABcAHQAaQBtAGUAcwAgAEUARgBfAGYAXABcAHIAaQBnAGgAdAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAXwBmAFwAIgAsACAAXAAiAHQAbwB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAG8AbwBkAHMAIAB0AHIAYQBuAHMAcABvAHIAdABlAGQAIABwAGUAcgAgAGYAcgBlAGkAZwBoAHQAIAB0AHkAcABlACAAZgBcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGYAXAAiACwAIABcACIAdABvAHQAYQBsACAAZABpAHMAdABhAG4AYwBlACAAdAByAGEAbgBzAHAAbwByAHQAZQBkACAAcABlAHIAIABmAHIAZQBpAGcAaAB0ACAAdAB5AHAAZQAgAGYAXAAiACwAIABcACIAawBtAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AZgBcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgByAGUAaQBnAGgAdAAgAHQAeQBwAGUAIABmAFwAIgAsACAAXAAiAHQAIABDAE8AMgBlAC8AKAB0ACAAawBtACkAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBmAFwAIgAsACAAXAAiAGYAcgBlAGkAZwBoAHQAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBHAGUAdABUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAFMAdAByAGkAbgBnACIALAAiAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAHUAZQBsAF8ARwBlAHQAUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAFMAdAByAGkAbgBnACIALAAiAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAHUAZQBsAF8AVABvAHQAYQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBVAG4AaQB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFUAbgBpAHQAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQB2AGUAcwB0AG8AYwBrAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAZQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATQBpAG4AZQByAGEAbABTAHUAcABwAGwAZQBtAGUAbgB0AHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwBYAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwBYAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADUAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAQQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADUAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAQQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA2AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQBtAGUAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADYAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAG0AZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADYAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAG0AZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA2AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQBtAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA2AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQBtAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABTAGUAcgB2AGkAYwBlAHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADcAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUwBlAHIAdgBpAGMAZQBzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABTAGUAcgB2AGkAYwBlAHMAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADcAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUwBlAHIAdgBpAGMAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA4AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFAAYQBjAGsAYQBnAGkAbgBnAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AOQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABHAHIAbwB3AE0AZQBkAGkAYQBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADkAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARwByAG8AdwBNAGUAZABpAGEAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAwAF8AMQBfADEAXwBfADEAXwBPAHQAaABlAHIAUAB1AHIAYwBoAGEAcwBlAGQARwBvAG8AZABzAEEAbgBkAFMAZQByAHYAaQBjAGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAFUAcABzAHQAcgBlAGEAbQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAdQBlAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABVAHAAcwB0AHIAZQBhAG0ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAHUAZQBsAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADIAXwBVAHAAcwB0AHIAZQBhAG0AVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAyAF8AVQBwAHMAdAByAGUAYQBtAFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMwBfAFUAcABzAHQAcgBlAGEAbQBTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMwBfAFUAcABzAHQAcgBlAGEAbQBTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMQBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADEAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMQBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADEAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAyAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAGEAbgB1AHIAZQBTAGUAbgB0AE8AZgBmAFMAaQB0AGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQA0AF8AMQBfADEAXwBfADEAXwBFAG0AYgBlAGQAZABlAGQARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBVAHAAcwB0AHIAZQBhAG0ARgByAGUAaQBnAGgAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -24188,11 +24247,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzACAAaQBuAGMAbAB1AGQAaQBuAGcAIABsAGkAcQB1AGUAZgBpAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgACAAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA1AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAAYwBvAG0AYgB1AHMAdABlAGQAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABDAG8AbgB0AGUAbgB0ACAARgBhAGMAdABvAHIAIAAoAEcASgAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwAKQBcACIALAAgAFwAIgBGAHUAZQBsACAAdQBuAGkAdABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAE8AMgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAEgANABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABOADIATwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAG8AbQBiAGkAbgBlAGQAIABnAGEAcwBlAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADAALgAyACwAIAAwAC4AMAAzACwAIAA1ADEALgA2ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AYQBsACAAbQBpAG4AZQAgAHcAYQBzAHQAZQAgAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4AOQAsACAANAAuADYALAAgADAALgAzACwAIAA1ADYALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAG0AcAByAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAoAHIAZQB2AGUAcgB0AGkAbgBnACAAdABvACAAcwB0AGEAbgBkAGEAcgBkACAAYwBvAG4AZABpAHQAaQBvAG4AcwApAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVQBuAHAAcgBvAGMAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAA2ADIAOQAsACAAXAAiAG0AMwBcACIALAAgADUANgAuADUALAAgADAALgAwADMALAAgADAALgAwADMALAAgADUANgAuADUANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBrAGUAIABvAHYAZQBuACAAZwBhAHMAXAAiACwAIAAwAC4AMAAxADgAMQAsACAAXAAiAG0AMwBcACIALAAgADMANwAuADAALAAgADAALgAwADMALAAgADAALgAwADUALAAgADMANwAuADAAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAbABhAHMAdAAgAGYAdQByAG4AYQBjAGUAIABnAGEAcwBcACIALAAgADAALgAwADAANAAwACwAIABcACIAbQAzAFwAIgAsACAAMgAzADQALgAwACwAIAAwAC4AMAAzACwAIAAwAC4AMAAyACwAIAAyADMANAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwBcACIALAAgADAALgAwADMAOQAwACwAIABcACIAbQAzAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADAANAAsACAAMAAuADAAMwAsACAANgAwAC4AMgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBMAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAGUAbwB1AHMAIABmAG8AcwBzAGkAbAAgAGYAdQBlAGwAcwAgAG8AdABoAGUAcgAgAHQAaABhAG4AIAB0AGgAbwBzAGUAIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMAAuADAAMwA5ADAALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABhAG4AZABmAGkAbABsACAAYgBpAG8AZwBhAHMAIAB0AGgAYQB0ACAAaQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAKABtAGUAdABoAGEAbgBlACAAbwBuAGwAeQApAFwAIgAsACAAMAAuADAAMwA3ADcALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAANgAuADQALAAgADAALgAwADMALAAgADYALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQBlAHQAaABhAG4AZQAgAG8AbgBsAHkAKQBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADYALgA0ACwAIAAwAC4AMAAzACwAIAA2AC4ANAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAsACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHQAaABvAHMAZQAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAwAC4AMAAzADcAMAAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAA2AC4ANAAsACAAMAAuADAAMwAsACAANgAuADQAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAG0AZQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAAMAAuADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAeQBkAHIAbwBnAGUAbgBcACIALAAgADAALgAwADEAMgAyACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADAALgAwACwAIAAwAC4ANQAsACAAMAAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAAiACwAIAAxACwAIABcACIARwBKAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAMQAsACAAXAAiAEcASgBcACIALAAgADYAMAAuADIALAAgADAALgAwADQALAAgADAALgAwADMALAAgADYAMAAuADIANwBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAVABvAHcAbgAgAGcAYQBzACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAB1ADAAMAAyADcAIAB3AGUAcgBlACAAYQBkAGQAZQBkACwAIABlAGEAYwBoACAAdwBpAHQAaAAgAGEAbgAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAMQAgAEcASgAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwALgAgAFQAaABpAHMAIABpAHMAIABmAG8AcgAgAHUAcwBlAHIAcwAgAHcAaABvACAAaABhAHYAZQAgAGYAdQBlAGwAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABkAGEAdABhACAAaQBuACAARwBKACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAbQAzAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBJAG4AZABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAC4AXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA2AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAdABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAE4AYQB0AHUAcgBhAGwAIABHAGEAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE0AZQB0AHIAbwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgAGYAbwByACAATgBhAHQAdQByAGEAbAAgAEcAYQBzACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgBvAG4AIAAtACAATQBlAHQAcgBvAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAMQAzAC4AMQAsACAAMQA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAMQAzAC4AMQAsACAAMQA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgADQALgAwACwAIAA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIAA4AC4AOAAsACAANwAuADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgADEAMAAuADcALAAgADEAMAAuADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIAA0AC4AMQAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIAA0AC4AMAAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgADQALgAxACwAIAA0AC4AMABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAE4AUwBXACAAYQBuAGQAIABBAEMAVAAgAHMAcABsAGkAdAAgAGkAbgB0AG8AIABzAGUAcABhAHIAYQB0AGUAIAByAG8AdwBzAC4AIABcAHUAMAAwADIANwBDAFwAdQAwADAAMgA3ACAAVgBhAGwAdQBlAHMAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAGEAbgBkACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAByAGUAcABsAGEAYwBlAGQAIAB3AGkAdABoACAAdABoAG8AcwBlACAAZgBvAHIAIABWAGkAYwB0AG8AcgBpAGEAIABhAG4AZAAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAHIAZQBzAHAAZQBjAHQAaQB2AGUAbAB5AC4AIAAoAFMAZQBlACAAYQBwAHAAZQBuAGQAaQBjAGUAcwApAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMgAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEEAcwAgAFMAYwBvAHAAZQAgADMAIABmAGEAYwB0AG8AcgBzACAAYQByAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAYQB0ACAAdABoAGUAIABwAG8AaQBuAHQAIAB3AGgAZQByAGUAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABpAHMAIABkAGUAbABpAHYAZQByAGUAZAAgAHQAbwAgAGUAbgBkACAAdQBzAGUAcgBzACwAIABpAHQAIABpAHMAIABuAGUAYwBlAHMAcwBhAHIAeQAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAYQB0ACAAZQBhAGMAaAAgAG8AZgAgAHQAaABlACAAbABvAGEAZAAgAGMAZQBuAHQAcgBlAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBHAGEAcwAgAHIAZQBhAGMAaABlAHMAIABlAG4AZAAgAHUAcwBlAHIAcwAgAGUAaQB0AGgAZQByACAAZgByAG8AbQAgAHQAaABlACAAbQBlAHQAcgBvACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABuAGUAdAB3AG8AcgBrAHMAIABvAHIAIABkAGkAcgBlAGMAdAAgAGYAcgBvAG0AIAB0AGgAZQAgAGgAaQBnAGgAIAAtACAAcAByAGUAcwBzAHUAcgBlACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABwAGkAcABlAGwAaQBuAGUAcwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAEgAbwB1AHMAZQBoAG8AbABkAHMAIABhAG4AZAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB1AHMAZQByAHMAIAB0AGUAbgBkACAAdABvACAAYgBlACAAcwBlAHIAdgBlAGQAIABiAHkAIAB0AGgAZQAgAGYAbwByAG0AZQByACwAIABhAG4AZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAGcAZQBuAGUAcgBhAHQAbwByAHMAIABhAG4AZAAgAGwAYQByAGcAZQAgAGkAbgBkAHUAcwB0AHIAaQBhAGwAIABwAGwAYQBuAHQAcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGwAYQB0AHQAZQByAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBNAGUAdAByAG8AIABpAHMAIABkAGUAZgBpAG4AZQBkACAAYQBzACAAbABvAGMAYQB0AGUAZAAgAG8AbgAgAG8AcgAgAGUAYQBzAHQAIABvAGYAIAB0AGgAZQAgAGQAaQB2AGkAZABpAG4AZwAgAHIAYQBuAGcAZQAgAGkAbgAgAE4AUwBXACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAEMAYQBuAGIAZQByAHIAYQAgAGEAbgBkACAAUQB1AGUAYQBuAGIAZQB5AGEAbgAsACAATQBlAGwAYgBvAHUAcgBuAGUALAAgAEIAcgBpAHMAYgBhAG4AZQAsACAAQQBkAGUAbABhAGkAZABlACAAbwByACAAUABlAHIAdABoAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIATwB0AGgAZQByAHcAaQBzAGUALAAgAHQAaABlACAAbgBvAG4AIAAtACAAbQBlAHQAcgBvACAAZgBhAGMAdABvAHIAIABzAGgAbwB1AGwAZAAgAGIAZQAgAHUAcwBlAGQALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEYAYQBjAHQAbwByAHMAIABhAHIAZQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAG8AcgAgAGEAbABsACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAHcAaABpAGMAaAAgAG0AYQB5ACAAaQBuAGMAbAB1AGQAZQAgAGMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIABcACIAVABhAGIAbABlACAANgAgAGkAcwAgAG4AbwB0ACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHQAbwAgAGUAdABoAGEAbgBlAC4AIABTAGUAZQAgAFQAYQBiAGwAZQAgADcAIABJAG4AZABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZQB0AGgAYQBuAGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEMAIAA9ACAAQwBvAG4AZgBpAGQAZQBuAHQAaQBhAGwALgAgAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIABhAG4AZAAgAHQAaABlACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIABhAHIAZQAgAG4AbwB0ACAAYQB2AGEAaQBsAGEAYgBsAGUAIABkAHUAZQAgAHQAbwAgAGMAbwBuAGYAaQBkAGUAbgB0AGkAYQBsAGkAdAB5ACAAYwBvAG4AcwB0AHIAYQBpAG4AdABzACAAdABoAGEAdAAgAGEAcgBpAHMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAGEAIABsAGkAbQBpAHQAZQBkACAAbgB1AG0AYgBlAHIAIABvAGYAIABOAEcARQBSACAAZABhAHQAYQAgAGkAbgBwAHUAdABzAC4AIABJAHQAIABpAHMAIABzAHUAZwBnAGUAcwB0AGUAZAAgAHQAaABhAHQAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAHQAaABlACAAdQBzAGUAIABvAGYAIAB0AGgAZQAgAFYAaQBjAHQAbwByAGkAYQBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGkAcwAgAGEAcABwAHIAbwBwAHIAaQBhAHQAZQAsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAHcAaABpAGwAZQAgAGYAbwByACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAdABoAGUAIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABpAHMAIABhAHAAcAByAG8AcAByAGkAYQB0AGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZABvACAAbgBvAHQAIABpAG4AYwBsAHUAZABlACAAZgB1AGcAaQB0AGkAdgBlACAAZQBtAGkAcwBzAGkAbwBuACAAbABlAGEAawBhAGcAZQAgAGYAcgBvAG0AIABsAG8AdwAgAHAAcgBlAHMAcwB1AHIAZQAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAcABpAHAAZQBsAGkAbgBlACAAbgBlAHQAdwBvAHIAawBzACAAdwBoAGkAbABlACAAdABoAG8AcwBlACAAZgByAG8AbQAgAGgAaQBnAGgAIABwAHIAZQBzAHMAdQByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAZwBhAHMAIABuAGUAdAB3AG8AcgBrAHMAIABhAHIAZQAgAGMAbwBuAHMAaQBkAGUAcgBlAGQAIABuAGUAZwBsAGkAZwBpAGIAbABlAC4AXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMALAAgAGkAbgBjAGwAdQBkAGkAbgBnACAAYwBlAHIAdABhAGkAbgAgAHAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMALgBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA4AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADUALAAgADgALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACAAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsAHMAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABwAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsACAAdQBzAGUAZAAgAGEAcwAgAGYAdQBlAGwAKQAsACAAZQAuAGcALgAgAGwAdQBiAHIAaQBjAGEAbgB0AHMAXAAiACwAIAAzADgALgA4ACwAIABcACIAawBsAFwAIgAsACAAMQAzAC4AOQAsACAAMAAuADAALAAgADAALgAwACwAIAAxADMALgA5ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABnAHIAZQBhAHMAZQBzAFwAIgAsACAAMwA4AC4AOAAsACAAXAAiAGsAbABcACIALAAgADMALgA1ACwAIAAwAC4AMAAsACAAMAAuADAALAAgADMALgA1ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAHUAZABlACAAbwBpAGwAIABpAG4AYwBsAHUAZABpAG4AZwAgAGMAcgB1AGQAZQAgAG8AaQBsACAAYwBvAG4AZABlAG4AcwBhAHQAZQBzAFwAIgAsACAANAA1AC4AMwAsACAAXAAiAHQAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAANgA5AC4AOAA4ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGwAaQBxAHUAaQBkAHMAXAAiACwAIAA0ADYALgA1ACwAIABcACIAdABcACIALAAgADYAMQAuADAALAAgADAALgAwADgALAAgADAALgAyACwAIAA2ADEALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB1AHQAbwBtAG8AdABpAHYAZQAgAGcAYQBzAG8AbABpAG4AZQAgAC8AIABwAGUAdAByAG8AbAAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADQALgAyACwAIABcACIAawBMAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADIALAAgADAALgAyACwAIAA2ADcALgA4ADAALAAgADEANwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AIABnAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADMALgAxACwAIABcACIAawBMAFwAIgAsACAANgA3ACwAIAAwAC4AMgAsACAAMAAuADIALAAgADYANwAuADQAMAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADcALgA1ACwAIABcACIAawBMAFwAIgAsACAANgA4AC4AOQAsACAAMAAuADAAMQAsACAAMAAuADIALAAgADYAOQAuADEAMQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgAgAHQAdQByAGIAaQBuAGUAIABmAHUAZQBsACAALwAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAAyACwAIAAwAC4AMgAsACAANgA5AC4AOAAyACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdABpAG4AZwAgAG8AaQBsAFwAIgAsACAAMwA3AC4AMwAsACAAXAAiAGsATABcACIALAAgADYAOQAuADUALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA3ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsATABcACIALAAgADYAOQAuADkALAAgADAALgAxACwAIAAwAC4AMgAsACAANwAwAC4AMgAwACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAG8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsATABcACIALAAgADcAMwAuADYALAAgADAALgAwADQALAAgADAALgAyACwAIAA3ADMALgA4ADQALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAGEAcgBvAG0AYQB0AGkAYwAgAGgAeQBkAHIAbwBjAGEAcgBiAG8AbgBzAFwAIgAsACAAMwA0AC4ANAAsACAAXAAiAGsATABcACIALAAgADYAOQAuADcALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA5ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AbAB2AGUAbgB0AHMAOgAgAG0AaQBuAGUAcgBhAGwAIAB0AHUAcgBwAGUAbgB0AGkAbgBlACAAbwByACAAdwBoAGkAdABlACAAcwBwAGkAcgBpAHQAcwBcACIALAAgADMANAAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA3ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4AOQAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABwAGUAdAByAG8AbABlAHUAbQAgAGcAYQBzACAAKABMAFAARwApAFwAIgAsACAAMgA1AC4ANwAsACAAXAAiAGsATABcACIALAAgADYAMAAuADIALAAgADAALgAyACwAIAAwAC4AMgAsACAANgAwAC4ANgAwACwAIAAyADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHAAaAB0AGgAYQBcACIALAAgADMAMQAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAA2ADkALgA4ADIALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGMAbwBrAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAdABcACIALAAgADkAMgAuADYALAAgADAALgAwADgALAAgADAALgAyACwAIAA5ADIALgA4ADgALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAZgBpAG4AZQByAHkAIABnAGEAcwAgAGEAbgBkACAAbABpAHEAdQBpAGQAcwBcACIALAAgADQAMgAuADkALAAgAFwAIgB0AFwAIgAsACAANQA0AC4ANwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAANQA0AC4ANwA2ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAaQBuAGUAcgB5ACAAYwBvAGsAZQBcACIALAAgADMANAAuADIALAAgAFwAIgB0AFwAIgAsACAAOQAyAC4ANgAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADkAMgAuADgAOAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAbwB0AGgAZQByACAAdABoAGEAbgAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAzADQALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOAAsACAAMAAuADAAMgAsACAAMAAuADEALAAgADYAOQAuADkAMgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA0AC4ANgAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBFAHQAaABhAG4AbwBsACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGEAIABmAHUAZQBsACAAaQBuACAAYQBuACAAaQBuAHQAZQByAG4AYQBsACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAGUAbgBnAGkAbgBlAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBmAHUAZQBsAHMAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAdABoAG8AcwBlACAAbQBlAG4AdABpAG8AbgBlAGQAIABpAG4AIAB0AGgAZQAgAGkAdABlAG0AcwAgAGEAYgBvAHYAZQAgAGEAbgBkACAAYgBlAGwAbwB3AFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGEAdgBpAGEAdABpAG8AbgAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADAALgAyADIALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMwAwACwAIABcACIATgBFAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAXAB1ADAAMAAyADcATgBFAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIABhAHMAIAB6AGUAcgBvACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AcwAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABUAHIAYQBuAHMAcABvAHIAdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAxACkAIABhAG4AZAAgAGkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAcwAgAGkAbgAgAGQAaQBmAGYAZQByAGUAbgB0ACAAdAByAGEAbgBzAHAAbwByAHQAIABlAHEAdQBpAHAAbQBlAG4AdABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAOQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIANgAsACAAMQAwACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBhAG4AcwBwAG8AcgB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBGAHUAZQBsACAAYwBvAG0AYgB1AHMAdABlAGQAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABDAG8AbgB0AGUAbgB0ACAARgBhAGMAdABvAHIAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIALAAgAFwAIgBTAG8AdQByAGMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEcAYQBzAG8AbABpAG4AZQBcACIALAAgADMANAAuADIALAAgAFwAIgBrAGwAXAAiACwAIAA2ADcALgA0ACwAIAAwAC4AMAAyACwAIAAwAC4AMgAsACAANgA3AC4ANgAyACwAIAAxADcALgAyACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADkALAAgADAALgAwADEALAAgADAALgA1ACwAIAA3ADAALgA0ADEALAAgADEANwAuADMALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAcABlAHQAcgBvAGwAZQB1AG0AIABnAGEAcwAgACgATABQAEcAKQBcACIALAAgADIANgAuADIALAAgAFwAIgBrAGwAXAAiACwAIAA2ADAALgAyACwAIAAwAC4ANQAsACAAMAAuADMALAAgADYAMQAuADAAMAAsACAAMgAwAC4AMgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARgB1AGUAbAAgAG8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsAbABcACIALAAgADcAMwAuADYALAAgADAALgAwADgALAAgADAALgA1ACwAIAA3ADQALgAxADgALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEUAdABoAGEAbgBvAGwAXAAiACwAIAAyADMALgA0ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAyACwAIAAwAC4AMgAsACAAMAAuADQALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBCAGkAbwBkAGkAZQBzAGUAbABcACIALAAgADMANAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADgALAAgADEALgA3ACwAIAAyAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADEALAAgADAALgA1ACwAIAAwAC4ANQAxACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATwB0AGgAZQByACAAYgBpAG8AZgB1AGUAbABzAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AOAAsACAAMQAuADcALAAgADIALgA1ACwAIABcACIATgBFAFwAIgAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQwBvAG0AcAByAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAANwAuADMALAAgADAALgAzACwAIAA1ADkALgAwACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAGcAaAB0ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgADIANQAuADMALAAgAFwAIgBrAGwAXAAiACwAIAA1ADEALgA0ACwAIAA3AC4AMwAsACAAMAAuADMALAAgADUAOQAuADAALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADIALgA4ACwAIAAwAC4AMwAsACAANQA0AC4ANQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBsAFwAIgAsACAANQAxAC4ANAAsACAAMgAuADgALAAgADAALgAzACwAIAA1ADQALgA1ACwAIAAxADgALgAwACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAHYAIABvAHIAIABoAGkAZwBoAGUAcgBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMAA3ACwAIAAwAC4ANAAsACAANwAwAC4AMwA3ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAGkAaQBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMQAsACAAMAAuADQALAAgADcAMAAuADQALAAgADEANwAuADMALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAIAAtACAARQB1AHIAbwAgAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA0ACwAIAA3ADAALgA1ACwAIAAxADcALgAzACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAHYAIABvAHIAIABoAGkAZwBoAGUAcgBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAANwAsACAAMAAuADQALAAgADAALgA0ADcALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAGkAaQBcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgA0ACwAIAAwAC4ANQAsACAAXAAiAE4ARQBcACIALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAIAATICAARQB1AHIAbwAgAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAyACwAIAAwAC4ANAAsACAAMAAuADYALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEcAYQBzAG8AbABpAG4AZQAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0AFwAIgAsACAAMwAzAC4AMQAsACAAXAAiAGsAbABcACIALAAgADYANwAuADAALAAgADAALgAwADYALAAgADAALgA2ACwAIAA2ADcALgA2ADYALAAgADEAOAAuADAALAAgAFwAIgBOAEcAQQBGACAAMgAwADIANQA6ACAAVABhAGIAbABlACAAOQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AXAAiACwAIABcACIASwBlAHIAbwBzAGUAbgBlACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGYAdQBlAGwAIABpAG4AIABhAG4AIABhAGkAcgBjAHIAYQBmAHQAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4ANgAsACAAMAAuADAAMQAsACAAMAAuADYALAAgADcAMAAuADIAMQAsACAAMQA4AC4AMAAsACAAXAAiAE4ARwBBAEYAIAAyADAAMgA1ADoAIABUAGEAYgBsAGUAIAA5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGEAdgBpAGEAdABpAG8AbgAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAMQAsACAAMAAuADYALAAgADAALgA2ADEALAAgAFwAIgBOAEUAXAAiACwAIABcACIATgBHAEEARgAgADIAMAAyADUAOgAgAFQAYQBiAGwAZQAgADkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAcwBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAawBMAFwAIgAsACAANgA3AC4ANAAsACAAMQAwAC4AMQAsACAAMAAuADMALAAgAFwAIgBcACIALAAgADEANwAuADIALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMgAsACAAMAAuADUALAAgAFwAIgBcACIALAAgADEANwAuADMALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4ANAAuADIALgAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAHMAXAAiACwAIABcACIARgB1AGUAbAAgAE8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsATABcACIALAAgADcAMwAuADYALAAgADAALgAyACwAIAAwAC4ANQAsACAAXAAiAFwAIgAsACAAMQA4AC4AMAAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBmAGYALQByAG8AYQBkACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACAAYQBuAGQAIABmAG8AcgBlAHMAdAByAHkAIABlAHEAdQBpAHAAbQBlAG4AdABcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsATABcACIALAAgADYAOQAuADkALAAgADAALgAzACwAIAAwAC4ANQAsACAAXAAiAFwAIgAsACAAMQA3AC4AMwAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgA0AC4AMgAuADEAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAXAB1ADAAMAAyADcATgBFAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIABhAHMAIAB6AGUAcgBvACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AcwAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAATwBmAGYALQByAGEAZAAgAGUAcQB1AGkAcABtAGUAbgB0ACAAYQBuAGQAIAB2AGUAcwBzAGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABPAGYAZgAtAHIAbwBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAxACkAIABhAG4AZAAgAGkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAIABpAG4AIABvAGYAZgAtAHIAbwBhAGQAIABlAHEAdQBpAHAAbQBlAG4AdAAgAGEAbgBkACAAdgBlAHMAcwBlAGwAcwBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADQALgAyAC4AMQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHQAeQBwAGUAIAB0AFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlACAAcQBcACIALAAgAFwAIgBFAEMAVAByAGEAbgBzACwAcQAgACgARwBKAC8AawBMACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEMATwAyACAARQBGAFQAcgBhAG4ALAAxACwAdABxAGcAIAAoAGsAZwAgAEMATwAyAC0AZQAvAEcASgApAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABDAEgANAAgAEUARgBUAHIAYQBuACwAMQAsAHQAZwBnACAAKABrAGcAIABDAE8AMgAtAGUALwBHAEoAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAATgAyAE8AIABFAEYAVAByAGEAbgAsADEALAB0AGcAZwAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUARgBUAHIAYQBuAHMALAAzACwAcQAgACgAawBnACAAQwBPADIALQBlAC8ARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAXAAiACwAIABcACIAUABlAHQAcgBvAGwAXAAiACwAIAAzADQALgAyACwAIAA2ADcALgA0ACwAIAAxADAALgAxACwAIAAwAC4AMwAsACAAMQA3AC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAZQBzAHMAZQBsAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsAFwAIgAsACAAMwA4AC4ANgAsACAANgA5AC4AOQAsACAAMAAuADIALAAgADAALgA1ACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVgBlAHMAcwBlAGwAXAAiACwAIABcACIARgB1AGUAbAAgAE8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAANwAzAC4ANgAsACAAMAAuADIALAAgADAALgA1ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBmAGYALQByAG8AYQBkACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACAAYQBuAGQAIABmAG8AcgBlAHMAdAByAHkAIABlAHEAdQBpAHAAbQBlAG4AdABcACIALAAgAFwAIgBEAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgADYAOQAuADkALAAgADAALgAzACwAIAAwAC4ANQAsACAAMQA3AC4AMwBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBGAHUAZQBsAF8ARwBlAHQAVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABTAHQAcgBpAG4AZwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALABcAG4AIAAgACAAIABMAEUARgBUACgAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsACAAXAAiACwAQwBlAGwAbAApACAALQAxACkAXABuACkAOwBcAG4AXABuAEYAdQBlAGwAXwBHAGUAdABTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwAUwB0AHIAaQBuAGcAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAXABuACAAIAAgACAAUgBJAEcASABUACgAQwBlAGwAbAAsAEwARQBOACgAQwBlAGwAbAApAC0ARgBJAE4ARAAoAFwAIgAsACAAXAAiACwAQwBlAGwAbAApACkAXABuACkAOwBcAG4AXABuAEYAdQBlAGwAXwBUAG8AdABhAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuAFwAbgA9ACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAHUAZQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgBBAHIAcgBhAHkALAAgAEYAdQBlAGwAVQBzAGUAQQByAHIAYQB5ACwAIABGAHUAZQBsAFUAcwBlACwAIABGAHUAZQBsAFQAeQBwAGUAQQByAHIAYQB5ACwAIABGAHUAZQBsAFQAeQBwAGUALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAUwBVAE0AKABcAG4AIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAEYAdQBlAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAKABGAHUAZQBsAFQAeQBwAGUAQQByAHIAYQB5ACAAPQAgAEYAdQBlAGwAVAB5AHAAZQApACAAKgAgAFwAbgAgACAAIAAgACAAIAAgACAAKABGAHUAZQBsAFUAcwBlAEEAcgByAGEAeQAgAD0AIABGAHUAZQBsAFUAcwBlACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgADAAXABuACAAIAApAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AOAA6ACAARgB1AGUAbAAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADgALgAxACAARgB1AGUAbAAgAFUAcwBlACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAAZgB1AGUAbABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRACwAIABFAEMALAAgAEUARgAsAFwAbgAgACAAIAAgACgAUQAgACoAIABFAEMAIAAqACAARQBGACkAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAbgBRACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAAawBMAFwAbgBFAEMAIAA6ACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAARwBKAC8AawBMAFwAbgBFAEYAIAA6ACAAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBUAHIAYQBuAHMAdABxACwAIABFAEMAXwBUAHIAYQBuAHMAcQAsACAARQBGAF8AVAByAGEAbgBzADEAdABxAGcALABcAG4AIAAgACAAIABWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACgAUQBfAFQAcgBhAG4AcwB0AHEALAAgAEUAQwBfAFQAcgBhAG4AcwBxACwAIABFAEYAXwBUAHIAYQBuAHMAMQB0AHEAZwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIAAyAC4AMwAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBnAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwB0ACAAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBxAFwAXABsAGUAZgB0ACgAUQBfAHsAVAByAGEAbgBzACwAdABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAVAByAGEAbgBzACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFQAcgBhAG4AcwAsADEALAB0AHEAZwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAFQAcgBhAG4AcwB0AHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIABjAG8AbQBiAHUAcwB0AGUAZAAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcACIALAAgAFwAIgBWAGEAcgBpAGUAcwAgAGIAYQBzAGUAZAAgAG8AbgAgAGYAdQBlAGwAIAB0AHkAcABlADoAIABrAEwALAAgAG0AMwAsACAARwBKAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAF8AVAByAGEAbgBzAHEAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXAAiACwAIABcACIARwBKACAALwAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AVAByAGEAbgBzADEAdABxAGcAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBhAG4AcwBcACIALAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBnAFwAIgAsACAAXAAiAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGYAdQBlAGwAcwBcAG4AUQAgADoAIABBAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIAB0AHkAcABlACAAcQAgAHUAcwBlAGQAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgADoAIABrAEwAXABuAEUAQwAgADoAIABFAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzACAAOgAgAEcASgAvAGsATABcAG4ARQBGACAAOgAgAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAIAA6ACAAawBnACAAQwBPADIAZQAgAC8AIABHAEoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AUwBDAHEALAAgAEUAQwBfAFMAQwBxACwAIABFAEYAXwBTAEMAMQBxAGcALABcAG4AIAAgACAAIABWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACgAUQBfAFMAQwBxACwAIABFAEMAXwBTAEMAcQAsACAARQBGAF8AUwBDADEAcQBnACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGcAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA4AC4AMgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMgAuADIAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGUAbgBlAHIAZwB5ACAAcwBvAHUAcgBjAGUAcwAgAC0AIABDAGEAbABjAHUAbABhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AZgAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZwA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AdAAgAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AcQBcAFwAbABlAGYAdAAoAFEAXwB7AFMAQwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUwBDACwAMQAsAHEAZwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AUwBDAHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAFMAQwBxAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIARwBKACAALwAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AUwBDADEAcQBnAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAgAC8AIABHAEoAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBxAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBDAFwAIgAsACAAXAAiAFMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZwBcACIALAAgAFwAIgBHAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADUAOgAgAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANQBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAHYAZQBzAHQAbwBjAGsAXABuAFQAbwB0AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAbABpAHYAZQBzAHQAbwBjAGsAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AbwBcAFwAbABlAGYAdAAoAE4AXwB7AGMAbwB9AFwAXAB0AGkAbQBlAHMAIABXAF8AewBjAG8AfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBjAG8AfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAE4AXwBjAG8AIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABhAG4AaQBtAGEAbABzACAAcAB1AHIAYwBoAGEAcwBlAGQAIABpAG4AIABsAGkAdgBlAHMAdABvAGMAawAgAHQAeQBwAGUAIABjACAAZgByAG8AbQAgAG8AcgBpAGcAaQBuACAAbwBcAG4AVwBfAGMAbwAgAD0AIABhAHYAZQByAGEAZwBlACAAbABpAHYAZQB3AGUAaQBnAGgAdAAgAG8AZgAgAHAAdQByAGMAaABhAHMAZQBkACAAbABpAHYAZQBzAHQAbwBjAGsAIABhAHQAIABwAG8AaQBuAHQAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAXABuAEUARgBfAGMAbwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAYQBuAGQAIABvAHIAaQBnAGkAbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBjAG8ALAAgAFcAXwBjAG8ALAAgAEUARgBfAGMAbwAsAFwAbgAgACAAIAAgACgATgBfAGMAbwAgACoAIABXAF8AYwBvACAAKgAgAEUARgBfAGMAbwApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQB2AGUAcwB0AG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGwAaQB2AGUAcwB0AG8AYwBrAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQB2AGUAcwB0AG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA1AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGMAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBvAFwAXABsAGUAZgB0ACgATgBfAHsAYwBvAH0AXABcAHQAaQBtAGUAcwAgAFcAXwB7AGMAbwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGMAbwB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AYwBvAFwAIgAsACAAXAAiAG4AdQBtAGIAZQByACAAbwBmACAAYQBuAGkAbQBhAGwAcwAgAHAAdQByAGMAaABhAHMAZQBkACAAaQBuACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlACAAYwAgAGYAcgBvAG0AIABvAHIAaQBnAGkAbgAgAG8AXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAXwBjAG8AXAAiACwAIABcACIAYQB2AGUAcgBhAGcAZQAgAGwAaQB2AGUAdwBlAGkAZwBoAHQAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGwAaQB2AGUAcwB0AG8AYwBrACAAYQB0ACAAcABvAGkAbgB0ACAAbwBmACAAcAB1AHIAYwBoAGEAcwBlAFwAIgAsACAAXAAiAGsAZwAvAGgAZQBhAGQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBjAG8AXAAiACwAIABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAGwAaQB2AGUAcwB0AG8AYwBrACAAdAB5AHAAZQAgAGEAbgBkACAAbwByAGkAZwBpAG4AXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAGsAZwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAIABcACIAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbwBcACIALAAgAFwAIgBvAHIAaQBnAGkAbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAZQBkAFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGYAZQBlAGQAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBqAFwAXABsAGUAZgB0ACgAUQBfAGoAXABcAHQAaQBtAGUAcwAgAEUARgBfAGoAXABcAHIAaQBnAGgAdAApAFwAbgBRAF8AagAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABmAGUAZQBkACAAdAB5AHAAZQAgAGoAIABwAHUAcgBjAGgAYQBzAGUAZABcAG4ARQBGAF8AagAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAG8AZgAgAHAAdQByAGMAaABhAHMAZQBkACAAZgBlAGUAZABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGoALAAgAEUARgBfAGoALABcAG4AIAAgACAAIABRAF8AagAgACoAIABFAEYAXwBqAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGYAZQBlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgAyAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGoAXABcAGwAZQBmAHQAKABRAF8AagBcAFwAdABpAG0AZQBzACAARQBGAF8AagBcAFwAcgBpAGcAaAB0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AagBcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABmAGUAZQBkACAAdAB5AHAAZQAgAGoAIABwAHUAcgBjAGgAYQBzAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AagBcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAG8AZgAgAHAAdQByAGMAaABhAHMAZQBkACAAZgBlAGUAZABcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8AawBnAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALAAgAFwAIgBmAGUAZQBkACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBcAG4AVABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABtAGkAbgBlAHIAYQBsACAAcwB1AHAAcABsAGUAbQBlAG4AdABzAFwAbgBFAFwAbgB0ACAAQwBPADIAZQBcAG4ARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AbQBcAFwAbABlAGYAdAAoAFEAXwBtAFwAXAB0AGkAbQBlAHMAIABFAEYAXwBtAFwAXAByAGkAZwBoAHQAKQBcAG4AUQBfAG0AIAA9ACAAdABvAHQAYQBsACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAbQBpAG4AZQByAGEAbAAgAHMAdQBwAHAAbABlAG0AZQBuAHQAIAB0AHkAcABlACAAbQAgAHUAcwBlAGQAXABuAEUARgBfAG0AIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG0AaQBuAGUAcgBhAGwAIABzAHUAcABwAGwAZQBtAGUAbgB0AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATQBpAG4AZQByAGEAbABTAHUAcABwAGwAZQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAG0ALAAgAEUARgBfAG0ALABcAG4AIAAgACAAIABRAF8AbQAgACoAIABFAEYAXwBtAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABtAGkAbgBlAHIAYQBsACAAcwB1AHAAcABsAGUAbQBlAG4AdABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATQBpAG4AZQByAGEAbABTAHUAcABwAGwAZQBtAGUAbgB0AHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA1AC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAG0AXABcAGwAZQBmAHQAKABRAF8AbQBcAFwAdABpAG0AZQBzACAARQBGAF8AbQBcAFwAcgBpAGcAaAB0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATQBpAG4AZQByAGEAbABTAHUAcABwAGwAZQBtAGUAbgB0AHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAG0AXAAiACwAIABcACIAdABvAHQAYQBsACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAbQBpAG4AZQByAGEAbAAgAHMAdQBwAHAAbABlAG0AZQBuAHQAIAB0AHkAcABlACAAbQAgAHUAcwBlAGQAXAAiACwAIABcACIAdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAG0AXAAiACwAIABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG0AaQBuAGUAcgBhAGwAIABzAHUAcABwAGwAZQBtAGUAbgB0AFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAGcAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBtAFwAIgAsACAAXAAiAG0AaQBuAGUAcgBhAGwAIABzAHUAcABwAGwAZQBtAGUAbgB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBmAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagBcAFwAbABlAGYAdAAoAFQATQBfAHsAagBmAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAGYAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBUAE0AXwBqAGYAIAA9ACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGEAbgBkACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXABuAEUARgBfAGYAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABNAF8AagBmACwAIABFAEYAXwBmACwAXABuACAAIAAgACAAKABUAE0AXwBqAGYAIAAqACAARQBGAF8AZgApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADQALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AZgBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGoAXABcAGwAZQBmAHQAKABUAE0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwBmAFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQATQBfAGoAZgBcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAHAAdQByAGMAaABhAHMAZQBkACAAYQBuAGQAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALAAgAFwAIgBrAGcAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBmAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAcAB1AHIAYwBoAGEAcwBlAGQAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAGsAZwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAIABcACIAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBcACIALAAgAFwAIgBpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYwBvAG0AcABvAG4AZQBuAHQAcwBcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGYAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagBcAFwAbABlAGYAdAAoACgARgBfAHsAYwBmAH0AXABcAHQAaQBtAGUAcwAgAFQATQBfAHsAagBmAH0AKQAvADEAMAAwAFwAXAB0AGkAbQBlAHMAIABFAEYAXwBjAFwAXAByAGkAZwBoAHQAKQBcAG4ARgBfAGMAZgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAG8AbQBwAG8AbgBlAG4AdAAgAGMAIABjAG8AbgB0AGEAaQBuAGUAZAAgAHcAaQB0AGgAaQBuACAAdABoAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABmAFwAbgBUAE0AXwBqAGYAIAA9ACAAcQB1AGEAbgB0AGkAdAB5ACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGEAbgBkACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXABuAEUARgBfAGMAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAaABlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAbwBtAHAAbwBuAGUAbgB0ACAAYwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAF8AYwBmACwAIABUAE0AXwBqAGYALAAgAEUARgBfAGMALABcAG4AIAAgACAAIAAoACgARgBfAGMAZgAgACoAIABUAE0AXwBqAGYAKQAgAC8AIAAxADAAMAApACAAKgAgAEUARgBfAGMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAF8AYwBmACwAIABUAE0AXwBqAGYALAAgAEUARgBfAGMALABcAG4AIAAgACAAIAAoAEYAXwBjAGYAIAAqACAAVABNAF8AagBmACkAIAAqACAARQBGAF8AYwAgACoAIAAxADAAXgAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYwBvAG0AcABvAG4AZQBuAHQAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADQALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGYAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagBcAFwAbABlAGYAdAAoAFwAXABmAHIAYQBjAHsARgBfAHsAYwBmAH0AXABcAHQAaQBtAGUAcwAgAFQATQBfAHsAagBmAH0AfQB7ADEAMAAwAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAGMAXABcAHIAaQBnAGgAdAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGYAXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjAFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagBcAFwAbABlAGYAdAAoAEYAXwB7AGMAZgB9AFwAXAB0AGkAbQBlAHMAIABUAE0AXwB7AGoAZgB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwBjAFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAGMAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAG8AbQBwAG8AbgBlAG4AdAAgAGMAIABjAG8AbgB0AGEAaQBuAGUAZAAgAHcAaQB0AGgAaQBuACAAdABoAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABmAFwAIgAsACAAXAAiAHcAdAAlAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABNAF8AagBmAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAcAB1AHIAYwBoAGEAcwBlAGQAIABhAG4AZAAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGMAXAAiACwAIABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAaABlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAbwBtAHAAbwBuAGUAbgB0ACAAYwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8AawBnACAAYwBvAG0AcABvAG4AZQBuAHQAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsACAAXAAiAGYAZQByAHQAaQBsAGkAcwBlAHIAIABjAG8AbQBwAG8AbgBlAG4AdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAIABcACIAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAIABcACIAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAHIAZQBtAG8AdgBlAHMAIABkAGkAdgBpAHMAaQBvAG4AIABiAHkAIAAxADAAMAAgAGYAbwByACAARgBfAGMAZgAsACAAdAByAGUAYQB0AGkAbgBnACAARgBfAGMAZgAgAGEAcwAgAGYAcgBhAGMAdABpAG8AbgAgAGkAbgBzAHQAZQBhAGQAIABvAGYAIABwAGUAcgBjAGUAbgB0ACAAYgBlAGMAYQB1AHMAZQAgAGkAdAAgAGkAcwAgAGEAIABmAHIAYQBjAHQAaQBvAG4AIABpAG4AIABzAGMAbwBwAGUAIAAxACAAZQBxAHUAYQB0AGkAbwBuAHMALgAgAEMAbwBuAHYAZQByAHQAIABrAGcAIAB0AG8AIAB0AG8AbgBuAGUAcwAgAGIAeQAgAG0AdQB0AGkAcABsAHkAaQBuAGcAIABiAHkAIAAxADAAXgAtADMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABwAHIAbwBkAHUAYwB0ACAAZABlAHIAaQB2AGUAZAAgAGYAcgBvAG0AIABjAG8AbQBwAG8AbgBlAG4AdABzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABGAF8AYwBmACwAIABFAEYAXwBjACwAXABuACAAIAAgACAARgBfAGMAZgAgACoAIABFAEYAXwBjAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwBYAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHAAcgBvAGQAdQBjAHQAIABkAGUAcgBpAHYAZQBkACAAZgByAG8AbQAgAGMAbwBtAHAAbwBuAGUAbgB0AHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwBYAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBPADIAZQAvAGsAZwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAEEARgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwBYAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwBmAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBjAFwAXABsAGUAZgB0ACgARgBfAHsAYwBmAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAGMAXABcAHIAaQBnAGgAdAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBfAGMAZgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAG8AbQBwAG8AbgBlAG4AdAAgAGMAIABjAG8AbgB0AGEAaQBuAGUAZAAgAHcAaQB0AGgAaQBuACAAdABoAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABmAFwAIgAsACAAXAAiAHcAdAAlAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AYwBcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdABoAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwBvAG0AcABvAG4AZQBuAHQAIABjAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAGcAIABjAG8AbQBwAG8AbgBlAG4AdABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAIABcACIAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGMAbwBtAHAAbwBuAGUAbgB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBcACIALAAgAFwAIgBpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABUAGgAaQBzACAAZQBxAHUAYQB0AGkAbwBuACAAaQBzACAAYQBkAGQAZQBkACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIABhAG4AIABFAEYAIAB2AGEAbAB1AGUAIABmAHIAbwBtACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGMAbwBtAHAAbwBuAGUAbgB0AHMAIAB0AGgAYQB0ACAAYwBhAG4AIABiAGUAIAB1AHMAZQBkACAAaQBuACAAMQA1AC4ANAAuADEALgAxACAAKAAxACkAXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXABuAFQAbwB0AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAYQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGgAXABcAGwAZQBmAHQAKABRAF8AaABcAFwAdABpAG0AZQBzACAARQBGAF8AaABcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAFEAXwBoACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAGEAYwB0AGkAdgBlACAAaQBuAGcAcgBlAGQAaQBlAG4AdABzACAAaQBuACAAYQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAIAB0AHkAcABlACAAaAAgAHAAdQByAGMAaABhAHMAZQBkACAAYQBuAGQAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAbgBFAEYAXwBoACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGEAZwByAGkAYwBoAGUAbQBpAGMAYQBsACAAYQBjAHQAaQB2AGUAIABpAG4AZwByAGUAZABpAGUAbgB0AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADUAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAQQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AaAAsACAARQBGAF8AaAAsAFwAbgAgACAAIAAgACgAUQBfAGgAIAAqACAARQBGAF8AaAApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHAAdQByAGMAaABhAHMAZQBkACAAYQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADUAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAQQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AaABcAFwAbABlAGYAdAAoAFEAXwBoAFwAXAB0AGkAbQBlAHMAIABFAEYAXwBoAFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBoAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAGEAYwB0AGkAdgBlACAAaQBuAGcAcgBlAGQAaQBlAG4AdABzACAAaQBuACAAYQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAIAB0AHkAcABlACAAaAAgAHAAdQByAGMAaABhAHMAZQBkACAAYQBuAGQAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAIgAsACAAXAAiAGsAZwAgAGEAaQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGgAXAAiACwAIABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHAAdQByAGMAaABhAHMAZQBkACAAYQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAIABhAGMAdABpAHYAZQAgAGkAbgBnAHIAZQBkAGkAZQBuAHQAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAGsAZwAgAGEAaQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGgAXAAiACwAIABcACIAYQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwA2AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQBtAGUAXABuAEUAbQBiAGUAZABkAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGwAaQBtAGUAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0ATQBfAGwAaQBtAGUAXABcAHQAaQBtAGUAcwAgAEUARgBfAGwAXABuAE0AXwBsAGkAbQBlACAAPQAgAHQAbwB0AGEAbAAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAGwAaQBtAGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAbgBFAEYAXwBsACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGwAaQBtAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AXwBsAGkAbQBlACwAIABFAEYAXwBsACwAXABuACAAIAAgACAATQBfAGwAaQBtAGUAIAAqACAARQBGAF8AbABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADYAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAG0AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGIAZQBkAGQAZQBkACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAG8AcgAgAHAAdQByAGMAaABhAHMAZQBkACAAbABpAG0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA2AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQBtAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADYALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADYAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAG0AZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AE0AXwB7AGwAaQBtAGUAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBsAGkAbQBlAFwAIgAsACAAXAAiAHQAbwB0AGEAbAAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAGwAaQBtAGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBsAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGwAaQBtAGUAXAAiACwAIABcACIAdAAgAEMATwAyAGUALwB0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAHMAZQByAHYAaQBjAGUAcwAgAGEAbgBkACAAYwBvAG4AdAByAGEAYwB0AG8AcgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBwAFwAXABsAGUAZgB0ACgAQQBfAHAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHAAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBBAF8AcAAgAD0AIABhAGMAdABpAHYAaQB0AHkAIABkAGEAdABhACAAbwBmACAAdABoAGUAIABzAGUAcgB2AGkAYwBlACAAdABoAGEAdAAgAHcAYQBzACAAcAB1AHIAYwBoAGEAcwBlAGQAXABuAEUARgBfAHAAIAA9ACAAbABpAGYAZQAgAGMAeQBjAGwAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGgAZQAgAHAAdQByAGMAaABhAHMAZQBkACAAcwBlAHIAdgBpAGMAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAF8AcAAsACAARQBGAF8AcAAsAFwAbgAgACAAIAAgACgAQQBfAHAAIAAqACAARQBGAF8AcAApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAHMAZQByAHYAaQBjAGUAcwAgAGEAbgBkACAAYwBvAG4AdAByAGEAYwB0AG8AcgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADcAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUwBlAHIAdgBpAGMAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgA3AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8ANwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABTAGUAcgB2AGkAYwBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBwAFwAXABsAGUAZgB0ACgAQQBfAHAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHAAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAF8AcABcACIALAAgAFwAIgBhAGMAdABpAHYAaQB0AHkAIABkAGEAdABhACAAbwBmACAAdABoAGUAIABzAGUAcgB2AGkAYwBlACAAdABoAGEAdAAgAHcAYQBzACAAcAB1AHIAYwBoAGEAcwBlAGQAXAAiACwAIABcACIAaABhACAAbwByACAAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAHAAXAAiACwAIABcACIAbABpAGYAZQAgAGMAeQBjAGwAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGgAZQAgAHAAdQByAGMAaABhAHMAZQBkACAAcwBlAHIAdgBpAGMAZQBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8AaABhACAAbwByACAAawBnACAAQwBPADIAZQAvAGgAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsACAAXAAiAHMAZQByAHYAaQBjAGUAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwA4AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFAAYQBjAGsAYQBnAGkAbgBnAFwAbgBFAG0AYgBlAGQAZABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHMAZQAgAG8AZgAgAHAAYQBjAGsAYQBnAGkAbgBnACAAbQBhAHQAZQByAGkAYQBsAHMAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBwAFwAXABsAGUAZgB0ACgAUQBfAHAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHAAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRAF8AcAAgAD0AIAB1AG4AaQB0AHMAIABvAGYAIABwAGEAYwBrAGEAZwBpAG4AZwAgAHQAeQBwAGUAIABwAFwAbgBFAEYAXwBwACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABwAGEAYwBrAGEAZwBpAG4AZwAgAHQAeQBwAGUAIABwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAHAALAAgAEUARgBfAHAALABcAG4AIAAgACAAIAAoAFEAXwBwACAAKgAgAEUARgBfAHAAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGIAZQBkAGQAZQBkACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdQBzAGUAIABvAGYAIABwAGEAYwBrAGEAZwBpAG4AZwAgAG0AYQB0AGUAcgBpAGEAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA4AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFAAYQBjAGsAYQBnAGkAbgBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA4AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFAAYQBjAGsAYQBnAGkAbgBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA1AC4AOAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHAAXABcAGwAZQBmAHQAKABRAF8AcABcAFwAdABpAG0AZQBzACAARQBGAF8AcABcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBfAHAAXAAiACwAIABcACIAdQBuAGkAdABzACAAbwBmACAAcABhAGMAawBhAGcAaQBuAGcAIAB0AHkAcABlACAAcABcACIALAAgAFwAIgB1AG4AaQB0AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBwAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABwAGEAYwBrAGEAZwBpAG4AZwAgAHQAeQBwAGUAIABwAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwB1AG4AaQB0AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcABcACIALAAgAFwAIgBwAGEAYwBrAGEAZwBpAG4AZwAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABDAGgAYQBuAGcAZQBkACAAdQBuAGkAdAAgAG8AZgAgAFEAIABmAHIAbwBtACAAXAB1ADAAMAAyADcAdQBuAGkAdABzAFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcAawBnAFwAdQAwADAAMgA3ACAAYQBzACAARQBGACAAZABhAHQAYQAgAGkAcwAgAGkAbgAgAGsAZwAuAFwAIgApADsAXABuACAAIABcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAFwAbgBFAG0AYgBlAGQAZABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHMAZQAgAG8AZgAgAGcAcgBvAHcAIABtAGUAZABpAGEAIABwAHIAbwBkAHUAYwB0AHMAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBnAFwAXABsAGUAZgB0ACgAUQBfAGcAXABcAHQAaQBtAGUAcwAgAEUARgBfAGcAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRAF8AZwAgAD0AIAB0AG8AdABhAGwAIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABnAHIAbwB3ACAAbQBlAGQAaQBhACAAdAB5AHAAZQAgAGcAXABuAEUARgBfAGcAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGcAcgBvAHcAIABtAGUAZABpAGEAIAB0AHkAcABlACAAZwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBnACwAIABFAEYAXwBnACwAXABuACAAIAAgACAAKABRAF8AZwAgACoAIABFAEYAXwBnACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADkAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARwByAG8AdwBNAGUAZABpAGEAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBiAGUAZABkAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHUAcwBlACAAbwBmACAAZwByAG8AdwAgAG0AZQBkAGkAYQAgAHAAcgBvAGQAdQBjAHQAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABHAHIAbwB3AE0AZQBkAGkAYQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AOQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABHAHIAbwB3AE0AZQBkAGkAYQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADkALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADkAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARwByAG8AdwBNAGUAZABpAGEAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADkAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARwByAG8AdwBNAGUAZABpAGEAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBnAFwAXABsAGUAZgB0ACgAUQBfAGcAXABcAHQAaQBtAGUAcwAgAEUARgBfAGcAXABcAHIAaQBnAGgAdAApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBnAFwAIgAsACAAXAAiAHQAbwB0AGEAbAAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAGcAcgBvAHcAIABtAGUAZABpAGEAIAB0AHkAcABlACAAZwBcACIALAAgAFwAIgBrAGcAIABvAHIAIABtADMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBnAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABnAHIAbwB3ACAAbQBlAGQAaQBhACAAdAB5AHAAZQAgAGcAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAGsAZwAgAG8AcgAgAGsAZwAgAEMATwAyAGUALwBtADMAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBnAFwAIgAsACAAXAAiAGcAcgBvAHcAIABtAGUAZABpAGEAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAFwAbgBPAHQAaABlAHIAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGcAbwBvAGQAcwAgAGEAbgBkACAAcwBlAHIAdgBpAGMAZQBzACAAZwBlAG4AZQByAGkAYwAgAGUAcwB0AGkAbQBhAHQAZQBcAG4AZQBtAGkAcwBzAGkAbwBuAHMAXABuAHQAIABDAE8AMgBlAFwAbgBlAG0AaQBzAHMAaQBvAG4AcwA9AGEAYwB0AGkAdgBpAHQAeQBfAGQAYQB0AGEAXABcAHQAaQBtAGUAcwAgAGUAbQBpAHMAcwBpAG8AbgBfAGYAYQBjAHQAbwByAFwAbgBhAGMAdABpAHYAaQB0AHkAXwBkAGEAdABhACAAPQAgAG0AZQBhAHMAdQByAGUAZAAgAGEAYwB0AGkAdgBpAHQAeQAgAGYAbwByACAAdABoAGUAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGcAbwBvAGQAIABvAHIAIABzAGUAcgB2AGkAYwBlAFwAbgBlAG0AaQBzAHMAaQBvAG4AXwBmAGEAYwB0AG8AcgAgAD0AIABsAGkAZgBlAGMAeQBjAGwAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAYQBjAHQAaQB2AGkAdAB5AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQBjAHQAaQB2AGkAdAB5AF8AZABhAHQAYQAsACAAZQBtAGkAcwBzAGkAbwBuAF8AZgBhAGMAdABvAHIALABcAG4AIAAgACAAIABhAGMAdABpAHYAaQB0AHkAXwBkAGEAdABhACAAKgAgAGUAbQBpAHMAcwBpAG8AbgBfAGYAYQBjAHQAbwByAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAwAF8AMQBfADEAXwBfADEAXwBPAHQAaABlAHIAUAB1AHIAYwBoAGEAcwBlAGQARwBvAG8AZABzAEEAbgBkAFMAZQByAHYAaQBjAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwB0AGgAZQByACAAcAB1AHIAYwBoAGEAcwBlAGQAIABnAG8AbwBkAHMAIABhAG4AZAAgAHMAZQByAHYAaQBjAGUAcwAgAGcAZQBuAGUAcgBpAGMAIABlAHMAdABpAG0AYQB0AGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGUAbQBpAHMAcwBpAG8AbgBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA1AC4AMQAwACwAIABnAGUAbgBlAHIAaQBjACAAcABsAGEAYwBlAGgAbwBsAGQAZQByACAAZQBxAHUAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZQBtAGkAcwBzAGkAbwBuAHMAPQBhAGMAdABpAHYAaQB0AHkAXABcAF8AZABhAHQAYQBcAFwAdABpAG0AZQBzACAAZQBtAGkAcwBzAGkAbwBuAFwAXABfAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGEAYwB0AGkAdgBpAHQAeQBfAGQAYQB0AGEAXAAiACwAIABcACIAbQBlAGEAcwB1AHIAZQBkACAAYQBjAHQAaQB2AGkAdAB5ACAAZgBvAHIAIAB0AGgAZQAgAHAAdQByAGMAaABhAHMAZQBkACAAZwBvAG8AZAAgAG8AcgAgAHMAZQByAHYAaQBjAGUAXAAiACwAIABcACIAdgBhAHIAaQBlAHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AXwBmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBsAGkAZgBlAGMAeQBjAGwAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAYQBjAHQAaQB2AGkAdAB5AFwAIgAsACAAXAAiAHYAYQByAGkAZQBzAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABVAHAAcwB0AHIAZQBhAG0ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAHUAZQBsAFwAbgBUAG8AdABhAGwAIAB1AHAAcwB0AHIAZQBhAG0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAGMAbwBwAGUAIAAxACAAZgB1AGUAbAAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgBcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHEARQBfAHsAVwBUAFQALAB0AHIAYQBuAHMALABxAH0AKwBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHEARQBfAHsAVwBUAFQALABTAEMALABxAH0AXABuAEUAXwBXAFQAVAB0AHIAYQBuAHMAcQAgAD0AIAB1AHAAcwB0AHIAZQBhAG0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAGMAbwBwAGUAIAAxACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsACAAdQBzAGUAXABuAEUAXwBXAFQAVABTAEMAcQAgAD0AIAB1AHAAcwB0AHIAZQBhAG0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAGMAbwBwAGUAIAAxACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABmAHUAZQBsACAAdQBzAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AVwBUAFQAdAByAGEAbgBzAHEALAAgAEUAXwBXAFQAVABTAEMAcQAsAFwAbgAgACAAIAAgAEUAXwBXAFQAVAB0AHIAYQBuAHMAcQAgACsAIABFAF8AVwBUAFQAUwBDAHEAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABVAHAAcwB0AHIAZQBhAG0ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAHUAZQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIAB1AHAAcwB0AHIAZQBhAG0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAGMAbwBwAGUAIAAxACAAZgB1AGUAbAAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABVAHAAcwB0AHIAZQBhAG0ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAHUAZQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADEAMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHEARQBfAHsAVwBUAFQALAB0AHIAYQBuAHMALABxAH0AKwBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAHEARQBfAHsAVwBUAFQALABTAEMALABxAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAFUAcABzAHQAcgBlAGEAbQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAdQBlAGwAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBfAFcAVABUAHQAcgBhAG4AcwBxAFwAIgAsACAAXAAiAHUAcABzAHQAcgBlAGEAbQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAYwBvAHAAZQAgADEAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAIAB1AHMAZQBcACIALAAgAFwAIgB0ACAAQwBPADIAZQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAYgB5ACAAMQA1AC4AMQAxAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBfAFcAVABUAFMAQwBxAFwAIgAsACAAXAAiAHUAcABzAHQAcgBlAGEAbQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAYwBvAHAAZQAgADEAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAGYAdQBlAGwAIAB1AHMAZQBcACIALAAgAFwAIgB0ACAAQwBPADIAZQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAYgB5ACAAMQA1AC4AMQAxAC4AMQAuADEAIAAoADMAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBVAHAAcwB0AHIAZQBhAG0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAGMAbwBwAGUAIAAxACAAZgB1AGUAbAAgAHUAcwBlACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAHAAdQByAHAAbwBzAGUAcwBcAG4ARQBfAFcAVABUAHQAcgBhAG4AcwBxAFwAbgB0ACAAQwBPADIAZQBcAG4ARQBfAHsAVwBUAFQALAB0AHIAYQBuAHMALABxAH0APQBRAF8AewBUAHIAYQBuAHMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAVAByAGEAbgBzACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFQAcgBhAG4AcwAsADMALABxAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAFEAXwBUAHIAYQBuAHMAcQAgAD0AIABhAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXABuAEUAQwBfAFQAcgBhAG4AcwBxACAAPQAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAbgBFAEYAXwBUAHIAYQBuAHMAMwBxACAAPQAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBUAHIAYQBuAHMAcQAsACAARQBDAF8AVAByAGEAbgBzAHEALAAgAEUARgBfAFQAcgBhAG4AcwAzAHEALABcAG4AIAAgACAAIAAoAFEAXwBUAHIAYQBuAHMAcQAgACoAIABFAEMAXwBUAHIAYQBuAHMAcQAgACoAIABFAEYAXwBUAHIAYQBuAHMAMwBxACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAyAF8AVQBwAHMAdAByAGUAYQBtAFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFUAcABzAHQAcgBlAGEAbQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAYwBvAHAAZQAgADEAIABmAHUAZQBsACAAdQBzAGUAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAcAB1AHIAcABvAHMAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AVwBUAFQAdAByAGEAbgBzAHEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAyAF8AVQBwAHMAdAByAGUAYQBtAFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADIAXwBVAHAAcwB0AHIAZQBhAG0AVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgAxADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAyAF8AVQBwAHMAdAByAGUAYQBtAFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAyAF8AVQBwAHMAdAByAGUAYQBtAFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBXAFQAVAAsAHQAcgBhAG4AcwAsAHEAfQA9AFEAXwB7AFQAcgBhAG4AcwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBUAHIAYQBuAHMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAVAByAGEAbgBzACwAMwAsAHEAfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADIAXwBVAHAAcwB0AHIAZQBhAG0AVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AVAByAGEAbgBzAHEAXAAiACwAIABcACIAYQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAcQAgAGMAbwBtAGIAdQBzAHQAZQBkACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgAsACAAXAAiAGsATABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBfAFQAcgBhAG4AcwBxAFwAIgAsACAAXAAiAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgAsACAAXAAiAEcASgAvAGsATAAgAG8AcgAgAEcASgAvAG0AMwBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFQAcgBhAG4AcwAzAHEAXAAiACwAIABcACIAcwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBHAEoAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBcAG4AVQBwAHMAdAByAGUAYQBtACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwBjAG8AcABlACAAMQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgB1AGUAbAAgAHUAcwBlAFwAbgBFAF8AVwBUAFQAUwBDAHEAXABuAHQAIABDAE8AMgBlAFwAbgBFAF8AewBXAFQAVAAsAFMAQwAsAHEAfQA9AFEAXwB7AFMAQwAsAHEAfQBcAFwAdABpAG0AZQBzACAARQBDAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAUwBDACwAMwAsAHEAfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4AUQBfAFMAQwBxACAAPQAgAGEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXABuAEUAQwBfAFMAQwBxACAAPQAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXABuAEUARgBfAFMAQwAzAHEAIAA9ACAAcwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEAXwBTAEMAcQAsACAARQBDAF8AUwBDAHEALAAgAEUARgBfAFMAQwAzAHEALABcAG4AIAAgACAAIAAoAFEAXwBTAEMAcQAgACoAIABFAEMAXwBTAEMAcQAgACoAIABFAEYAXwBTAEMAMwBxACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVQBwAHMAdAByAGUAYQBtACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwBjAG8AcABlACAAMQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgB1AGUAbAAgAHUAcwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMwBfAFUAcABzAHQAcgBlAGEAbQBTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBXAFQAVABTAEMAcQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADUALgAxADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAVwBUAFQALABTAEMALABxAH0APQBRAF8AewBTAEMALABxAH0AXABcAHQAaQBtAGUAcwAgAEUAQwBfAHsAUwBDACwAcQB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFMAQwAsADMALABxAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AUwBDAHEAXAAiACwAIABcACIAYQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAcQAgAHUAcwBlAGQAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwBcACIALAAgAFwAIgBrAEwAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEMAXwBTAEMAcQBcACIALAAgAFwAIgBlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzAFwAIgAsACAAXAAiAEcASgAvAGsATABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAFMAQwAzAHEAXAAiACwAIABcACIAcwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAawBnACAAQwBPADIAZQAvAEcASgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAcwB0AGEAdABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQBcACIALAAgAFwAIgBtAGUAdAByAG8AcABvAGwAaQB0AGEAbgAvAG4AbwBuAC0AbQBlAHQAcgBvAHAAbwBsAGkAdABhAG4AIABsAG8AYwBhAHQAaQBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHMAdABhAHQAZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAbQBlAHQAcgBvAC8AbgBvAG4ALQBtAGUAdAByAG8AXAB1ADAAMAAyADcAIABhAHIAZwB1AG0AZQBuAHQAcwAgAGEAcwAgAGcAYQBzAGUAbwB1AHMAIABzAGMAbwBwAGUAIAAzACAARQBGAHMAIABhAHIAZQAgAHMAdABhAHQAZQAgAGEAbgBkACAAbQBlAHQAcgBvAC8AbgBvAG4ALQBtAGUAdAByAG8AIABsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQALgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAFwAbgBTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABsAG8AYwBhAHQAaQBvAG4AIABiAGEAcwBlAGQAXABuAEUAXwAzAGUAbABlAGMAXABuAHQAIABDAE8AMgBlAFwAbgBFAF8AewAzACwAZQBsAGUAYwB9AD0AUQBfAHsAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7ADMALABlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAFEAXwBlAGwAZQBjACAAPQAgAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAbgBFAEYAXwAzAGUAbABlAGMAIAA9ACAAcwBjAG8AcABlACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMQBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAF8AZQBsAGUAYwAsACAARQBGAF8AMwBlAGwAZQBjACwAXABuACAAIAAgACAAKABRAF8AZQBsAGUAYwAgACoAIABFAEYAXwAzAGUAbABlAGMAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADEAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAGwAbwBjAGEAdABpAG8AbgAgAGIAYQBzAGUAZABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADEAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwAzAGUAbABlAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADEAMgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADEAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAMwAsAGUAbABlAGMAfQA9AFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewAzACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMQBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAF8AZQBsAGUAYwBcACIALAAgAFwAIgBhAG0AbwB1AG4AdAAgAG8AZgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHAAdQByAGMAaABhAHMAZQBkACAAZgByAG8AbQAgAHQAaABlACAAZwByAGkAZABcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfADMAZQBsAGUAYwBcACIALAAgAFwAIgBzAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHAAdQByAGMAaABhAHMAZQBkACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUALwBrAFcAaABcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGcAXAAiACwAIABcACIAZwByAGkAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAHcAYQBzACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAFwAbgBTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABtAGEAcgBrAGUAdAAgAGIAYQBzAGUAZABcAG4ARQBfADMAZQBsAGUAYwBcAG4AdAAgAEMATwAyAGUAXABuAEUAXwB7ADMALABlAGwAZQBjAH0APQBcAFwAbABlAGYAdABbAFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0ACgAMQAtACgAUgBQAFAAKwBKAFIAUABQACkAXABcAHIAaQBnAGgAdAApAC0AXABcAGwAZQBmAHQAKABSAEUAQwBfAHsAcwB1AHIAcgBlAG4AZABlAHIAZQBkAH0ALQBSAEUAQwBfAHsAbwBuAHMAaQB0AGUAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABcAHIAaQBnAGgAdABdAFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AFIATQBGADMALABlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAFEAXwBlAGwAZQBjACAAPQAgAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAbgBSAFAAUAAgAD0AIAByAGUAbgBlAHcAYQBiAGwAZQAgAHAAbwB3AGUAcgAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIAB1AG4AZABlAHIAIABMAFIARQBUACAAZgBvAHIAIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAYgBsAGUAIABwAGUAcgBpAG8AZABcAG4ASgBSAFAAUAAgAD0AIABqAHUAcgBpAHMAZABpAGMAdABpAG8AbgBhAGwAIAByAGUAbgBlAHcAYQBiAGwAZQAgAHAAbwB3AGUAcgAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABmAG8AcgAgAHQAaABlACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHAAZQByAGkAbwBkAFwAbgBSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAgAD0AIABlAGwAaQBnAGkAYgBsAGUAIAByAGUAbgBlAHcAYQBiAGwAZQAgAGUAbgBlAHIAZwB5ACAAYwBlAHIAdABpAGYAaQBjAGEAdABlAHMAIAB2AG8AbAB1AG4AdABhAHIAaQBsAHkAIABzAHUAcgByAGUAbgBkAGUAcgBlAGQAXABuAFIARQBDAF8AbwBuAHMAaQB0AGUAIAA9ACAAZQBsAGkAZwBpAGIAbABlACAAcgBlAG4AZQB3AGEAYgBsAGUAIABlAG4AZQByAGcAeQAgAGMAZQByAHQAaQBmAGkAYwBhAHQAZQBzACAAaQBzAHMAdQBlAGQAIABmAG8AcgAgAG8AbgBzAGkAdABlACAAZwBlAG4AZQByAGEAdABlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXABuAEUARgBfAFIATQBGADMAZQBsAGUAYwAgAD0AIABzAGMAbwBwAGUAIAAzACAAcgBlAHMAaQBkAHUAYQBsACAAbQBpAHgAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAyAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAFIAUABQACwAIABKAFIAUABQACwAIABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAsACAAUgBFAEMAXwBvAG4AcwBpAHQAZQAsACAARQBGAF8AUgBNAEYAMwBlAGwAZQBjACwAXABuACAAIAAgACAAKAAoAFEAXwBlAGwAZQBjACAAKgAgACgAMQAgAC0AIAAoAFIAUABQACAAKwAgAEoAUgBQAFAAKQApACkAIAAtACAAKAAoAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAALQAgAFIARQBDAF8AbwBuAHMAaQB0AGUAKQAgACoAIAAxADAAIABeACAALQAzACkAKQAgACoAIABFAEYAXwBSAE0ARgAzAGUAbABlAGMAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAyAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBNAGEAcgBrAGUAdABCAGEAcwBlAGQAVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBfAGUAbABlAGMALAAgAFIAUABQACwAIABKAFIAUABQACwAIABSAEUAQwBfAHMAdQByAHIAZQBuAGQAZQByAGUAZAAsACAAUgBFAEMAXwBvAG4AcwBpAHQAZQAsACAARQBGAF8AUgBNAEYAMwBlAGwAZQBjACwAXABuACAAIAAgACAAKAAoAFEAXwBlAGwAZQBjACAAKgAgACgAMQAgAC0AIAAoAFIAUABQACAAKwAgAEoAUgBQAFAAKQApACkAIAAtACAAKAAoAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkACAALQAgAFIARQBDAF8AbwBuAHMAaQB0AGUAKQAgACoAIAAxADAAIABeACAAMwApACkAIAAqACAARQBGAF8AUgBNAEYAMwBlAGwAZQBjACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAGMAbwBwAGUAIAAzACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAIABtAGEAcgBrAGUAdAAgAGIAYQBzAGUAZABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfADMAZQBsAGUAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADEAMgAuADEALgAyACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7ADMALABlAGwAZQBjAH0APQAgAFsAIABRAF8AewBlAGwAZQBjAH0AXABcAHQAaQBtAGUAcwBcAFwAbABlAGYAdAAoADEALQAoAFIAUABQACsASgBSAFAAUAApAFwAXAByAGkAZwBoAHQAKQAtAFwAXABsAGUAZgB0AFwAXABsAGUAZgB0ACgAKABSAEUAQwBfAHsAcwB1AHIAcgBlAG4AZABlAHIAZQBkAH0ALQBSAEUAQwBfAHsAbwBuAHMAaQB0AGUAfQBcAFwAcgBpAGcAaAB0ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABcAHIAaQBnAGgAdAApAFwAXAByAGkAZwBoAHQAXQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBSAE0ARgAzACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAMwAsAGUAbABlAGMAfQA9ACAAWwAgAFEAXwB7AGUAbABlAGMAfQBcAFwAdABpAG0AZQBzAFwAXABsAGUAZgB0ACgAMQAtACgAUgBQAFAAKwBKAFIAUABQACkAXABcAHIAaQBnAGgAdAApAC0AXABcAGwAZQBmAHQAXABcAGwAZQBmAHQAKAAoAFIARQBDAF8AewBzAHUAcgByAGUAbgBkAGUAcgBlAGQAfQAtAFIARQBDAF8AewBvAG4AcwBpAHQAZQB9AFwAXAByAGkAZwBoAHQAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAzAH0AXABcAHIAaQBnAGgAdAApAFwAXAByAGkAZwBoAHQAXQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBSAE0ARgAzACwAZQBsAGUAYwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAXwBlAGwAZQBjAFwAIgAsACAAXAAiAGEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAIgAsACAAXAAiAGsAVwBoAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBQAFAAXAAiACwAIABcACIAcgBlAG4AZQB3AGEAYgBsAGUAIABwAG8AdwBlAHIAIABwAGUAcgBjAGUAbgB0AGEAZwBlACAAdQBuAGQAZQByACAATABSAEUAVAAgAGYAbwByACAAdABoAGUAIABhAHAAcABsAGkAYwBhAGIAbABlACAAcABlAHIAaQBvAGQAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgBSAFAAUABcACIALAAgAFwAIgBqAHUAcgBpAHMAZABpAGMAdABpAG8AbgBhAGwAIAByAGUAbgBlAHcAYQBiAGwAZQAgAHAAbwB3AGUAcgAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABmAG8AcgAgAHQAaABlACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHAAZQByAGkAbwBkAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIARQBDAF8AcwB1AHIAcgBlAG4AZABlAHIAZQBkAFwAIgAsACAAXAAiAGUAbABpAGcAaQBiAGwAZQAgAHIAZQBuAGUAdwBhAGIAbABlACAAZQBuAGUAcgBnAHkAIABjAGUAcgB0AGkAZgBpAGMAYQB0AGUAcwAgAHYAbwBsAHUAbgB0AGEAcgBpAGwAeQAgAHMAdQByAHIAZQBuAGQAZQByAGUAZABcACIALAAgAFwAIgBNAFcAaABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIARQBDAF8AbwBuAHMAaQB0AGUAXAAiACwAIABcACIAZQBsAGkAZwBpAGIAbABlACAAcgBlAG4AZQB3AGEAYgBsAGUAIABlAG4AZQByAGcAeQAgAGMAZQByAHQAaQBmAGkAYwBhAHQAZQBzACAAaQBzAHMAdQBlAGQAIABmAG8AcgAgAG8AbgBzAGkAdABlACAAZwBlAG4AZQByAGEAdABlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACwAIABcACIATQBXAGgAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBSAE0ARgAzAGUAbABlAGMAXAAiACwAIABcACIAcwBjAG8AcABlACAAMwAgAHIAZQBzAGkAZAB1AGEAbAAgAG0AaQB4ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlAC8AawBXAGgAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAHMAdABhAHQAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAEkAbgAgAG8AcgBkAGUAcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABtAGUAZwBhAHcAYQB0AHQAIABoAG8AdQByAHMAIAB0AG8AIABrAGkAbABvAHcAYQB0AHQAIABoAG8AdQByAHMALAAgAHQAaABlACAAUgBFAEMAXwBzAHUAcgByAGUAbgBkAGUAcgBlAGQAIABhAG4AZAAgAFIARQBDAF8AbwBuAHMAaQB0AGUAIAB2AGEAcgBpAGEAYgBsAGUAcwAgAGEAcgBlACAAbQB1AGwAdABpAHAAbABpAGUAZAAgAGIAeQAgADEAMABeADMAIABpAG4AcwB0AGUAYQBkACAAbwBmACAAMQAwAF4ALQAzAC4AXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAHMAZQBuAHQAIABvAGYAZgAgAHMAaQB0AGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAaQBuACAAYQBuAG8AdABoAGUAcgAgAGYAYQByAG0AaQBuAGcAIABzAHkAcwB0AGUAbQAgAG8AcgAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAXABuAEUAXABuAHQAIABOADIATwBcAG4ARQA9AEUAXwB7AE4AMgBPAH0AKwBFAF8AewBhAGQAfQArAEUAXwB7AGwAZQBhAGMAaAB9AFwAbgBFAF8ATgAyAE8AIAA9ACAAZABpAHIAZQBjAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIABzAG8AaQBsAHMAIABvAHUAdABzAGkAZABlACAAbwBmACAAcwBjAG8AcABlACAAMQAgAGIAbwB1AG4AZABhAHIAeQBcAG4ARQBfAGEAZAAgAD0AIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAcwBvAGkAbABzAFwAbgBFAF8AbABlAGEAYwBoACAAPQAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIABzAG8AaQBsAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEUAXwBhAGQALAAgAEUAXwBsAGUAYQBjAGgALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAArACAARQBfAGEAZAAgACsAIABFAF8AbABlAGEAYwBoAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABzAGUAbgB0ACAAbwBmAGYAIABzAGkAdABlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGkAbgAgAGEAbgBvAHQAaABlAHIAIABmAGEAcgBtAGkAbgBnACAAcwB5AHMAdABlAG0AIABvAHIAIABlAG4AdABlAHIAcAByAGkAcwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADEAMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBFAF8AewBOADIATwB9ACsARQBfAHsAYQBkAH0AKwBFAF8AewBsAGUAYQBjAGgAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAF8ATgAyAE8AXAAiACwAIABcACIAZABpAHIAZQBjAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIABzAG8AaQBsAHMAIABvAHUAdABzAGkAZABlACAAbwBmACAAcwBjAG8AcABlACAAMQAgAGIAbwB1AG4AZABhAHIAeQBcACIALAAgAFwAIgB0ACAATgAyAE8AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBfAGEAZABcACIALAAgAFwAIgBuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAcwBvAGkAbABzAFwAIgAsACAAXAAiAHQAIABOADIATwBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAF8AbABlAGEAYwBoAFwAIgAsACAAXAAiAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIABzAG8AaQBsAHMAXAAiACwAIABcACIAdAAgAE4AMgBPAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEANQBfADEAMwBfADEAXwAzAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AbABpAGQAVwBhAHMAdABlAFQAcgBlAGEAdABtAGUAbgB0AEYAYQBjAGkAbABpAHQAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMwBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGwAaQBkAFcAYQBzAHQAZQBUAHIAZQBhAHQAbQBlAG4AdABGAGEAYwBpAGwAaQB0AHkAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBfAE4AMgBPACwAIABFAF8AYQBkACwAIABFAF8AbABlAGEAYwBoACwAXABuACAAIAAgACAARQBfAE4AMgBPACAAKwAgAEUAXwBhAGQAIAArACAARQBfAGwAZQBhAGMAaABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMwBfADEAXwAzAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AbABpAGQAVwBhAHMAdABlAFQAcgBlAGEAdABtAGUAbgB0AEYAYQBjAGkAbABpAHQAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcwBvAGwAaQBkACAAdwBhAHMAdABlACAAcwBlAG4AdAAgAHQAbwAgAGEAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAGYAYQBjAGkAbABpAHQAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADMAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBsAGkAZABXAGEAcwB0AGUAVAByAGUAYQB0AG0AZQBuAHQARgBhAGMAaQBsAGkAdAB5AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMwBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGwAaQBkAFcAYQBzAHQAZQBUAHIAZQBhAHQAbQBlAG4AdABGAGEAYwBpAGwAaQB0AHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADMAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAbwBsAGkAZABXAGEAcwB0AGUAVAByAGUAYQB0AG0AZQBuAHQARgBhAGMAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEANQAuADEAMwAuADEALgAzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMwBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGwAaQBkAFcAYQBzAHQAZQBUAHIAZQBhAHQAbQBlAG4AdABGAGEAYwBpAGwAaQB0AHkAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEAMwBfADEAXwAzAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAG8AbABpAGQAVwBhAHMAdABlAFQAcgBlAGEAdABtAGUAbgB0AEYAYQBjAGkAbABpAHQAeQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMwBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwBvAGwAaQBkAFcAYQBzAHQAZQBUAHIAZQBhAHQAbQBlAG4AdABGAGEAYwBpAGwAaQB0AHkAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMQA1AF8AMQA0AF8AMQBfADEAXwBfADEAXwBFAG0AYgBlAGQAZABlAGQARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBVAHAAcwB0AHIAZQBhAG0ARgByAGUAaQBnAGgAdABcAG4ARQBtAGIAZQBkAGQAZQBkACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdQBwAHMAdAByAGUAYQBtACAAZgByAGUAaQBnAGgAdABcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGYAXABcAGwAZQBmAHQAKAAoAFcAXwBmAFwAXAB0AGkAbQBlAHMAIABEAF8AZgApAFwAXAB0AGkAbQBlAHMAIABFAEYAXwBmAFwAXAByAGkAZwBoAHQAKQBcAG4AVwBfAGYAIAA9ACAAdABvAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAbwBvAGQAcwAgAHQAcgBhAG4AcwBwAG8AcgB0AGUAZAAgAHAAZQByACAAZgByAGUAaQBnAGgAdAAgAHQAeQBwAGUAIABmAFwAbgBEAF8AZgAgAD0AIAB0AG8AdABhAGwAIABkAGkAcwB0AGEAbgBjAGUAIAB0AHIAYQBuAHMAcABvAHIAdABlAGQAIABwAGUAcgAgAGYAcgBlAGkAZwBoAHQAIAB0AHkAcABlACAAZgBcAG4ARQBGAF8AZgAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgByAGUAaQBnAGgAdAAgAHQAeQBwAGUAIABmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVwBfAGYALAAgAEQAXwBmACwAIABFAEYAXwBmACwAXABuACAAIAAgACAAKABXAF8AZgAgACoAIABEAF8AZgApACAAKgAgAEUARgBfAGYAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AYgBlAGQAZABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHAAcwB0AHIAZQBhAG0AIABmAHIAZQBpAGcAaAB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMQA1AC4AMQA0AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AZgBcAFwAbABlAGYAdAAoACgAVwBfAGYAXABcAHQAaQBtAGUAcwAgAEQAXwBmACkAXABcAHQAaQBtAGUAcwAgAEUARgBfAGYAXABcAHIAaQBnAGgAdAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAXwBmAFwAIgAsACAAXAAiAHQAbwB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAG8AbwBkAHMAIAB0AHIAYQBuAHMAcABvAHIAdABlAGQAIABwAGUAcgAgAGYAcgBlAGkAZwBoAHQAIAB0AHkAcABlACAAZgBcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGYAXAAiACwAIABcACIAdABvAHQAYQBsACAAZABpAHMAdABhAG4AYwBlACAAdAByAGEAbgBzAHAAbwByAHQAZQBkACAAcABlAHIAIABmAHIAZQBpAGcAaAB0ACAAdAB5AHAAZQAgAGYAXAAiACwAIABcACIAawBtAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AZgBcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZgByAGUAaQBnAGgAdAAgAHQAeQBwAGUAIABmAFwAIgAsACAAXAAiAHQAIABDAE8AMgBlAC8AKAB0ACAAawBtACkAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBmAFwAIgAsACAAXAAiAGYAcgBlAGkAZwBoAHQAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AE8AZgBmAFIAbwBhAGQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABPAGYAZgBSAG8AYQBkAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQATwBmAGYAUgBvAGEAZABfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBHAGUAdABUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAFMAdAByAGkAbgBnACIALAAiAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAHUAZQBsAF8ARwBlAHQAUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAFMAdAByAGkAbgBnACIALAAiAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAHUAZQBsAF8AVABvAHQAYQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBVAG4AaQB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFUAbgBpAHQAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQB2AGUAcwB0AG8AYwBrAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHMAdABvAGMAawBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAyAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAZQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADIAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABNAGkAbgBlAHIAYQBsAFMAdQBwAHAAbABlAG0AZQBuAHQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATQBpAG4AZQByAGEAbABTAHUAcABwAGwAZQBtAGUAbgB0AHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAE0AaQBuAGUAcgBhAGwAUwB1AHAAcABsAGUAbQBlAG4AdABzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwBYAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANABfADEAXwAxAF8AXwBYAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARgBlAHIAdABpAGwAaQBzAGUAcgBDAG8AbQBwAG8AbgBlAG4AdABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADQAXwAxAF8AMQBfAF8AWABfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEYAZQByAHQAaQBsAGkAcwBlAHIAQwBvAG0AcABvAG4AZQBuAHQAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA0AF8AMQBfADEAXwBfAFgAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABGAGUAcgB0AGkAbABpAHMAZQByAEMAbwBtAHAAbwBuAGUAbgB0AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADUAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAQQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABBAGcAcgBpAGMAaABlAG0AaQBjAGEAbABzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADUAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAQQBnAHIAaQBjAGgAZQBtAGkAYwBhAGwAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA1AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEEAZwByAGkAYwBoAGUAbQBpAGMAYQBsAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA2AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQBtAGUAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADYAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAG0AZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANgBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAbQBlAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADYAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAG0AZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA2AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQBtAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA2AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEwAaQBtAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABTAGUAcgB2AGkAYwBlAHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADcAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUwBlAHIAdgBpAGMAZQBzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8ANwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABTAGUAcgB2AGkAYwBlAHMAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA3AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFMAZQByAHYAaQBjAGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADcAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUwBlAHIAdgBpAGMAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA4AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAFAAYQBjAGsAYQBnAGkAbgBnAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADgAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQAUABhAGMAawBhAGcAaQBuAGcAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AOABfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABQAGEAYwBrAGEAZwBpAG4AZwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AOQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAHUAcgBjAGgAYQBzAGUAZABHAHIAbwB3AE0AZQBkAGkAYQBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADkAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUAB1AHIAYwBoAGEAcwBlAGQARwByAG8AdwBNAGUAZABpAGEAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwA5AF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAdQByAGMAaABhAHMAZQBkAEcAcgBvAHcATQBlAGQAaQBhAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADAAXwAxAF8AMQBfAF8AMQBfAE8AdABoAGUAcgBQAHUAcgBjAGgAYQBzAGUAZABHAG8AbwBkAHMAQQBuAGQAUwBlAHIAdgBpAGMAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAwAF8AMQBfADEAXwBfADEAXwBPAHQAaABlAHIAUAB1AHIAYwBoAGEAcwBlAGQARwBvAG8AZABzAEEAbgBkAFMAZQByAHYAaQBjAGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMABfADEAXwAxAF8AXwAxAF8ATwB0AGgAZQByAFAAdQByAGMAaABhAHMAZQBkAEcAbwBvAGQAcwBBAG4AZABTAGUAcgB2AGkAYwBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAFUAcABzAHQAcgBlAGEAbQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEYAdQBlAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABVAHAAcwB0AHIAZQBhAG0ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBGAHUAZQBsAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAVQBwAHMAdAByAGUAYQBtAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ARgB1AGUAbABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADIAXwBVAHAAcwB0AHIAZQBhAG0AVAByAGEAbgBzAHAAbwByAHQARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAyAF8AVQBwAHMAdAByAGUAYQBtAFQAcgBhAG4AcwBwAG8AcgB0AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMgBfAFUAcABzAHQAcgBlAGEAbQBUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMwBfAFUAcABzAHQAcgBlAGEAbQBTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADEAXwAxAF8AMQBfAF8AMwBfAFUAcABzAHQAcgBlAGEAbQBTAHQAYQB0AGkAbwBuAGEAcgB5AEYAdQBlAGwARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAxAF8AMQBfADEAXwBfADMAXwBVAHAAcwB0AHIAZQBhAG0AUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMQBfADEAXwAxAF8AXwAzAF8AVQBwAHMAdAByAGUAYQBtAFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMQBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADEAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMQBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAxAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADEAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAFUAbgBpAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMgBfADEAXwAyAF8AXwAxAF8AVQBwAHMAdAByAGUAYQBtAFAAdQByAGMAaABhAHMAZQBkAEUAbABlAGMAdAByAGkAYwBpAHQAeQBNAGEAcgBrAGUAdABCAGEAcwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADIAXwAxAF8AMgBfAF8AMQBfAFUAcABzAHQAcgBlAGEAbQBQAHUAcgBjAGgAYQBzAGUAZABFAGwAZQBjAHQAcgBpAGMAaQB0AHkATQBhAHIAawBlAHQAQgBhAHMAZQBkAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAyAF8AMQBfADIAXwBfADEAXwBVAHAAcwB0AHIAZQBhAG0AUAB1AHIAYwBoAGEAcwBlAGQARQBsAGUAYwB0AHIAaQBjAGkAdAB5AE0AYQByAGsAZQB0AEIAYQBzAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8AVQBuAGkAdAAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQAzAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAE0AYQBuAHUAcgBlAFMAZQBuAHQATwBmAGYAUwBpAHQAZQBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEAMwBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBNAGEAbgB1AHIAZQBTAGUAbgB0AE8AZgBmAFMAaQB0AGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADMAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0ATQBhAG4AdQByAGUAUwBlAG4AdABPAGYAZgBTAGkAdABlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXwBVAG4AaQB0ACIALAAiAFMAYwBvAHAAZQAzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADUAXwAxADQAXwAxAF8AMQBfAF8AMQBfAEUAbQBiAGUAZABkAGUAZABFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFUAcABzAHQAcgBlAGEAbQBGAHIAZQBpAGcAaAB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQA1AF8AMQA0AF8AMQBfADEAXwBfADEAXwBFAG0AYgBlAGQAZABlAGQARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBVAHAAcwB0AHIAZQBhAG0ARgByAGUAaQBnAGgAdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEANQBfADEANABfADEAXwAxAF8AXwAxAF8ARQBtAGIAZQBkAGQAZQBkAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AVQBwAHMAdAByAGUAYQBtAEYAcgBlAGkAZwBoAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24211,29 +24277,18 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>